--- a/database/event/7993/event_7993_evp_summary.xlsx
+++ b/database/event/7993/event_7993_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -508,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.2864</v>
+        <v>7.1255</v>
       </c>
       <c r="C2" t="n">
-        <v>2.91456</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2.399788929158694</v>
+        <v>2.4572</v>
       </c>
       <c r="E2" t="n">
-        <v>74.6478</v>
+        <v>7.1255</v>
       </c>
       <c r="F2" t="n">
-        <v>45.26479074185137</v>
+        <v>4.84</v>
       </c>
       <c r="G2" t="n">
-        <v>29.38303485275527</v>
+        <v>2.2855</v>
       </c>
       <c r="H2" t="n">
-        <v>95.27873849922415</v>
+        <v>5.286</v>
       </c>
       <c r="I2" t="n">
-        <v>82.5657934770895</v>
+        <v>5.286</v>
       </c>
       <c r="J2" t="n">
-        <v>29.38303485275527</v>
+        <v>2.2855</v>
       </c>
       <c r="K2" t="n">
         <v>151</v>
@@ -541,7 +529,7 @@
         <v>63</v>
       </c>
       <c r="M2" t="n">
-        <v>111.9488</v>
+        <v>7.571499999999999</v>
       </c>
       <c r="N2" t="n">
         <v>214</v>
@@ -554,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.9465</v>
+        <v>6.6646</v>
       </c>
       <c r="C3" t="n">
-        <v>2.7786</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.204664531698813</v>
+        <v>2.271</v>
       </c>
       <c r="E3" t="n">
-        <v>68.5783</v>
+        <v>6.6646</v>
       </c>
       <c r="F3" t="n">
-        <v>32.90287943869181</v>
+        <v>3.8751</v>
       </c>
       <c r="G3" t="n">
-        <v>35.67540736695798</v>
+        <v>2.7895</v>
       </c>
       <c r="H3" t="n">
-        <v>44.77573521411875</v>
+        <v>3.8751</v>
       </c>
       <c r="I3" t="n">
-        <v>38.80135447536259</v>
+        <v>3.8751</v>
       </c>
       <c r="J3" t="n">
-        <v>35.67540736695798</v>
+        <v>2.7895</v>
       </c>
       <c r="K3" t="n">
         <v>151</v>
@@ -587,7 +575,7 @@
         <v>63</v>
       </c>
       <c r="M3" t="n">
-        <v>74.4768</v>
+        <v>6.6646</v>
       </c>
       <c r="N3" t="n">
         <v>214</v>
@@ -600,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.7744</v>
+        <v>4.8757</v>
       </c>
       <c r="C4" t="n">
-        <v>2.30976</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1.613694830778713</v>
+        <v>1.5483</v>
       </c>
       <c r="E4" t="n">
-        <v>50.1956</v>
+        <v>4.8757</v>
       </c>
       <c r="F4" t="n">
-        <v>1.898671179449445</v>
+        <v>1.5954</v>
       </c>
       <c r="G4" t="n">
-        <v>48.29691428527617</v>
+        <v>3.2803</v>
       </c>
       <c r="H4" t="n">
-        <v>1.898671179449445</v>
+        <v>1.5954</v>
       </c>
       <c r="I4" t="n">
-        <v>1.64533341805949</v>
+        <v>1.5954</v>
       </c>
       <c r="J4" t="n">
-        <v>48.29691428527617</v>
+        <v>3.2803</v>
       </c>
       <c r="K4" t="n">
         <v>151</v>
@@ -633,7 +621,7 @@
         <v>63</v>
       </c>
       <c r="M4" t="n">
-        <v>49.9422</v>
+        <v>4.8757</v>
       </c>
       <c r="N4" t="n">
         <v>214</v>
@@ -646,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.7983</v>
+        <v>4.463</v>
       </c>
       <c r="C5" t="n">
-        <v>1.51932</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8535465755137682</v>
+        <v>1.3816</v>
       </c>
       <c r="E5" t="n">
-        <v>26.5504</v>
+        <v>4.463</v>
       </c>
       <c r="F5" t="n">
-        <v>26.55041663525072</v>
+        <v>4.463</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>30.37498826267249</v>
+        <v>4.6949</v>
       </c>
       <c r="I5" t="n">
-        <v>41.6621072871089</v>
+        <v>4.6949</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -679,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>41.6621</v>
+        <v>4.6949</v>
       </c>
       <c r="N5" t="n">
         <v>239</v>
@@ -688,584 +676,584 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.4317</v>
+        <v>3.5998</v>
       </c>
       <c r="C6" t="n">
-        <v>0.57268</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2281493415088373</v>
+        <v>1.0329</v>
       </c>
       <c r="E6" t="n">
-        <v>7.0968</v>
+        <v>3.5998</v>
       </c>
       <c r="F6" t="n">
-        <v>7.09681257694885</v>
+        <v>4.4373</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0.8375</v>
       </c>
       <c r="H6" t="n">
-        <v>7.09681257694885</v>
+        <v>4.6546</v>
       </c>
       <c r="I6" t="n">
-        <v>5.253881333867442</v>
+        <v>4.698</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0.8375</v>
       </c>
       <c r="K6" t="n">
-        <v>129</v>
+        <v>240</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M6" t="n">
-        <v>5.2539</v>
+        <v>3.8605</v>
       </c>
       <c r="N6" t="n">
-        <v>129</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.2946</v>
+        <v>2.9353</v>
       </c>
       <c r="C7" t="n">
-        <v>0.51784</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1992129476027565</v>
+        <v>0.7644</v>
       </c>
       <c r="E7" t="n">
-        <v>6.1967</v>
+        <v>2.9353</v>
       </c>
       <c r="F7" t="n">
-        <v>6.19671721464746</v>
+        <v>2.9353</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>6.19671721464746</v>
+        <v>2.9353</v>
       </c>
       <c r="I7" t="n">
-        <v>3.947406661841423</v>
+        <v>2.9353</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>111</v>
+        <v>239</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9474</v>
+        <v>2.9353</v>
       </c>
       <c r="N7" t="n">
-        <v>111</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2692</v>
+        <v>2.226</v>
       </c>
       <c r="C8" t="n">
-        <v>0.50768</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1939229439696952</v>
+        <v>0.4779</v>
       </c>
       <c r="E8" t="n">
-        <v>6.0322</v>
+        <v>2.226</v>
       </c>
       <c r="F8" t="n">
-        <v>6.032166381114766</v>
+        <v>2.4674</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0.2414</v>
       </c>
       <c r="H8" t="n">
-        <v>6.032166381114766</v>
+        <v>2.4674</v>
       </c>
       <c r="I8" t="n">
-        <v>8.27367440508711</v>
+        <v>2.4905</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0.2414</v>
       </c>
       <c r="K8" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M8" t="n">
-        <v>8.2737</v>
+        <v>2.2491</v>
       </c>
       <c r="N8" t="n">
-        <v>239</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.2559</v>
+        <v>1.7458</v>
       </c>
       <c r="C9" t="n">
-        <v>0.50236</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1911786491938445</v>
+        <v>0.2839</v>
       </c>
       <c r="E9" t="n">
-        <v>5.9468</v>
+        <v>1.7458</v>
       </c>
       <c r="F9" t="n">
-        <v>5.946802357921397</v>
+        <v>1.7458</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>5.946802357921397</v>
+        <v>1.7458</v>
       </c>
       <c r="I9" t="n">
-        <v>8.258973719466159</v>
+        <v>1.7458</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>8.259</v>
+        <v>1.7458</v>
       </c>
       <c r="N9" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.0452</v>
+        <v>1.5576</v>
       </c>
       <c r="C10" t="n">
-        <v>0.41808</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1483206039718095</v>
+        <v>0.2079</v>
       </c>
       <c r="E10" t="n">
-        <v>4.6137</v>
+        <v>1.5576</v>
       </c>
       <c r="F10" t="n">
-        <v>4.613660161044187</v>
+        <v>1.5576</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4.613660161044187</v>
+        <v>1.5576</v>
       </c>
       <c r="I10" t="n">
-        <v>2.938974335012366</v>
+        <v>1.5576</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>111</v>
+        <v>242</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.939</v>
+        <v>1.5576</v>
       </c>
       <c r="N10" t="n">
-        <v>111</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1893</v>
+        <v>1.1279</v>
       </c>
       <c r="C11" t="n">
-        <v>0.07572000000000001</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.01061800042245063</v>
+        <v>0.0343</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3303</v>
+        <v>1.1279</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3302834820462411</v>
+        <v>1.1279</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3302834820462411</v>
+        <v>1.1279</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4530143598797798</v>
+        <v>1.1279</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>239</v>
+        <v>176</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.453</v>
+        <v>1.1279</v>
       </c>
       <c r="N11" t="n">
-        <v>239</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1301</v>
+        <v>1.0577</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.05204</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.06834521973127376</v>
+        <v>0.0059</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1259</v>
+        <v>1.0577</v>
       </c>
       <c r="F12" t="n">
-        <v>22.69710457128397</v>
+        <v>1.0577</v>
       </c>
       <c r="G12" t="n">
-        <v>-24.82305072460412</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>24.0043702254411</v>
+        <v>1.0577</v>
       </c>
       <c r="I12" t="n">
-        <v>33.06197333776679</v>
+        <v>1.0577</v>
       </c>
       <c r="J12" t="n">
-        <v>-24.82305072460412</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="L12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>8.238899999999999</v>
+        <v>1.0577</v>
       </c>
       <c r="N12" t="n">
-        <v>303</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.343</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1372</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1086357115223585</v>
+        <v>-0.0274</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3792</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.379222042627714</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.379222042627714</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.055653007279987</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.0557</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>106</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.5623</v>
+        <v>0.9563</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.22492</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1517349829463323</v>
+        <v>-0.035</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.7199</v>
+        <v>0.9563</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.719867820854262</v>
+        <v>1.3566</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.4003</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.719867820854262</v>
+        <v>1.3566</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.871196493604314</v>
+        <v>1.3692</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.4003</v>
       </c>
       <c r="K14" t="n">
-        <v>106</v>
+        <v>240</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.8712</v>
+        <v>0.9689</v>
       </c>
       <c r="N14" t="n">
-        <v>106</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.6405</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.2562</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1674965348250253</v>
+        <v>-0.1284</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.2101</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.210146595560289</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.210146595560289</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-5.262472314597479</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>176</v>
+        <v>239</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.2625</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>176</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.8387</v>
+        <v>0.7209</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.33548</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.20845035255437</v>
+        <v>-0.1301</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.4841</v>
+        <v>0.7209</v>
       </c>
       <c r="F16" t="n">
-        <v>7.641608940441846</v>
+        <v>0.7209</v>
       </c>
       <c r="G16" t="n">
-        <v>-14.12566483950291</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>7.641608940441846</v>
+        <v>0.7209</v>
       </c>
       <c r="I16" t="n">
-        <v>10.52502809587399</v>
+        <v>0.7209</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.12566483950291</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>240</v>
+        <v>106</v>
       </c>
       <c r="L16" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.6006</v>
+        <v>0.7209</v>
       </c>
       <c r="N16" t="n">
-        <v>303</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.9637</v>
+        <v>0.6246</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.38548</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.235016511427657</v>
+        <v>-0.169</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.3104</v>
+        <v>0.6246</v>
       </c>
       <c r="F17" t="n">
-        <v>-7.310422739159364</v>
+        <v>0.6246</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-7.310422739159364</v>
+        <v>0.6246</v>
       </c>
       <c r="I17" t="n">
-        <v>-5.412020277483833</v>
+        <v>0.6246</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-5.412</v>
+        <v>0.6246</v>
       </c>
       <c r="N17" t="n">
-        <v>129</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1.2783</v>
+        <v>0.5478</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.51132</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3044595713552697</v>
+        <v>-0.2001</v>
       </c>
       <c r="E18" t="n">
-        <v>-9.470499999999999</v>
+        <v>0.5478</v>
       </c>
       <c r="F18" t="n">
-        <v>-9.470518305584678</v>
+        <v>0.5478</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-9.470518305584678</v>
+        <v>0.5478</v>
       </c>
       <c r="I18" t="n">
-        <v>-6.03286962364361</v>
+        <v>0.5478</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1277,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-6.0329</v>
+        <v>0.5478</v>
       </c>
       <c r="N18" t="n">
         <v>111</v>
@@ -1286,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.3234</v>
+        <v>0.514</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.5293599999999999</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.314725105686426</v>
+        <v>-0.2137</v>
       </c>
       <c r="E19" t="n">
-        <v>-9.7898</v>
+        <v>0.514</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8675865330707228</v>
+        <v>0.514</v>
       </c>
       <c r="G19" t="n">
-        <v>-8.922251445622145</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8675865330707228</v>
+        <v>0.514</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7518253457313007</v>
+        <v>0.514</v>
       </c>
       <c r="J19" t="n">
-        <v>-8.922251445622145</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="L19" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-9.674099999999999</v>
+        <v>0.514</v>
       </c>
       <c r="N19" t="n">
-        <v>214</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.406</v>
+        <v>0.4356</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.5624</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3337491788037085</v>
+        <v>-0.2454</v>
       </c>
       <c r="E20" t="n">
-        <v>-10.3816</v>
+        <v>0.4356</v>
       </c>
       <c r="F20" t="n">
-        <v>-10.38160072703416</v>
+        <v>0.4356</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-10.38160072703416</v>
+        <v>0.4356</v>
       </c>
       <c r="I20" t="n">
-        <v>-14.23932610479864</v>
+        <v>0.4356</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>239</v>
+        <v>129</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-14.2393</v>
+        <v>0.4356</v>
       </c>
       <c r="N20" t="n">
-        <v>239</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21">
@@ -1382,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-1.6001</v>
+        <v>0.3516</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.6400400000000001</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3795471263020831</v>
+        <v>-0.2793</v>
       </c>
       <c r="E21" t="n">
-        <v>-11.8062</v>
+        <v>0.3516</v>
       </c>
       <c r="F21" t="n">
-        <v>-11.80619151329473</v>
+        <v>0.3516</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-11.80619151329473</v>
+        <v>0.3516</v>
       </c>
       <c r="I21" t="n">
-        <v>-16.19328419900971</v>
+        <v>0.3516</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1415,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-16.1933</v>
+        <v>0.3516</v>
       </c>
       <c r="N21" t="n">
         <v>239</v>
@@ -1424,216 +1412,216 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-1.6409</v>
+        <v>0.254</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.6563600000000001</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3893824640368216</v>
+        <v>-0.3188</v>
       </c>
       <c r="E22" t="n">
-        <v>-12.1121</v>
+        <v>0.254</v>
       </c>
       <c r="F22" t="n">
-        <v>-12.1121294926587</v>
+        <v>0.254</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-12.1121294926587</v>
+        <v>0.254</v>
       </c>
       <c r="I22" t="n">
-        <v>-8.96679887835278</v>
+        <v>0.254</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-8.966799999999999</v>
+        <v>0.254</v>
       </c>
       <c r="N22" t="n">
-        <v>129</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-1.6614</v>
+        <v>0.2299</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.66456</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3943366638646323</v>
+        <v>-0.3285</v>
       </c>
       <c r="E23" t="n">
-        <v>-12.2662</v>
+        <v>0.2299</v>
       </c>
       <c r="F23" t="n">
-        <v>-12.26623481426166</v>
+        <v>0.2299</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-12.26623481426166</v>
+        <v>0.2299</v>
       </c>
       <c r="I23" t="n">
-        <v>-17.03545954118406</v>
+        <v>0.2299</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>242</v>
+        <v>111</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-17.0355</v>
+        <v>0.2299</v>
       </c>
       <c r="N23" t="n">
-        <v>242</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.7574</v>
+        <v>0.2221</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.70296</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4178118878460764</v>
+        <v>-0.3316</v>
       </c>
       <c r="E24" t="n">
-        <v>-12.9965</v>
+        <v>0.2221</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.99645504499483</v>
+        <v>0.2221</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-12.99645504499483</v>
+        <v>0.2221</v>
       </c>
       <c r="I24" t="n">
-        <v>-18.0495961026614</v>
+        <v>0.2221</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>242</v>
+        <v>176</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-18.0496</v>
+        <v>0.2221</v>
       </c>
       <c r="N24" t="n">
-        <v>242</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-2.0338</v>
+        <v>0.2202</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.81352</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4876260961441427</v>
+        <v>-0.3324</v>
       </c>
       <c r="E25" t="n">
-        <v>-15.1681</v>
+        <v>0.2202</v>
       </c>
       <c r="F25" t="n">
-        <v>-15.16809555126494</v>
+        <v>1.0535</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.8333</v>
       </c>
       <c r="H25" t="n">
-        <v>-15.15481789313812</v>
+        <v>1.0535</v>
       </c>
       <c r="I25" t="n">
-        <v>-15.3070183597837</v>
+        <v>1.0535</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.8333</v>
       </c>
       <c r="K25" t="n">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M25" t="n">
-        <v>-15.307</v>
+        <v>0.2202000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>176</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-2.2559</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.9023600000000001</v>
+        <v>-0</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5462044094792534</v>
+        <v>-0.4216</v>
       </c>
       <c r="E26" t="n">
-        <v>-16.9902</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-16.9902323501869</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-16.93911816599742</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-23.52520284746844</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1645,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-23.5252</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>242</v>
@@ -1654,691 +1642,691 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-2.2839</v>
+        <v>-0.0617</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.91356</v>
+        <v>-0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5537551175914849</v>
+        <v>-0.4463</v>
       </c>
       <c r="E27" t="n">
-        <v>-17.2251</v>
+        <v>-0.0617</v>
       </c>
       <c r="F27" t="n">
-        <v>-17.22510464892495</v>
+        <v>-0.0617</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-17.18390263446752</v>
+        <v>-0.0617</v>
       </c>
       <c r="I27" t="n">
-        <v>-17.35648128359416</v>
+        <v>-0.0617</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>176</v>
+        <v>106</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-17.3565</v>
+        <v>-0.0617</v>
       </c>
       <c r="N27" t="n">
-        <v>176</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-2.3639</v>
+        <v>-0.1686</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.9455600000000001</v>
+        <v>-0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5755399877461455</v>
+        <v>-0.4895</v>
       </c>
       <c r="E28" t="n">
-        <v>-17.9027</v>
+        <v>-0.1686</v>
       </c>
       <c r="F28" t="n">
-        <v>-11.12034287350435</v>
+        <v>-0.1686</v>
       </c>
       <c r="G28" t="n">
-        <v>-6.782401866241566</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-11.12034287350435</v>
+        <v>-0.1686</v>
       </c>
       <c r="I28" t="n">
-        <v>-9.636566851645092</v>
+        <v>-0.1686</v>
       </c>
       <c r="J28" t="n">
-        <v>-6.782401866241566</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="L28" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-16.419</v>
+        <v>-0.1686</v>
       </c>
       <c r="N28" t="n">
-        <v>214</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-2.6628</v>
+        <v>-0.2964</v>
       </c>
       <c r="C29" t="n">
-        <v>-1.06512</v>
+        <v>-0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6596004260683956</v>
+        <v>-0.5411</v>
       </c>
       <c r="E29" t="n">
-        <v>-20.5175</v>
+        <v>-0.2964</v>
       </c>
       <c r="F29" t="n">
-        <v>-20.51752842469497</v>
+        <v>-0.2964</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-21.01201068608625</v>
+        <v>-0.2964</v>
       </c>
       <c r="I29" t="n">
-        <v>-12.78205528106251</v>
+        <v>-0.2964</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>106</v>
+        <v>242</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-12.7821</v>
+        <v>-0.2964</v>
       </c>
       <c r="N29" t="n">
-        <v>106</v>
+        <v>242</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.7093</v>
+        <v>-0.2995</v>
       </c>
       <c r="C30" t="n">
-        <v>-1.08372</v>
+        <v>-0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6730751448855921</v>
+        <v>-0.5424</v>
       </c>
       <c r="E30" t="n">
-        <v>-20.9367</v>
+        <v>-0.2995</v>
       </c>
       <c r="F30" t="n">
-        <v>-3.581672545085908</v>
+        <v>0.3524</v>
       </c>
       <c r="G30" t="n">
-        <v>-17.35500043352409</v>
+        <v>-0.6519</v>
       </c>
       <c r="H30" t="n">
-        <v>-3.581672545085908</v>
+        <v>0.3524</v>
       </c>
       <c r="I30" t="n">
-        <v>-4.93315013383425</v>
+        <v>0.3524</v>
       </c>
       <c r="J30" t="n">
-        <v>-17.35500043352409</v>
+        <v>-0.6519</v>
       </c>
       <c r="K30" t="n">
-        <v>240</v>
+        <v>151</v>
       </c>
       <c r="L30" t="n">
         <v>63</v>
       </c>
       <c r="M30" t="n">
-        <v>-22.2882</v>
+        <v>-0.2995</v>
       </c>
       <c r="N30" t="n">
-        <v>303</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.8505</v>
+        <v>-0.3229</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.1402</v>
+        <v>-0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7146534202613586</v>
+        <v>-0.5518</v>
       </c>
       <c r="E31" t="n">
-        <v>-22.23</v>
+        <v>-0.3229</v>
       </c>
       <c r="F31" t="n">
-        <v>-22.23000665936118</v>
+        <v>0.4261</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.749</v>
       </c>
       <c r="H31" t="n">
-        <v>-23.32912874869973</v>
+        <v>0.4261</v>
       </c>
       <c r="I31" t="n">
-        <v>-14.19160773235106</v>
+        <v>0.4301</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.749</v>
       </c>
       <c r="K31" t="n">
-        <v>106</v>
+        <v>240</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M31" t="n">
-        <v>-14.1916</v>
+        <v>-0.3189</v>
       </c>
       <c r="N31" t="n">
-        <v>106</v>
+        <v>303</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-2.9721</v>
+        <v>-0.394</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.18884</v>
+        <v>-0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7513187363779634</v>
+        <v>-0.5805</v>
       </c>
       <c r="E32" t="n">
-        <v>-23.3705</v>
+        <v>-0.394</v>
       </c>
       <c r="F32" t="n">
-        <v>-5.827171460555355</v>
+        <v>-0.394</v>
       </c>
       <c r="G32" t="n">
-        <v>-17.54334638693059</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-5.827171460555355</v>
+        <v>-0.394</v>
       </c>
       <c r="I32" t="n">
-        <v>-8.025946344523875</v>
+        <v>-0.394</v>
       </c>
       <c r="J32" t="n">
-        <v>-17.54334638693059</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>240</v>
+        <v>129</v>
       </c>
       <c r="L32" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-25.5693</v>
+        <v>-0.394</v>
       </c>
       <c r="N32" t="n">
-        <v>303</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-3.0367</v>
+        <v>-0.4787</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.21468</v>
+        <v>-0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7710889426265074</v>
+        <v>-0.6147</v>
       </c>
       <c r="E33" t="n">
-        <v>-23.9855</v>
+        <v>-0.4787</v>
       </c>
       <c r="F33" t="n">
-        <v>-23.98548981026106</v>
+        <v>-0.4787</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-25.96990246708696</v>
+        <v>-0.4787</v>
       </c>
       <c r="I33" t="n">
-        <v>-26.2307192780907</v>
+        <v>-0.4787</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>176</v>
+        <v>242</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-26.2307</v>
+        <v>-0.4787</v>
       </c>
       <c r="N33" t="n">
-        <v>176</v>
+        <v>242</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-3.3424</v>
+        <v>-0.8495</v>
       </c>
       <c r="C34" t="n">
-        <v>-1.33696</v>
+        <v>-0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.867799346924345</v>
+        <v>-0.7645</v>
       </c>
       <c r="E34" t="n">
-        <v>-26.9938</v>
+        <v>-0.8495</v>
       </c>
       <c r="F34" t="n">
-        <v>-26.99376329027072</v>
+        <v>-0.4842</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.3653</v>
       </c>
       <c r="H34" t="n">
-        <v>-31.20885318977146</v>
+        <v>-0.4842</v>
       </c>
       <c r="I34" t="n">
-        <v>-31.52228500085955</v>
+        <v>-0.4887</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.3653</v>
       </c>
       <c r="K34" t="n">
-        <v>176</v>
+        <v>240</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M34" t="n">
-        <v>-31.5223</v>
+        <v>-0.8540000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>176</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>kauez</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-3.3485</v>
+        <v>-1.1275</v>
       </c>
       <c r="C35" t="n">
-        <v>-1.3394</v>
+        <v>-0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8697836808878142</v>
+        <v>-0.8768</v>
       </c>
       <c r="E35" t="n">
-        <v>-27.0555</v>
+        <v>-1.1275</v>
       </c>
       <c r="F35" t="n">
-        <v>-27.05548797523226</v>
+        <v>-1.1275</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-31.32674882901996</v>
+        <v>-1.1275</v>
       </c>
       <c r="I35" t="n">
-        <v>-23.19168205993443</v>
+        <v>-1.1275</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>129</v>
+        <v>242</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-23.1917</v>
+        <v>-1.1275</v>
       </c>
       <c r="N35" t="n">
-        <v>129</v>
+        <v>242</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kauez</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-3.4916</v>
+        <v>-1.2378</v>
       </c>
       <c r="C36" t="n">
-        <v>-1.39664</v>
+        <v>-0</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9169033554914136</v>
+        <v>-0.9214</v>
       </c>
       <c r="E36" t="n">
-        <v>-28.5212</v>
+        <v>-1.2378</v>
       </c>
       <c r="F36" t="n">
-        <v>-28.52119239996148</v>
+        <v>-1.2378</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-34.26095678796162</v>
+        <v>-1.2378</v>
       </c>
       <c r="I36" t="n">
-        <v>-47.58193137840294</v>
+        <v>-1.2378</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>242</v>
+        <v>129</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-47.5819</v>
+        <v>-1.2378</v>
       </c>
       <c r="N36" t="n">
-        <v>242</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-3.6</v>
+        <v>-1.2674</v>
       </c>
       <c r="C37" t="n">
-        <v>-1.44</v>
+        <v>-0</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.953385557535424</v>
+        <v>-0.9334</v>
       </c>
       <c r="E37" t="n">
-        <v>-29.656</v>
+        <v>-1.2674</v>
       </c>
       <c r="F37" t="n">
-        <v>-29.65600764241833</v>
+        <v>-1.2674</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-36.72022888693491</v>
+        <v>-1.2674</v>
       </c>
       <c r="I37" t="n">
-        <v>-27.18455969247979</v>
+        <v>-1.2674</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-27.1846</v>
+        <v>-1.2674</v>
       </c>
       <c r="N37" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-3.6118</v>
+        <v>-1.3352</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.44472</v>
+        <v>-0</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9573900530484973</v>
+        <v>-0.9608</v>
       </c>
       <c r="E38" t="n">
-        <v>-29.7806</v>
+        <v>-1.3352</v>
       </c>
       <c r="F38" t="n">
-        <v>-7.302579471989397</v>
+        <v>-1.3352</v>
       </c>
       <c r="G38" t="n">
-        <v>-22.47799199311441</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-7.302579471989397</v>
+        <v>-1.3352</v>
       </c>
       <c r="I38" t="n">
-        <v>-10.05807215654207</v>
+        <v>-1.3352</v>
       </c>
       <c r="J38" t="n">
-        <v>-22.47799199311441</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="L38" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-32.5361</v>
+        <v>-1.3352</v>
       </c>
       <c r="N38" t="n">
-        <v>303</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-3.6802</v>
+        <v>-1.5706</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.47208</v>
+        <v>-0</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9808343588551129</v>
+        <v>-1.0558</v>
       </c>
       <c r="E39" t="n">
-        <v>-30.5098</v>
+        <v>-1.5706</v>
       </c>
       <c r="F39" t="n">
-        <v>-30.50982995520459</v>
+        <v>-1.5706</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-38.68625737941426</v>
+        <v>-1.5706</v>
       </c>
       <c r="I39" t="n">
-        <v>-24.64375649420363</v>
+        <v>-1.5706</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>111</v>
+        <v>176</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-24.6438</v>
+        <v>-1.5706</v>
       </c>
       <c r="N39" t="n">
-        <v>111</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.9102</v>
+        <v>-1.6027</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.56408</v>
+        <v>-0</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.061654192632895</v>
+        <v>-1.0688</v>
       </c>
       <c r="E40" t="n">
-        <v>-33.0238</v>
+        <v>-1.6027</v>
       </c>
       <c r="F40" t="n">
-        <v>-33.02381140712504</v>
+        <v>-1.6027</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-45.10772979299986</v>
+        <v>-1.6027</v>
       </c>
       <c r="I40" t="n">
-        <v>-28.73433576483778</v>
+        <v>-1.6027</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-28.7343</v>
+        <v>-1.6027</v>
       </c>
       <c r="N40" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.1186</v>
+        <v>-1.7667</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.64744</v>
+        <v>-0</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.137768878872533</v>
+        <v>-1.1351</v>
       </c>
       <c r="E41" t="n">
-        <v>-35.3914</v>
+        <v>-1.7667</v>
       </c>
       <c r="F41" t="n">
-        <v>-35.3914345570479</v>
+        <v>-1.7667</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-52.12696448575816</v>
+        <v>-1.7667</v>
       </c>
       <c r="I41" t="n">
-        <v>-31.70994683208244</v>
+        <v>-1.7667</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-31.7099</v>
+        <v>-1.7667</v>
       </c>
       <c r="N41" t="n">
-        <v>106</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -2356,52 +2344,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -2441,10 +2429,10 @@
         <v>1.54</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7934396296725681</v>
+        <v>1.2649</v>
       </c>
       <c r="J2" t="n">
-        <v>15.86879259345136</v>
+        <v>25.298</v>
       </c>
     </row>
     <row r="3">
@@ -2481,10 +2469,10 @@
         <v>1.49</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7168160063924794</v>
+        <v>1.1649</v>
       </c>
       <c r="J3" t="n">
-        <v>14.33632012784959</v>
+        <v>23.298</v>
       </c>
     </row>
     <row r="4">
@@ -2521,10 +2509,10 @@
         <v>1.45</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6548156552248587</v>
+        <v>1.0825</v>
       </c>
       <c r="J4" t="n">
-        <v>13.09631310449717</v>
+        <v>21.65</v>
       </c>
     </row>
     <row r="5">
@@ -2561,10 +2549,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0429278129753814</v>
+        <v>-0.1488</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.858556259507628</v>
+        <v>-2.976</v>
       </c>
     </row>
     <row r="6">
@@ -2601,10 +2589,10 @@
         <v>0.9</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2173285611392135</v>
+        <v>-0.4969</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.346571222784271</v>
+        <v>-9.938000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2641,10 +2629,10 @@
         <v>1.23</v>
       </c>
       <c r="I7" t="n">
-        <v>0.227441666073517</v>
+        <v>0.4793</v>
       </c>
       <c r="J7" t="n">
-        <v>4.548833321470341</v>
+        <v>9.586</v>
       </c>
     </row>
     <row r="8">
@@ -2681,10 +2669,10 @@
         <v>1.06</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.07015393959636419</v>
+        <v>0.2137</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.403078791927284</v>
+        <v>4.274</v>
       </c>
     </row>
     <row r="9">
@@ -2721,10 +2709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2530499160349761</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.060998320699522</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2749,10 @@
         <v>0.58</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7668287080347528</v>
+        <v>-0.6457000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-15.33657416069506</v>
+        <v>-12.914</v>
       </c>
     </row>
     <row r="11">
@@ -2801,10 +2789,10 @@
         <v>0.46</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9356678107224466</v>
+        <v>-0.7916</v>
       </c>
       <c r="J11" t="n">
-        <v>-18.71335621444893</v>
+        <v>-15.832</v>
       </c>
     </row>
     <row r="12">
@@ -2841,10 +2829,10 @@
         <v>1.92</v>
       </c>
       <c r="I12" t="n">
-        <v>1.310135118890569</v>
+        <v>1.9451</v>
       </c>
       <c r="J12" t="n">
-        <v>27.51283749670195</v>
+        <v>40.8471</v>
       </c>
     </row>
     <row r="13">
@@ -2881,10 +2869,10 @@
         <v>1.3</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4027636637217652</v>
+        <v>0.7558</v>
       </c>
       <c r="J13" t="n">
-        <v>8.458036938157068</v>
+        <v>15.8718</v>
       </c>
     </row>
     <row r="14">
@@ -2921,10 +2909,10 @@
         <v>1.23</v>
       </c>
       <c r="I14" t="n">
-        <v>0.307296449148076</v>
+        <v>0.5569</v>
       </c>
       <c r="J14" t="n">
-        <v>6.453225432109595</v>
+        <v>11.6949</v>
       </c>
     </row>
     <row r="15">
@@ -2961,10 +2949,10 @@
         <v>1.05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02154955231276544</v>
+        <v>0.0611</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4525405985680743</v>
+        <v>1.2831</v>
       </c>
     </row>
     <row r="16">
@@ -3001,10 +2989,10 @@
         <v>0.79</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4199848960109905</v>
+        <v>-0.7665</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.819682816230801</v>
+        <v>-16.0965</v>
       </c>
     </row>
     <row r="17">
@@ -3041,10 +3029,10 @@
         <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.07878890847191859</v>
+        <v>0.1686</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.65456707791029</v>
+        <v>3.5406</v>
       </c>
     </row>
     <row r="18">
@@ -3081,10 +3069,10 @@
         <v>1.01</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1248181032272697</v>
+        <v>0.1002</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.621180167772664</v>
+        <v>2.1042</v>
       </c>
     </row>
     <row r="19">
@@ -3121,10 +3109,10 @@
         <v>0.87</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3269646865460427</v>
+        <v>-0.2183</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.866258417466896</v>
+        <v>-4.5843</v>
       </c>
     </row>
     <row r="20">
@@ -3161,10 +3149,10 @@
         <v>0.78</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4516894464462545</v>
+        <v>-0.3758</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.485478375371343</v>
+        <v>-7.8918</v>
       </c>
     </row>
     <row r="21">
@@ -3201,10 +3189,10 @@
         <v>0.65</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6441529325968426</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-13.52721158453369</v>
+        <v>-11.739</v>
       </c>
     </row>
     <row r="22">
@@ -3241,10 +3229,10 @@
         <v>1.62</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9837560476400844</v>
+        <v>1.484</v>
       </c>
       <c r="J22" t="n">
-        <v>21.64263304808185</v>
+        <v>32.648</v>
       </c>
     </row>
     <row r="23">
@@ -3281,10 +3269,10 @@
         <v>1.45</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7329940377432367</v>
+        <v>1.1501</v>
       </c>
       <c r="J23" t="n">
-        <v>16.12586883035121</v>
+        <v>25.3022</v>
       </c>
     </row>
     <row r="24">
@@ -3321,10 +3309,10 @@
         <v>1.36</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5937137118516289</v>
+        <v>0.9595</v>
       </c>
       <c r="J24" t="n">
-        <v>13.06170166073584</v>
+        <v>21.109</v>
       </c>
     </row>
     <row r="25">
@@ -3361,10 +3349,10 @@
         <v>0.65</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5590472353572888</v>
+        <v>-1.0503</v>
       </c>
       <c r="J25" t="n">
-        <v>-12.29903917786035</v>
+        <v>-23.1066</v>
       </c>
     </row>
     <row r="26">
@@ -3401,10 +3389,10 @@
         <v>0.63</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5924416891361337</v>
+        <v>-1.0922</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.03371716099494</v>
+        <v>-24.0284</v>
       </c>
     </row>
     <row r="27">
@@ -3441,10 +3429,10 @@
         <v>1.13</v>
       </c>
       <c r="I27" t="n">
-        <v>0.172326817967773</v>
+        <v>0.3261</v>
       </c>
       <c r="J27" t="n">
-        <v>3.791189995291005</v>
+        <v>7.1742</v>
       </c>
     </row>
     <row r="28">
@@ -3481,10 +3469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1471412578274675</v>
+        <v>-0.0793</v>
       </c>
       <c r="J28" t="n">
-        <v>-3.237107672204286</v>
+        <v>-1.7446</v>
       </c>
     </row>
     <row r="29">
@@ -3521,10 +3509,10 @@
         <v>0.92</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1768082767218724</v>
+        <v>-0.118</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.889782087881192</v>
+        <v>-2.596</v>
       </c>
     </row>
     <row r="30">
@@ -3561,10 +3549,10 @@
         <v>0.79</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3559958857272169</v>
+        <v>-0.3604</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.831909485998771</v>
+        <v>-7.9288</v>
       </c>
     </row>
     <row r="31">
@@ -3601,10 +3589,10 @@
         <v>0.57</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6835261517057972</v>
+        <v>-0.6613</v>
       </c>
       <c r="J31" t="n">
-        <v>-15.03757533752754</v>
+        <v>-14.5486</v>
       </c>
     </row>
     <row r="32">
@@ -3641,10 +3629,10 @@
         <v>1.22</v>
       </c>
       <c r="I32" t="n">
-        <v>0.07041500661131006</v>
+        <v>0.4004</v>
       </c>
       <c r="J32" t="n">
-        <v>1.619545152060131</v>
+        <v>9.209199999999999</v>
       </c>
     </row>
     <row r="33">
@@ -3681,10 +3669,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.02766981707459704</v>
+        <v>0.3274</v>
       </c>
       <c r="J33" t="n">
-        <v>0.6364057927157319</v>
+        <v>7.5302</v>
       </c>
     </row>
     <row r="34">
@@ -3721,10 +3709,10 @@
         <v>1.16</v>
       </c>
       <c r="I34" t="n">
-        <v>0.01945475090655371</v>
+        <v>0.3121</v>
       </c>
       <c r="J34" t="n">
-        <v>0.4474592708507354</v>
+        <v>7.1783</v>
       </c>
     </row>
     <row r="35">
@@ -3761,10 +3749,10 @@
         <v>1.05</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1084577528532616</v>
+        <v>0.1184</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.494528315625018</v>
+        <v>2.7232</v>
       </c>
     </row>
     <row r="36">
@@ -3801,10 +3789,10 @@
         <v>0.57</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7251902151184925</v>
+        <v>-0.6863</v>
       </c>
       <c r="J36" t="n">
-        <v>-16.67937494772533</v>
+        <v>-15.7849</v>
       </c>
     </row>
     <row r="37">
@@ -3841,10 +3829,10 @@
         <v>1.41</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4189772570171855</v>
+        <v>1.0616</v>
       </c>
       <c r="J37" t="n">
-        <v>9.636476911395267</v>
+        <v>24.4168</v>
       </c>
     </row>
     <row r="38">
@@ -3881,10 +3869,10 @@
         <v>1.31</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2982209156226219</v>
+        <v>0.8423</v>
       </c>
       <c r="J38" t="n">
-        <v>6.859081059320304</v>
+        <v>19.3729</v>
       </c>
     </row>
     <row r="39">
@@ -3921,10 +3909,10 @@
         <v>1.26</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2373200913014838</v>
+        <v>0.7246</v>
       </c>
       <c r="J39" t="n">
-        <v>5.458362099934128</v>
+        <v>16.6658</v>
       </c>
     </row>
     <row r="40">
@@ -3961,10 +3949,10 @@
         <v>0.92</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1267815557269976</v>
+        <v>-0.4039</v>
       </c>
       <c r="J40" t="n">
-        <v>-2.915975781720946</v>
+        <v>-9.2897</v>
       </c>
     </row>
     <row r="41">
@@ -4001,10 +3989,10 @@
         <v>0.86</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.186523147195907</v>
+        <v>-0.5685</v>
       </c>
       <c r="J41" t="n">
-        <v>-4.290032385505862</v>
+        <v>-13.0755</v>
       </c>
     </row>
     <row r="42">
@@ -4041,10 +4029,10 @@
         <v>1.28</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1348618637835422</v>
+        <v>0.4675</v>
       </c>
       <c r="J42" t="n">
-        <v>4.855027096207519</v>
+        <v>16.83</v>
       </c>
     </row>
     <row r="43">
@@ -4081,10 +4069,10 @@
         <v>1.23</v>
       </c>
       <c r="I43" t="n">
-        <v>0.09100334877343552</v>
+        <v>0.3989</v>
       </c>
       <c r="J43" t="n">
-        <v>3.276120555843679</v>
+        <v>14.3604</v>
       </c>
     </row>
     <row r="44">
@@ -4121,10 +4109,10 @@
         <v>1.09</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.04087925084667669</v>
+        <v>0.1739</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.471653030480361</v>
+        <v>6.2604</v>
       </c>
     </row>
     <row r="45">
@@ -4161,10 +4149,10 @@
         <v>1.09</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.04087925084667669</v>
+        <v>0.1739</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.471653030480361</v>
+        <v>6.2604</v>
       </c>
     </row>
     <row r="46">
@@ -4201,10 +4189,10 @@
         <v>0.71</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5311490195676096</v>
+        <v>-0.5206</v>
       </c>
       <c r="J46" t="n">
-        <v>-19.12136470443395</v>
+        <v>-18.7416</v>
       </c>
     </row>
     <row r="47">
@@ -4241,10 +4229,10 @@
         <v>1.51</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5651121962526975</v>
+        <v>1.3115</v>
       </c>
       <c r="J47" t="n">
-        <v>20.34403906509711</v>
+        <v>47.214</v>
       </c>
     </row>
     <row r="48">
@@ -4281,10 +4269,10 @@
         <v>1.34</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3665781180923012</v>
+        <v>0.957</v>
       </c>
       <c r="J48" t="n">
-        <v>13.19681225132284</v>
+        <v>34.452</v>
       </c>
     </row>
     <row r="49">
@@ -4321,10 +4309,10 @@
         <v>0.88</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1407452810750969</v>
+        <v>-0.4848</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.066830118703487</v>
+        <v>-17.4528</v>
       </c>
     </row>
     <row r="50">
@@ -4361,10 +4349,10 @@
         <v>0.8</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2206495564181476</v>
+        <v>-0.6917</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.943384031053313</v>
+        <v>-24.9012</v>
       </c>
     </row>
     <row r="51">
@@ -4401,10 +4389,10 @@
         <v>0.8</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2206495564181476</v>
+        <v>-0.6917</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.943384031053313</v>
+        <v>-24.9012</v>
       </c>
     </row>
     <row r="52">
@@ -4441,10 +4429,10 @@
         <v>1.58</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5368353620208268</v>
+        <v>1.4373</v>
       </c>
       <c r="J52" t="n">
-        <v>12.34721332647902</v>
+        <v>33.0579</v>
       </c>
     </row>
     <row r="53">
@@ -4481,10 +4469,10 @@
         <v>1.15</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1532248091653067</v>
+        <v>0.4818</v>
       </c>
       <c r="J53" t="n">
-        <v>3.524170610802054</v>
+        <v>11.0814</v>
       </c>
     </row>
     <row r="54">
@@ -4521,10 +4509,10 @@
         <v>0.99</v>
       </c>
       <c r="I54" t="n">
-        <v>0.01617568580558811</v>
+        <v>-0.1322</v>
       </c>
       <c r="J54" t="n">
-        <v>0.3720407735285264</v>
+        <v>-3.0406</v>
       </c>
     </row>
     <row r="55">
@@ -4561,10 +4549,10 @@
         <v>0.96</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.01552128326262027</v>
+        <v>-0.2501</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.3569895150402662</v>
+        <v>-5.7523</v>
       </c>
     </row>
     <row r="56">
@@ -4601,10 +4589,10 @@
         <v>0.75</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.278593900346819</v>
+        <v>-0.8167</v>
       </c>
       <c r="J56" t="n">
-        <v>-6.407659707976838</v>
+        <v>-18.7841</v>
       </c>
     </row>
     <row r="57">
@@ -4641,10 +4629,10 @@
         <v>1.35</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2643938360247519</v>
+        <v>0.6107</v>
       </c>
       <c r="J57" t="n">
-        <v>6.081058228569293</v>
+        <v>14.0461</v>
       </c>
     </row>
     <row r="58">
@@ -4681,10 +4669,10 @@
         <v>0.95</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1141837484006943</v>
+        <v>-0.0859</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.626226213215968</v>
+        <v>-1.9757</v>
       </c>
     </row>
     <row r="59">
@@ -4721,10 +4709,10 @@
         <v>0.91</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1586624476417297</v>
+        <v>-0.1777</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.649236295759783</v>
+        <v>-4.0871</v>
       </c>
     </row>
     <row r="60">
@@ -4761,10 +4749,10 @@
         <v>0.71</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4220655417953026</v>
+        <v>-0.4914</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.707507461291961</v>
+        <v>-11.3022</v>
       </c>
     </row>
     <row r="61">
@@ -4801,10 +4789,10 @@
         <v>0.7</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4353348813047943</v>
+        <v>-0.5049</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.01270227001027</v>
+        <v>-11.6127</v>
       </c>
     </row>
     <row r="62">
@@ -4841,10 +4829,10 @@
         <v>1.86</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7098963940728872</v>
+        <v>1.8115</v>
       </c>
       <c r="J62" t="n">
-        <v>13.48803148738486</v>
+        <v>34.4185</v>
       </c>
     </row>
     <row r="63">
@@ -4881,10 +4869,10 @@
         <v>1.54</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4417172249732971</v>
+        <v>1.2224</v>
       </c>
       <c r="J63" t="n">
-        <v>8.392627274492645</v>
+        <v>23.2256</v>
       </c>
     </row>
     <row r="64">
@@ -4921,10 +4909,10 @@
         <v>1.46</v>
       </c>
       <c r="I64" t="n">
-        <v>0.371258165192301</v>
+        <v>1.0575</v>
       </c>
       <c r="J64" t="n">
-        <v>7.05390513865372</v>
+        <v>20.0925</v>
       </c>
     </row>
     <row r="65">
@@ -4961,10 +4949,10 @@
         <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.04406212151341119</v>
+        <v>-0.1735</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.8371803087548126</v>
+        <v>-3.2965</v>
       </c>
     </row>
     <row r="66">
@@ -5001,10 +4989,10 @@
         <v>0.97</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.08133057914064783</v>
+        <v>-0.3082</v>
       </c>
       <c r="J66" t="n">
-        <v>-1.545281003672309</v>
+        <v>-5.8558</v>
       </c>
     </row>
     <row r="67">
@@ -5041,10 +5029,10 @@
         <v>0.91</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.228165056968785</v>
+        <v>-0.0813</v>
       </c>
       <c r="J67" t="n">
-        <v>-4.335136082406915</v>
+        <v>-1.5447</v>
       </c>
     </row>
     <row r="68">
@@ -5081,10 +5069,10 @@
         <v>0.8</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.3706402965808749</v>
+        <v>-0.2673</v>
       </c>
       <c r="J68" t="n">
-        <v>-7.042165635036624</v>
+        <v>-5.0787</v>
       </c>
     </row>
     <row r="69">
@@ -5121,10 +5109,10 @@
         <v>0.76</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4175849293521116</v>
+        <v>-0.338</v>
       </c>
       <c r="J69" t="n">
-        <v>-7.934113657690121</v>
+        <v>-6.422</v>
       </c>
     </row>
     <row r="70">
@@ -5161,10 +5149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4969102206078768</v>
+        <v>-0.4652</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.441294191549659</v>
+        <v>-8.838800000000001</v>
       </c>
     </row>
     <row r="71">
@@ -5201,10 +5189,10 @@
         <v>0.6</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6110885389549923</v>
+        <v>-0.5942</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.61068224014485</v>
+        <v>-11.2898</v>
       </c>
     </row>
     <row r="72">
@@ -5241,10 +5229,10 @@
         <v>1.35</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3619571313357418</v>
+        <v>0.9182</v>
       </c>
       <c r="J72" t="n">
-        <v>7.96305688938632</v>
+        <v>20.2004</v>
       </c>
     </row>
     <row r="73">
@@ -5281,10 +5269,10 @@
         <v>1.33</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3377521168916269</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>7.430546571615791</v>
+        <v>19.217</v>
       </c>
     </row>
     <row r="74">
@@ -5321,10 +5309,10 @@
         <v>1.15</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1323106397669983</v>
+        <v>0.393</v>
       </c>
       <c r="J74" t="n">
-        <v>2.910834074873962</v>
+        <v>8.646000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -5361,10 +5349,10 @@
         <v>1.13</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1093991426299466</v>
+        <v>0.335</v>
       </c>
       <c r="J75" t="n">
-        <v>2.406781137858824</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="76">
@@ -5401,10 +5389,10 @@
         <v>0.93</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1040059991868533</v>
+        <v>-0.3831</v>
       </c>
       <c r="J76" t="n">
-        <v>-2.288131982110773</v>
+        <v>-8.4282</v>
       </c>
     </row>
     <row r="77">
@@ -5441,10 +5429,10 @@
         <v>1.34</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2227574011123269</v>
+        <v>0.5722</v>
       </c>
       <c r="J77" t="n">
-        <v>4.900662824471191</v>
+        <v>12.5884</v>
       </c>
     </row>
     <row r="78">
@@ -5481,10 +5469,10 @@
         <v>1.1</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.04012637749874483</v>
+        <v>0.2287</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.8827803049723862</v>
+        <v>5.0314</v>
       </c>
     </row>
     <row r="79">
@@ -5521,10 +5509,10 @@
         <v>1.08</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.06155728611861685</v>
+        <v>0.1935</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.354260294609571</v>
+        <v>4.257</v>
       </c>
     </row>
     <row r="80">
@@ -5561,10 +5549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2001200273123136</v>
+        <v>-0.1545</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.402640600870899</v>
+        <v>-3.399</v>
       </c>
     </row>
     <row r="81">
@@ -5601,10 +5589,10 @@
         <v>0.53</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6274897069326607</v>
+        <v>-0.7288</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.80477355251853</v>
+        <v>-16.0336</v>
       </c>
     </row>
     <row r="82">
@@ -5641,10 +5629,10 @@
         <v>1.21</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1479053440083152</v>
+        <v>0.3945</v>
       </c>
       <c r="J82" t="n">
-        <v>4.437160320249455</v>
+        <v>11.835</v>
       </c>
     </row>
     <row r="83">
@@ -5681,10 +5669,10 @@
         <v>1.03</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.05029586734610303</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.508876020383091</v>
+        <v>2.607</v>
       </c>
     </row>
     <row r="84">
@@ -5721,10 +5709,10 @@
         <v>0.97</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1015083319933554</v>
+        <v>-0.0968</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.045249959800663</v>
+        <v>-2.904</v>
       </c>
     </row>
     <row r="85">
@@ -5761,10 +5749,10 @@
         <v>0.93</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1403793956499862</v>
+        <v>-0.1779</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.211381869499585</v>
+        <v>-5.337</v>
       </c>
     </row>
     <row r="86">
@@ -5801,10 +5789,10 @@
         <v>0.91</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1602608127631393</v>
+        <v>-0.2138</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.80782438289418</v>
+        <v>-6.414</v>
       </c>
     </row>
     <row r="87">
@@ -5841,10 +5829,10 @@
         <v>1.69</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7016680609539474</v>
+        <v>0.9385</v>
       </c>
       <c r="J87" t="n">
-        <v>21.05004182861842</v>
+        <v>28.155</v>
       </c>
     </row>
     <row r="88">
@@ -5881,10 +5869,10 @@
         <v>1.31</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2995272929504179</v>
+        <v>0.4987</v>
       </c>
       <c r="J88" t="n">
-        <v>8.985818788512535</v>
+        <v>14.961</v>
       </c>
     </row>
     <row r="89">
@@ -5921,10 +5909,10 @@
         <v>0.86</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1816957371271137</v>
+        <v>-0.3181</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.450872113813412</v>
+        <v>-9.542999999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5961,10 +5949,10 @@
         <v>0.85</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1925121312846474</v>
+        <v>-0.3331</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.775363938539422</v>
+        <v>-9.993</v>
       </c>
     </row>
     <row r="91">
@@ -6001,10 +5989,10 @@
         <v>0.82</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2248300395137697</v>
+        <v>-0.3767</v>
       </c>
       <c r="J91" t="n">
-        <v>-6.74490118541309</v>
+        <v>-11.301</v>
       </c>
     </row>
     <row r="92">
@@ -6041,10 +6029,10 @@
         <v>1.83</v>
       </c>
       <c r="I92" t="n">
-        <v>0.8595398507254781</v>
+        <v>1.8556</v>
       </c>
       <c r="J92" t="n">
-        <v>20.62895641741147</v>
+        <v>44.5344</v>
       </c>
     </row>
     <row r="93">
@@ -6081,10 +6069,10 @@
         <v>1.24</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1923583574264797</v>
+        <v>0.673</v>
       </c>
       <c r="J93" t="n">
-        <v>4.616600578235513</v>
+        <v>16.152</v>
       </c>
     </row>
     <row r="94">
@@ -6121,10 +6109,10 @@
         <v>1.02</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.04698432744684776</v>
+        <v>-0.0044</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.127623858724346</v>
+        <v>-0.1056</v>
       </c>
     </row>
     <row r="95">
@@ -6161,10 +6149,10 @@
         <v>0.93</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.13394673634506</v>
+        <v>-0.3756</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.214721672281439</v>
+        <v>-9.0144</v>
       </c>
     </row>
     <row r="96">
@@ -6201,10 +6189,10 @@
         <v>0.76</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3011080239497707</v>
+        <v>-0.8122</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.226592574794496</v>
+        <v>-19.4928</v>
       </c>
     </row>
     <row r="97">
@@ -6241,10 +6229,10 @@
         <v>1.59</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5301207553981844</v>
+        <v>0.8602</v>
       </c>
       <c r="J97" t="n">
-        <v>12.72289812955642</v>
+        <v>20.6448</v>
       </c>
     </row>
     <row r="98">
@@ -6281,10 +6269,10 @@
         <v>1.03</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.0731734021672051</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.756161652012922</v>
+        <v>2.0304</v>
       </c>
     </row>
     <row r="99">
@@ -6321,10 +6309,10 @@
         <v>1.03</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0731734021672051</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="J99" t="n">
-        <v>-1.756161652012922</v>
+        <v>2.0304</v>
       </c>
     </row>
     <row r="100">
@@ -6361,10 +6349,10 @@
         <v>0.84</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2686899468880911</v>
+        <v>-0.3279</v>
       </c>
       <c r="J100" t="n">
-        <v>-6.448558725314186</v>
+        <v>-7.8696</v>
       </c>
     </row>
     <row r="101">
@@ -6401,10 +6389,10 @@
         <v>0.58</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.539406400222183</v>
+        <v>-0.6718</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.94575360533239</v>
+        <v>-16.1232</v>
       </c>
     </row>
     <row r="102">
@@ -6441,10 +6429,10 @@
         <v>1.45</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4285935453022001</v>
+        <v>0.6842</v>
       </c>
       <c r="J102" t="n">
-        <v>9.857651541950602</v>
+        <v>15.7366</v>
       </c>
     </row>
     <row r="103">
@@ -6481,10 +6469,10 @@
         <v>1.11</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1184391050513402</v>
+        <v>0.2182</v>
       </c>
       <c r="J103" t="n">
-        <v>2.724099416180825</v>
+        <v>5.0186</v>
       </c>
     </row>
     <row r="104">
@@ -6521,10 +6509,10 @@
         <v>1.01</v>
       </c>
       <c r="I104" t="n">
-        <v>0.03626646023914575</v>
+        <v>0.0002</v>
       </c>
       <c r="J104" t="n">
-        <v>0.8341285855003522</v>
+        <v>0.0046</v>
       </c>
     </row>
     <row r="105">
@@ -6561,10 +6549,10 @@
         <v>0.93</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.04626206331718782</v>
+        <v>-0.1948</v>
       </c>
       <c r="J105" t="n">
-        <v>-1.06402745629532</v>
+        <v>-4.4804</v>
       </c>
     </row>
     <row r="106">
@@ -6601,10 +6589,10 @@
         <v>0.83</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1744433458912975</v>
+        <v>-0.3546</v>
       </c>
       <c r="J106" t="n">
-        <v>-4.012196955499841</v>
+        <v>-8.155799999999999</v>
       </c>
     </row>
     <row r="107">
@@ -6641,10 +6629,10 @@
         <v>1.62</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5652142262629674</v>
+        <v>0.9104</v>
       </c>
       <c r="J107" t="n">
-        <v>12.99992720404825</v>
+        <v>20.9392</v>
       </c>
     </row>
     <row r="108">
@@ -6681,10 +6669,10 @@
         <v>1.01</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.055588210644334</v>
+        <v>0.0599</v>
       </c>
       <c r="J108" t="n">
-        <v>-1.278528844819682</v>
+        <v>1.3777</v>
       </c>
     </row>
     <row r="109">
@@ -6721,10 +6709,10 @@
         <v>0.93</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1353316745711002</v>
+        <v>-0.1595</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.112628515135305</v>
+        <v>-3.6685</v>
       </c>
     </row>
     <row r="110">
@@ -6761,10 +6749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2712816686209187</v>
+        <v>-0.36</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.23947837828113</v>
+        <v>-8.279999999999999</v>
       </c>
     </row>
     <row r="111">
@@ -6801,10 +6789,10 @@
         <v>0.45</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6652767271592352</v>
+        <v>-0.8168</v>
       </c>
       <c r="J111" t="n">
-        <v>-15.30136472466241</v>
+        <v>-18.7864</v>
       </c>
     </row>
     <row r="112">
@@ -6841,10 +6829,10 @@
         <v>1.2</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1328848946506093</v>
+        <v>0.4136</v>
       </c>
       <c r="J112" t="n">
-        <v>3.056352576964014</v>
+        <v>9.5128</v>
       </c>
     </row>
     <row r="113">
@@ -6881,10 +6869,10 @@
         <v>0.99</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.07960271127974236</v>
+        <v>0.011</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.830862359434074</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="114">
@@ -6921,10 +6909,10 @@
         <v>0.86</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2311958132888191</v>
+        <v>-0.2654</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.31750370564284</v>
+        <v>-6.1042</v>
       </c>
     </row>
     <row r="115">
@@ -6961,10 +6949,10 @@
         <v>0.83</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2687532070533695</v>
+        <v>-0.3145</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.181323762227499</v>
+        <v>-7.2335</v>
       </c>
     </row>
     <row r="116">
@@ -7001,10 +6989,10 @@
         <v>0.7</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4338126436377291</v>
+        <v>-0.5031</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.97769080366777</v>
+        <v>-11.5713</v>
       </c>
     </row>
     <row r="117">
@@ -7041,10 +7029,10 @@
         <v>1.66</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6489903760338205</v>
+        <v>1.5527</v>
       </c>
       <c r="J117" t="n">
-        <v>14.92677864877787</v>
+        <v>35.7121</v>
       </c>
     </row>
     <row r="118">
@@ -7081,10 +7069,10 @@
         <v>1.39</v>
       </c>
       <c r="I118" t="n">
-        <v>0.381301809982126</v>
+        <v>1.0181</v>
       </c>
       <c r="J118" t="n">
-        <v>8.769941629588898</v>
+        <v>23.4163</v>
       </c>
     </row>
     <row r="119">
@@ -7121,10 +7109,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.05497769642057795</v>
+        <v>-0.2441</v>
       </c>
       <c r="J119" t="n">
-        <v>-1.264487017673293</v>
+        <v>-5.6143</v>
       </c>
     </row>
     <row r="120">
@@ -7161,10 +7149,10 @@
         <v>0.96</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.06629595166641773</v>
+        <v>-0.2791</v>
       </c>
       <c r="J120" t="n">
-        <v>-1.524806888327608</v>
+        <v>-6.4193</v>
       </c>
     </row>
     <row r="121">
@@ -7201,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2534135995275539</v>
+        <v>-0.7419</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.82851278913374</v>
+        <v>-17.0637</v>
       </c>
     </row>
     <row r="122">
@@ -7241,10 +7229,10 @@
         <v>1.02</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.01398591033517727</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="J122" t="n">
-        <v>-0.3356618480442544</v>
+        <v>2.3328</v>
       </c>
     </row>
     <row r="123">
@@ -7281,10 +7269,10 @@
         <v>0.99</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.05158654251406844</v>
+        <v>0.001</v>
       </c>
       <c r="J123" t="n">
-        <v>-1.238077020337643</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="124">
@@ -7321,10 +7309,10 @@
         <v>0.96</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.08778076720675144</v>
+        <v>-0.0718</v>
       </c>
       <c r="J124" t="n">
-        <v>-2.106738412962035</v>
+        <v>-1.7232</v>
       </c>
     </row>
     <row r="125">
@@ -7361,10 +7349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1095420497955225</v>
+        <v>-0.1182</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.629009195092539</v>
+        <v>-2.8368</v>
       </c>
     </row>
     <row r="126">
@@ -7401,10 +7389,10 @@
         <v>0.78</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3060479593582232</v>
+        <v>-0.397</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.345151024597356</v>
+        <v>-9.528</v>
       </c>
     </row>
     <row r="127">
@@ -7441,10 +7429,10 @@
         <v>1.23</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2244011994011166</v>
+        <v>0.6822</v>
       </c>
       <c r="J127" t="n">
-        <v>5.385628785626798</v>
+        <v>16.3728</v>
       </c>
     </row>
     <row r="128">
@@ -7481,10 +7469,10 @@
         <v>1.16</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1503380357612965</v>
+        <v>0.4999</v>
       </c>
       <c r="J128" t="n">
-        <v>3.608112858271115</v>
+        <v>11.9976</v>
       </c>
     </row>
     <row r="129">
@@ -7521,10 +7509,10 @@
         <v>1.1</v>
       </c>
       <c r="I129" t="n">
-        <v>0.09245590847439733</v>
+        <v>0.3111</v>
       </c>
       <c r="J129" t="n">
-        <v>2.218941803385536</v>
+        <v>7.4664</v>
       </c>
     </row>
     <row r="130">
@@ -7561,10 +7549,10 @@
         <v>1.1</v>
       </c>
       <c r="I130" t="n">
-        <v>0.09245590847439733</v>
+        <v>0.3111</v>
       </c>
       <c r="J130" t="n">
-        <v>2.218941803385536</v>
+        <v>7.4664</v>
       </c>
     </row>
     <row r="131">
@@ -7601,10 +7589,10 @@
         <v>0.91</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1063833696021489</v>
+        <v>-0.4137</v>
       </c>
       <c r="J131" t="n">
-        <v>-2.553200870451573</v>
+        <v>-9.928800000000001</v>
       </c>
     </row>
     <row r="132">
@@ -7641,10 +7629,10 @@
         <v>1.91</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7801286462582367</v>
+        <v>1.9324</v>
       </c>
       <c r="J132" t="n">
-        <v>14.8224442789065</v>
+        <v>36.7156</v>
       </c>
     </row>
     <row r="133">
@@ -7681,10 +7669,10 @@
         <v>1.69</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6124526293665054</v>
+        <v>1.5624</v>
       </c>
       <c r="J133" t="n">
-        <v>11.6365999579636</v>
+        <v>29.6856</v>
       </c>
     </row>
     <row r="134">
@@ -7721,10 +7709,10 @@
         <v>1.21</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2117249832079023</v>
+        <v>0.5105</v>
       </c>
       <c r="J134" t="n">
-        <v>4.022774680950144</v>
+        <v>9.6995</v>
       </c>
     </row>
     <row r="135">
@@ -7761,10 +7749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2036378078359811</v>
+        <v>-0.7174</v>
       </c>
       <c r="J135" t="n">
-        <v>-3.869118348883641</v>
+        <v>-13.6306</v>
       </c>
     </row>
     <row r="136">
@@ -7801,10 +7789,10 @@
         <v>0.62</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4321588164993478</v>
+        <v>-1.1312</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.21101751348761</v>
+        <v>-21.4928</v>
       </c>
     </row>
     <row r="137">
@@ -7841,10 +7829,10 @@
         <v>1.13</v>
       </c>
       <c r="I137" t="n">
-        <v>0.03213002991864868</v>
+        <v>0.3468</v>
       </c>
       <c r="J137" t="n">
-        <v>0.6104705684543248</v>
+        <v>6.5892</v>
       </c>
     </row>
     <row r="138">
@@ -7881,10 +7869,10 @@
         <v>0.86</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.3101787873096355</v>
+        <v>-0.2005</v>
       </c>
       <c r="J138" t="n">
-        <v>-5.893396958883074</v>
+        <v>-3.8095</v>
       </c>
     </row>
     <row r="139">
@@ -7921,10 +7909,10 @@
         <v>0.79</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3896398140750861</v>
+        <v>-0.3369</v>
       </c>
       <c r="J139" t="n">
-        <v>-7.403156467426635</v>
+        <v>-6.4011</v>
       </c>
     </row>
     <row r="140">
@@ -7961,10 +7949,10 @@
         <v>0.74</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4524330088493485</v>
+        <v>-0.417</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.59622716813762</v>
+        <v>-7.923</v>
       </c>
     </row>
     <row r="141">
@@ -8001,10 +7989,10 @@
         <v>0.57</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6725191715945503</v>
+        <v>-0.6508</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.77786426029646</v>
+        <v>-12.3652</v>
       </c>
     </row>
     <row r="142">
@@ -8041,10 +8029,10 @@
         <v>1.09</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.03935059397937821</v>
+        <v>0.3216</v>
       </c>
       <c r="J142" t="n">
-        <v>-0.7083106916288078</v>
+        <v>5.7888</v>
       </c>
     </row>
     <row r="143">
@@ -8081,10 +8069,10 @@
         <v>0.99</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.165453992540541</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="J143" t="n">
-        <v>-2.978171865729738</v>
+        <v>1.6776</v>
       </c>
     </row>
     <row r="144">
@@ -8121,10 +8109,10 @@
         <v>0.57</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.6725517275884029</v>
+        <v>-0.6268</v>
       </c>
       <c r="J144" t="n">
-        <v>-12.10593109659125</v>
+        <v>-11.2824</v>
       </c>
     </row>
     <row r="145">
@@ -8161,10 +8149,10 @@
         <v>0.55</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.6970546262357779</v>
+        <v>-0.6536</v>
       </c>
       <c r="J145" t="n">
-        <v>-12.546983272244</v>
+        <v>-11.7648</v>
       </c>
     </row>
     <row r="146">
@@ -8201,10 +8189,10 @@
         <v>0.43</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.8418628607107063</v>
+        <v>-0.8061</v>
       </c>
       <c r="J146" t="n">
-        <v>-15.15353149279271</v>
+        <v>-14.5098</v>
       </c>
     </row>
     <row r="147">
@@ -8241,10 +8229,10 @@
         <v>2.83</v>
       </c>
       <c r="I147" t="n">
-        <v>1.237119532609076</v>
+        <v>1.8657</v>
       </c>
       <c r="J147" t="n">
-        <v>22.26815158696337</v>
+        <v>33.5826</v>
       </c>
     </row>
     <row r="148">
@@ -8281,10 +8269,10 @@
         <v>1.41</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2690679705202184</v>
+        <v>0.4928</v>
       </c>
       <c r="J148" t="n">
-        <v>4.843223469363931</v>
+        <v>8.8704</v>
       </c>
     </row>
     <row r="149">
@@ -8321,10 +8309,10 @@
         <v>1.33</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2025594074470981</v>
+        <v>0.3926</v>
       </c>
       <c r="J149" t="n">
-        <v>3.646069334047766</v>
+        <v>7.0668</v>
       </c>
     </row>
     <row r="150">
@@ -8361,10 +8349,10 @@
         <v>1.27</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1519602706612925</v>
+        <v>0.3165</v>
       </c>
       <c r="J150" t="n">
-        <v>2.735284871903266</v>
+        <v>5.697</v>
       </c>
     </row>
     <row r="151">
@@ -8401,10 +8389,10 @@
         <v>0.58</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6049976662699629</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.88995799285933</v>
+        <v>-12.8196</v>
       </c>
     </row>
     <row r="152">
@@ -8441,10 +8429,10 @@
         <v>1.62</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5164563614164612</v>
+        <v>1.4699</v>
       </c>
       <c r="J152" t="n">
-        <v>11.36203995116215</v>
+        <v>32.3378</v>
       </c>
     </row>
     <row r="153">
@@ -8481,10 +8469,10 @@
         <v>1.6</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5000991842805536</v>
+        <v>1.432</v>
       </c>
       <c r="J153" t="n">
-        <v>11.00218205417218</v>
+        <v>31.504</v>
       </c>
     </row>
     <row r="154">
@@ -8521,10 +8509,10 @@
         <v>1.08</v>
       </c>
       <c r="I154" t="n">
-        <v>0.05338788839618867</v>
+        <v>0.1919</v>
       </c>
       <c r="J154" t="n">
-        <v>1.174533544716151</v>
+        <v>4.2218</v>
       </c>
     </row>
     <row r="155">
@@ -8561,10 +8549,10 @@
         <v>0.84</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2292531791229581</v>
+        <v>-0.6247</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.043569940705079</v>
+        <v>-13.7434</v>
       </c>
     </row>
     <row r="156">
@@ -8601,10 +8589,10 @@
         <v>0.71</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3936765180692182</v>
+        <v>-0.9274</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.660883397522801</v>
+        <v>-20.4028</v>
       </c>
     </row>
     <row r="157">
@@ -8641,10 +8629,10 @@
         <v>1.39</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2397983893294509</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="J157" t="n">
-        <v>5.27556456524792</v>
+        <v>14.2714</v>
       </c>
     </row>
     <row r="158">
@@ -8681,10 +8669,10 @@
         <v>1.11</v>
       </c>
       <c r="I158" t="n">
-        <v>0.004127272744398192</v>
+        <v>0.2614</v>
       </c>
       <c r="J158" t="n">
-        <v>0.09080000037676023</v>
+        <v>5.7508</v>
       </c>
     </row>
     <row r="159">
@@ -8721,10 +8709,10 @@
         <v>1.04</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.08747926042088985</v>
+        <v>0.1338</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.924543729259577</v>
+        <v>2.9436</v>
       </c>
     </row>
     <row r="160">
@@ -8761,10 +8749,10 @@
         <v>0.68</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.5503479144480946</v>
+        <v>-0.538</v>
       </c>
       <c r="J160" t="n">
-        <v>-12.10765411785808</v>
+        <v>-11.836</v>
       </c>
     </row>
     <row r="161">
@@ -8801,10 +8789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7025993354582276</v>
+        <v>-0.6877</v>
       </c>
       <c r="J161" t="n">
-        <v>-15.45718538008101</v>
+        <v>-15.1294</v>
       </c>
     </row>
     <row r="162">
@@ -8841,10 +8829,10 @@
         <v>1.3</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3668125876205275</v>
+        <v>0.4927</v>
       </c>
       <c r="J162" t="n">
-        <v>10.27075245337477</v>
+        <v>13.7956</v>
       </c>
     </row>
     <row r="163">
@@ -8881,10 +8869,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2935537675714539</v>
+        <v>0.4116</v>
       </c>
       <c r="J163" t="n">
-        <v>8.21950549200071</v>
+        <v>11.5248</v>
       </c>
     </row>
     <row r="164">
@@ -8921,10 +8909,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1273807609938668</v>
+        <v>0.1912</v>
       </c>
       <c r="J164" t="n">
-        <v>3.56666130782827</v>
+        <v>5.3536</v>
       </c>
     </row>
     <row r="165">
@@ -8961,10 +8949,10 @@
         <v>1.08</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1086765239053651</v>
+        <v>0.1463</v>
       </c>
       <c r="J165" t="n">
-        <v>3.042942669350222</v>
+        <v>4.0964</v>
       </c>
     </row>
     <row r="166">
@@ -9001,10 +8989,10 @@
         <v>0.7</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2778253437221885</v>
+        <v>-0.534</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.779109624221279</v>
+        <v>-14.952</v>
       </c>
     </row>
     <row r="167">
@@ -9041,10 +9029,10 @@
         <v>1.71</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4978481147516784</v>
+        <v>0.9805</v>
       </c>
       <c r="J167" t="n">
-        <v>13.939747213047</v>
+        <v>27.454</v>
       </c>
     </row>
     <row r="168">
@@ -9081,10 +9069,10 @@
         <v>0.98</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1874179657020582</v>
+        <v>-0.0857</v>
       </c>
       <c r="J168" t="n">
-        <v>-5.247703039657628</v>
+        <v>-2.3996</v>
       </c>
     </row>
     <row r="169">
@@ -9121,10 +9109,10 @@
         <v>0.97</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.199967305414747</v>
+        <v>-0.1085</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.599084551612916</v>
+        <v>-3.038</v>
       </c>
     </row>
     <row r="170">
@@ -9161,10 +9149,10 @@
         <v>0.87</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.328720705097343</v>
+        <v>-0.2882</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.204179742725604</v>
+        <v>-8.069599999999999</v>
       </c>
     </row>
     <row r="171">
@@ -9201,10 +9189,10 @@
         <v>0.67</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.581610726788538</v>
+        <v>-0.5653</v>
       </c>
       <c r="J171" t="n">
-        <v>-16.28510035007906</v>
+        <v>-15.8284</v>
       </c>
     </row>
     <row r="172">
@@ -9241,10 +9229,10 @@
         <v>0.95</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.1628601926363795</v>
+        <v>-0.0434</v>
       </c>
       <c r="J172" t="n">
-        <v>-3.094343660091211</v>
+        <v>-0.8246</v>
       </c>
     </row>
     <row r="173">
@@ -9281,10 +9269,10 @@
         <v>0.93</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1826271341114097</v>
+        <v>-0.082</v>
       </c>
       <c r="J173" t="n">
-        <v>-3.469915548116783</v>
+        <v>-1.558</v>
       </c>
     </row>
     <row r="174">
@@ -9321,10 +9309,10 @@
         <v>0.91</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2021871147157394</v>
+        <v>-0.1191</v>
       </c>
       <c r="J174" t="n">
-        <v>-3.841555179599048</v>
+        <v>-2.2629</v>
       </c>
     </row>
     <row r="175">
@@ -9361,10 +9349,10 @@
         <v>0.7</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3941647014170338</v>
+        <v>-0.4811</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.489129326923642</v>
+        <v>-9.1409</v>
       </c>
     </row>
     <row r="176">
@@ -9401,10 +9389,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4135055881445208</v>
+        <v>-0.5091</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.856606174745894</v>
+        <v>-9.6729</v>
       </c>
     </row>
     <row r="177">
@@ -9441,10 +9429,10 @@
         <v>2.11</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9282105807624499</v>
+        <v>2.0593</v>
       </c>
       <c r="J177" t="n">
-        <v>17.63600103448655</v>
+        <v>39.1267</v>
       </c>
     </row>
     <row r="178">
@@ -9481,10 +9469,10 @@
         <v>1.13</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1217336130316575</v>
+        <v>0.2849</v>
       </c>
       <c r="J178" t="n">
-        <v>2.312938647601492</v>
+        <v>5.4131</v>
       </c>
     </row>
     <row r="179">
@@ -9521,10 +9509,10 @@
         <v>1.09</v>
       </c>
       <c r="I179" t="n">
-        <v>0.08449560118753653</v>
+        <v>0.1745</v>
       </c>
       <c r="J179" t="n">
-        <v>1.605416422563194</v>
+        <v>3.3155</v>
       </c>
     </row>
     <row r="180">
@@ -9561,10 +9549,10 @@
         <v>1.07</v>
       </c>
       <c r="I180" t="n">
-        <v>0.06586161349895685</v>
+        <v>0.116</v>
       </c>
       <c r="J180" t="n">
-        <v>1.25137065648018</v>
+        <v>2.204</v>
       </c>
     </row>
     <row r="181">
@@ -9601,10 +9589,10 @@
         <v>0.99</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.01152107140059939</v>
+        <v>-0.2073</v>
       </c>
       <c r="J181" t="n">
-        <v>-0.2189003566113884</v>
+        <v>-3.9387</v>
       </c>
     </row>
     <row r="182">
@@ -9641,10 +9629,10 @@
         <v>1.35</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2831708559923972</v>
+        <v>0.6405</v>
       </c>
       <c r="J182" t="n">
-        <v>5.663417119847943</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="183">
@@ -9681,10 +9669,10 @@
         <v>0.85</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2463809415683862</v>
+        <v>-0.2379</v>
       </c>
       <c r="J183" t="n">
-        <v>-4.927618831367724</v>
+        <v>-4.758</v>
       </c>
     </row>
     <row r="184">
@@ -9721,10 +9709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2794151737318493</v>
+        <v>-0.3178</v>
       </c>
       <c r="J184" t="n">
-        <v>-5.588303474636986</v>
+        <v>-6.356</v>
       </c>
     </row>
     <row r="185">
@@ -9761,10 +9749,10 @@
         <v>0.67</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4133999937580676</v>
+        <v>-0.5262</v>
       </c>
       <c r="J185" t="n">
-        <v>-8.267999875161353</v>
+        <v>-10.524</v>
       </c>
     </row>
     <row r="186">
@@ -9801,10 +9789,10 @@
         <v>0.55</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5274281623431345</v>
+        <v>-0.6816</v>
       </c>
       <c r="J186" t="n">
-        <v>-10.54856324686269</v>
+        <v>-13.632</v>
       </c>
     </row>
     <row r="187">
@@ -9841,10 +9829,10 @@
         <v>1.6</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5057759383419697</v>
+        <v>1.3765</v>
       </c>
       <c r="J187" t="n">
-        <v>10.11551876683939</v>
+        <v>27.53</v>
       </c>
     </row>
     <row r="188">
@@ -9881,10 +9869,10 @@
         <v>1.59</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4971452429318995</v>
+        <v>1.3574</v>
       </c>
       <c r="J188" t="n">
-        <v>9.942904858637991</v>
+        <v>27.148</v>
       </c>
     </row>
     <row r="189">
@@ -9921,10 +9909,10 @@
         <v>1.37</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3016658799607644</v>
+        <v>0.9038</v>
       </c>
       <c r="J189" t="n">
-        <v>6.033317599215289</v>
+        <v>18.076</v>
       </c>
     </row>
     <row r="190">
@@ -9961,10 +9949,10 @@
         <v>1.17</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1314123336065535</v>
+        <v>0.3864</v>
       </c>
       <c r="J190" t="n">
-        <v>2.628246672131071</v>
+        <v>7.728</v>
       </c>
     </row>
     <row r="191">
@@ -10001,10 +9989,10 @@
         <v>0.7</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3967256044260173</v>
+        <v>-0.9712</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.934512088520346</v>
+        <v>-19.424</v>
       </c>
     </row>
     <row r="192">
@@ -10041,10 +10029,10 @@
         <v>2.13</v>
       </c>
       <c r="I192" t="n">
-        <v>0.9259806144879796</v>
+        <v>2.0593</v>
       </c>
       <c r="J192" t="n">
-        <v>15.74167044629565</v>
+        <v>35.0081</v>
       </c>
     </row>
     <row r="193">
@@ -10081,10 +10069,10 @@
         <v>1.4</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3544030389489769</v>
+        <v>0.9103</v>
       </c>
       <c r="J193" t="n">
-        <v>6.024851662132607</v>
+        <v>15.4751</v>
       </c>
     </row>
     <row r="194">
@@ -10121,10 +10109,10 @@
         <v>1.24</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2248332010980826</v>
+        <v>0.5173</v>
       </c>
       <c r="J194" t="n">
-        <v>3.822164418667405</v>
+        <v>8.7941</v>
       </c>
     </row>
     <row r="195">
@@ -10161,10 +10149,10 @@
         <v>1.15</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1456591571716173</v>
+        <v>0.2988</v>
       </c>
       <c r="J195" t="n">
-        <v>2.476205671917494</v>
+        <v>5.0796</v>
       </c>
     </row>
     <row r="196">
@@ -10201,10 +10189,10 @@
         <v>1</v>
       </c>
       <c r="I196" t="n">
-        <v>0.01463525607019514</v>
+        <v>-0.1779</v>
       </c>
       <c r="J196" t="n">
-        <v>0.2487993531933174</v>
+        <v>-3.0243</v>
       </c>
     </row>
     <row r="197">
@@ -10241,10 +10229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.2822059425880775</v>
+        <v>-0.212</v>
       </c>
       <c r="J197" t="n">
-        <v>-4.797501023997317</v>
+        <v>-3.604</v>
       </c>
     </row>
     <row r="198">
@@ -10281,10 +10269,10 @@
         <v>0.7</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.3933778601334998</v>
+        <v>-0.3902</v>
       </c>
       <c r="J198" t="n">
-        <v>-6.687423622269497</v>
+        <v>-6.6334</v>
       </c>
     </row>
     <row r="199">
@@ -10321,10 +10309,10 @@
         <v>0.67</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.4180464230474584</v>
+        <v>-0.4536</v>
       </c>
       <c r="J199" t="n">
-        <v>-7.106789191806794</v>
+        <v>-7.7112</v>
       </c>
     </row>
     <row r="200">
@@ -10361,10 +10349,10 @@
         <v>0.64</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4454846557134493</v>
+        <v>-0.5057</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.573239147128638</v>
+        <v>-8.5969</v>
       </c>
     </row>
     <row r="201">
@@ -10401,10 +10389,10 @@
         <v>0.57</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5152585317938794</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.759395040495949</v>
+        <v>-10.3768</v>
       </c>
     </row>
     <row r="202">
@@ -10441,10 +10429,10 @@
         <v>2.41</v>
       </c>
       <c r="I202" t="n">
-        <v>1.025371450139196</v>
+        <v>2.0593</v>
       </c>
       <c r="J202" t="n">
-        <v>14.35520030194875</v>
+        <v>28.8302</v>
       </c>
     </row>
     <row r="203">
@@ -10481,10 +10469,10 @@
         <v>1.79</v>
       </c>
       <c r="I203" t="n">
-        <v>0.5555262205500263</v>
+        <v>1.5595</v>
       </c>
       <c r="J203" t="n">
-        <v>7.777367087700369</v>
+        <v>21.833</v>
       </c>
     </row>
     <row r="204">
@@ -10521,10 +10509,10 @@
         <v>1.55</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3683093099624599</v>
+        <v>1.0655</v>
       </c>
       <c r="J204" t="n">
-        <v>5.156330339474438</v>
+        <v>14.917</v>
       </c>
     </row>
     <row r="205">
@@ -10561,10 +10549,10 @@
         <v>1.46</v>
       </c>
       <c r="I205" t="n">
-        <v>0.29214051463141</v>
+        <v>0.8885</v>
       </c>
       <c r="J205" t="n">
-        <v>4.08996720483974</v>
+        <v>12.439</v>
       </c>
     </row>
     <row r="206">
@@ -10601,10 +10589,10 @@
         <v>1.19</v>
       </c>
       <c r="I206" t="n">
-        <v>0.06720954552166648</v>
+        <v>0.3223</v>
       </c>
       <c r="J206" t="n">
-        <v>0.9409336373033308</v>
+        <v>4.5122</v>
       </c>
     </row>
     <row r="207">
@@ -10641,10 +10629,10 @@
         <v>0.99</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.2090928760717778</v>
+        <v>0.1409</v>
       </c>
       <c r="J207" t="n">
-        <v>-2.927300265004889</v>
+        <v>1.9726</v>
       </c>
     </row>
     <row r="208">
@@ -10681,10 +10669,10 @@
         <v>0.8</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.4011367948284006</v>
+        <v>-0.2026</v>
       </c>
       <c r="J208" t="n">
-        <v>-5.615915127597608</v>
+        <v>-2.8364</v>
       </c>
     </row>
     <row r="209">
@@ -10721,10 +10709,10 @@
         <v>0.58</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.6080012004898497</v>
+        <v>-0.5737</v>
       </c>
       <c r="J209" t="n">
-        <v>-8.512016806857897</v>
+        <v>-8.0318</v>
       </c>
     </row>
     <row r="210">
@@ -10761,10 +10749,10 @@
         <v>0.41</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.7743371096164696</v>
+        <v>-0.8097</v>
       </c>
       <c r="J210" t="n">
-        <v>-10.84071953463057</v>
+        <v>-11.3358</v>
       </c>
     </row>
     <row r="211">
@@ -10801,10 +10789,10 @@
         <v>0.37</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.8131718740360225</v>
+        <v>-0.8603</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.38440623650432</v>
+        <v>-12.0442</v>
       </c>
     </row>
     <row r="212">
@@ -10841,10 +10829,10 @@
         <v>1.17</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.01676822316723439</v>
+        <v>0.3459</v>
       </c>
       <c r="J212" t="n">
-        <v>-0.3353644633446878</v>
+        <v>6.918</v>
       </c>
     </row>
     <row r="213">
@@ -10881,10 +10869,10 @@
         <v>1.11</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.09757459191622024</v>
+        <v>0.2516</v>
       </c>
       <c r="J213" t="n">
-        <v>-1.951491838324405</v>
+        <v>5.032</v>
       </c>
     </row>
     <row r="214">
@@ -10921,10 +10909,10 @@
         <v>0.95</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2978699458325888</v>
+        <v>-0.1275</v>
       </c>
       <c r="J214" t="n">
-        <v>-5.957398916651776</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="215">
@@ -10961,10 +10949,10 @@
         <v>0.88</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3887326603929582</v>
+        <v>-0.2558</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.774653207859164</v>
+        <v>-5.116</v>
       </c>
     </row>
     <row r="216">
@@ -11001,10 +10989,10 @@
         <v>0.8</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4950175857654375</v>
+        <v>-0.3793</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.900351715308751</v>
+        <v>-7.586</v>
       </c>
     </row>
     <row r="217">
@@ -11041,10 +11029,10 @@
         <v>1.42</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3335423083483659</v>
+        <v>1.0417</v>
       </c>
       <c r="J217" t="n">
-        <v>6.670846166967318</v>
+        <v>20.834</v>
       </c>
     </row>
     <row r="218">
@@ -11081,10 +11069,10 @@
         <v>1.4</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3159655361038461</v>
+        <v>0.999</v>
       </c>
       <c r="J218" t="n">
-        <v>6.319310722076922</v>
+        <v>19.98</v>
       </c>
     </row>
     <row r="219">
@@ -11121,10 +11109,10 @@
         <v>1.36</v>
       </c>
       <c r="I219" t="n">
-        <v>0.2806974601361222</v>
+        <v>0.9113</v>
       </c>
       <c r="J219" t="n">
-        <v>5.613949202722443</v>
+        <v>18.226</v>
       </c>
     </row>
     <row r="220">
@@ -11161,10 +11149,10 @@
         <v>1.16</v>
       </c>
       <c r="I220" t="n">
-        <v>0.1145101617194601</v>
+        <v>0.3867</v>
       </c>
       <c r="J220" t="n">
-        <v>2.290203234389202</v>
+        <v>7.734</v>
       </c>
     </row>
     <row r="221">
@@ -11201,10 +11189,10 @@
         <v>0.82</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2684689570932083</v>
+        <v>-0.6898</v>
       </c>
       <c r="J221" t="n">
-        <v>-5.369379141864165</v>
+        <v>-13.796</v>
       </c>
     </row>
     <row r="222">
@@ -11241,10 +11229,10 @@
         <v>1.13</v>
       </c>
       <c r="I222" t="n">
-        <v>0.0734206476776794</v>
+        <v>0.3124</v>
       </c>
       <c r="J222" t="n">
-        <v>1.688674896586626</v>
+        <v>7.1852</v>
       </c>
     </row>
     <row r="223">
@@ -11281,10 +11269,10 @@
         <v>0.9</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.1843989546306616</v>
+        <v>-0.1858</v>
       </c>
       <c r="J223" t="n">
-        <v>-4.241175956505217</v>
+        <v>-4.2734</v>
       </c>
     </row>
     <row r="224">
@@ -11321,10 +11309,10 @@
         <v>0.88</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2077413241396815</v>
+        <v>-0.2254</v>
       </c>
       <c r="J224" t="n">
-        <v>-4.778050455212674</v>
+        <v>-5.1842</v>
       </c>
     </row>
     <row r="225">
@@ -11361,10 +11349,10 @@
         <v>0.88</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2077413241396815</v>
+        <v>-0.2254</v>
       </c>
       <c r="J225" t="n">
-        <v>-4.778050455212674</v>
+        <v>-5.1842</v>
       </c>
     </row>
     <row r="226">
@@ -11401,10 +11389,10 @@
         <v>0.74</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3911113815188847</v>
+        <v>-0.4455</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.995561774934348</v>
+        <v>-10.2465</v>
       </c>
     </row>
     <row r="227">
@@ -11441,10 +11429,10 @@
         <v>1.51</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4226275357170595</v>
+        <v>1.2652</v>
       </c>
       <c r="J227" t="n">
-        <v>9.720433321492369</v>
+        <v>29.0996</v>
       </c>
     </row>
     <row r="228">
@@ -11481,10 +11469,10 @@
         <v>1.18</v>
       </c>
       <c r="I228" t="n">
-        <v>0.1377656059495334</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="J228" t="n">
-        <v>3.168608936839268</v>
+        <v>11.8588</v>
       </c>
     </row>
     <row r="229">
@@ -11521,10 +11509,10 @@
         <v>1.06</v>
       </c>
       <c r="I229" t="n">
-        <v>0.04019852375361849</v>
+        <v>0.1373</v>
       </c>
       <c r="J229" t="n">
-        <v>0.9245660463332253</v>
+        <v>3.1579</v>
       </c>
     </row>
     <row r="230">
@@ -11561,10 +11549,10 @@
         <v>1.02</v>
       </c>
       <c r="I230" t="n">
-        <v>0.004463244959053115</v>
+        <v>-0.0035</v>
       </c>
       <c r="J230" t="n">
-        <v>0.1026546340582216</v>
+        <v>-0.0805</v>
       </c>
     </row>
     <row r="231">
@@ -11601,10 +11589,10 @@
         <v>1</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.01996144237420281</v>
+        <v>-0.1051</v>
       </c>
       <c r="J231" t="n">
-        <v>-0.4591131746066646</v>
+        <v>-2.4173</v>
       </c>
     </row>
     <row r="232">
@@ -11641,10 +11629,10 @@
         <v>1.15</v>
       </c>
       <c r="I232" t="n">
-        <v>0.106095089278434</v>
+        <v>0.3141</v>
       </c>
       <c r="J232" t="n">
-        <v>2.546282142682416</v>
+        <v>7.5384</v>
       </c>
     </row>
     <row r="233">
@@ -11681,10 +11669,10 @@
         <v>1.12</v>
       </c>
       <c r="I233" t="n">
-        <v>0.07392087182984251</v>
+        <v>0.2666</v>
       </c>
       <c r="J233" t="n">
-        <v>1.77410092391622</v>
+        <v>6.3984</v>
       </c>
     </row>
     <row r="234">
@@ -11721,10 +11709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1071307908694371</v>
+        <v>-0.1496</v>
       </c>
       <c r="J234" t="n">
-        <v>-2.571138980866489</v>
+        <v>-3.5904</v>
       </c>
     </row>
     <row r="235">
@@ -11761,10 +11749,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1405468189783901</v>
+        <v>-0.2057</v>
       </c>
       <c r="J235" t="n">
-        <v>-3.373123655481362</v>
+        <v>-4.9368</v>
       </c>
     </row>
     <row r="236">
@@ -11801,10 +11789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2555040529243536</v>
+        <v>-0.3657</v>
       </c>
       <c r="J236" t="n">
-        <v>-6.132097270184486</v>
+        <v>-8.7768</v>
       </c>
     </row>
     <row r="237">
@@ -11841,10 +11829,10 @@
         <v>1.41</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4003881970287393</v>
+        <v>1.1242</v>
       </c>
       <c r="J237" t="n">
-        <v>9.609316728689745</v>
+        <v>26.9808</v>
       </c>
     </row>
     <row r="238">
@@ -11881,10 +11869,10 @@
         <v>1.1</v>
       </c>
       <c r="I238" t="n">
-        <v>0.1063540409611941</v>
+        <v>0.3715</v>
       </c>
       <c r="J238" t="n">
-        <v>2.552496983068659</v>
+        <v>8.916</v>
       </c>
     </row>
     <row r="239">
@@ -11921,10 +11909,10 @@
         <v>1.08</v>
       </c>
       <c r="I239" t="n">
-        <v>0.08785621120871644</v>
+        <v>0.3087</v>
       </c>
       <c r="J239" t="n">
-        <v>2.108549069009194</v>
+        <v>7.4088</v>
       </c>
     </row>
     <row r="240">
@@ -11961,10 +11949,10 @@
         <v>0.85</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1524463192496076</v>
+        <v>-0.5535</v>
       </c>
       <c r="J240" t="n">
-        <v>-3.658711661990583</v>
+        <v>-13.284</v>
       </c>
     </row>
     <row r="241">
@@ -12001,10 +11989,10 @@
         <v>0.74</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2903668378641794</v>
+        <v>-0.8248</v>
       </c>
       <c r="J241" t="n">
-        <v>-6.968804108740306</v>
+        <v>-19.7952</v>
       </c>
     </row>
     <row r="242">
@@ -12041,10 +12029,10 @@
         <v>1.75</v>
       </c>
       <c r="I242" t="n">
-        <v>0.7322934636959444</v>
+        <v>0.9736</v>
       </c>
       <c r="J242" t="n">
-        <v>15.37816273761483</v>
+        <v>20.4456</v>
       </c>
     </row>
     <row r="243">
@@ -12081,10 +12069,10 @@
         <v>1.21</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1890155495806083</v>
+        <v>0.3225</v>
       </c>
       <c r="J243" t="n">
-        <v>3.969326541192775</v>
+        <v>6.7725</v>
       </c>
     </row>
     <row r="244">
@@ -12121,10 +12109,10 @@
         <v>1.14</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1229190814237019</v>
+        <v>0.2011</v>
       </c>
       <c r="J244" t="n">
-        <v>2.581300709897739</v>
+        <v>4.2231</v>
       </c>
     </row>
     <row r="245">
@@ -12161,10 +12149,10 @@
         <v>1.08</v>
       </c>
       <c r="I245" t="n">
-        <v>0.0592827846207553</v>
+        <v>0.1018</v>
       </c>
       <c r="J245" t="n">
-        <v>1.244938477035861</v>
+        <v>2.1378</v>
       </c>
     </row>
     <row r="246">
@@ -12201,10 +12189,10 @@
         <v>0.82</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2260167358702311</v>
+        <v>-0.392</v>
       </c>
       <c r="J246" t="n">
-        <v>-4.746351453274854</v>
+        <v>-8.231999999999999</v>
       </c>
     </row>
     <row r="247">
@@ -12241,10 +12229,10 @@
         <v>1.6</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4155650873317283</v>
+        <v>0.8878</v>
       </c>
       <c r="J247" t="n">
-        <v>8.726866833966294</v>
+        <v>18.6438</v>
       </c>
     </row>
     <row r="248">
@@ -12281,10 +12269,10 @@
         <v>1.2</v>
       </c>
       <c r="I248" t="n">
-        <v>0.05393063717740634</v>
+        <v>0.3956</v>
       </c>
       <c r="J248" t="n">
-        <v>1.132543380725533</v>
+        <v>8.307600000000001</v>
       </c>
     </row>
     <row r="249">
@@ -12321,10 +12309,10 @@
         <v>0.73</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.4975701100034809</v>
+        <v>-0.4737</v>
       </c>
       <c r="J249" t="n">
-        <v>-10.4489723100731</v>
+        <v>-9.947699999999999</v>
       </c>
     </row>
     <row r="250">
@@ -12361,10 +12349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.5461961952817985</v>
+        <v>-0.5269</v>
       </c>
       <c r="J250" t="n">
-        <v>-11.47012010091777</v>
+        <v>-11.0649</v>
       </c>
     </row>
     <row r="251">
@@ -12401,10 +12389,10 @@
         <v>0.61</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6414609571604606</v>
+        <v>-0.6284</v>
       </c>
       <c r="J251" t="n">
-        <v>-13.47068010036967</v>
+        <v>-13.1964</v>
       </c>
     </row>
     <row r="252">
@@ -12441,10 +12429,10 @@
         <v>1.15</v>
       </c>
       <c r="I252" t="n">
-        <v>0.09038213367325321</v>
+        <v>0.3464</v>
       </c>
       <c r="J252" t="n">
-        <v>1.988406940811571</v>
+        <v>7.6208</v>
       </c>
     </row>
     <row r="253">
@@ -12481,10 +12469,10 @@
         <v>0.86</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.2213014674799794</v>
+        <v>-0.2573</v>
       </c>
       <c r="J253" t="n">
-        <v>-4.868632284559546</v>
+        <v>-5.6606</v>
       </c>
     </row>
     <row r="254">
@@ -12521,10 +12509,10 @@
         <v>0.84</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2430598209578564</v>
+        <v>-0.2914</v>
       </c>
       <c r="J254" t="n">
-        <v>-5.34731606107284</v>
+        <v>-6.4108</v>
       </c>
     </row>
     <row r="255">
@@ -12561,10 +12549,10 @@
         <v>0.83</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2541224464014842</v>
+        <v>-0.3078</v>
       </c>
       <c r="J255" t="n">
-        <v>-5.590693820832652</v>
+        <v>-6.7716</v>
       </c>
     </row>
     <row r="256">
@@ -12601,10 +12589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.2764720023437996</v>
+        <v>-0.3396</v>
       </c>
       <c r="J256" t="n">
-        <v>-6.082384051563591</v>
+        <v>-7.4712</v>
       </c>
     </row>
     <row r="257">
@@ -12641,10 +12629,10 @@
         <v>1.31</v>
       </c>
       <c r="I257" t="n">
-        <v>0.2806054226493075</v>
+        <v>0.8323</v>
       </c>
       <c r="J257" t="n">
-        <v>6.173319298284765</v>
+        <v>18.3106</v>
       </c>
     </row>
     <row r="258">
@@ -12681,10 +12669,10 @@
         <v>1.31</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2806054226493075</v>
+        <v>0.8323</v>
       </c>
       <c r="J258" t="n">
-        <v>6.173319298284765</v>
+        <v>18.3106</v>
       </c>
     </row>
     <row r="259">
@@ -12721,10 +12709,10 @@
         <v>1.24</v>
       </c>
       <c r="I259" t="n">
-        <v>0.2145922789714169</v>
+        <v>0.6642</v>
       </c>
       <c r="J259" t="n">
-        <v>4.721030137371171</v>
+        <v>14.6124</v>
       </c>
     </row>
     <row r="260">
@@ -12761,10 +12749,10 @@
         <v>1.01</v>
       </c>
       <c r="I260" t="n">
-        <v>0.00612339571981981</v>
+        <v>-0.0529</v>
       </c>
       <c r="J260" t="n">
-        <v>0.1347147058360358</v>
+        <v>-1.1638</v>
       </c>
     </row>
     <row r="261">
@@ -12801,10 +12789,10 @@
         <v>0.98</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.02978064440031155</v>
+        <v>-0.2126</v>
       </c>
       <c r="J261" t="n">
-        <v>-0.655174176806854</v>
+        <v>-4.6772</v>
       </c>
     </row>
     <row r="262">
@@ -12841,10 +12829,10 @@
         <v>1.8</v>
       </c>
       <c r="I262" t="n">
-        <v>0.6071097651227276</v>
+        <v>1.7405</v>
       </c>
       <c r="J262" t="n">
-        <v>12.74930506757728</v>
+        <v>36.5505</v>
       </c>
     </row>
     <row r="263">
@@ -12881,10 +12869,10 @@
         <v>1.47</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3439700742907802</v>
+        <v>1.1171</v>
       </c>
       <c r="J263" t="n">
-        <v>7.223371560106385</v>
+        <v>23.4591</v>
       </c>
     </row>
     <row r="264">
@@ -12921,10 +12909,10 @@
         <v>1.33</v>
       </c>
       <c r="I264" t="n">
-        <v>0.2269794253097445</v>
+        <v>0.8077</v>
       </c>
       <c r="J264" t="n">
-        <v>4.766567931504635</v>
+        <v>16.9617</v>
       </c>
     </row>
     <row r="265">
@@ -12961,10 +12949,10 @@
         <v>1</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.07420761295390811</v>
+        <v>-0.1529</v>
       </c>
       <c r="J265" t="n">
-        <v>-1.55835987203207</v>
+        <v>-3.2109</v>
       </c>
     </row>
     <row r="266">
@@ -13001,10 +12989,10 @@
         <v>0.85</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2650246863336203</v>
+        <v>-0.6298</v>
       </c>
       <c r="J266" t="n">
-        <v>-5.565518413006027</v>
+        <v>-13.2258</v>
       </c>
     </row>
     <row r="267">
@@ -13041,10 +13029,10 @@
         <v>1.08</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.01261347252082342</v>
+        <v>0.2482</v>
       </c>
       <c r="J267" t="n">
-        <v>-0.2648829229372918</v>
+        <v>5.2122</v>
       </c>
     </row>
     <row r="268">
@@ -13081,10 +13069,10 @@
         <v>0.92</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1716525004127028</v>
+        <v>-0.1121</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.604702508666759</v>
+        <v>-2.3541</v>
       </c>
     </row>
     <row r="269">
@@ -13121,10 +13109,10 @@
         <v>0.88</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2088113736285008</v>
+        <v>-0.1869</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.385038846198517</v>
+        <v>-3.9249</v>
       </c>
     </row>
     <row r="270">
@@ -13161,10 +13149,10 @@
         <v>0.75</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3252189709678646</v>
+        <v>-0.4167</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.829598390325156</v>
+        <v>-8.7507</v>
       </c>
     </row>
     <row r="271">
@@ -13201,10 +13189,10 @@
         <v>0.66</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4122092034356314</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="J271" t="n">
-        <v>-8.656393272148261</v>
+        <v>-11.3988</v>
       </c>
     </row>
     <row r="272">
@@ -13241,10 +13229,10 @@
         <v>2.31</v>
       </c>
       <c r="I272" t="n">
-        <v>0.9778195010604022</v>
+        <v>2.0593</v>
       </c>
       <c r="J272" t="n">
-        <v>15.64511201696643</v>
+        <v>32.9488</v>
       </c>
     </row>
     <row r="273">
@@ -13281,10 +13269,10 @@
         <v>1.82</v>
       </c>
       <c r="I273" t="n">
-        <v>0.6339098445631757</v>
+        <v>1.6982</v>
       </c>
       <c r="J273" t="n">
-        <v>10.14255751301081</v>
+        <v>27.1712</v>
       </c>
     </row>
     <row r="274">
@@ -13321,10 +13309,10 @@
         <v>1.58</v>
       </c>
       <c r="I274" t="n">
-        <v>0.4418593564260691</v>
+        <v>1.2517</v>
       </c>
       <c r="J274" t="n">
-        <v>7.069749702817106</v>
+        <v>20.0272</v>
       </c>
     </row>
     <row r="275">
@@ -13361,10 +13349,10 @@
         <v>0.84</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2423041174267582</v>
+        <v>-0.6883</v>
       </c>
       <c r="J275" t="n">
-        <v>-3.876865878828132</v>
+        <v>-11.0128</v>
       </c>
     </row>
     <row r="276">
@@ -13401,10 +13389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2784326328803363</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="J276" t="n">
-        <v>-4.454922126085381</v>
+        <v>-12.1376</v>
       </c>
     </row>
     <row r="277">
@@ -13441,10 +13429,10 @@
         <v>0.85</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.2933283002667835</v>
+        <v>-0.1673</v>
       </c>
       <c r="J277" t="n">
-        <v>-4.693252804268536</v>
+        <v>-2.6768</v>
       </c>
     </row>
     <row r="278">
@@ -13481,10 +13469,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.4344645392962728</v>
+        <v>-0.4474</v>
       </c>
       <c r="J278" t="n">
-        <v>-6.951432628740364</v>
+        <v>-7.1584</v>
       </c>
     </row>
     <row r="279">
@@ -13521,10 +13509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.4344645392962728</v>
+        <v>-0.4474</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.951432628740364</v>
+        <v>-7.1584</v>
       </c>
     </row>
     <row r="280">
@@ -13561,10 +13549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4344645392962728</v>
+        <v>-0.4474</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.951432628740364</v>
+        <v>-7.1584</v>
       </c>
     </row>
     <row r="281">
@@ -13601,10 +13589,10 @@
         <v>0.67</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4520737801322711</v>
+        <v>-0.4798</v>
       </c>
       <c r="J281" t="n">
-        <v>-7.233180482116337</v>
+        <v>-7.6768</v>
       </c>
     </row>
     <row r="282">
@@ -13641,10 +13629,10 @@
         <v>2.02</v>
       </c>
       <c r="I282" t="n">
-        <v>0.8565956223805548</v>
+        <v>1.2014</v>
       </c>
       <c r="J282" t="n">
-        <v>15.41872120284999</v>
+        <v>21.6252</v>
       </c>
     </row>
     <row r="283">
@@ -13681,10 +13669,10 @@
         <v>1.35</v>
       </c>
       <c r="I283" t="n">
-        <v>0.3030844191120926</v>
+        <v>0.4685</v>
       </c>
       <c r="J283" t="n">
-        <v>5.455519544017667</v>
+        <v>8.433</v>
       </c>
     </row>
     <row r="284">
@@ -13721,10 +13709,10 @@
         <v>1.22</v>
       </c>
       <c r="I284" t="n">
-        <v>0.1931454317889455</v>
+        <v>0.2792</v>
       </c>
       <c r="J284" t="n">
-        <v>3.476617772201018</v>
+        <v>5.0256</v>
       </c>
     </row>
     <row r="285">
@@ -13761,10 +13749,10 @@
         <v>1.16</v>
       </c>
       <c r="I285" t="n">
-        <v>0.1380532300511615</v>
+        <v>0.194</v>
       </c>
       <c r="J285" t="n">
-        <v>2.484958140920907</v>
+        <v>3.492</v>
       </c>
     </row>
     <row r="286">
@@ -13801,10 +13789,10 @@
         <v>0.97</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.04956911523977937</v>
+        <v>-0.1741</v>
       </c>
       <c r="J286" t="n">
-        <v>-0.8922440743160286</v>
+        <v>-3.1338</v>
       </c>
     </row>
     <row r="287">
@@ -13841,10 +13829,10 @@
         <v>1.31</v>
       </c>
       <c r="I287" t="n">
-        <v>0.1606444579620553</v>
+        <v>0.6146</v>
       </c>
       <c r="J287" t="n">
-        <v>2.891600243316996</v>
+        <v>11.0628</v>
       </c>
     </row>
     <row r="288">
@@ -13881,10 +13869,10 @@
         <v>0.91</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.2751505194579826</v>
+        <v>-0.0969</v>
       </c>
       <c r="J288" t="n">
-        <v>-4.952709350243687</v>
+        <v>-1.7442</v>
       </c>
     </row>
     <row r="289">
@@ -13921,10 +13909,10 @@
         <v>0.7</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.5270544214374575</v>
+        <v>-0.4644</v>
       </c>
       <c r="J289" t="n">
-        <v>-9.486979585874234</v>
+        <v>-8.3592</v>
       </c>
     </row>
     <row r="290">
@@ -13961,10 +13949,10 @@
         <v>0.53</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.7405369357980424</v>
+        <v>-0.6944</v>
       </c>
       <c r="J290" t="n">
-        <v>-13.32966484436476</v>
+        <v>-12.4992</v>
       </c>
     </row>
     <row r="291">
@@ -14001,10 +13989,10 @@
         <v>0.48</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.8018267425596539</v>
+        <v>-0.7564</v>
       </c>
       <c r="J291" t="n">
-        <v>-14.43288136607377</v>
+        <v>-13.6152</v>
       </c>
     </row>
     <row r="292">
@@ -14041,10 +14029,10 @@
         <v>1.25</v>
       </c>
       <c r="I292" t="n">
-        <v>0.1781290356787055</v>
+        <v>0.4605</v>
       </c>
       <c r="J292" t="n">
-        <v>4.275096856288931</v>
+        <v>11.052</v>
       </c>
     </row>
     <row r="293">
@@ -14081,10 +14069,10 @@
         <v>1.04</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.01706539629262016</v>
+        <v>0.1236</v>
       </c>
       <c r="J293" t="n">
-        <v>-0.4095695110228837</v>
+        <v>2.9664</v>
       </c>
     </row>
     <row r="294">
@@ -14121,10 +14109,10 @@
         <v>0.92</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1553229564180965</v>
+        <v>-0.1854</v>
       </c>
       <c r="J294" t="n">
-        <v>-3.727750954034316</v>
+        <v>-4.4496</v>
       </c>
     </row>
     <row r="295">
@@ -14161,10 +14149,10 @@
         <v>0.9</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.180592243362222</v>
+        <v>-0.2212</v>
       </c>
       <c r="J295" t="n">
-        <v>-4.334213840693327</v>
+        <v>-5.3088</v>
       </c>
     </row>
     <row r="296">
@@ -14201,10 +14189,10 @@
         <v>0.79</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3222408642075734</v>
+        <v>-0.3933</v>
       </c>
       <c r="J296" t="n">
-        <v>-7.733780740981761</v>
+        <v>-9.4392</v>
       </c>
     </row>
     <row r="297">
@@ -14241,10 +14229,10 @@
         <v>1.5</v>
       </c>
       <c r="I297" t="n">
-        <v>0.4249193052362339</v>
+        <v>1.2861</v>
       </c>
       <c r="J297" t="n">
-        <v>10.19806332566962</v>
+        <v>30.8664</v>
       </c>
     </row>
     <row r="298">
@@ -14281,10 +14269,10 @@
         <v>1.38</v>
       </c>
       <c r="I298" t="n">
-        <v>0.3235966713942079</v>
+        <v>1.0384</v>
       </c>
       <c r="J298" t="n">
-        <v>7.766320113460989</v>
+        <v>24.9216</v>
       </c>
     </row>
     <row r="299">
@@ -14321,10 +14309,10 @@
         <v>1.12</v>
       </c>
       <c r="I299" t="n">
-        <v>0.09391779360915542</v>
+        <v>0.4022</v>
       </c>
       <c r="J299" t="n">
-        <v>2.25402704661973</v>
+        <v>9.652799999999999</v>
       </c>
     </row>
     <row r="300">
@@ -14361,10 +14349,10 @@
         <v>0.82</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2352926049034579</v>
+        <v>-0.6456</v>
       </c>
       <c r="J300" t="n">
-        <v>-5.64702251768299</v>
+        <v>-15.4944</v>
       </c>
     </row>
     <row r="301">
@@ -14401,10 +14389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5651164311398508</v>
+        <v>-1.223</v>
       </c>
       <c r="J301" t="n">
-        <v>-13.56279434735642</v>
+        <v>-29.352</v>
       </c>
     </row>
     <row r="302">
@@ -14441,10 +14429,10 @@
         <v>0.95</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.139203667966339</v>
+        <v>-0.039</v>
       </c>
       <c r="J302" t="n">
-        <v>-2.923277027293119</v>
+        <v>-0.819</v>
       </c>
     </row>
     <row r="303">
@@ -14481,10 +14469,10 @@
         <v>0.9</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.2026746805817438</v>
+        <v>-0.1325</v>
       </c>
       <c r="J303" t="n">
-        <v>-4.25616829221662</v>
+        <v>-2.7825</v>
       </c>
     </row>
     <row r="304">
@@ -14521,10 +14509,10 @@
         <v>0.89</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.2151350748693709</v>
+        <v>-0.1504</v>
       </c>
       <c r="J304" t="n">
-        <v>-4.517836572256789</v>
+        <v>-3.1584</v>
       </c>
     </row>
     <row r="305">
@@ -14561,10 +14549,10 @@
         <v>0.7</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4376111442284443</v>
+        <v>-0.4779</v>
       </c>
       <c r="J305" t="n">
-        <v>-9.18983402879733</v>
+        <v>-10.0359</v>
       </c>
     </row>
     <row r="306">
@@ -14601,10 +14589,10 @@
         <v>0.68</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4625368540133129</v>
+        <v>-0.5061</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.71327393427957</v>
+        <v>-10.6281</v>
       </c>
     </row>
     <row r="307">
@@ -14641,10 +14629,10 @@
         <v>1.56</v>
       </c>
       <c r="I307" t="n">
-        <v>0.4583828020304938</v>
+        <v>1.3144</v>
       </c>
       <c r="J307" t="n">
-        <v>9.626038842640369</v>
+        <v>27.6024</v>
       </c>
     </row>
     <row r="308">
@@ -14681,10 +14669,10 @@
         <v>1.36</v>
       </c>
       <c r="I308" t="n">
-        <v>0.2878407254739094</v>
+        <v>0.8992</v>
       </c>
       <c r="J308" t="n">
-        <v>6.044655234952098</v>
+        <v>18.8832</v>
       </c>
     </row>
     <row r="309">
@@ -14721,10 +14709,10 @@
         <v>1.25</v>
       </c>
       <c r="I309" t="n">
-        <v>0.1991243913079689</v>
+        <v>0.6171</v>
       </c>
       <c r="J309" t="n">
-        <v>4.181612217467347</v>
+        <v>12.9591</v>
       </c>
     </row>
     <row r="310">
@@ -14761,10 +14749,10 @@
         <v>1.22</v>
       </c>
       <c r="I310" t="n">
-        <v>0.1760764420975919</v>
+        <v>0.533</v>
       </c>
       <c r="J310" t="n">
-        <v>3.69760528404943</v>
+        <v>11.193</v>
       </c>
     </row>
     <row r="311">
@@ -14801,10 +14789,10 @@
         <v>0.88</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.1823085444556717</v>
+        <v>-0.5448</v>
       </c>
       <c r="J311" t="n">
-        <v>-3.828479433569106</v>
+        <v>-11.4408</v>
       </c>
     </row>
     <row r="312">
@@ -14841,10 +14829,10 @@
         <v>0.86</v>
       </c>
       <c r="I312" t="n">
-        <v>-0.2519416981503213</v>
+        <v>-0.1595</v>
       </c>
       <c r="J312" t="n">
-        <v>-4.786892264856105</v>
+        <v>-3.0305</v>
       </c>
     </row>
     <row r="313">
@@ -14881,10 +14869,10 @@
         <v>0.84</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.2775878791624238</v>
+        <v>-0.1926</v>
       </c>
       <c r="J313" t="n">
-        <v>-5.274169704086053</v>
+        <v>-3.6594</v>
       </c>
     </row>
     <row r="314">
@@ -14921,10 +14909,10 @@
         <v>0.75</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.3873894185607396</v>
+        <v>-0.3439</v>
       </c>
       <c r="J314" t="n">
-        <v>-7.360398952654053</v>
+        <v>-6.5341</v>
       </c>
     </row>
     <row r="315">
@@ -14961,10 +14949,10 @@
         <v>0.63</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.5260247825008016</v>
+        <v>-0.5471</v>
       </c>
       <c r="J315" t="n">
-        <v>-9.994470867515231</v>
+        <v>-10.3949</v>
       </c>
     </row>
     <row r="316">
@@ -15001,10 +14989,10 @@
         <v>0.6</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5635199346251593</v>
+        <v>-0.5891</v>
       </c>
       <c r="J316" t="n">
-        <v>-10.70687875787803</v>
+        <v>-11.1929</v>
       </c>
     </row>
     <row r="317">
@@ -15041,10 +15029,10 @@
         <v>1.98</v>
       </c>
       <c r="I317" t="n">
-        <v>0.9617396910489545</v>
+        <v>1.9891</v>
       </c>
       <c r="J317" t="n">
-        <v>18.27305412993013</v>
+        <v>37.7929</v>
       </c>
     </row>
     <row r="318">
@@ -15081,10 +15069,10 @@
         <v>1.74</v>
       </c>
       <c r="I318" t="n">
-        <v>0.748220579439585</v>
+        <v>1.6248</v>
       </c>
       <c r="J318" t="n">
-        <v>14.21619100935211</v>
+        <v>30.8712</v>
       </c>
     </row>
     <row r="319">
@@ -15121,10 +15109,10 @@
         <v>1.08</v>
       </c>
       <c r="I319" t="n">
-        <v>0.09327624475659295</v>
+        <v>0.1346</v>
       </c>
       <c r="J319" t="n">
-        <v>1.772248650375266</v>
+        <v>2.5574</v>
       </c>
     </row>
     <row r="320">
@@ -15161,10 +15149,10 @@
         <v>0.9</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1018138685636591</v>
+        <v>-0.5052</v>
       </c>
       <c r="J320" t="n">
-        <v>-1.934463502709523</v>
+        <v>-9.598800000000001</v>
       </c>
     </row>
     <row r="321">
@@ -15201,10 +15189,10 @@
         <v>0.85</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.1565097555350043</v>
+        <v>-0.6342</v>
       </c>
       <c r="J321" t="n">
-        <v>-2.973685355165081</v>
+        <v>-12.0498</v>
       </c>
     </row>
     <row r="322">
@@ -15241,10 +15229,10 @@
         <v>1.21</v>
       </c>
       <c r="I322" t="n">
-        <v>0.1000099758493534</v>
+        <v>0.4375</v>
       </c>
       <c r="J322" t="n">
-        <v>2.000199516987069</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="323">
@@ -15281,10 +15269,10 @@
         <v>1.01</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.1097322894147739</v>
+        <v>0.0919</v>
       </c>
       <c r="J323" t="n">
-        <v>-2.194645788295477</v>
+        <v>1.838</v>
       </c>
     </row>
     <row r="324">
@@ -15321,10 +15309,10 @@
         <v>0.8</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.367687433271519</v>
+        <v>-0.3523</v>
       </c>
       <c r="J324" t="n">
-        <v>-7.35374866543038</v>
+        <v>-7.046</v>
       </c>
     </row>
     <row r="325">
@@ -15361,10 +15349,10 @@
         <v>0.76</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.4194355333684077</v>
+        <v>-0.4123</v>
       </c>
       <c r="J325" t="n">
-        <v>-8.388710667368155</v>
+        <v>-8.246</v>
       </c>
     </row>
     <row r="326">
@@ -15401,10 +15389,10 @@
         <v>0.67</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.5356471819480844</v>
+        <v>-0.5371</v>
       </c>
       <c r="J326" t="n">
-        <v>-10.71294363896169</v>
+        <v>-10.742</v>
       </c>
     </row>
     <row r="327">
@@ -15441,10 +15429,10 @@
         <v>1.45</v>
       </c>
       <c r="I327" t="n">
-        <v>0.5186177156242404</v>
+        <v>1.146</v>
       </c>
       <c r="J327" t="n">
-        <v>10.37235431248481</v>
+        <v>22.92</v>
       </c>
     </row>
     <row r="328">
@@ -15481,10 +15469,10 @@
         <v>1.2</v>
       </c>
       <c r="I328" t="n">
-        <v>0.2579745172649014</v>
+        <v>0.5738</v>
       </c>
       <c r="J328" t="n">
-        <v>5.159490345298028</v>
+        <v>11.476</v>
       </c>
     </row>
     <row r="329">
@@ -15521,10 +15509,10 @@
         <v>1.15</v>
       </c>
       <c r="I329" t="n">
-        <v>0.2107736403702417</v>
+        <v>0.4234</v>
       </c>
       <c r="J329" t="n">
-        <v>4.215472807404835</v>
+        <v>8.468</v>
       </c>
     </row>
     <row r="330">
@@ -15561,10 +15549,10 @@
         <v>1.05</v>
       </c>
       <c r="I330" t="n">
-        <v>0.1107759242081254</v>
+        <v>0.1065</v>
       </c>
       <c r="J330" t="n">
-        <v>2.215518484162508</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="331">
@@ -15601,10 +15589,10 @@
         <v>0.9</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.05161163903892867</v>
+        <v>-0.4604</v>
       </c>
       <c r="J331" t="n">
-        <v>-1.032232780778573</v>
+        <v>-9.208</v>
       </c>
     </row>
     <row r="332">
@@ -15641,10 +15629,10 @@
         <v>1.83</v>
       </c>
       <c r="I332" t="n">
-        <v>0.7076063931460359</v>
+        <v>1.7849</v>
       </c>
       <c r="J332" t="n">
-        <v>14.15212786292072</v>
+        <v>35.698</v>
       </c>
     </row>
     <row r="333">
@@ -15681,10 +15669,10 @@
         <v>1.43</v>
       </c>
       <c r="I333" t="n">
-        <v>0.3554138907877882</v>
+        <v>1.0239</v>
       </c>
       <c r="J333" t="n">
-        <v>7.108277815755764</v>
+        <v>20.478</v>
       </c>
     </row>
     <row r="334">
@@ -15721,10 +15709,10 @@
         <v>1.33</v>
       </c>
       <c r="I334" t="n">
-        <v>0.2652129155916124</v>
+        <v>0.7946</v>
       </c>
       <c r="J334" t="n">
-        <v>5.304258311832247</v>
+        <v>15.892</v>
       </c>
     </row>
     <row r="335">
@@ -15761,10 +15749,10 @@
         <v>1.2</v>
       </c>
       <c r="I335" t="n">
-        <v>0.1528110644091922</v>
+        <v>0.4525</v>
       </c>
       <c r="J335" t="n">
-        <v>3.056221288183844</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="336">
@@ -15801,10 +15789,10 @@
         <v>0.75</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.3422498234968224</v>
+        <v>-0.8667</v>
       </c>
       <c r="J336" t="n">
-        <v>-6.844996469936449</v>
+        <v>-17.334</v>
       </c>
     </row>
     <row r="337">
@@ -15841,10 +15829,10 @@
         <v>1.15</v>
       </c>
       <c r="I337" t="n">
-        <v>0.05419405702547871</v>
+        <v>0.3713</v>
       </c>
       <c r="J337" t="n">
-        <v>1.083881140509574</v>
+        <v>7.426</v>
       </c>
     </row>
     <row r="338">
@@ -15881,10 +15869,10 @@
         <v>0.85</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.2665745388528218</v>
+        <v>-0.2284</v>
       </c>
       <c r="J338" t="n">
-        <v>-5.331490777056436</v>
+        <v>-4.568</v>
       </c>
     </row>
     <row r="339">
@@ -15921,10 +15909,10 @@
         <v>0.8</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.3107828594639673</v>
+        <v>-0.3285</v>
       </c>
       <c r="J339" t="n">
-        <v>-6.215657189279345</v>
+        <v>-6.57</v>
       </c>
     </row>
     <row r="340">
@@ -15961,10 +15949,10 @@
         <v>0.73</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3822138011911849</v>
+        <v>-0.4379</v>
       </c>
       <c r="J340" t="n">
-        <v>-7.644276023823697</v>
+        <v>-8.757999999999999</v>
       </c>
     </row>
     <row r="341">
@@ -16001,10 +15989,10 @@
         <v>0.64</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4760190407969316</v>
+        <v>-0.5634</v>
       </c>
       <c r="J341" t="n">
-        <v>-9.520380815938633</v>
+        <v>-11.268</v>
       </c>
     </row>
     <row r="342">
@@ -16041,10 +16029,10 @@
         <v>2.17</v>
       </c>
       <c r="I342" t="n">
-        <v>0.8745500001306519</v>
+        <v>2.0593</v>
       </c>
       <c r="J342" t="n">
-        <v>20.98920000313564</v>
+        <v>49.4232</v>
       </c>
     </row>
     <row r="343">
@@ -16081,10 +16069,10 @@
         <v>1.79</v>
       </c>
       <c r="I343" t="n">
-        <v>0.5806734761927574</v>
+        <v>1.7283</v>
       </c>
       <c r="J343" t="n">
-        <v>13.93616342862618</v>
+        <v>41.4792</v>
       </c>
     </row>
     <row r="344">
@@ -16121,10 +16109,10 @@
         <v>1.21</v>
       </c>
       <c r="I344" t="n">
-        <v>0.06064013674600333</v>
+        <v>0.4925</v>
       </c>
       <c r="J344" t="n">
-        <v>1.45536328190408</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="345">
@@ -16161,10 +16149,10 @@
         <v>0.82</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.3965336372758295</v>
+        <v>-0.7002</v>
       </c>
       <c r="J345" t="n">
-        <v>-9.516807294619907</v>
+        <v>-16.8048</v>
       </c>
     </row>
     <row r="346">
@@ -16201,10 +16189,10 @@
         <v>0.4</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.8588642853034499</v>
+        <v>-1.5558</v>
       </c>
       <c r="J346" t="n">
-        <v>-20.6127428472828</v>
+        <v>-37.3392</v>
       </c>
     </row>
     <row r="347">
@@ -16241,10 +16229,10 @@
         <v>1.22</v>
       </c>
       <c r="I347" t="n">
-        <v>0.1141785942912871</v>
+        <v>0.4162</v>
       </c>
       <c r="J347" t="n">
-        <v>2.740286262990891</v>
+        <v>9.988799999999999</v>
       </c>
     </row>
     <row r="348">
@@ -16281,10 +16269,10 @@
         <v>1.2</v>
       </c>
       <c r="I348" t="n">
-        <v>0.0917216285146211</v>
+        <v>0.3878</v>
       </c>
       <c r="J348" t="n">
-        <v>2.201319084350907</v>
+        <v>9.3072</v>
       </c>
     </row>
     <row r="349">
@@ -16321,10 +16309,10 @@
         <v>1.13</v>
       </c>
       <c r="I349" t="n">
-        <v>0.01210564919465444</v>
+        <v>0.282</v>
       </c>
       <c r="J349" t="n">
-        <v>0.2905355806717065</v>
+        <v>6.768</v>
       </c>
     </row>
     <row r="350">
@@ -16361,10 +16349,10 @@
         <v>0.84</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2865925374045705</v>
+        <v>-0.3212</v>
       </c>
       <c r="J350" t="n">
-        <v>-6.878220897709692</v>
+        <v>-7.7088</v>
       </c>
     </row>
     <row r="351">
@@ -16401,10 +16389,10 @@
         <v>0.55</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.5842232560775875</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="J351" t="n">
-        <v>-14.0213581458621</v>
+        <v>-16.8984</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7993/event_7993_evp_summary.xlsx
+++ b/database/event/7993/event_7993_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>7.1255</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1.7855</v>
       </c>
       <c r="D2" t="n">
         <v>2.4572</v>
@@ -545,7 +545,7 @@
         <v>6.6646</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="D3" t="n">
         <v>2.271</v>
@@ -591,7 +591,7 @@
         <v>4.8757</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1.2217</v>
       </c>
       <c r="D4" t="n">
         <v>1.5483</v>
@@ -637,7 +637,7 @@
         <v>4.463</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1.1183</v>
       </c>
       <c r="D5" t="n">
         <v>1.3816</v>
@@ -683,7 +683,7 @@
         <v>3.5998</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.902</v>
       </c>
       <c r="D6" t="n">
         <v>1.0329</v>
@@ -729,7 +729,7 @@
         <v>2.9353</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.7355</v>
       </c>
       <c r="D7" t="n">
         <v>0.7644</v>
@@ -775,7 +775,7 @@
         <v>2.226</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.5578</v>
       </c>
       <c r="D8" t="n">
         <v>0.4779</v>
@@ -821,7 +821,7 @@
         <v>1.7458</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.4374</v>
       </c>
       <c r="D9" t="n">
         <v>0.2839</v>
@@ -867,7 +867,7 @@
         <v>1.5576</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.3903</v>
       </c>
       <c r="D10" t="n">
         <v>0.2079</v>
@@ -913,7 +913,7 @@
         <v>1.1279</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.2826</v>
       </c>
       <c r="D11" t="n">
         <v>0.0343</v>
@@ -959,7 +959,7 @@
         <v>1.0577</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.265</v>
       </c>
       <c r="D12" t="n">
         <v>0.0059</v>
@@ -1005,7 +1005,7 @@
         <v>0.9752999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.2444</v>
       </c>
       <c r="D13" t="n">
         <v>-0.0274</v>
@@ -1051,7 +1051,7 @@
         <v>0.9563</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.2396</v>
       </c>
       <c r="D14" t="n">
         <v>-0.035</v>
@@ -1097,7 +1097,7 @@
         <v>0.7252999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.1817</v>
       </c>
       <c r="D15" t="n">
         <v>-0.1284</v>
@@ -1143,7 +1143,7 @@
         <v>0.7209</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.1806</v>
       </c>
       <c r="D16" t="n">
         <v>-0.1301</v>
@@ -1189,7 +1189,7 @@
         <v>0.6246</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.1565</v>
       </c>
       <c r="D17" t="n">
         <v>-0.169</v>
@@ -1235,7 +1235,7 @@
         <v>0.5478</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.1373</v>
       </c>
       <c r="D18" t="n">
         <v>-0.2001</v>
@@ -1281,7 +1281,7 @@
         <v>0.514</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.1288</v>
       </c>
       <c r="D19" t="n">
         <v>-0.2137</v>
@@ -1327,7 +1327,7 @@
         <v>0.4356</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.1091</v>
       </c>
       <c r="D20" t="n">
         <v>-0.2454</v>
@@ -1373,7 +1373,7 @@
         <v>0.3516</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.0881</v>
       </c>
       <c r="D21" t="n">
         <v>-0.2793</v>
@@ -1419,7 +1419,7 @@
         <v>0.254</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.0636</v>
       </c>
       <c r="D22" t="n">
         <v>-0.3188</v>
@@ -1465,7 +1465,7 @@
         <v>0.2299</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.0576</v>
       </c>
       <c r="D23" t="n">
         <v>-0.3285</v>
@@ -1511,7 +1511,7 @@
         <v>0.2221</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.0557</v>
       </c>
       <c r="D24" t="n">
         <v>-0.3316</v>
@@ -1557,7 +1557,7 @@
         <v>0.2202</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.0552</v>
       </c>
       <c r="D25" t="n">
         <v>-0.3324</v>
@@ -1603,7 +1603,7 @@
         <v>-0.0005999999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>-0</v>
+        <v>-0.0002</v>
       </c>
       <c r="D26" t="n">
         <v>-0.4216</v>
@@ -1649,7 +1649,7 @@
         <v>-0.0617</v>
       </c>
       <c r="C27" t="n">
-        <v>-0</v>
+        <v>-0.0155</v>
       </c>
       <c r="D27" t="n">
         <v>-0.4463</v>
@@ -1695,7 +1695,7 @@
         <v>-0.1686</v>
       </c>
       <c r="C28" t="n">
-        <v>-0</v>
+        <v>-0.0422</v>
       </c>
       <c r="D28" t="n">
         <v>-0.4895</v>
@@ -1741,7 +1741,7 @@
         <v>-0.2964</v>
       </c>
       <c r="C29" t="n">
-        <v>-0</v>
+        <v>-0.0743</v>
       </c>
       <c r="D29" t="n">
         <v>-0.5411</v>
@@ -1787,7 +1787,7 @@
         <v>-0.2995</v>
       </c>
       <c r="C30" t="n">
-        <v>-0</v>
+        <v>-0.075</v>
       </c>
       <c r="D30" t="n">
         <v>-0.5424</v>
@@ -1833,7 +1833,7 @@
         <v>-0.3229</v>
       </c>
       <c r="C31" t="n">
-        <v>-0</v>
+        <v>-0.0809</v>
       </c>
       <c r="D31" t="n">
         <v>-0.5518</v>
@@ -1879,7 +1879,7 @@
         <v>-0.394</v>
       </c>
       <c r="C32" t="n">
-        <v>-0</v>
+        <v>-0.0987</v>
       </c>
       <c r="D32" t="n">
         <v>-0.5805</v>
@@ -1925,7 +1925,7 @@
         <v>-0.4787</v>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>-0.1199</v>
       </c>
       <c r="D33" t="n">
         <v>-0.6147</v>
@@ -1971,7 +1971,7 @@
         <v>-0.8495</v>
       </c>
       <c r="C34" t="n">
-        <v>-0</v>
+        <v>-0.2129</v>
       </c>
       <c r="D34" t="n">
         <v>-0.7645</v>
@@ -2017,7 +2017,7 @@
         <v>-1.1275</v>
       </c>
       <c r="C35" t="n">
-        <v>-0</v>
+        <v>-0.2825</v>
       </c>
       <c r="D35" t="n">
         <v>-0.8768</v>
@@ -2063,7 +2063,7 @@
         <v>-1.2378</v>
       </c>
       <c r="C36" t="n">
-        <v>-0</v>
+        <v>-0.3102</v>
       </c>
       <c r="D36" t="n">
         <v>-0.9214</v>
@@ -2109,7 +2109,7 @@
         <v>-1.2674</v>
       </c>
       <c r="C37" t="n">
-        <v>-0</v>
+        <v>-0.3176</v>
       </c>
       <c r="D37" t="n">
         <v>-0.9334</v>
@@ -2155,7 +2155,7 @@
         <v>-1.3352</v>
       </c>
       <c r="C38" t="n">
-        <v>-0</v>
+        <v>-0.3346</v>
       </c>
       <c r="D38" t="n">
         <v>-0.9608</v>
@@ -2201,7 +2201,7 @@
         <v>-1.5706</v>
       </c>
       <c r="C39" t="n">
-        <v>-0</v>
+        <v>-0.3935</v>
       </c>
       <c r="D39" t="n">
         <v>-1.0558</v>
@@ -2247,7 +2247,7 @@
         <v>-1.6027</v>
       </c>
       <c r="C40" t="n">
-        <v>-0</v>
+        <v>-0.4016</v>
       </c>
       <c r="D40" t="n">
         <v>-1.0688</v>
@@ -2293,7 +2293,7 @@
         <v>-1.7667</v>
       </c>
       <c r="C41" t="n">
-        <v>-0</v>
+        <v>-0.4427</v>
       </c>
       <c r="D41" t="n">
         <v>-1.1351</v>

--- a/database/event/7993/event_7993_evp_summary.xlsx
+++ b/database/event/7993/event_7993_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.7855</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4572</v>
+        <v>2.3949</v>
       </c>
       <c r="E2" t="n">
         <v>7.1255</v>
@@ -548,7 +548,7 @@
         <v>1.67</v>
       </c>
       <c r="D3" t="n">
-        <v>2.271</v>
+        <v>2.2113</v>
       </c>
       <c r="E3" t="n">
         <v>6.6646</v>
@@ -594,7 +594,7 @@
         <v>1.2217</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5483</v>
+        <v>1.4986</v>
       </c>
       <c r="E4" t="n">
         <v>4.8757</v>
@@ -640,7 +640,7 @@
         <v>1.1183</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3816</v>
+        <v>1.3341</v>
       </c>
       <c r="E5" t="n">
         <v>4.463</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5998</v>
+        <v>3.5777</v>
       </c>
       <c r="C6" t="n">
-        <v>0.902</v>
+        <v>0.8965</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0329</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5998</v>
+        <v>3.5777</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4373</v>
+        <v>4.4152</v>
       </c>
       <c r="G6" t="n">
         <v>-0.8375</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6546</v>
+        <v>4.6199</v>
       </c>
       <c r="I6" t="n">
         <v>4.698</v>
@@ -732,7 +732,7 @@
         <v>0.7355</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7644</v>
+        <v>0.7255</v>
       </c>
       <c r="E7" t="n">
         <v>2.9353</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.226</v>
+        <v>2.2077</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5578</v>
+        <v>0.5532</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4779</v>
+        <v>0.4356</v>
       </c>
       <c r="E8" t="n">
-        <v>2.226</v>
+        <v>2.2077</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4674</v>
+        <v>2.4491</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2414</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4674</v>
+        <v>2.4491</v>
       </c>
       <c r="I8" t="n">
         <v>2.4905</v>
@@ -824,7 +824,7 @@
         <v>0.4374</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2839</v>
+        <v>0.2516</v>
       </c>
       <c r="E9" t="n">
         <v>1.7458</v>
@@ -870,7 +870,7 @@
         <v>0.3903</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2079</v>
+        <v>0.1766</v>
       </c>
       <c r="E10" t="n">
         <v>1.5576</v>
@@ -916,7 +916,7 @@
         <v>0.2826</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0343</v>
+        <v>0.0054</v>
       </c>
       <c r="E11" t="n">
         <v>1.1279</v>
@@ -962,7 +962,7 @@
         <v>0.265</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0059</v>
+        <v>-0.0225</v>
       </c>
       <c r="E12" t="n">
         <v>1.0577</v>
@@ -1008,7 +1008,7 @@
         <v>0.2444</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0274</v>
+        <v>-0.0554</v>
       </c>
       <c r="E13" t="n">
         <v>0.9752999999999999</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9563</v>
+        <v>0.9462</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2396</v>
+        <v>0.2371</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.035</v>
+        <v>-0.0669</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9563</v>
+        <v>0.9462</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3566</v>
+        <v>1.3465</v>
       </c>
       <c r="G14" t="n">
         <v>-0.4003</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3566</v>
+        <v>1.3465</v>
       </c>
       <c r="I14" t="n">
         <v>1.3692</v>
@@ -1100,7 +1100,7 @@
         <v>0.1817</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1284</v>
+        <v>-0.155</v>
       </c>
       <c r="E15" t="n">
         <v>0.7252999999999999</v>
@@ -1146,7 +1146,7 @@
         <v>0.1806</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1301</v>
+        <v>-0.1567</v>
       </c>
       <c r="E16" t="n">
         <v>0.7209</v>
@@ -1192,7 +1192,7 @@
         <v>0.1565</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.169</v>
+        <v>-0.1951</v>
       </c>
       <c r="E17" t="n">
         <v>0.6246</v>
@@ -1238,7 +1238,7 @@
         <v>0.1373</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2001</v>
+        <v>-0.2257</v>
       </c>
       <c r="E18" t="n">
         <v>0.5478</v>
@@ -1284,7 +1284,7 @@
         <v>0.1288</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2137</v>
+        <v>-0.2391</v>
       </c>
       <c r="E19" t="n">
         <v>0.514</v>
@@ -1330,7 +1330,7 @@
         <v>0.1091</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2454</v>
+        <v>-0.2704</v>
       </c>
       <c r="E20" t="n">
         <v>0.4356</v>
@@ -1376,7 +1376,7 @@
         <v>0.0881</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2793</v>
+        <v>-0.3038</v>
       </c>
       <c r="E21" t="n">
         <v>0.3516</v>
@@ -1422,7 +1422,7 @@
         <v>0.0636</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3188</v>
+        <v>-0.3427</v>
       </c>
       <c r="E22" t="n">
         <v>0.254</v>
@@ -1468,7 +1468,7 @@
         <v>0.0576</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3285</v>
+        <v>-0.3523</v>
       </c>
       <c r="E23" t="n">
         <v>0.2299</v>
@@ -1514,7 +1514,7 @@
         <v>0.0557</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3316</v>
+        <v>-0.3554</v>
       </c>
       <c r="E24" t="n">
         <v>0.2221</v>
@@ -1560,7 +1560,7 @@
         <v>0.0552</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3324</v>
+        <v>-0.3562</v>
       </c>
       <c r="E25" t="n">
         <v>0.2202</v>
@@ -1606,7 +1606,7 @@
         <v>-0.0002</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4216</v>
+        <v>-0.4441</v>
       </c>
       <c r="E26" t="n">
         <v>-0.0005999999999999999</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0155</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4463</v>
+        <v>-0.4685</v>
       </c>
       <c r="E27" t="n">
         <v>-0.0617</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0422</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4895</v>
+        <v>-0.5111</v>
       </c>
       <c r="E28" t="n">
         <v>-0.1686</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0743</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5411</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="E29" t="n">
         <v>-0.2964</v>
@@ -1790,7 +1790,7 @@
         <v>-0.075</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5424</v>
+        <v>-0.5632</v>
       </c>
       <c r="E30" t="n">
         <v>-0.2995</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3229</v>
+        <v>-0.3261</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0809</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5518</v>
+        <v>-0.5738</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3229</v>
+        <v>-0.3261</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4261</v>
+        <v>0.4229</v>
       </c>
       <c r="G31" t="n">
         <v>-0.749</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4261</v>
+        <v>0.4229</v>
       </c>
       <c r="I31" t="n">
         <v>0.4301</v>
@@ -1882,7 +1882,7 @@
         <v>-0.0987</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5805</v>
+        <v>-0.6009</v>
       </c>
       <c r="E32" t="n">
         <v>-0.394</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1199</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6147</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="E33" t="n">
         <v>-0.4787</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8495</v>
+        <v>-0.8459</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2129</v>
+        <v>-0.212</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7645</v>
+        <v>-0.7809</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8495</v>
+        <v>-0.8459</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4842</v>
+        <v>-0.4806</v>
       </c>
       <c r="G34" t="n">
         <v>-0.3653</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4842</v>
+        <v>-0.4806</v>
       </c>
       <c r="I34" t="n">
         <v>-0.4887</v>
@@ -2020,7 +2020,7 @@
         <v>-0.2825</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8768</v>
+        <v>-0.8931</v>
       </c>
       <c r="E35" t="n">
         <v>-1.1275</v>
@@ -2066,7 +2066,7 @@
         <v>-0.3102</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9214</v>
+        <v>-0.9371</v>
       </c>
       <c r="E36" t="n">
         <v>-1.2378</v>
@@ -2112,7 +2112,7 @@
         <v>-0.3176</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9334</v>
+        <v>-0.9488</v>
       </c>
       <c r="E37" t="n">
         <v>-1.2674</v>
@@ -2158,7 +2158,7 @@
         <v>-0.3346</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9608</v>
+        <v>-0.9759</v>
       </c>
       <c r="E38" t="n">
         <v>-1.3352</v>
@@ -2204,7 +2204,7 @@
         <v>-0.3935</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0558</v>
+        <v>-1.0696</v>
       </c>
       <c r="E39" t="n">
         <v>-1.5706</v>
@@ -2250,7 +2250,7 @@
         <v>-0.4016</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0688</v>
+        <v>-1.0824</v>
       </c>
       <c r="E40" t="n">
         <v>-1.6027</v>
@@ -2296,7 +2296,7 @@
         <v>-0.4427</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1351</v>
+        <v>-1.1478</v>
       </c>
       <c r="E41" t="n">
         <v>-1.7667</v>

--- a/database/event/7993/event_7993_evp_summary.xlsx
+++ b/database/event/7993/event_7993_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.1255</v>
+        <v>7.8597</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7855</v>
+        <v>1.9694</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3949</v>
+        <v>2.9102</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1255</v>
+        <v>7.8597</v>
       </c>
       <c r="F2" t="n">
-        <v>4.84</v>
+        <v>5.599</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2855</v>
+        <v>2.2607</v>
       </c>
       <c r="H2" t="n">
-        <v>5.286</v>
+        <v>8.9344</v>
       </c>
       <c r="I2" t="n">
-        <v>5.286</v>
+        <v>8.9344</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2855</v>
+        <v>2.2607</v>
       </c>
       <c r="K2" t="n">
         <v>151</v>
@@ -529,7 +529,7 @@
         <v>63</v>
       </c>
       <c r="M2" t="n">
-        <v>7.571499999999999</v>
+        <v>11.1951</v>
       </c>
       <c r="N2" t="n">
         <v>214</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.6646</v>
+        <v>6.4986</v>
       </c>
       <c r="C3" t="n">
-        <v>1.67</v>
+        <v>1.6284</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2113</v>
+        <v>2.2958</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6646</v>
+        <v>6.4986</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8751</v>
+        <v>3.7241</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7895</v>
+        <v>2.7745</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8751</v>
+        <v>4.8176</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8751</v>
+        <v>4.8176</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7895</v>
+        <v>2.7745</v>
       </c>
       <c r="K3" t="n">
         <v>151</v>
@@ -575,7 +575,7 @@
         <v>63</v>
       </c>
       <c r="M3" t="n">
-        <v>6.6646</v>
+        <v>7.5921</v>
       </c>
       <c r="N3" t="n">
         <v>214</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8757</v>
+        <v>4.8461</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2217</v>
+        <v>1.2143</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4986</v>
+        <v>1.5498</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8757</v>
+        <v>4.8461</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5954</v>
+        <v>1.9636</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2803</v>
+        <v>2.8825</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5954</v>
+        <v>1.9636</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5954</v>
+        <v>1.9636</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2803</v>
+        <v>2.8825</v>
       </c>
       <c r="K4" t="n">
         <v>151</v>
@@ -621,7 +621,7 @@
         <v>63</v>
       </c>
       <c r="M4" t="n">
-        <v>4.8757</v>
+        <v>4.8461</v>
       </c>
       <c r="N4" t="n">
         <v>214</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.463</v>
+        <v>4.6493</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1183</v>
+        <v>1.165</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3341</v>
+        <v>1.4609</v>
       </c>
       <c r="E5" t="n">
-        <v>4.463</v>
+        <v>4.6493</v>
       </c>
       <c r="F5" t="n">
-        <v>4.463</v>
+        <v>4.6493</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6949</v>
+        <v>6.8491</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6949</v>
+        <v>6.8491</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6949</v>
+        <v>6.8491</v>
       </c>
       <c r="N5" t="n">
         <v>239</v>
@@ -676,952 +676,952 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5777</v>
+        <v>3.4883</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8965</v>
+        <v>0.8741</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9368</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5777</v>
+        <v>3.4883</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4152</v>
+        <v>3.4883</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8375</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6199</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
-        <v>4.698</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8375</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L6" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8605</v>
+        <v>4.3</v>
       </c>
       <c r="N6" t="n">
-        <v>303</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.9353</v>
+        <v>3.3395</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7355</v>
+        <v>0.8368</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7255</v>
+        <v>0.8696</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9353</v>
+        <v>3.3395</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9353</v>
+        <v>3.8511</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9353</v>
+        <v>5.0965</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9353</v>
+        <v>5.5243</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9353</v>
+        <v>5.012700000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>239</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2077</v>
+        <v>2.9054</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5532</v>
+        <v>0.728</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4356</v>
+        <v>0.6736</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2077</v>
+        <v>2.9054</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4491</v>
+        <v>2.9054</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2414</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4491</v>
+        <v>3.0201</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4905</v>
+        <v>3.0201</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2414</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L8" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.2491</v>
+        <v>3.0201</v>
       </c>
       <c r="N8" t="n">
-        <v>303</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.7458</v>
+        <v>2.669</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4374</v>
+        <v>0.6688</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2516</v>
+        <v>0.5669</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7458</v>
+        <v>2.669</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7458</v>
+        <v>2.7808</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0.1118</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7458</v>
+        <v>2.7808</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7458</v>
+        <v>3.0142</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0.1118</v>
       </c>
       <c r="K9" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M9" t="n">
-        <v>1.7458</v>
+        <v>2.9024</v>
       </c>
       <c r="N9" t="n">
-        <v>239</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.5576</v>
+        <v>2.1941</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3903</v>
+        <v>0.5498</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1766</v>
+        <v>0.3525</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5576</v>
+        <v>2.1941</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5576</v>
+        <v>2.1941</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5576</v>
+        <v>2.1941</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5576</v>
+        <v>2.1941</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.5576</v>
+        <v>2.1941</v>
       </c>
       <c r="N10" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.1279</v>
+        <v>1.514</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2826</v>
+        <v>0.3794</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0054</v>
+        <v>0.0455</v>
       </c>
       <c r="E11" t="n">
-        <v>1.1279</v>
+        <v>1.514</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1279</v>
+        <v>1.5524</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0.0384</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1279</v>
+        <v>1.5524</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1279</v>
+        <v>1.6827</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.0384</v>
       </c>
       <c r="K11" t="n">
-        <v>176</v>
+        <v>240</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1279</v>
+        <v>1.6443</v>
       </c>
       <c r="N11" t="n">
-        <v>176</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.0577</v>
+        <v>1.4878</v>
       </c>
       <c r="C12" t="n">
-        <v>0.265</v>
+        <v>0.3728</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0225</v>
+        <v>0.0337</v>
       </c>
       <c r="E12" t="n">
-        <v>1.0577</v>
+        <v>1.4878</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0577</v>
+        <v>1.4878</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0577</v>
+        <v>1.4878</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0577</v>
+        <v>1.4878</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.0577</v>
+        <v>1.4878</v>
       </c>
       <c r="N12" t="n">
-        <v>111</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.426</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2444</v>
+        <v>0.3573</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0554</v>
+        <v>0.0058</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.426</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.426</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.426</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.426</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9752999999999999</v>
+        <v>1.426</v>
       </c>
       <c r="N13" t="n">
-        <v>129</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9462</v>
+        <v>1.3047</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2371</v>
+        <v>0.3269</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0669</v>
+        <v>-0.049</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9462</v>
+        <v>1.3047</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3465</v>
+        <v>1.3047</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4003</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3465</v>
+        <v>1.3047</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3692</v>
+        <v>1.3047</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4003</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>240</v>
+        <v>129</v>
       </c>
       <c r="L14" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9689</v>
+        <v>1.3047</v>
       </c>
       <c r="N14" t="n">
-        <v>303</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7252999999999999</v>
+        <v>1.2694</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1817</v>
+        <v>0.3181</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.155</v>
+        <v>-0.0649</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7252999999999999</v>
+        <v>1.2694</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7252999999999999</v>
+        <v>1.2694</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7252999999999999</v>
+        <v>1.2694</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7252999999999999</v>
+        <v>1.2694</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>239</v>
+        <v>111</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7252999999999999</v>
+        <v>1.2694</v>
       </c>
       <c r="N15" t="n">
-        <v>239</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7209</v>
+        <v>1.2225</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1806</v>
+        <v>0.3063</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1567</v>
+        <v>-0.0861</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7209</v>
+        <v>1.2225</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7209</v>
+        <v>1.2225</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7209</v>
+        <v>1.2225</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7209</v>
+        <v>1.2225</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7209</v>
+        <v>1.2225</v>
       </c>
       <c r="N16" t="n">
-        <v>106</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6246</v>
+        <v>1.1991</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1565</v>
+        <v>0.3005</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1951</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6246</v>
+        <v>1.1991</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6246</v>
+        <v>1.1991</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6246</v>
+        <v>1.1991</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6246</v>
+        <v>1.1991</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>106</v>
+        <v>239</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6246</v>
+        <v>1.1991</v>
       </c>
       <c r="N17" t="n">
-        <v>106</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5478</v>
+        <v>0.9644</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1373</v>
+        <v>0.2417</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2257</v>
+        <v>-0.2026</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5478</v>
+        <v>0.9644</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5478</v>
+        <v>0.9644</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5478</v>
+        <v>0.9644</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5478</v>
+        <v>0.9644</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>111</v>
+        <v>239</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5478</v>
+        <v>0.9644</v>
       </c>
       <c r="N18" t="n">
-        <v>111</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.514</v>
+        <v>0.8693</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1288</v>
+        <v>0.2178</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2391</v>
+        <v>-0.2456</v>
       </c>
       <c r="E19" t="n">
-        <v>0.514</v>
+        <v>0.8693</v>
       </c>
       <c r="F19" t="n">
-        <v>0.514</v>
+        <v>0.8693</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.514</v>
+        <v>0.8693</v>
       </c>
       <c r="I19" t="n">
-        <v>0.514</v>
+        <v>0.8693</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.514</v>
+        <v>0.8693</v>
       </c>
       <c r="N19" t="n">
-        <v>129</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4356</v>
+        <v>0.8329</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1091</v>
+        <v>0.2087</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2704</v>
+        <v>-0.262</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4356</v>
+        <v>0.8329</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4356</v>
+        <v>0.8329</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4356</v>
+        <v>0.8329</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4356</v>
+        <v>0.8329</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4356</v>
+        <v>0.8329</v>
       </c>
       <c r="N20" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3516</v>
+        <v>0.7902</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0881</v>
+        <v>0.198</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3038</v>
+        <v>-0.2813</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3516</v>
+        <v>0.7902</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3516</v>
+        <v>0.7902</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3516</v>
+        <v>0.7902</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3516</v>
+        <v>0.7902</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>239</v>
+        <v>129</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3516</v>
+        <v>0.7902</v>
       </c>
       <c r="N21" t="n">
-        <v>239</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.254</v>
+        <v>0.7857</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0636</v>
+        <v>0.1969</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3427</v>
+        <v>-0.2833</v>
       </c>
       <c r="E22" t="n">
-        <v>0.254</v>
+        <v>0.7857</v>
       </c>
       <c r="F22" t="n">
-        <v>0.254</v>
+        <v>1.5068</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.7211</v>
       </c>
       <c r="H22" t="n">
-        <v>0.254</v>
+        <v>1.5068</v>
       </c>
       <c r="I22" t="n">
-        <v>0.254</v>
+        <v>1.5068</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.7211</v>
       </c>
       <c r="K22" t="n">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M22" t="n">
-        <v>0.254</v>
+        <v>0.7857</v>
       </c>
       <c r="N22" t="n">
-        <v>176</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2299</v>
+        <v>0.7764</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0576</v>
+        <v>0.1945</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3523</v>
+        <v>-0.2875</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2299</v>
+        <v>0.7764</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2299</v>
+        <v>0.7764</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2299</v>
+        <v>0.7764</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2299</v>
+        <v>0.7764</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2299</v>
+        <v>0.7764</v>
       </c>
       <c r="N23" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2221</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0557</v>
+        <v>0.1944</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3554</v>
+        <v>-0.2878</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2221</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2221</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2221</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2221</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>176</v>
+        <v>242</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2221</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>176</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2202</v>
+        <v>0.6694</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0552</v>
+        <v>0.1677</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3562</v>
+        <v>-0.3358</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2202</v>
+        <v>0.6694</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0535</v>
+        <v>0.6694</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.8333</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.0535</v>
+        <v>0.6694</v>
       </c>
       <c r="I25" t="n">
-        <v>1.0535</v>
+        <v>0.6694</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.8333</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="L25" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2202000000000001</v>
+        <v>0.6694</v>
       </c>
       <c r="N25" t="n">
-        <v>214</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.4854</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0002</v>
+        <v>0.1216</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4441</v>
+        <v>-0.4189</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.4854</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.4854</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.4854</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.4854</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.4854</v>
       </c>
       <c r="N26" t="n">
         <v>242</v>
@@ -1642,78 +1642,78 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0617</v>
+        <v>0.4501</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0155</v>
+        <v>0.1128</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4685</v>
+        <v>-0.4348</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0617</v>
+        <v>0.4501</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0617</v>
+        <v>0.4501</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0617</v>
+        <v>0.4501</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0617</v>
+        <v>0.4501</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0617</v>
+        <v>0.4501</v>
       </c>
       <c r="N27" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1686</v>
+        <v>0.193</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0422</v>
+        <v>0.0484</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5111</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1686</v>
+        <v>0.193</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1686</v>
+        <v>0.193</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1686</v>
+        <v>0.193</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1686</v>
+        <v>0.193</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1686</v>
+        <v>0.193</v>
       </c>
       <c r="N28" t="n">
         <v>106</v>
@@ -1734,32 +1734,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2964</v>
+        <v>0.1706</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0743</v>
+        <v>0.0427</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2964</v>
+        <v>0.1706</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2964</v>
+        <v>0.1706</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2964</v>
+        <v>0.1706</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2964</v>
+        <v>0.1706</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2964</v>
+        <v>0.1706</v>
       </c>
       <c r="N29" t="n">
         <v>242</v>
@@ -1780,81 +1780,81 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2995</v>
+        <v>0.1418</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.075</v>
+        <v>0.0355</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5632</v>
+        <v>-0.574</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2995</v>
+        <v>0.1418</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3524</v>
+        <v>0.1418</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.6519</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3524</v>
+        <v>0.1418</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3524</v>
+        <v>0.1418</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.6519</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="L30" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2995</v>
+        <v>0.1418</v>
       </c>
       <c r="N30" t="n">
-        <v>214</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3261</v>
+        <v>0.0505</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.08169999999999999</v>
+        <v>0.0127</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5738</v>
+        <v>-0.6152</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3261</v>
+        <v>0.0505</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4229</v>
+        <v>0.1697</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.749</v>
+        <v>-0.1192</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4229</v>
+        <v>0.1697</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4301</v>
+        <v>0.1839</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.749</v>
+        <v>-0.1192</v>
       </c>
       <c r="K31" t="n">
         <v>240</v>
@@ -1863,7 +1863,7 @@
         <v>63</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3189</v>
+        <v>0.06470000000000001</v>
       </c>
       <c r="N31" t="n">
         <v>303</v>
@@ -1872,277 +1872,277 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.394</v>
+        <v>0.0339</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0987</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6009</v>
+        <v>-0.6227</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.394</v>
+        <v>0.0339</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.394</v>
+        <v>0.5735</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.5396</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.394</v>
+        <v>0.5735</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.394</v>
+        <v>0.6216</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.5396</v>
       </c>
       <c r="K32" t="n">
-        <v>129</v>
+        <v>240</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.394</v>
+        <v>0.08200000000000007</v>
       </c>
       <c r="N32" t="n">
-        <v>129</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4787</v>
+        <v>-0.0151</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1199</v>
+        <v>-0.0038</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.6448</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4787</v>
+        <v>-0.0151</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4787</v>
+        <v>0.6185</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4787</v>
+        <v>0.6185</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4787</v>
+        <v>0.6185</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>242</v>
+        <v>151</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4787</v>
+        <v>-0.0151</v>
       </c>
       <c r="N33" t="n">
-        <v>242</v>
+        <v>214</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8459</v>
+        <v>-0.1898</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.212</v>
+        <v>-0.0476</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7809</v>
+        <v>-0.7237</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8459</v>
+        <v>-0.1898</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4806</v>
+        <v>-0.1898</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.3653</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4806</v>
+        <v>-0.1898</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4887</v>
+        <v>-0.1898</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.3653</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>240</v>
+        <v>129</v>
       </c>
       <c r="L34" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8540000000000001</v>
+        <v>-0.1898</v>
       </c>
       <c r="N34" t="n">
-        <v>303</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kauez</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1275</v>
+        <v>-0.448</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2825</v>
+        <v>-0.1123</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8931</v>
+        <v>-0.8403</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1275</v>
+        <v>-0.448</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.1275</v>
+        <v>-0.448</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.1275</v>
+        <v>-0.448</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.1275</v>
+        <v>-0.448</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>242</v>
+        <v>129</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1275</v>
+        <v>-0.448</v>
       </c>
       <c r="N35" t="n">
-        <v>242</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2378</v>
+        <v>-0.7195</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3102</v>
+        <v>-0.1803</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9371</v>
+        <v>-0.9628</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2378</v>
+        <v>-0.7195</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.2378</v>
+        <v>-0.7195</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2378</v>
+        <v>-0.7195</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.2378</v>
+        <v>-0.7195</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.2378</v>
+        <v>-0.7195</v>
       </c>
       <c r="N36" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>kauez</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2674</v>
+        <v>-0.7425</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3176</v>
+        <v>-0.1861</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9488</v>
+        <v>-0.9732</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2674</v>
+        <v>-0.7425</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2674</v>
+        <v>-0.7425</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2674</v>
+        <v>-0.7425</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2674</v>
+        <v>-0.7425</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>111</v>
+        <v>242</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2674</v>
+        <v>-0.7425</v>
       </c>
       <c r="N37" t="n">
-        <v>111</v>
+        <v>242</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3352</v>
+        <v>-0.8165</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3346</v>
+        <v>-0.2046</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9759</v>
+        <v>-1.0066</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3352</v>
+        <v>-0.8165</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.3352</v>
+        <v>-0.8165</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3352</v>
+        <v>-0.8165</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.3352</v>
+        <v>-0.8165</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3352</v>
+        <v>-0.8165</v>
       </c>
       <c r="N38" t="n">
         <v>111</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5706</v>
+        <v>-0.9886</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3935</v>
+        <v>-0.2477</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0696</v>
+        <v>-1.0843</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5706</v>
+        <v>-0.9886</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5706</v>
+        <v>-0.9886</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5706</v>
+        <v>-0.9886</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.5706</v>
+        <v>-0.9886</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>176</v>
+        <v>106</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.5706</v>
+        <v>-0.9886</v>
       </c>
       <c r="N39" t="n">
-        <v>176</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.6027</v>
+        <v>-1</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4016</v>
+        <v>-0.2506</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0824</v>
+        <v>-1.0895</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.6027</v>
+        <v>-1</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.6027</v>
+        <v>-1</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.6027</v>
+        <v>-1</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.6027</v>
+        <v>-1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.6027</v>
+        <v>-1</v>
       </c>
       <c r="N40" t="n">
-        <v>106</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.7667</v>
+        <v>-1.2682</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4427</v>
+        <v>-0.3178</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1478</v>
+        <v>-1.2105</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.7667</v>
+        <v>-1.2682</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.7667</v>
+        <v>-1.2682</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.7667</v>
+        <v>-1.2682</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.7667</v>
+        <v>-1.2682</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.7667</v>
+        <v>-1.2682</v>
       </c>
       <c r="N41" t="n">
         <v>176</v>
@@ -2429,10 +2429,10 @@
         <v>1.54</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2649</v>
+        <v>1.1745</v>
       </c>
       <c r="J2" t="n">
-        <v>25.298</v>
+        <v>23.49</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.49</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1649</v>
+        <v>1.112</v>
       </c>
       <c r="J3" t="n">
-        <v>23.298</v>
+        <v>22.24</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.45</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0825</v>
+        <v>1.0614</v>
       </c>
       <c r="J4" t="n">
-        <v>21.65</v>
+        <v>21.228</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1488</v>
+        <v>-0.0672</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.976</v>
+        <v>-1.344</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.9</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4969</v>
+        <v>-0.4217</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.938000000000001</v>
+        <v>-8.433999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.23</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4793</v>
+        <v>0.5567</v>
       </c>
       <c r="J7" t="n">
-        <v>9.586</v>
+        <v>11.134</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.06</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2137</v>
+        <v>0.2064</v>
       </c>
       <c r="J8" t="n">
-        <v>4.274</v>
+        <v>4.128</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.44</v>
+        <v>-1.458</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.58</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.4307</v>
       </c>
       <c r="J10" t="n">
-        <v>-12.914</v>
+        <v>-8.614000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.46</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7916</v>
+        <v>-0.5406</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.832</v>
+        <v>-10.812</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.92</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9451</v>
+        <v>1.6387</v>
       </c>
       <c r="J12" t="n">
-        <v>40.8471</v>
+        <v>34.4127</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.3</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7558</v>
+        <v>0.7796</v>
       </c>
       <c r="J13" t="n">
-        <v>15.8718</v>
+        <v>16.3716</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.23</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5569</v>
+        <v>0.6219</v>
       </c>
       <c r="J14" t="n">
-        <v>11.6949</v>
+        <v>13.0599</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0611</v>
+        <v>0.1382</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2831</v>
+        <v>2.9022</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.79</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7665</v>
+        <v>-0.714</v>
       </c>
       <c r="J16" t="n">
-        <v>-16.0965</v>
+        <v>-14.994</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1686</v>
+        <v>0.1521</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5406</v>
+        <v>3.1941</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.01</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1002</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1042</v>
+        <v>1.4595</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.87</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2183</v>
+        <v>-0.1531</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.5843</v>
+        <v>-3.2151</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.78</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3758</v>
+        <v>-0.2429</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.8918</v>
+        <v>-5.1009</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.65</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.3676</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.739</v>
+        <v>-7.7196</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.62</v>
       </c>
       <c r="I22" t="n">
-        <v>1.484</v>
+        <v>1.311</v>
       </c>
       <c r="J22" t="n">
-        <v>32.648</v>
+        <v>28.842</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.45</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1501</v>
+        <v>1.0912</v>
       </c>
       <c r="J23" t="n">
-        <v>25.3022</v>
+        <v>24.0064</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.36</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9595</v>
+        <v>0.948</v>
       </c>
       <c r="J24" t="n">
-        <v>21.109</v>
+        <v>20.856</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.65</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0503</v>
+        <v>-1.0316</v>
       </c>
       <c r="J25" t="n">
-        <v>-23.1066</v>
+        <v>-22.6952</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.63</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.0922</v>
+        <v>-1.079</v>
       </c>
       <c r="J26" t="n">
-        <v>-24.0284</v>
+        <v>-23.738</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.13</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3261</v>
+        <v>0.3519</v>
       </c>
       <c r="J27" t="n">
-        <v>7.1742</v>
+        <v>7.7418</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0793</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.7446</v>
+        <v>-1.6566</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.92</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.118</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.596</v>
+        <v>-2.1802</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.79</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3604</v>
+        <v>-0.233</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.9288</v>
+        <v>-5.126</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.57</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6613</v>
+        <v>-0.442</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.5486</v>
+        <v>-9.724</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.22</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4004</v>
+        <v>0.4645</v>
       </c>
       <c r="J32" t="n">
-        <v>9.209199999999999</v>
+        <v>10.6835</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3274</v>
+        <v>0.3733</v>
       </c>
       <c r="J33" t="n">
-        <v>7.5302</v>
+        <v>8.585900000000001</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.16</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3121</v>
+        <v>0.3547</v>
       </c>
       <c r="J34" t="n">
-        <v>7.1783</v>
+        <v>8.158099999999999</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.05</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1184</v>
+        <v>0.1334</v>
       </c>
       <c r="J35" t="n">
-        <v>2.7232</v>
+        <v>3.0682</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.57</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6863</v>
+        <v>-0.4598</v>
       </c>
       <c r="J36" t="n">
-        <v>-15.7849</v>
+        <v>-10.5754</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.41</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0616</v>
+        <v>1.034</v>
       </c>
       <c r="J37" t="n">
-        <v>24.4168</v>
+        <v>23.782</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.31</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8423</v>
+        <v>0.8315</v>
       </c>
       <c r="J38" t="n">
-        <v>19.3729</v>
+        <v>19.1245</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.26</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7246</v>
+        <v>0.7137</v>
       </c>
       <c r="J39" t="n">
-        <v>16.6658</v>
+        <v>16.4151</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.92</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4039</v>
+        <v>-0.3321</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.2897</v>
+        <v>-7.6383</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.86</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5685</v>
+        <v>-0.5038</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.0755</v>
+        <v>-11.5874</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.28</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4675</v>
+        <v>0.556</v>
       </c>
       <c r="J42" t="n">
-        <v>16.83</v>
+        <v>20.016</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.23</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3989</v>
+        <v>0.4695</v>
       </c>
       <c r="J43" t="n">
-        <v>14.3604</v>
+        <v>16.902</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.09</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1739</v>
+        <v>0.2108</v>
       </c>
       <c r="J44" t="n">
-        <v>6.2604</v>
+        <v>7.5888</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.09</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1739</v>
+        <v>0.2108</v>
       </c>
       <c r="J45" t="n">
-        <v>6.2604</v>
+        <v>7.5888</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.71</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5206</v>
+        <v>-0.3353</v>
       </c>
       <c r="J46" t="n">
-        <v>-18.7416</v>
+        <v>-12.0708</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.51</v>
       </c>
       <c r="I47" t="n">
-        <v>1.3115</v>
+        <v>1.1942</v>
       </c>
       <c r="J47" t="n">
-        <v>47.214</v>
+        <v>42.9912</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.34</v>
       </c>
       <c r="I48" t="n">
-        <v>0.957</v>
+        <v>0.9353</v>
       </c>
       <c r="J48" t="n">
-        <v>34.452</v>
+        <v>33.6708</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.88</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4848</v>
+        <v>-0.4249</v>
       </c>
       <c r="J49" t="n">
-        <v>-17.4528</v>
+        <v>-15.2964</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.8</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6917</v>
+        <v>-0.6404</v>
       </c>
       <c r="J50" t="n">
-        <v>-24.9012</v>
+        <v>-23.0544</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.8</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6917</v>
+        <v>-0.6404</v>
       </c>
       <c r="J51" t="n">
-        <v>-24.9012</v>
+        <v>-23.0544</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.58</v>
       </c>
       <c r="I52" t="n">
-        <v>1.4373</v>
+        <v>1.2791</v>
       </c>
       <c r="J52" t="n">
-        <v>33.0579</v>
+        <v>29.4193</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.15</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4818</v>
+        <v>0.4592</v>
       </c>
       <c r="J53" t="n">
-        <v>11.0814</v>
+        <v>10.5616</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.99</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1322</v>
+        <v>-0.074</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.0406</v>
+        <v>-1.702</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.96</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2501</v>
+        <v>-0.1871</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.7523</v>
+        <v>-4.3033</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.75</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8167</v>
+        <v>-0.7735</v>
       </c>
       <c r="J56" t="n">
-        <v>-18.7841</v>
+        <v>-17.7905</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.35</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6107</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>14.0461</v>
+        <v>16.9832</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.95</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0859</v>
+        <v>-0.0696</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.9757</v>
+        <v>-1.6008</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.91</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1777</v>
+        <v>-0.1153</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.0871</v>
+        <v>-2.6519</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.71</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4914</v>
+        <v>-0.3177</v>
       </c>
       <c r="J60" t="n">
-        <v>-11.3022</v>
+        <v>-7.3071</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.7</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5049</v>
+        <v>-0.3272</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.6127</v>
+        <v>-7.5256</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.86</v>
       </c>
       <c r="I62" t="n">
-        <v>1.8115</v>
+        <v>1.5366</v>
       </c>
       <c r="J62" t="n">
-        <v>34.4185</v>
+        <v>29.1954</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.54</v>
       </c>
       <c r="I63" t="n">
-        <v>1.2224</v>
+        <v>1.1576</v>
       </c>
       <c r="J63" t="n">
-        <v>23.2256</v>
+        <v>21.9944</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.46</v>
       </c>
       <c r="I64" t="n">
-        <v>1.0575</v>
+        <v>1.0597</v>
       </c>
       <c r="J64" t="n">
-        <v>20.0925</v>
+        <v>20.1343</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1735</v>
+        <v>-0.0876</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.2965</v>
+        <v>-1.6644</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.97</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3082</v>
+        <v>-0.2208</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.8558</v>
+        <v>-4.1952</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.91</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.0813</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J67" t="n">
-        <v>-1.5447</v>
+        <v>-1.6986</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.8</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2673</v>
+        <v>-0.2099</v>
       </c>
       <c r="J68" t="n">
-        <v>-5.0787</v>
+        <v>-3.9881</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.76</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.338</v>
+        <v>-0.2485</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.422</v>
+        <v>-4.7215</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4652</v>
+        <v>-0.3131</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.838800000000001</v>
+        <v>-5.9489</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.6</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5942</v>
+        <v>-0.3975</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.2898</v>
+        <v>-7.5525</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.35</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9182</v>
+        <v>0.9143</v>
       </c>
       <c r="J72" t="n">
-        <v>20.2004</v>
+        <v>20.1146</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.33</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8735000000000001</v>
+        <v>0.8691</v>
       </c>
       <c r="J73" t="n">
-        <v>19.217</v>
+        <v>19.1202</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.15</v>
       </c>
       <c r="I74" t="n">
-        <v>0.393</v>
+        <v>0.4414</v>
       </c>
       <c r="J74" t="n">
-        <v>8.646000000000001</v>
+        <v>9.710800000000001</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.13</v>
       </c>
       <c r="I75" t="n">
-        <v>0.335</v>
+        <v>0.3894</v>
       </c>
       <c r="J75" t="n">
-        <v>7.37</v>
+        <v>8.566800000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.93</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3831</v>
+        <v>-0.3084</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.4282</v>
+        <v>-6.7848</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.34</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5722</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>12.5884</v>
+        <v>15.114</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2287</v>
+        <v>0.2469</v>
       </c>
       <c r="J78" t="n">
-        <v>5.0314</v>
+        <v>5.4318</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.08</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1935</v>
+        <v>0.2054</v>
       </c>
       <c r="J79" t="n">
-        <v>4.257</v>
+        <v>4.5188</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1545</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.399</v>
+        <v>-1.9338</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.53</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7288</v>
+        <v>-0.4924</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.0336</v>
+        <v>-10.8328</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.21</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3945</v>
+        <v>0.3472</v>
       </c>
       <c r="J82" t="n">
-        <v>11.835</v>
+        <v>10.416</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.03</v>
       </c>
       <c r="I83" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>2.607</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.97</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0968</v>
+        <v>-0.0509</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.904</v>
+        <v>-1.527</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.93</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1779</v>
+        <v>-0.1011</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.337</v>
+        <v>-3.033</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.91</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2138</v>
+        <v>-0.1241</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.414</v>
+        <v>-3.723</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.69</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9385</v>
+        <v>0.8554</v>
       </c>
       <c r="J87" t="n">
-        <v>28.155</v>
+        <v>25.662</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.31</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4987</v>
+        <v>0.4267</v>
       </c>
       <c r="J88" t="n">
-        <v>14.961</v>
+        <v>12.801</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.86</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3181</v>
+        <v>-0.1892</v>
       </c>
       <c r="J89" t="n">
-        <v>-9.542999999999999</v>
+        <v>-5.676</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.85</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3331</v>
+        <v>-0.1997</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.993</v>
+        <v>-5.991</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.82</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3767</v>
+        <v>-0.2305</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.301</v>
+        <v>-6.915</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.83</v>
       </c>
       <c r="I92" t="n">
-        <v>1.8556</v>
+        <v>1.568</v>
       </c>
       <c r="J92" t="n">
-        <v>44.5344</v>
+        <v>37.632</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.24</v>
       </c>
       <c r="I93" t="n">
-        <v>0.673</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="J93" t="n">
-        <v>16.152</v>
+        <v>15.9552</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.02</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0044</v>
+        <v>0.0585</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.1056</v>
+        <v>1.404</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.93</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3756</v>
+        <v>-0.3026</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.0144</v>
+        <v>-7.2624</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.76</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.8122</v>
+        <v>-0.7663</v>
       </c>
       <c r="J96" t="n">
-        <v>-19.4928</v>
+        <v>-18.3912</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.59</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8602</v>
+        <v>1.0535</v>
       </c>
       <c r="J97" t="n">
-        <v>20.6448</v>
+        <v>25.284</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.03</v>
       </c>
       <c r="I98" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0896</v>
       </c>
       <c r="J98" t="n">
-        <v>2.0304</v>
+        <v>2.1504</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.03</v>
       </c>
       <c r="I99" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0896</v>
       </c>
       <c r="J99" t="n">
-        <v>2.0304</v>
+        <v>2.1504</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.84</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3279</v>
+        <v>-0.2</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.8696</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.58</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6718</v>
+        <v>-0.4489</v>
       </c>
       <c r="J101" t="n">
-        <v>-16.1232</v>
+        <v>-10.7736</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.45</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6842</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
-        <v>15.7366</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.11</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2182</v>
+        <v>0.1796</v>
       </c>
       <c r="J103" t="n">
-        <v>5.0186</v>
+        <v>4.1308</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.01</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0002</v>
+        <v>0.0203</v>
       </c>
       <c r="J104" t="n">
-        <v>0.0046</v>
+        <v>0.4669</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.93</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1948</v>
+        <v>-0.1071</v>
       </c>
       <c r="J105" t="n">
-        <v>-4.4804</v>
+        <v>-2.4633</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.83</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3546</v>
+        <v>-0.2161</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.155799999999999</v>
+        <v>-4.9703</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.62</v>
       </c>
       <c r="I107" t="n">
-        <v>0.9104</v>
+        <v>0.8939</v>
       </c>
       <c r="J107" t="n">
-        <v>20.9392</v>
+        <v>20.5597</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.01</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0599</v>
+        <v>0.0336</v>
       </c>
       <c r="J108" t="n">
-        <v>1.3777</v>
+        <v>0.7728</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.93</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1595</v>
+        <v>-0.0964</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.6685</v>
+        <v>-2.2172</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.36</v>
+        <v>-0.2247</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.279999999999999</v>
+        <v>-5.1681</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.45</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.8168</v>
+        <v>-0.5605</v>
       </c>
       <c r="J111" t="n">
-        <v>-18.7864</v>
+        <v>-12.8915</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.2</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4136</v>
+        <v>0.4698</v>
       </c>
       <c r="J112" t="n">
-        <v>9.5128</v>
+        <v>10.8054</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.99</v>
       </c>
       <c r="I113" t="n">
-        <v>0.011</v>
+        <v>-0.0124</v>
       </c>
       <c r="J113" t="n">
-        <v>0.253</v>
+        <v>-0.2852</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.86</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2654</v>
+        <v>-0.1678</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.1042</v>
+        <v>-3.8594</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.83</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3145</v>
+        <v>-0.1986</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.2335</v>
+        <v>-4.5678</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.7</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5031</v>
+        <v>-0.3262</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.5713</v>
+        <v>-7.5026</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.66</v>
       </c>
       <c r="I117" t="n">
-        <v>1.5527</v>
+        <v>1.3577</v>
       </c>
       <c r="J117" t="n">
-        <v>35.7121</v>
+        <v>31.2271</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.39</v>
       </c>
       <c r="I118" t="n">
-        <v>1.0181</v>
+        <v>1.0013</v>
       </c>
       <c r="J118" t="n">
-        <v>23.4163</v>
+        <v>23.0299</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2441</v>
+        <v>-0.1702</v>
       </c>
       <c r="J119" t="n">
-        <v>-5.6143</v>
+        <v>-3.9146</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.96</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2791</v>
+        <v>-0.2052</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.4193</v>
+        <v>-4.7196</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7419</v>
+        <v>-0.6896</v>
       </c>
       <c r="J121" t="n">
-        <v>-17.0637</v>
+        <v>-15.8608</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.02</v>
       </c>
       <c r="I122" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.079</v>
       </c>
       <c r="J122" t="n">
-        <v>2.3328</v>
+        <v>1.896</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.99</v>
       </c>
       <c r="I123" t="n">
-        <v>0.001</v>
+        <v>-0.0152</v>
       </c>
       <c r="J123" t="n">
-        <v>0.024</v>
+        <v>-0.3648</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.96</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0718</v>
+        <v>-0.0584</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.7232</v>
+        <v>-1.4016</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1182</v>
+        <v>-0.0828</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.8368</v>
+        <v>-1.9872</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.78</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.397</v>
+        <v>-0.2515</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.528</v>
+        <v>-6.036</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.23</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6822</v>
+        <v>0.6577</v>
       </c>
       <c r="J127" t="n">
-        <v>16.3728</v>
+        <v>15.7848</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.16</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4999</v>
+        <v>0.4814</v>
       </c>
       <c r="J128" t="n">
-        <v>11.9976</v>
+        <v>11.5536</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.1</v>
       </c>
       <c r="I129" t="n">
-        <v>0.3111</v>
+        <v>0.3231</v>
       </c>
       <c r="J129" t="n">
-        <v>7.4664</v>
+        <v>7.7544</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.1</v>
       </c>
       <c r="I130" t="n">
-        <v>0.3111</v>
+        <v>0.3231</v>
       </c>
       <c r="J130" t="n">
-        <v>7.4664</v>
+        <v>7.7544</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.91</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4137</v>
+        <v>-0.348</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.928800000000001</v>
+        <v>-8.352</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.91</v>
       </c>
       <c r="I132" t="n">
-        <v>1.9324</v>
+        <v>1.6304</v>
       </c>
       <c r="J132" t="n">
-        <v>36.7156</v>
+        <v>30.9776</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.69</v>
       </c>
       <c r="I133" t="n">
-        <v>1.5624</v>
+        <v>1.3661</v>
       </c>
       <c r="J133" t="n">
-        <v>29.6856</v>
+        <v>25.9559</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.21</v>
       </c>
       <c r="I134" t="n">
-        <v>0.5105</v>
+        <v>0.5764</v>
       </c>
       <c r="J134" t="n">
-        <v>9.6995</v>
+        <v>10.9516</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.7174</v>
+        <v>-0.6603</v>
       </c>
       <c r="J135" t="n">
-        <v>-13.6306</v>
+        <v>-12.5457</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.62</v>
       </c>
       <c r="I136" t="n">
-        <v>-1.1312</v>
+        <v>-1.1242</v>
       </c>
       <c r="J136" t="n">
-        <v>-21.4928</v>
+        <v>-21.3598</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.13</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3468</v>
+        <v>0.377</v>
       </c>
       <c r="J137" t="n">
-        <v>6.5892</v>
+        <v>7.163</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.86</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.2005</v>
+        <v>-0.1581</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.8095</v>
+        <v>-3.0039</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.79</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3369</v>
+        <v>-0.2267</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.4011</v>
+        <v>-4.3073</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.74</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.417</v>
+        <v>-0.2748</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.923</v>
+        <v>-5.2212</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.57</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6508</v>
+        <v>-0.4352</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.3652</v>
+        <v>-8.268800000000001</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.09</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3216</v>
+        <v>0.2637</v>
       </c>
       <c r="J142" t="n">
-        <v>5.7888</v>
+        <v>4.7466</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.99</v>
       </c>
       <c r="I143" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.0411</v>
       </c>
       <c r="J143" t="n">
-        <v>1.6776</v>
+        <v>0.7398</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.57</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.6268</v>
+        <v>-0.4215</v>
       </c>
       <c r="J144" t="n">
-        <v>-11.2824</v>
+        <v>-7.587</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.55</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.6536</v>
+        <v>-0.4402</v>
       </c>
       <c r="J145" t="n">
-        <v>-11.7648</v>
+        <v>-7.9236</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.43</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.8061</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="J146" t="n">
-        <v>-14.5098</v>
+        <v>-9.934200000000001</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>2.83</v>
       </c>
       <c r="I147" t="n">
-        <v>1.8657</v>
+        <v>1.4914</v>
       </c>
       <c r="J147" t="n">
-        <v>33.5826</v>
+        <v>26.8452</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.41</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4928</v>
+        <v>0.4927</v>
       </c>
       <c r="J148" t="n">
-        <v>8.8704</v>
+        <v>8.868600000000001</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.33</v>
       </c>
       <c r="I149" t="n">
-        <v>0.3926</v>
+        <v>0.4057</v>
       </c>
       <c r="J149" t="n">
-        <v>7.0668</v>
+        <v>7.3026</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.27</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3165</v>
+        <v>0.3371</v>
       </c>
       <c r="J150" t="n">
-        <v>5.697</v>
+        <v>6.0678</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.58</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7122000000000001</v>
+        <v>-0.482</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.8196</v>
+        <v>-8.676</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.62</v>
       </c>
       <c r="I152" t="n">
-        <v>1.4699</v>
+        <v>1.3022</v>
       </c>
       <c r="J152" t="n">
-        <v>32.3378</v>
+        <v>28.6484</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.6</v>
       </c>
       <c r="I153" t="n">
-        <v>1.432</v>
+        <v>1.2769</v>
       </c>
       <c r="J153" t="n">
-        <v>31.504</v>
+        <v>28.0918</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.08</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1919</v>
+        <v>0.252</v>
       </c>
       <c r="J154" t="n">
-        <v>4.2218</v>
+        <v>5.544</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.84</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.6247</v>
+        <v>-0.5626</v>
       </c>
       <c r="J155" t="n">
-        <v>-13.7434</v>
+        <v>-12.3772</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.71</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.9274</v>
+        <v>-0.8935</v>
       </c>
       <c r="J156" t="n">
-        <v>-20.4028</v>
+        <v>-19.657</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.39</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.7915</v>
       </c>
       <c r="J157" t="n">
-        <v>14.2714</v>
+        <v>17.413</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.11</v>
       </c>
       <c r="I158" t="n">
-        <v>0.2614</v>
+        <v>0.279</v>
       </c>
       <c r="J158" t="n">
-        <v>5.7508</v>
+        <v>6.138</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.04</v>
       </c>
       <c r="I159" t="n">
-        <v>0.1338</v>
+        <v>0.1257</v>
       </c>
       <c r="J159" t="n">
-        <v>2.9436</v>
+        <v>2.7654</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.68</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.538</v>
+        <v>-0.3501</v>
       </c>
       <c r="J160" t="n">
-        <v>-11.836</v>
+        <v>-7.7022</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6877</v>
+        <v>-0.4611</v>
       </c>
       <c r="J161" t="n">
-        <v>-15.1294</v>
+        <v>-10.1442</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.3</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4927</v>
+        <v>0.4192</v>
       </c>
       <c r="J162" t="n">
-        <v>13.7956</v>
+        <v>11.7376</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4116</v>
+        <v>0.346</v>
       </c>
       <c r="J163" t="n">
-        <v>11.5248</v>
+        <v>9.688000000000001</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1912</v>
+        <v>0.1637</v>
       </c>
       <c r="J164" t="n">
-        <v>5.3536</v>
+        <v>4.5836</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.08</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1463</v>
+        <v>0.1359</v>
       </c>
       <c r="J165" t="n">
-        <v>4.0964</v>
+        <v>3.8052</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.7</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.534</v>
+        <v>-0.3451</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.952</v>
+        <v>-9.662800000000001</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.71</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9805</v>
+        <v>0.9638</v>
       </c>
       <c r="J167" t="n">
-        <v>27.454</v>
+        <v>26.9864</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.98</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0857</v>
+        <v>-0.0396</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.3996</v>
+        <v>-1.1088</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.97</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1085</v>
+        <v>-0.0539</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.038</v>
+        <v>-1.5092</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.87</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2882</v>
+        <v>-0.1714</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.069599999999999</v>
+        <v>-4.7992</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.67</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5653</v>
+        <v>-0.3688</v>
       </c>
       <c r="J171" t="n">
-        <v>-15.8284</v>
+        <v>-10.3264</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.95</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0434</v>
+        <v>-0.0568</v>
       </c>
       <c r="J172" t="n">
-        <v>-0.8246</v>
+        <v>-1.0792</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.93</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.082</v>
+        <v>-0.0818</v>
       </c>
       <c r="J173" t="n">
-        <v>-1.558</v>
+        <v>-1.5542</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.91</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1191</v>
+        <v>-0.1055</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.2629</v>
+        <v>-2.0045</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.7</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4811</v>
+        <v>-0.3153</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.1409</v>
+        <v>-5.9907</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5091</v>
+        <v>-0.3343</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.6729</v>
+        <v>-6.3517</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>2.11</v>
       </c>
       <c r="I177" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J177" t="n">
-        <v>39.1267</v>
+        <v>34.8422</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.13</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2849</v>
+        <v>0.367</v>
       </c>
       <c r="J178" t="n">
-        <v>5.4131</v>
+        <v>6.973</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.09</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1745</v>
+        <v>0.2555</v>
       </c>
       <c r="J179" t="n">
-        <v>3.3155</v>
+        <v>4.8545</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.07</v>
       </c>
       <c r="I180" t="n">
-        <v>0.116</v>
+        <v>0.1962</v>
       </c>
       <c r="J180" t="n">
-        <v>2.204</v>
+        <v>3.7278</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.99</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2073</v>
+        <v>-0.1226</v>
       </c>
       <c r="J181" t="n">
-        <v>-3.9387</v>
+        <v>-2.3294</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.35</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6405</v>
+        <v>0.7839</v>
       </c>
       <c r="J182" t="n">
-        <v>12.81</v>
+        <v>15.678</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.85</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2379</v>
+        <v>-0.1713</v>
       </c>
       <c r="J183" t="n">
-        <v>-4.758</v>
+        <v>-3.426</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.3178</v>
+        <v>-0.2104</v>
       </c>
       <c r="J184" t="n">
-        <v>-6.356</v>
+        <v>-4.208</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.67</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.5262</v>
+        <v>-0.3455</v>
       </c>
       <c r="J185" t="n">
-        <v>-10.524</v>
+        <v>-6.91</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.55</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6816</v>
+        <v>-0.4574</v>
       </c>
       <c r="J186" t="n">
-        <v>-13.632</v>
+        <v>-9.148</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.6</v>
       </c>
       <c r="I187" t="n">
-        <v>1.3765</v>
+        <v>1.2465</v>
       </c>
       <c r="J187" t="n">
-        <v>27.53</v>
+        <v>24.93</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.59</v>
       </c>
       <c r="I188" t="n">
-        <v>1.3574</v>
+        <v>1.2342</v>
       </c>
       <c r="J188" t="n">
-        <v>27.148</v>
+        <v>24.684</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.37</v>
       </c>
       <c r="I189" t="n">
-        <v>0.9038</v>
+        <v>0.9271</v>
       </c>
       <c r="J189" t="n">
-        <v>18.076</v>
+        <v>18.542</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.17</v>
       </c>
       <c r="I190" t="n">
-        <v>0.3864</v>
+        <v>0.4697</v>
       </c>
       <c r="J190" t="n">
-        <v>7.728</v>
+        <v>9.394</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.7</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.9712</v>
+        <v>-0.9424</v>
       </c>
       <c r="J191" t="n">
-        <v>-19.424</v>
+        <v>-18.848</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>2.13</v>
       </c>
       <c r="I192" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J192" t="n">
-        <v>35.0081</v>
+        <v>31.1746</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.4</v>
       </c>
       <c r="I193" t="n">
-        <v>0.9103</v>
+        <v>0.9676</v>
       </c>
       <c r="J193" t="n">
-        <v>15.4751</v>
+        <v>16.4492</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.24</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5173</v>
+        <v>0.6204</v>
       </c>
       <c r="J194" t="n">
-        <v>8.7941</v>
+        <v>10.5468</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.15</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2988</v>
+        <v>0.3963</v>
       </c>
       <c r="J195" t="n">
-        <v>5.0796</v>
+        <v>6.7371</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1779</v>
+        <v>-0.0915</v>
       </c>
       <c r="J196" t="n">
-        <v>-3.0243</v>
+        <v>-1.5555</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.212</v>
+        <v>-0.1843</v>
       </c>
       <c r="J197" t="n">
-        <v>-3.604</v>
+        <v>-3.1331</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.7</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.3902</v>
+        <v>-0.295</v>
       </c>
       <c r="J198" t="n">
-        <v>-6.6334</v>
+        <v>-5.015</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.67</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.4536</v>
+        <v>-0.3215</v>
       </c>
       <c r="J199" t="n">
-        <v>-7.7112</v>
+        <v>-5.4655</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.64</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5057</v>
+        <v>-0.3486</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.5969</v>
+        <v>-5.9262</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.57</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.4135</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.3768</v>
+        <v>-7.0295</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>2.41</v>
       </c>
       <c r="I202" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J202" t="n">
-        <v>28.8302</v>
+        <v>25.6732</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.79</v>
       </c>
       <c r="I203" t="n">
-        <v>1.5595</v>
+        <v>1.4022</v>
       </c>
       <c r="J203" t="n">
-        <v>21.833</v>
+        <v>19.6308</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.55</v>
       </c>
       <c r="I204" t="n">
-        <v>1.0655</v>
+        <v>1.1367</v>
       </c>
       <c r="J204" t="n">
-        <v>14.917</v>
+        <v>15.9138</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.46</v>
       </c>
       <c r="I205" t="n">
-        <v>0.8885</v>
+        <v>1.0263</v>
       </c>
       <c r="J205" t="n">
-        <v>12.439</v>
+        <v>14.3682</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.19</v>
       </c>
       <c r="I206" t="n">
-        <v>0.3223</v>
+        <v>0.4405</v>
       </c>
       <c r="J206" t="n">
-        <v>4.5122</v>
+        <v>6.167</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.99</v>
       </c>
       <c r="I207" t="n">
-        <v>0.1409</v>
+        <v>0.1218</v>
       </c>
       <c r="J207" t="n">
-        <v>1.9726</v>
+        <v>1.7052</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.8</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2026</v>
+        <v>-0.1815</v>
       </c>
       <c r="J208" t="n">
-        <v>-2.8364</v>
+        <v>-2.541</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.58</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.5737</v>
+        <v>-0.396</v>
       </c>
       <c r="J209" t="n">
-        <v>-8.0318</v>
+        <v>-5.544</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.41</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.8097</v>
+        <v>-0.5558</v>
       </c>
       <c r="J210" t="n">
-        <v>-11.3358</v>
+        <v>-7.7812</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.37</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.8603</v>
+        <v>-0.5938</v>
       </c>
       <c r="J211" t="n">
-        <v>-12.0442</v>
+        <v>-8.3132</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.17</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3459</v>
+        <v>0.3885</v>
       </c>
       <c r="J212" t="n">
-        <v>6.918</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.11</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2516</v>
+        <v>0.2714</v>
       </c>
       <c r="J213" t="n">
-        <v>5.032</v>
+        <v>5.428</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.95</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1275</v>
+        <v>-0.0742</v>
       </c>
       <c r="J214" t="n">
-        <v>-2.55</v>
+        <v>-1.484</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.88</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2558</v>
+        <v>-0.1541</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.116</v>
+        <v>-3.082</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.8</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3793</v>
+        <v>-0.2369</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.586</v>
+        <v>-4.738</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.42</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0417</v>
+        <v>1.029</v>
       </c>
       <c r="J217" t="n">
-        <v>20.834</v>
+        <v>20.58</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.4</v>
       </c>
       <c r="I218" t="n">
-        <v>0.999</v>
+        <v>0.9971</v>
       </c>
       <c r="J218" t="n">
-        <v>19.98</v>
+        <v>19.942</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.36</v>
       </c>
       <c r="I219" t="n">
-        <v>0.9113</v>
+        <v>0.9196</v>
       </c>
       <c r="J219" t="n">
-        <v>18.226</v>
+        <v>18.392</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.16</v>
       </c>
       <c r="I220" t="n">
-        <v>0.3867</v>
+        <v>0.456</v>
       </c>
       <c r="J220" t="n">
-        <v>7.734</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.82</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6898</v>
+        <v>-0.6306</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.796</v>
+        <v>-12.612</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.13</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3124</v>
+        <v>0.337</v>
       </c>
       <c r="J222" t="n">
-        <v>7.1852</v>
+        <v>7.751</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.9</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.1858</v>
+        <v>-0.1247</v>
       </c>
       <c r="J223" t="n">
-        <v>-4.2734</v>
+        <v>-2.8681</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.88</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2254</v>
+        <v>-0.1458</v>
       </c>
       <c r="J224" t="n">
-        <v>-5.1842</v>
+        <v>-3.3534</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.88</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2254</v>
+        <v>-0.1458</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.1842</v>
+        <v>-3.3534</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.74</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4455</v>
+        <v>-0.2865</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.2465</v>
+        <v>-6.5895</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.51</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2652</v>
+        <v>1.1664</v>
       </c>
       <c r="J227" t="n">
-        <v>29.0996</v>
+        <v>26.8272</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.18</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.5193</v>
       </c>
       <c r="J228" t="n">
-        <v>11.8588</v>
+        <v>11.9439</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.06</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1373</v>
+        <v>0.1954</v>
       </c>
       <c r="J229" t="n">
-        <v>3.1579</v>
+        <v>4.4942</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.02</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.0035</v>
+        <v>0.059</v>
       </c>
       <c r="J230" t="n">
-        <v>-0.0805</v>
+        <v>1.357</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.1051</v>
+        <v>-0.0369</v>
       </c>
       <c r="J231" t="n">
-        <v>-2.4173</v>
+        <v>-0.8487</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.15</v>
       </c>
       <c r="I232" t="n">
-        <v>0.3141</v>
+        <v>0.3491</v>
       </c>
       <c r="J232" t="n">
-        <v>7.5384</v>
+        <v>8.378399999999999</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.12</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2666</v>
+        <v>0.2904</v>
       </c>
       <c r="J233" t="n">
-        <v>6.3984</v>
+        <v>6.9696</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1496</v>
+        <v>-0.0867</v>
       </c>
       <c r="J234" t="n">
-        <v>-3.5904</v>
+        <v>-2.0808</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2057</v>
+        <v>-0.1215</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.9368</v>
+        <v>-2.916</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3657</v>
+        <v>-0.2273</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.7768</v>
+        <v>-5.4552</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.41</v>
       </c>
       <c r="I237" t="n">
-        <v>1.1242</v>
+        <v>1.0692</v>
       </c>
       <c r="J237" t="n">
-        <v>26.9808</v>
+        <v>25.6608</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.1</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3715</v>
+        <v>0.3373</v>
       </c>
       <c r="J238" t="n">
-        <v>8.916</v>
+        <v>8.0952</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.08</v>
       </c>
       <c r="I239" t="n">
-        <v>0.3087</v>
+        <v>0.2795</v>
       </c>
       <c r="J239" t="n">
-        <v>7.4088</v>
+        <v>6.708</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.85</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5535</v>
+        <v>-0.4991</v>
       </c>
       <c r="J240" t="n">
-        <v>-13.284</v>
+        <v>-11.9784</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.74</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.8248</v>
+        <v>-0.7848000000000001</v>
       </c>
       <c r="J241" t="n">
-        <v>-19.7952</v>
+        <v>-18.8352</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.75</v>
       </c>
       <c r="I242" t="n">
-        <v>0.9736</v>
+        <v>0.8904</v>
       </c>
       <c r="J242" t="n">
-        <v>20.4456</v>
+        <v>18.6984</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.21</v>
       </c>
       <c r="I243" t="n">
-        <v>0.3225</v>
+        <v>0.2934</v>
       </c>
       <c r="J243" t="n">
-        <v>6.7725</v>
+        <v>6.1614</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.14</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2011</v>
+        <v>0.2067</v>
       </c>
       <c r="J244" t="n">
-        <v>4.2231</v>
+        <v>4.3407</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.08</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1018</v>
+        <v>0.1231</v>
       </c>
       <c r="J245" t="n">
-        <v>2.1378</v>
+        <v>2.5851</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.82</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.392</v>
+        <v>-0.2398</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.231999999999999</v>
+        <v>-5.0358</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.6</v>
       </c>
       <c r="I247" t="n">
-        <v>0.8878</v>
+        <v>0.8683</v>
       </c>
       <c r="J247" t="n">
-        <v>18.6438</v>
+        <v>18.2343</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.2</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3956</v>
+        <v>0.3445</v>
       </c>
       <c r="J248" t="n">
-        <v>8.307600000000001</v>
+        <v>7.2345</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.73</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.4737</v>
+        <v>-0.3036</v>
       </c>
       <c r="J249" t="n">
-        <v>-9.947699999999999</v>
+        <v>-6.3756</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.5269</v>
+        <v>-0.3418</v>
       </c>
       <c r="J250" t="n">
-        <v>-11.0649</v>
+        <v>-7.1778</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.61</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6284</v>
+        <v>-0.4164</v>
       </c>
       <c r="J251" t="n">
-        <v>-13.1964</v>
+        <v>-8.744400000000001</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.15</v>
       </c>
       <c r="I252" t="n">
-        <v>0.3464</v>
+        <v>0.3804</v>
       </c>
       <c r="J252" t="n">
-        <v>7.6208</v>
+        <v>8.3688</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.86</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.2573</v>
+        <v>-0.1658</v>
       </c>
       <c r="J253" t="n">
-        <v>-5.6606</v>
+        <v>-3.6476</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.84</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2914</v>
+        <v>-0.1863</v>
       </c>
       <c r="J254" t="n">
-        <v>-6.4108</v>
+        <v>-4.0986</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.83</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3078</v>
+        <v>-0.1965</v>
       </c>
       <c r="J255" t="n">
-        <v>-6.7716</v>
+        <v>-4.323</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3396</v>
+        <v>-0.2166</v>
       </c>
       <c r="J256" t="n">
-        <v>-7.4712</v>
+        <v>-4.7652</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.31</v>
       </c>
       <c r="I257" t="n">
-        <v>0.8323</v>
+        <v>0.8256</v>
       </c>
       <c r="J257" t="n">
-        <v>18.3106</v>
+        <v>18.1632</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.31</v>
       </c>
       <c r="I258" t="n">
-        <v>0.8323</v>
+        <v>0.8256</v>
       </c>
       <c r="J258" t="n">
-        <v>18.3106</v>
+        <v>18.1632</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.24</v>
       </c>
       <c r="I259" t="n">
-        <v>0.6642</v>
+        <v>0.6611</v>
       </c>
       <c r="J259" t="n">
-        <v>14.6124</v>
+        <v>14.5442</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.01</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.0529</v>
+        <v>0.0139</v>
       </c>
       <c r="J260" t="n">
-        <v>-1.1638</v>
+        <v>0.3058</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.98</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2126</v>
+        <v>-0.1371</v>
       </c>
       <c r="J261" t="n">
-        <v>-4.6772</v>
+        <v>-3.0162</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.8</v>
       </c>
       <c r="I262" t="n">
-        <v>1.7405</v>
+        <v>1.4867</v>
       </c>
       <c r="J262" t="n">
-        <v>36.5505</v>
+        <v>31.2207</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.47</v>
       </c>
       <c r="I263" t="n">
-        <v>1.1171</v>
+        <v>1.0843</v>
       </c>
       <c r="J263" t="n">
-        <v>23.4591</v>
+        <v>22.7703</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.33</v>
       </c>
       <c r="I264" t="n">
-        <v>0.8077</v>
+        <v>0.8398</v>
       </c>
       <c r="J264" t="n">
-        <v>16.9617</v>
+        <v>17.6358</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1529</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="J265" t="n">
-        <v>-3.2109</v>
+        <v>-1.4805</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.85</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.6298</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="J266" t="n">
-        <v>-13.2258</v>
+        <v>-11.844</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.08</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2482</v>
+        <v>0.2504</v>
       </c>
       <c r="J267" t="n">
-        <v>5.2122</v>
+        <v>5.2584</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.92</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1121</v>
+        <v>-0.0975</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.3541</v>
+        <v>-2.0475</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.88</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1869</v>
+        <v>-0.1419</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.9249</v>
+        <v>-2.9799</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.75</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4167</v>
+        <v>-0.2706</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.7507</v>
+        <v>-5.6826</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.66</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.3565</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.3988</v>
+        <v>-7.4865</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.31</v>
       </c>
       <c r="I272" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J272" t="n">
-        <v>32.9488</v>
+        <v>29.3408</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.82</v>
       </c>
       <c r="I273" t="n">
-        <v>1.6982</v>
+        <v>1.4669</v>
       </c>
       <c r="J273" t="n">
-        <v>27.1712</v>
+        <v>23.4704</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.58</v>
       </c>
       <c r="I274" t="n">
-        <v>1.2517</v>
+        <v>1.1899</v>
       </c>
       <c r="J274" t="n">
-        <v>20.0272</v>
+        <v>19.0384</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.84</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.6883</v>
+        <v>-0.6266</v>
       </c>
       <c r="J275" t="n">
-        <v>-11.0128</v>
+        <v>-10.0256</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.7586000000000001</v>
+        <v>-0.7045</v>
       </c>
       <c r="J276" t="n">
-        <v>-12.1376</v>
+        <v>-11.272</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>0.85</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.1673</v>
+        <v>-0.1504</v>
       </c>
       <c r="J277" t="n">
-        <v>-2.6768</v>
+        <v>-2.4064</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.4474</v>
+        <v>-0.3084</v>
       </c>
       <c r="J278" t="n">
-        <v>-7.1584</v>
+        <v>-4.9344</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.4474</v>
+        <v>-0.3084</v>
       </c>
       <c r="J279" t="n">
-        <v>-7.1584</v>
+        <v>-4.9344</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4474</v>
+        <v>-0.3084</v>
       </c>
       <c r="J280" t="n">
-        <v>-7.1584</v>
+        <v>-4.9344</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.67</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4798</v>
+        <v>-0.3268</v>
       </c>
       <c r="J281" t="n">
-        <v>-7.6768</v>
+        <v>-5.2288</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>2.02</v>
       </c>
       <c r="I282" t="n">
-        <v>1.2014</v>
+        <v>1.0728</v>
       </c>
       <c r="J282" t="n">
-        <v>21.6252</v>
+        <v>19.3104</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.35</v>
       </c>
       <c r="I283" t="n">
-        <v>0.4685</v>
+        <v>0.4396</v>
       </c>
       <c r="J283" t="n">
-        <v>8.433</v>
+        <v>7.9128</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.22</v>
       </c>
       <c r="I284" t="n">
-        <v>0.2792</v>
+        <v>0.2921</v>
       </c>
       <c r="J284" t="n">
-        <v>5.0256</v>
+        <v>5.2578</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.16</v>
       </c>
       <c r="I285" t="n">
-        <v>0.194</v>
+        <v>0.2168</v>
       </c>
       <c r="J285" t="n">
-        <v>3.492</v>
+        <v>3.9024</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.97</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.1741</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J286" t="n">
-        <v>-3.1338</v>
+        <v>-1.4958</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.31</v>
       </c>
       <c r="I287" t="n">
-        <v>0.6146</v>
+        <v>0.5756</v>
       </c>
       <c r="J287" t="n">
-        <v>11.0628</v>
+        <v>10.3608</v>
       </c>
     </row>
     <row r="288">
@@ -13909,10 +13909,10 @@
         <v>0.7</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.4644</v>
+        <v>-0.3085</v>
       </c>
       <c r="J289" t="n">
-        <v>-8.3592</v>
+        <v>-5.553</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.53</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.6944</v>
+        <v>-0.4678</v>
       </c>
       <c r="J290" t="n">
-        <v>-12.4992</v>
+        <v>-8.420400000000001</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.48</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.7564</v>
+        <v>-0.514</v>
       </c>
       <c r="J291" t="n">
-        <v>-13.6152</v>
+        <v>-9.252000000000001</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.25</v>
       </c>
       <c r="I292" t="n">
-        <v>0.4605</v>
+        <v>0.5364</v>
       </c>
       <c r="J292" t="n">
-        <v>11.052</v>
+        <v>12.8736</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.04</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1236</v>
+        <v>0.1201</v>
       </c>
       <c r="J293" t="n">
-        <v>2.9664</v>
+        <v>2.8824</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.92</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1854</v>
+        <v>-0.1095</v>
       </c>
       <c r="J294" t="n">
-        <v>-4.4496</v>
+        <v>-2.628</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.9</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2212</v>
+        <v>-0.132</v>
       </c>
       <c r="J295" t="n">
-        <v>-5.3088</v>
+        <v>-3.168</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.79</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3933</v>
+        <v>-0.2466</v>
       </c>
       <c r="J296" t="n">
-        <v>-9.4392</v>
+        <v>-5.9184</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.5</v>
       </c>
       <c r="I297" t="n">
-        <v>1.2861</v>
+        <v>1.1774</v>
       </c>
       <c r="J297" t="n">
-        <v>30.8664</v>
+        <v>28.2576</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.38</v>
       </c>
       <c r="I298" t="n">
-        <v>1.0384</v>
+        <v>1.0098</v>
       </c>
       <c r="J298" t="n">
-        <v>24.9216</v>
+        <v>24.2352</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.12</v>
       </c>
       <c r="I299" t="n">
-        <v>0.4022</v>
+        <v>0.3819</v>
       </c>
       <c r="J299" t="n">
-        <v>9.652799999999999</v>
+        <v>9.1656</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.82</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.6456</v>
+        <v>-0.5908</v>
       </c>
       <c r="J300" t="n">
-        <v>-15.4944</v>
+        <v>-14.1792</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.223</v>
+        <v>-1.2282</v>
       </c>
       <c r="J301" t="n">
-        <v>-29.352</v>
+        <v>-29.4768</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>0.95</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.039</v>
+        <v>-0.0549</v>
       </c>
       <c r="J302" t="n">
-        <v>-0.819</v>
+        <v>-1.1529</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.9</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.1325</v>
+        <v>-0.1153</v>
       </c>
       <c r="J303" t="n">
-        <v>-2.7825</v>
+        <v>-2.4213</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.89</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1504</v>
+        <v>-0.1266</v>
       </c>
       <c r="J304" t="n">
-        <v>-3.1584</v>
+        <v>-2.6586</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.7</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4779</v>
+        <v>-0.3139</v>
       </c>
       <c r="J305" t="n">
-        <v>-10.0359</v>
+        <v>-6.5919</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.68</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5061</v>
+        <v>-0.3329</v>
       </c>
       <c r="J306" t="n">
-        <v>-10.6281</v>
+        <v>-6.9909</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.56</v>
       </c>
       <c r="I307" t="n">
-        <v>1.3144</v>
+        <v>1.2044</v>
       </c>
       <c r="J307" t="n">
-        <v>27.6024</v>
+        <v>25.2924</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.36</v>
       </c>
       <c r="I308" t="n">
-        <v>0.8992</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="J308" t="n">
-        <v>18.8832</v>
+        <v>19.1898</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.25</v>
       </c>
       <c r="I309" t="n">
-        <v>0.6171</v>
+        <v>0.6684</v>
       </c>
       <c r="J309" t="n">
-        <v>12.9591</v>
+        <v>14.0364</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.22</v>
       </c>
       <c r="I310" t="n">
-        <v>0.533</v>
+        <v>0.5991</v>
       </c>
       <c r="J310" t="n">
-        <v>11.193</v>
+        <v>12.5811</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.88</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5448</v>
+        <v>-0.4735</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.4408</v>
+        <v>-9.9435</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>0.86</v>
       </c>
       <c r="I312" t="n">
-        <v>-0.1595</v>
+        <v>-0.1434</v>
       </c>
       <c r="J312" t="n">
-        <v>-3.0305</v>
+        <v>-2.7246</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.84</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.1926</v>
+        <v>-0.1653</v>
       </c>
       <c r="J313" t="n">
-        <v>-3.6594</v>
+        <v>-3.1407</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.75</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.3439</v>
+        <v>-0.2561</v>
       </c>
       <c r="J314" t="n">
-        <v>-6.5341</v>
+        <v>-4.8659</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.63</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.5471</v>
+        <v>-0.3669</v>
       </c>
       <c r="J315" t="n">
-        <v>-10.3949</v>
+        <v>-6.9711</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.6</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5891</v>
+        <v>-0.395</v>
       </c>
       <c r="J316" t="n">
-        <v>-11.1929</v>
+        <v>-7.505</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.98</v>
       </c>
       <c r="I317" t="n">
-        <v>1.9891</v>
+        <v>1.6917</v>
       </c>
       <c r="J317" t="n">
-        <v>37.7929</v>
+        <v>32.1423</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.74</v>
       </c>
       <c r="I318" t="n">
-        <v>1.6248</v>
+        <v>1.4099</v>
       </c>
       <c r="J318" t="n">
-        <v>30.8712</v>
+        <v>26.7881</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.08</v>
       </c>
       <c r="I319" t="n">
-        <v>0.1346</v>
+        <v>0.2188</v>
       </c>
       <c r="J319" t="n">
-        <v>2.5574</v>
+        <v>4.1572</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.9</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.5052</v>
+        <v>-0.4293</v>
       </c>
       <c r="J320" t="n">
-        <v>-9.598800000000001</v>
+        <v>-8.156700000000001</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.85</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.6342</v>
+        <v>-0.5684</v>
       </c>
       <c r="J321" t="n">
-        <v>-12.0498</v>
+        <v>-10.7996</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.21</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4375</v>
+        <v>0.5004</v>
       </c>
       <c r="J322" t="n">
-        <v>8.75</v>
+        <v>10.008</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.01</v>
       </c>
       <c r="I323" t="n">
-        <v>0.0919</v>
+        <v>0.0631</v>
       </c>
       <c r="J323" t="n">
-        <v>1.838</v>
+        <v>1.262</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.8</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.3523</v>
+        <v>-0.2256</v>
       </c>
       <c r="J324" t="n">
-        <v>-7.046</v>
+        <v>-4.512</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.76</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.4123</v>
+        <v>-0.265</v>
       </c>
       <c r="J325" t="n">
-        <v>-8.246</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.67</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.5371</v>
+        <v>-0.3513</v>
       </c>
       <c r="J326" t="n">
-        <v>-10.742</v>
+        <v>-7.026</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.45</v>
       </c>
       <c r="I327" t="n">
-        <v>1.146</v>
+        <v>1.0892</v>
       </c>
       <c r="J327" t="n">
-        <v>22.92</v>
+        <v>21.784</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.2</v>
       </c>
       <c r="I328" t="n">
-        <v>0.5738</v>
+        <v>0.5694</v>
       </c>
       <c r="J328" t="n">
-        <v>11.476</v>
+        <v>11.388</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.15</v>
       </c>
       <c r="I329" t="n">
-        <v>0.4234</v>
+        <v>0.4458</v>
       </c>
       <c r="J329" t="n">
-        <v>8.468</v>
+        <v>8.916</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.05</v>
       </c>
       <c r="I330" t="n">
-        <v>0.1065</v>
+        <v>0.1646</v>
       </c>
       <c r="J330" t="n">
-        <v>2.13</v>
+        <v>3.292</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.9</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4604</v>
+        <v>-0.3907</v>
       </c>
       <c r="J331" t="n">
-        <v>-9.208</v>
+        <v>-7.814</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.83</v>
       </c>
       <c r="I332" t="n">
-        <v>1.7849</v>
+        <v>1.5171</v>
       </c>
       <c r="J332" t="n">
-        <v>35.698</v>
+        <v>30.342</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.43</v>
       </c>
       <c r="I333" t="n">
-        <v>1.0239</v>
+        <v>1.0284</v>
       </c>
       <c r="J333" t="n">
-        <v>20.478</v>
+        <v>20.568</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.33</v>
       </c>
       <c r="I334" t="n">
-        <v>0.7946</v>
+        <v>0.8365</v>
       </c>
       <c r="J334" t="n">
-        <v>15.892</v>
+        <v>16.73</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.2</v>
       </c>
       <c r="I335" t="n">
-        <v>0.4525</v>
+        <v>0.5399</v>
       </c>
       <c r="J335" t="n">
-        <v>9.050000000000001</v>
+        <v>10.798</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.75</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.8667</v>
+        <v>-0.8249</v>
       </c>
       <c r="J336" t="n">
-        <v>-17.334</v>
+        <v>-16.498</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.15</v>
       </c>
       <c r="I337" t="n">
-        <v>0.3713</v>
+        <v>0.41</v>
       </c>
       <c r="J337" t="n">
-        <v>7.426</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.85</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.2284</v>
+        <v>-0.1703</v>
       </c>
       <c r="J338" t="n">
-        <v>-4.568</v>
+        <v>-3.406</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.8</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.3285</v>
+        <v>-0.2188</v>
       </c>
       <c r="J339" t="n">
-        <v>-6.57</v>
+        <v>-4.376</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.73</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.4379</v>
+        <v>-0.2866</v>
       </c>
       <c r="J340" t="n">
-        <v>-8.757999999999999</v>
+        <v>-5.732</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.64</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.5634</v>
+        <v>-0.3721</v>
       </c>
       <c r="J341" t="n">
-        <v>-11.268</v>
+        <v>-7.442</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>2.17</v>
       </c>
       <c r="I342" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J342" t="n">
-        <v>49.4232</v>
+        <v>44.0112</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.79</v>
       </c>
       <c r="I343" t="n">
-        <v>1.7283</v>
+        <v>1.4783</v>
       </c>
       <c r="J343" t="n">
-        <v>41.4792</v>
+        <v>35.4792</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.21</v>
       </c>
       <c r="I344" t="n">
-        <v>0.4925</v>
+        <v>0.5705</v>
       </c>
       <c r="J344" t="n">
-        <v>11.82</v>
+        <v>13.692</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.82</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.7002</v>
+        <v>-0.641</v>
       </c>
       <c r="J345" t="n">
-        <v>-16.8048</v>
+        <v>-15.384</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.4</v>
       </c>
       <c r="I346" t="n">
-        <v>-1.5558</v>
+        <v>-1.6223</v>
       </c>
       <c r="J346" t="n">
-        <v>-37.3392</v>
+        <v>-38.9352</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.22</v>
       </c>
       <c r="I347" t="n">
-        <v>0.4162</v>
+        <v>0.4793</v>
       </c>
       <c r="J347" t="n">
-        <v>9.988799999999999</v>
+        <v>11.5032</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.2</v>
       </c>
       <c r="I348" t="n">
-        <v>0.3878</v>
+        <v>0.4426</v>
       </c>
       <c r="J348" t="n">
-        <v>9.3072</v>
+        <v>10.6224</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.13</v>
       </c>
       <c r="I349" t="n">
-        <v>0.282</v>
+        <v>0.3096</v>
       </c>
       <c r="J349" t="n">
-        <v>6.768</v>
+        <v>7.4304</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.84</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3212</v>
+        <v>-0.1969</v>
       </c>
       <c r="J350" t="n">
-        <v>-7.7088</v>
+        <v>-4.7256</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.55</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-0.4734</v>
       </c>
       <c r="J351" t="n">
-        <v>-16.8984</v>
+        <v>-11.3616</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7993/event_7993_evp_summary.xlsx
+++ b/database/event/7993/event_7993_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.8597</v>
+        <v>7.6171</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9694</v>
+        <v>1.9086</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9102</v>
+        <v>2.8433</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8597</v>
+        <v>7.6171</v>
       </c>
       <c r="F2" t="n">
-        <v>5.599</v>
+        <v>5.3786</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2607</v>
+        <v>2.2385</v>
       </c>
       <c r="H2" t="n">
-        <v>8.9344</v>
+        <v>9.0472</v>
       </c>
       <c r="I2" t="n">
-        <v>8.9344</v>
+        <v>9.0472</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2607</v>
+        <v>2.2385</v>
       </c>
       <c r="K2" t="n">
         <v>151</v>
@@ -529,7 +529,7 @@
         <v>63</v>
       </c>
       <c r="M2" t="n">
-        <v>11.1951</v>
+        <v>11.2857</v>
       </c>
       <c r="N2" t="n">
         <v>214</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4986</v>
+        <v>6.1428</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6284</v>
+        <v>1.5392</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2958</v>
+        <v>2.1721</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4986</v>
+        <v>6.1428</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7241</v>
+        <v>3.4498</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7745</v>
+        <v>2.693</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8176</v>
+        <v>4.8255</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8176</v>
+        <v>4.8255</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7745</v>
+        <v>2.693</v>
       </c>
       <c r="K3" t="n">
         <v>151</v>
@@ -575,7 +575,7 @@
         <v>63</v>
       </c>
       <c r="M3" t="n">
-        <v>7.5921</v>
+        <v>7.5185</v>
       </c>
       <c r="N3" t="n">
         <v>214</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8461</v>
+        <v>5.0729</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2143</v>
+        <v>1.2711</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5498</v>
+        <v>1.6851</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8461</v>
+        <v>5.0729</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9636</v>
+        <v>1.9673</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8825</v>
+        <v>3.1056</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9636</v>
+        <v>1.9673</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9636</v>
+        <v>1.9673</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8825</v>
+        <v>3.1056</v>
       </c>
       <c r="K4" t="n">
         <v>151</v>
@@ -621,7 +621,7 @@
         <v>63</v>
       </c>
       <c r="M4" t="n">
-        <v>4.8461</v>
+        <v>5.0729</v>
       </c>
       <c r="N4" t="n">
         <v>214</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6493</v>
+        <v>4.375</v>
       </c>
       <c r="C5" t="n">
-        <v>1.165</v>
+        <v>1.0963</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4609</v>
+        <v>1.3674</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6493</v>
+        <v>4.375</v>
       </c>
       <c r="F5" t="n">
-        <v>4.6493</v>
+        <v>4.375</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6.8491</v>
+        <v>6.8505</v>
       </c>
       <c r="I5" t="n">
-        <v>6.8491</v>
+        <v>6.8505</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>6.8491</v>
+        <v>6.8505</v>
       </c>
       <c r="N5" t="n">
         <v>239</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.4883</v>
+        <v>3.1383</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8741</v>
+        <v>0.7864</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9368</v>
+        <v>0.8044</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4883</v>
+        <v>3.1383</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4883</v>
+        <v>3.1383</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>4.1439</v>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>4.1439</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3</v>
+        <v>4.1439</v>
       </c>
       <c r="N6" t="n">
         <v>239</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3395</v>
+        <v>2.9795</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8368</v>
+        <v>0.7466</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8696</v>
+        <v>0.7321</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3395</v>
+        <v>2.9795</v>
       </c>
       <c r="F7" t="n">
-        <v>3.8511</v>
+        <v>3.5201</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5116000000000001</v>
+        <v>-0.5406</v>
       </c>
       <c r="H7" t="n">
-        <v>5.0965</v>
+        <v>4.9796</v>
       </c>
       <c r="I7" t="n">
-        <v>5.5243</v>
+        <v>5.2395</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5116000000000001</v>
+        <v>-0.5406</v>
       </c>
       <c r="K7" t="n">
         <v>240</v>
@@ -759,7 +759,7 @@
         <v>63</v>
       </c>
       <c r="M7" t="n">
-        <v>5.012700000000001</v>
+        <v>4.6989</v>
       </c>
       <c r="N7" t="n">
         <v>303</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9054</v>
+        <v>2.5455</v>
       </c>
       <c r="C8" t="n">
-        <v>0.728</v>
+        <v>0.6378</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6736</v>
+        <v>0.5346</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9054</v>
+        <v>2.5455</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9054</v>
+        <v>2.5455</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0201</v>
+        <v>2.8464</v>
       </c>
       <c r="I8" t="n">
-        <v>3.0201</v>
+        <v>2.8464</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0201</v>
+        <v>2.8464</v>
       </c>
       <c r="N8" t="n">
         <v>242</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.669</v>
+        <v>2.3921</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6688</v>
+        <v>0.5994</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5669</v>
+        <v>0.4647</v>
       </c>
       <c r="E9" t="n">
-        <v>2.669</v>
+        <v>2.3921</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7808</v>
+        <v>2.5382</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1118</v>
+        <v>-0.1461</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7808</v>
+        <v>2.8304</v>
       </c>
       <c r="I9" t="n">
-        <v>3.0142</v>
+        <v>2.9781</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1118</v>
+        <v>-0.1461</v>
       </c>
       <c r="K9" t="n">
         <v>240</v>
@@ -851,7 +851,7 @@
         <v>63</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9024</v>
+        <v>2.832</v>
       </c>
       <c r="N9" t="n">
         <v>303</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1941</v>
+        <v>2.1718</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5498</v>
+        <v>0.5442</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3525</v>
+        <v>0.3644</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1941</v>
+        <v>2.1718</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1941</v>
+        <v>2.1718</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1941</v>
+        <v>2.1718</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1941</v>
+        <v>2.1718</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1941</v>
+        <v>2.1718</v>
       </c>
       <c r="N10" t="n">
         <v>239</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.514</v>
+        <v>1.5137</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3794</v>
+        <v>0.3793</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0455</v>
+        <v>0.0649</v>
       </c>
       <c r="E11" t="n">
-        <v>1.514</v>
+        <v>1.5137</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5524</v>
+        <v>1.6042</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0384</v>
+        <v>-0.0905</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5524</v>
+        <v>1.6042</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6827</v>
+        <v>1.6879</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0384</v>
+        <v>-0.0905</v>
       </c>
       <c r="K11" t="n">
         <v>240</v>
@@ -943,7 +943,7 @@
         <v>63</v>
       </c>
       <c r="M11" t="n">
-        <v>1.6443</v>
+        <v>1.5974</v>
       </c>
       <c r="N11" t="n">
         <v>303</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.4878</v>
+        <v>1.4136</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3728</v>
+        <v>0.3542</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0337</v>
+        <v>0.0193</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4878</v>
+        <v>1.4136</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4878</v>
+        <v>1.4136</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4878</v>
+        <v>1.4136</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4878</v>
+        <v>1.4136</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4878</v>
+        <v>1.4136</v>
       </c>
       <c r="N12" t="n">
         <v>129</v>
@@ -998,216 +998,216 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.426</v>
+        <v>1.33</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3573</v>
+        <v>0.3333</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0058</v>
+        <v>-0.0188</v>
       </c>
       <c r="E13" t="n">
-        <v>1.426</v>
+        <v>1.33</v>
       </c>
       <c r="F13" t="n">
-        <v>1.426</v>
+        <v>1.33</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.426</v>
+        <v>1.33</v>
       </c>
       <c r="I13" t="n">
-        <v>1.426</v>
+        <v>1.33</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>176</v>
+        <v>129</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.426</v>
+        <v>1.33</v>
       </c>
       <c r="N13" t="n">
-        <v>176</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.3047</v>
+        <v>1.3149</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3269</v>
+        <v>0.3295</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.049</v>
+        <v>-0.0256</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3047</v>
+        <v>1.3149</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3047</v>
+        <v>1.3149</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3047</v>
+        <v>1.3149</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3047</v>
+        <v>1.3149</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3047</v>
+        <v>1.3149</v>
       </c>
       <c r="N14" t="n">
-        <v>129</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.2694</v>
+        <v>1.2648</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3181</v>
+        <v>0.3169</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0649</v>
+        <v>-0.0484</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2694</v>
+        <v>1.2648</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2694</v>
+        <v>1.2648</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2694</v>
+        <v>1.2648</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2694</v>
+        <v>1.2648</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>111</v>
+        <v>239</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2694</v>
+        <v>1.2648</v>
       </c>
       <c r="N15" t="n">
-        <v>111</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2225</v>
+        <v>1.2456</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3063</v>
+        <v>0.3121</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0861</v>
+        <v>-0.0572</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2225</v>
+        <v>1.2456</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2225</v>
+        <v>1.2456</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2225</v>
+        <v>1.2456</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2225</v>
+        <v>1.2456</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>176</v>
+        <v>111</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2225</v>
+        <v>1.2456</v>
       </c>
       <c r="N16" t="n">
-        <v>176</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1991</v>
+        <v>1.1123</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3005</v>
+        <v>0.2787</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09669999999999999</v>
+        <v>-0.1179</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1991</v>
+        <v>1.1123</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1991</v>
+        <v>1.1123</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1991</v>
+        <v>1.1123</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1991</v>
+        <v>1.1123</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1991</v>
+        <v>1.1123</v>
       </c>
       <c r="N17" t="n">
         <v>239</v>
@@ -1228,231 +1228,231 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9644</v>
+        <v>1.0778</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2417</v>
+        <v>0.2701</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2026</v>
+        <v>-0.1336</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9644</v>
+        <v>1.0778</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9644</v>
+        <v>1.0778</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9644</v>
+        <v>1.0778</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9644</v>
+        <v>1.0778</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>239</v>
+        <v>176</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9644</v>
+        <v>1.0778</v>
       </c>
       <c r="N18" t="n">
-        <v>239</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8693</v>
+        <v>0.9406</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2178</v>
+        <v>0.2357</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2456</v>
+        <v>-0.196</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8693</v>
+        <v>0.9406</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8693</v>
+        <v>1.571</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.6304</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8693</v>
+        <v>1.571</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8693</v>
+        <v>1.571</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.6304</v>
       </c>
       <c r="K19" t="n">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8693</v>
+        <v>0.9406</v>
       </c>
       <c r="N19" t="n">
-        <v>106</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8329</v>
+        <v>0.8418</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2087</v>
+        <v>0.2109</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.262</v>
+        <v>-0.241</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8329</v>
+        <v>0.8418</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8329</v>
+        <v>0.8418</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8329</v>
+        <v>0.8418</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8329</v>
+        <v>0.8418</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8329</v>
+        <v>0.8418</v>
       </c>
       <c r="N20" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7902</v>
+        <v>0.7579</v>
       </c>
       <c r="C21" t="n">
-        <v>0.198</v>
+        <v>0.1899</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2813</v>
+        <v>-0.2792</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7902</v>
+        <v>0.7579</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7902</v>
+        <v>0.7579</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7902</v>
+        <v>0.7579</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7902</v>
+        <v>0.7579</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7902</v>
+        <v>0.7579</v>
       </c>
       <c r="N21" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7857</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1969</v>
+        <v>0.1898</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2833</v>
+        <v>-0.2793</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7857</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5068</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7211</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5068</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5068</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7211</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="L22" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7857</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>214</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7764</v>
+        <v>0.7332</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1945</v>
+        <v>0.1837</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2875</v>
+        <v>-0.2904</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7764</v>
+        <v>0.7332</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7764</v>
+        <v>0.7332</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7764</v>
+        <v>0.7332</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7764</v>
+        <v>0.7332</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7764</v>
+        <v>0.7332</v>
       </c>
       <c r="N23" t="n">
         <v>106</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.6687</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1944</v>
+        <v>0.1676</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2878</v>
+        <v>-0.3198</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.6687</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.6687</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.6687</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.6687</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.6687</v>
       </c>
       <c r="N24" t="n">
         <v>242</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6694</v>
+        <v>0.5913</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1677</v>
+        <v>0.1482</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3358</v>
+        <v>-0.355</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6694</v>
+        <v>0.5913</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6694</v>
+        <v>0.5913</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6694</v>
+        <v>0.5913</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6694</v>
+        <v>0.5913</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6694</v>
+        <v>0.5913</v>
       </c>
       <c r="N25" t="n">
         <v>176</v>
@@ -1596,185 +1596,185 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4854</v>
+        <v>0.4401</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1216</v>
+        <v>0.1103</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4189</v>
+        <v>-0.4239</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4854</v>
+        <v>0.4401</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4854</v>
+        <v>0.4401</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4854</v>
+        <v>0.4401</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4854</v>
+        <v>0.4401</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>242</v>
+        <v>111</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4854</v>
+        <v>0.4401</v>
       </c>
       <c r="N26" t="n">
-        <v>242</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4501</v>
+        <v>0.347</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1128</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4348</v>
+        <v>-0.4662</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4501</v>
+        <v>0.347</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4501</v>
+        <v>0.347</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4501</v>
+        <v>0.347</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4501</v>
+        <v>0.347</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>111</v>
+        <v>242</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4501</v>
+        <v>0.347</v>
       </c>
       <c r="N27" t="n">
-        <v>111</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.193</v>
+        <v>0.2661</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0484</v>
+        <v>0.0667</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.5031</v>
       </c>
       <c r="E28" t="n">
-        <v>0.193</v>
+        <v>0.2661</v>
       </c>
       <c r="F28" t="n">
-        <v>0.193</v>
+        <v>0.7624</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.4963</v>
       </c>
       <c r="H28" t="n">
-        <v>0.193</v>
+        <v>0.7624</v>
       </c>
       <c r="I28" t="n">
-        <v>0.193</v>
+        <v>0.7624</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.4963</v>
       </c>
       <c r="K28" t="n">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M28" t="n">
-        <v>0.193</v>
+        <v>0.2660999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>106</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1706</v>
+        <v>0.1669</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0427</v>
+        <v>0.0418</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.5482</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1706</v>
+        <v>0.1669</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1706</v>
+        <v>0.1669</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1706</v>
+        <v>0.1669</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1706</v>
+        <v>0.1669</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>242</v>
+        <v>106</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1706</v>
+        <v>0.1669</v>
       </c>
       <c r="N29" t="n">
-        <v>242</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1418</v>
+        <v>0.1171</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0355</v>
+        <v>0.0293</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.574</v>
+        <v>-0.5709</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1418</v>
+        <v>0.1171</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1418</v>
+        <v>0.1171</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1418</v>
+        <v>0.1171</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1418</v>
+        <v>0.1171</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1418</v>
+        <v>0.1171</v>
       </c>
       <c r="N30" t="n">
         <v>106</v>
@@ -1826,47 +1826,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0505</v>
+        <v>0.0804</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0127</v>
+        <v>0.0201</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6152</v>
+        <v>-0.5876</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0505</v>
+        <v>0.0804</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1697</v>
+        <v>0.0804</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.1192</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1697</v>
+        <v>0.0804</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1839</v>
+        <v>0.0804</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.1192</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L31" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.06470000000000001</v>
+        <v>0.0804</v>
       </c>
       <c r="N31" t="n">
-        <v>303</v>
+        <v>242</v>
       </c>
     </row>
     <row r="32">
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0339</v>
+        <v>0.0411</v>
       </c>
       <c r="C32" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0103</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6227</v>
+        <v>-0.6055</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0339</v>
+        <v>0.0411</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5735</v>
+        <v>0.6233</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.5396</v>
+        <v>-0.5822000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5735</v>
+        <v>0.6233</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6216</v>
+        <v>0.6558</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.5396</v>
+        <v>-0.5822000000000001</v>
       </c>
       <c r="K32" t="n">
         <v>240</v>
@@ -1909,7 +1909,7 @@
         <v>63</v>
       </c>
       <c r="M32" t="n">
-        <v>0.08200000000000007</v>
+        <v>0.0736</v>
       </c>
       <c r="N32" t="n">
         <v>303</v>
@@ -1918,47 +1918,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0151</v>
+        <v>0.0211</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0038</v>
+        <v>0.0053</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6448</v>
+        <v>-0.6146</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.0151</v>
+        <v>0.0211</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6185</v>
+        <v>0.1568</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.1357</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6185</v>
+        <v>0.1568</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6185</v>
+        <v>0.165</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.1357</v>
       </c>
       <c r="K33" t="n">
-        <v>151</v>
+        <v>240</v>
       </c>
       <c r="L33" t="n">
         <v>63</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.0151</v>
+        <v>0.02930000000000002</v>
       </c>
       <c r="N33" t="n">
-        <v>214</v>
+        <v>303</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.1898</v>
+        <v>-0.2172</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0476</v>
+        <v>-0.0544</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7237</v>
+        <v>-0.7231</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.1898</v>
+        <v>-0.2172</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.1898</v>
+        <v>-0.2172</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1898</v>
+        <v>-0.2172</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1898</v>
+        <v>-0.2172</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.1898</v>
+        <v>-0.2172</v>
       </c>
       <c r="N34" t="n">
         <v>129</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.448</v>
+        <v>-0.5303</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1123</v>
+        <v>-0.1329</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8403</v>
+        <v>-0.8656</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.448</v>
+        <v>-0.5303</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.448</v>
+        <v>-0.5303</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.448</v>
+        <v>-0.5303</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.448</v>
+        <v>-0.5303</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.448</v>
+        <v>-0.5303</v>
       </c>
       <c r="N35" t="n">
         <v>129</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7195</v>
+        <v>-0.7601</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1803</v>
+        <v>-0.1905</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9628</v>
+        <v>-0.9702</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7195</v>
+        <v>-0.7601</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7195</v>
+        <v>-0.7601</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7195</v>
+        <v>-0.7601</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7195</v>
+        <v>-0.7601</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7195</v>
+        <v>-0.7601</v>
       </c>
       <c r="N36" t="n">
         <v>111</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7425</v>
+        <v>-0.7672</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1861</v>
+        <v>-0.1922</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9732</v>
+        <v>-0.9734</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7425</v>
+        <v>-0.7672</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7425</v>
+        <v>-0.7672</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7425</v>
+        <v>-0.7672</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7425</v>
+        <v>-0.7672</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7425</v>
+        <v>-0.7672</v>
       </c>
       <c r="N37" t="n">
         <v>242</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.8165</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2046</v>
+        <v>-0.2166</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0066</v>
+        <v>-1.0177</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8165</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8165</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8165</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8165</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8165</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="N38" t="n">
         <v>111</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9886</v>
+        <v>-1.047</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2477</v>
+        <v>-0.2623</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0843</v>
+        <v>-1.1008</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9886</v>
+        <v>-1.047</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9886</v>
+        <v>-1.047</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9886</v>
+        <v>-1.047</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9886</v>
+        <v>-1.047</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9886</v>
+        <v>-1.047</v>
       </c>
       <c r="N39" t="n">
         <v>106</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1</v>
+        <v>-1.0515</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2506</v>
+        <v>-0.2635</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0895</v>
+        <v>-1.1029</v>
       </c>
       <c r="E40" t="n">
-        <v>-1</v>
+        <v>-1.0515</v>
       </c>
       <c r="F40" t="n">
-        <v>-1</v>
+        <v>-1.0515</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1</v>
+        <v>-1.0515</v>
       </c>
       <c r="I40" t="n">
-        <v>-1</v>
+        <v>-1.0515</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1</v>
+        <v>-1.0515</v>
       </c>
       <c r="N40" t="n">
         <v>176</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.2682</v>
+        <v>-1.2972</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3178</v>
+        <v>-0.325</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2105</v>
+        <v>-1.2147</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.2682</v>
+        <v>-1.2972</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.2682</v>
+        <v>-1.2972</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.2682</v>
+        <v>-1.2972</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.2682</v>
+        <v>-1.2972</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.2682</v>
+        <v>-1.2972</v>
       </c>
       <c r="N41" t="n">
         <v>176</v>
@@ -2429,10 +2429,10 @@
         <v>1.54</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1745</v>
+        <v>1.192</v>
       </c>
       <c r="J2" t="n">
-        <v>23.49</v>
+        <v>23.84</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.49</v>
       </c>
       <c r="I3" t="n">
-        <v>1.112</v>
+        <v>1.1012</v>
       </c>
       <c r="J3" t="n">
-        <v>22.24</v>
+        <v>22.024</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.45</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0614</v>
+        <v>1.0274</v>
       </c>
       <c r="J4" t="n">
-        <v>21.228</v>
+        <v>20.548</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0672</v>
+        <v>-0.0466</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.344</v>
+        <v>-0.9320000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.9</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4217</v>
+        <v>-0.3929</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.433999999999999</v>
+        <v>-7.858</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.23</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5567</v>
+        <v>0.5309</v>
       </c>
       <c r="J7" t="n">
-        <v>11.134</v>
+        <v>10.618</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.06</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2064</v>
+        <v>0.2027</v>
       </c>
       <c r="J8" t="n">
-        <v>4.128</v>
+        <v>4.054</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.458</v>
+        <v>-1.748</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.58</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4307</v>
+        <v>-0.4414</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.614000000000001</v>
+        <v>-8.827999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.46</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5406</v>
+        <v>-0.5451</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.812</v>
+        <v>-10.902</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.92</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6387</v>
+        <v>1.7724</v>
       </c>
       <c r="J12" t="n">
-        <v>34.4127</v>
+        <v>37.2204</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.3</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7796</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>16.3716</v>
+        <v>15.6114</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.23</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6219</v>
+        <v>0.6028</v>
       </c>
       <c r="J14" t="n">
-        <v>13.0599</v>
+        <v>12.6588</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1382</v>
+        <v>0.1596</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9022</v>
+        <v>3.3516</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.79</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.714</v>
+        <v>-0.6575</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.994</v>
+        <v>-13.8075</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1521</v>
+        <v>0.1507</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1941</v>
+        <v>3.1647</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.01</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0663</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4595</v>
+        <v>1.3923</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.87</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1531</v>
+        <v>-0.1696</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.2151</v>
+        <v>-3.5616</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.78</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2429</v>
+        <v>-0.2596</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.1009</v>
+        <v>-5.4516</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.65</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3676</v>
+        <v>-0.3807</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.7196</v>
+        <v>-7.9947</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.62</v>
       </c>
       <c r="I22" t="n">
-        <v>1.311</v>
+        <v>1.3798</v>
       </c>
       <c r="J22" t="n">
-        <v>28.842</v>
+        <v>30.3556</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.45</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0912</v>
+        <v>1.0628</v>
       </c>
       <c r="J23" t="n">
-        <v>24.0064</v>
+        <v>23.3816</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.36</v>
       </c>
       <c r="I24" t="n">
-        <v>0.948</v>
+        <v>0.8869</v>
       </c>
       <c r="J24" t="n">
-        <v>20.856</v>
+        <v>19.5118</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.65</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0316</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>-22.6952</v>
+        <v>-20.68</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.63</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.079</v>
+        <v>-0.9809</v>
       </c>
       <c r="J26" t="n">
-        <v>-23.738</v>
+        <v>-21.5798</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.13</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3519</v>
+        <v>0.3431</v>
       </c>
       <c r="J27" t="n">
-        <v>7.7418</v>
+        <v>7.5482</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.0892</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.6566</v>
+        <v>-1.9624</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.92</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.1141</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.1802</v>
+        <v>-2.5102</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.79</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.233</v>
+        <v>-0.2499</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.126</v>
+        <v>-5.4978</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.57</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.442</v>
+        <v>-0.4518</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.724</v>
+        <v>-9.9396</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.22</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4645</v>
+        <v>0.4597</v>
       </c>
       <c r="J32" t="n">
-        <v>10.6835</v>
+        <v>10.5731</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3733</v>
+        <v>0.3748</v>
       </c>
       <c r="J33" t="n">
-        <v>8.585900000000001</v>
+        <v>8.6204</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.16</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3547</v>
+        <v>0.3573</v>
       </c>
       <c r="J34" t="n">
-        <v>8.158099999999999</v>
+        <v>8.2179</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.05</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1334</v>
+        <v>0.1437</v>
       </c>
       <c r="J35" t="n">
-        <v>3.0682</v>
+        <v>3.3051</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.57</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4598</v>
+        <v>-0.4659</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.5754</v>
+        <v>-10.7157</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.41</v>
       </c>
       <c r="I37" t="n">
-        <v>1.034</v>
+        <v>0.9786</v>
       </c>
       <c r="J37" t="n">
-        <v>23.782</v>
+        <v>22.5078</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.31</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8315</v>
+        <v>0.7836</v>
       </c>
       <c r="J38" t="n">
-        <v>19.1245</v>
+        <v>18.0228</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.26</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7137</v>
+        <v>0.68</v>
       </c>
       <c r="J39" t="n">
-        <v>16.4151</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.92</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3321</v>
+        <v>-0.3169</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.6383</v>
+        <v>-7.2887</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.86</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5038</v>
+        <v>-0.4741</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.5874</v>
+        <v>-10.9043</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.28</v>
       </c>
       <c r="I42" t="n">
-        <v>0.556</v>
+        <v>0.5463</v>
       </c>
       <c r="J42" t="n">
-        <v>20.016</v>
+        <v>19.6668</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.23</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4695</v>
+        <v>0.4667</v>
       </c>
       <c r="J43" t="n">
-        <v>16.902</v>
+        <v>16.8012</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.09</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2108</v>
+        <v>0.2219</v>
       </c>
       <c r="J44" t="n">
-        <v>7.5888</v>
+        <v>7.9884</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.09</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2108</v>
+        <v>0.2219</v>
       </c>
       <c r="J45" t="n">
-        <v>7.5888</v>
+        <v>7.9884</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.71</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3353</v>
+        <v>-0.3452</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.0708</v>
+        <v>-12.4272</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.51</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1942</v>
+        <v>1.1533</v>
       </c>
       <c r="J47" t="n">
-        <v>42.9912</v>
+        <v>41.5188</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.34</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9353</v>
+        <v>0.8694</v>
       </c>
       <c r="J48" t="n">
-        <v>33.6708</v>
+        <v>31.2984</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.88</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4249</v>
+        <v>-0.4073</v>
       </c>
       <c r="J49" t="n">
-        <v>-15.2964</v>
+        <v>-14.6628</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.8</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6404</v>
+        <v>-0.6009</v>
       </c>
       <c r="J50" t="n">
-        <v>-23.0544</v>
+        <v>-21.6324</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.8</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6404</v>
+        <v>-0.6009</v>
       </c>
       <c r="J51" t="n">
-        <v>-23.0544</v>
+        <v>-21.6324</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.58</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2791</v>
+        <v>1.2448</v>
       </c>
       <c r="J52" t="n">
-        <v>29.4193</v>
+        <v>28.6304</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.15</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4592</v>
+        <v>0.4486</v>
       </c>
       <c r="J53" t="n">
-        <v>10.5616</v>
+        <v>10.3178</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.99</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.074</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>-1.702</v>
+        <v>-1.6767</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.96</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1871</v>
+        <v>-0.1845</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.3033</v>
+        <v>-4.2435</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.75</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7735</v>
+        <v>-0.7175</v>
       </c>
       <c r="J56" t="n">
-        <v>-17.7905</v>
+        <v>-16.5025</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.35</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.7013</v>
       </c>
       <c r="J57" t="n">
-        <v>16.9832</v>
+        <v>16.1299</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.95</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0696</v>
+        <v>-0.0813</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.6008</v>
+        <v>-1.8699</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.91</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1153</v>
+        <v>-0.1295</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.6519</v>
+        <v>-2.9785</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.71</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3177</v>
+        <v>-0.3313</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.3071</v>
+        <v>-7.6199</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.7</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3272</v>
+        <v>-0.3406</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.5256</v>
+        <v>-7.8338</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.86</v>
       </c>
       <c r="I62" t="n">
-        <v>1.5366</v>
+        <v>1.5306</v>
       </c>
       <c r="J62" t="n">
-        <v>29.1954</v>
+        <v>29.0814</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.54</v>
       </c>
       <c r="I63" t="n">
-        <v>1.1576</v>
+        <v>1.1282</v>
       </c>
       <c r="J63" t="n">
-        <v>21.9944</v>
+        <v>21.4358</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.46</v>
       </c>
       <c r="I64" t="n">
-        <v>1.0597</v>
+        <v>1.019</v>
       </c>
       <c r="J64" t="n">
-        <v>20.1343</v>
+        <v>19.361</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0876</v>
+        <v>-0.0609</v>
       </c>
       <c r="J65" t="n">
-        <v>-1.6644</v>
+        <v>-1.1571</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.97</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2208</v>
+        <v>-0.1988</v>
       </c>
       <c r="J66" t="n">
-        <v>-4.1952</v>
+        <v>-3.7772</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.91</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.1095</v>
       </c>
       <c r="J67" t="n">
-        <v>-1.6986</v>
+        <v>-2.0805</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.8</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2099</v>
+        <v>-0.23</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.9881</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.76</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2485</v>
+        <v>-0.2681</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.7215</v>
+        <v>-5.0939</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3131</v>
+        <v>-0.3314</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.9489</v>
+        <v>-6.2966</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.6</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3975</v>
+        <v>-0.4123</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.5525</v>
+        <v>-7.8337</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.35</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9143</v>
+        <v>0.8578</v>
       </c>
       <c r="J72" t="n">
-        <v>20.1146</v>
+        <v>18.8716</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.33</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8691</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="J73" t="n">
-        <v>19.1202</v>
+        <v>17.996</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.15</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4414</v>
+        <v>0.4366</v>
       </c>
       <c r="J74" t="n">
-        <v>9.710800000000001</v>
+        <v>9.6052</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.13</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3894</v>
+        <v>0.389</v>
       </c>
       <c r="J75" t="n">
-        <v>8.566800000000001</v>
+        <v>8.558</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.93</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3084</v>
+        <v>-0.2932</v>
       </c>
       <c r="J76" t="n">
-        <v>-6.7848</v>
+        <v>-6.4504</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.34</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6605</v>
       </c>
       <c r="J77" t="n">
-        <v>15.114</v>
+        <v>14.531</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2469</v>
+        <v>0.2528</v>
       </c>
       <c r="J78" t="n">
-        <v>5.4318</v>
+        <v>5.5616</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.08</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2054</v>
+        <v>0.2127</v>
       </c>
       <c r="J79" t="n">
-        <v>4.5188</v>
+        <v>4.6794</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.0989</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.9338</v>
+        <v>-2.1758</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.53</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4924</v>
+        <v>-0.4974</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.8328</v>
+        <v>-10.9428</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.21</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3472</v>
+        <v>0.3512</v>
       </c>
       <c r="J82" t="n">
-        <v>10.416</v>
+        <v>10.536</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.03</v>
       </c>
       <c r="I83" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0774</v>
       </c>
       <c r="J83" t="n">
-        <v>2.07</v>
+        <v>2.322</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.97</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0509</v>
+        <v>-0.0589</v>
       </c>
       <c r="J84" t="n">
-        <v>-1.527</v>
+        <v>-1.767</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.93</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1011</v>
+        <v>-0.1123</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.033</v>
+        <v>-3.369</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.91</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1241</v>
+        <v>-0.1363</v>
       </c>
       <c r="J86" t="n">
-        <v>-3.723</v>
+        <v>-4.089</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.69</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8554</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="J87" t="n">
-        <v>25.662</v>
+        <v>25.056</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.31</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4267</v>
+        <v>0.4364</v>
       </c>
       <c r="J88" t="n">
-        <v>12.801</v>
+        <v>13.092</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.86</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1892</v>
+        <v>-0.2</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.676</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.85</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1997</v>
+        <v>-0.2106</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.991</v>
+        <v>-6.318</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.82</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2305</v>
+        <v>-0.2415</v>
       </c>
       <c r="J91" t="n">
-        <v>-6.915</v>
+        <v>-7.245</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.83</v>
       </c>
       <c r="I92" t="n">
-        <v>1.568</v>
+        <v>1.5529</v>
       </c>
       <c r="J92" t="n">
-        <v>37.632</v>
+        <v>37.2696</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.24</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6369</v>
       </c>
       <c r="J93" t="n">
-        <v>15.9552</v>
+        <v>15.2856</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.02</v>
       </c>
       <c r="I94" t="n">
-        <v>0.0585</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="J94" t="n">
-        <v>1.404</v>
+        <v>1.8096</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.93</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3026</v>
+        <v>-0.2892</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.2624</v>
+        <v>-6.9408</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.76</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.7663</v>
+        <v>-0.708</v>
       </c>
       <c r="J96" t="n">
-        <v>-18.3912</v>
+        <v>-16.992</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.59</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0535</v>
+        <v>1.0125</v>
       </c>
       <c r="J97" t="n">
-        <v>25.284</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.03</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0896</v>
+        <v>0.0984</v>
       </c>
       <c r="J98" t="n">
-        <v>2.1504</v>
+        <v>2.3616</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.03</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0896</v>
+        <v>0.0984</v>
       </c>
       <c r="J99" t="n">
-        <v>2.1504</v>
+        <v>2.3616</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.84</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2</v>
+        <v>-0.2132</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.8</v>
+        <v>-5.1168</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.58</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4489</v>
+        <v>-0.4557</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.7736</v>
+        <v>-10.9368</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.45</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>0.5978</v>
       </c>
       <c r="J102" t="n">
-        <v>13.8</v>
+        <v>13.7494</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.11</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1796</v>
+        <v>0.1943</v>
       </c>
       <c r="J103" t="n">
-        <v>4.1308</v>
+        <v>4.4689</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.01</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0203</v>
+        <v>0.0273</v>
       </c>
       <c r="J104" t="n">
-        <v>0.4669</v>
+        <v>0.6279</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.93</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1071</v>
+        <v>-0.117</v>
       </c>
       <c r="J105" t="n">
-        <v>-2.4633</v>
+        <v>-2.691</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.83</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2161</v>
+        <v>-0.228</v>
       </c>
       <c r="J106" t="n">
-        <v>-4.9703</v>
+        <v>-5.244</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.62</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8939</v>
+        <v>0.8499</v>
       </c>
       <c r="J107" t="n">
-        <v>20.5597</v>
+        <v>19.5477</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.01</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0336</v>
+        <v>0.0374</v>
       </c>
       <c r="J108" t="n">
-        <v>0.7728</v>
+        <v>0.8602</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.93</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0964</v>
+        <v>-0.1087</v>
       </c>
       <c r="J109" t="n">
-        <v>-2.2172</v>
+        <v>-2.5001</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2247</v>
+        <v>-0.2391</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.1681</v>
+        <v>-5.4993</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.45</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5605</v>
+        <v>-0.5622</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.8915</v>
+        <v>-12.9306</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.2</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4698</v>
+        <v>0.4566</v>
       </c>
       <c r="J112" t="n">
-        <v>10.8054</v>
+        <v>10.5018</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.99</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0124</v>
+        <v>-0.019</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.2852</v>
+        <v>-0.437</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.86</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1678</v>
+        <v>-0.1834</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.8594</v>
+        <v>-4.2182</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.83</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1986</v>
+        <v>-0.2144</v>
       </c>
       <c r="J115" t="n">
-        <v>-4.5678</v>
+        <v>-4.9312</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.7</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3262</v>
+        <v>-0.3398</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.5026</v>
+        <v>-7.8154</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.66</v>
       </c>
       <c r="I117" t="n">
-        <v>1.3577</v>
+        <v>1.332</v>
       </c>
       <c r="J117" t="n">
-        <v>31.2271</v>
+        <v>30.636</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.39</v>
       </c>
       <c r="I118" t="n">
-        <v>1.0013</v>
+        <v>0.9418</v>
       </c>
       <c r="J118" t="n">
-        <v>23.0299</v>
+        <v>21.6614</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1702</v>
+        <v>-0.1633</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.9146</v>
+        <v>-3.7559</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.96</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2052</v>
+        <v>-0.1971</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.7196</v>
+        <v>-4.5333</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6896</v>
+        <v>-0.6403</v>
       </c>
       <c r="J121" t="n">
-        <v>-15.8608</v>
+        <v>-14.7269</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.02</v>
       </c>
       <c r="I122" t="n">
-        <v>0.079</v>
+        <v>0.0827</v>
       </c>
       <c r="J122" t="n">
-        <v>1.896</v>
+        <v>1.9848</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.99</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0152</v>
+        <v>-0.0212</v>
       </c>
       <c r="J123" t="n">
-        <v>-0.3648</v>
+        <v>-0.5088</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.96</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0584</v>
+        <v>-0.0689</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.4016</v>
+        <v>-1.6536</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0828</v>
+        <v>-0.095</v>
       </c>
       <c r="J125" t="n">
-        <v>-1.9872</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.78</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2515</v>
+        <v>-0.2663</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.036</v>
+        <v>-6.3912</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.23</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6577</v>
+        <v>0.6273</v>
       </c>
       <c r="J127" t="n">
-        <v>15.7848</v>
+        <v>15.0552</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.16</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4814</v>
+        <v>0.4695</v>
       </c>
       <c r="J128" t="n">
-        <v>11.5536</v>
+        <v>11.268</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.1</v>
       </c>
       <c r="I129" t="n">
-        <v>0.3231</v>
+        <v>0.3243</v>
       </c>
       <c r="J129" t="n">
-        <v>7.7544</v>
+        <v>7.7832</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.1</v>
       </c>
       <c r="I130" t="n">
-        <v>0.3231</v>
+        <v>0.3243</v>
       </c>
       <c r="J130" t="n">
-        <v>7.7544</v>
+        <v>7.7832</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.91</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.348</v>
+        <v>-0.3348</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.352</v>
+        <v>-8.0352</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.91</v>
       </c>
       <c r="I132" t="n">
-        <v>1.6304</v>
+        <v>1.6232</v>
       </c>
       <c r="J132" t="n">
-        <v>30.9776</v>
+        <v>30.8408</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.69</v>
       </c>
       <c r="I133" t="n">
-        <v>1.3661</v>
+        <v>1.3457</v>
       </c>
       <c r="J133" t="n">
-        <v>25.9559</v>
+        <v>25.5683</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.21</v>
       </c>
       <c r="I134" t="n">
-        <v>0.5764</v>
+        <v>0.5616</v>
       </c>
       <c r="J134" t="n">
-        <v>10.9516</v>
+        <v>10.6704</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.6603</v>
+        <v>-0.6102</v>
       </c>
       <c r="J135" t="n">
-        <v>-12.5457</v>
+        <v>-11.5938</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.62</v>
       </c>
       <c r="I136" t="n">
-        <v>-1.1242</v>
+        <v>-1.0165</v>
       </c>
       <c r="J136" t="n">
-        <v>-21.3598</v>
+        <v>-19.3135</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.13</v>
       </c>
       <c r="I137" t="n">
-        <v>0.377</v>
+        <v>0.3615</v>
       </c>
       <c r="J137" t="n">
-        <v>7.163</v>
+        <v>6.8685</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.86</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1581</v>
+        <v>-0.176</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.0039</v>
+        <v>-3.344</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.79</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2267</v>
+        <v>-0.245</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.3073</v>
+        <v>-4.655</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.74</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2748</v>
+        <v>-0.2924</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.2212</v>
+        <v>-5.5556</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.57</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4352</v>
+        <v>-0.4464</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.268800000000001</v>
+        <v>-8.4816</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.09</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2637</v>
+        <v>0.2507</v>
       </c>
       <c r="J142" t="n">
-        <v>4.7466</v>
+        <v>4.5126</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.99</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0411</v>
+        <v>0.0183</v>
       </c>
       <c r="J143" t="n">
-        <v>0.7398</v>
+        <v>0.3294</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.57</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.4215</v>
+        <v>-0.4357</v>
       </c>
       <c r="J144" t="n">
-        <v>-7.587</v>
+        <v>-7.8426</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.55</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4402</v>
+        <v>-0.4534</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.9236</v>
+        <v>-8.161199999999999</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.43</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.934200000000001</v>
+        <v>-10.044</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>2.83</v>
       </c>
       <c r="I147" t="n">
-        <v>1.4914</v>
+        <v>1.5386</v>
       </c>
       <c r="J147" t="n">
-        <v>26.8452</v>
+        <v>27.6948</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.41</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4927</v>
+        <v>0.5083</v>
       </c>
       <c r="J148" t="n">
-        <v>8.868600000000001</v>
+        <v>9.1494</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.33</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4057</v>
+        <v>0.4252</v>
       </c>
       <c r="J149" t="n">
-        <v>7.3026</v>
+        <v>7.6536</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.27</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3371</v>
+        <v>0.3592</v>
       </c>
       <c r="J150" t="n">
-        <v>6.0678</v>
+        <v>6.4656</v>
       </c>
     </row>
     <row r="151">
@@ -8429,10 +8429,10 @@
         <v>1.62</v>
       </c>
       <c r="I152" t="n">
-        <v>1.3022</v>
+        <v>1.2741</v>
       </c>
       <c r="J152" t="n">
-        <v>28.6484</v>
+        <v>28.0302</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.6</v>
       </c>
       <c r="I153" t="n">
-        <v>1.2769</v>
+        <v>1.2473</v>
       </c>
       <c r="J153" t="n">
-        <v>28.0918</v>
+        <v>27.4406</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.08</v>
       </c>
       <c r="I154" t="n">
-        <v>0.252</v>
+        <v>0.2616</v>
       </c>
       <c r="J154" t="n">
-        <v>5.544</v>
+        <v>5.7552</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.84</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5626</v>
+        <v>-0.5262</v>
       </c>
       <c r="J155" t="n">
-        <v>-12.3772</v>
+        <v>-11.5764</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.71</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.8935</v>
+        <v>-0.8189</v>
       </c>
       <c r="J156" t="n">
-        <v>-19.657</v>
+        <v>-18.0158</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.39</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7915</v>
+        <v>0.7513</v>
       </c>
       <c r="J157" t="n">
-        <v>17.413</v>
+        <v>16.5286</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.11</v>
       </c>
       <c r="I158" t="n">
-        <v>0.279</v>
+        <v>0.2809</v>
       </c>
       <c r="J158" t="n">
-        <v>6.138</v>
+        <v>6.1798</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.04</v>
       </c>
       <c r="I159" t="n">
-        <v>0.1257</v>
+        <v>0.1316</v>
       </c>
       <c r="J159" t="n">
-        <v>2.7654</v>
+        <v>2.8952</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.68</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3501</v>
+        <v>-0.362</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.7022</v>
+        <v>-7.964</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4611</v>
+        <v>-0.4683</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.1442</v>
+        <v>-10.3026</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.3</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4192</v>
+        <v>0.4284</v>
       </c>
       <c r="J162" t="n">
-        <v>11.7376</v>
+        <v>11.9952</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.346</v>
+        <v>0.3582</v>
       </c>
       <c r="J163" t="n">
-        <v>9.688000000000001</v>
+        <v>10.0296</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1637</v>
+        <v>0.1788</v>
       </c>
       <c r="J164" t="n">
-        <v>4.5836</v>
+        <v>5.0064</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.08</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1359</v>
+        <v>0.1504</v>
       </c>
       <c r="J165" t="n">
-        <v>3.8052</v>
+        <v>4.2112</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.7</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3451</v>
+        <v>-0.3547</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.662800000000001</v>
+        <v>-9.9316</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.71</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9638</v>
+        <v>0.9207</v>
       </c>
       <c r="J167" t="n">
-        <v>26.9864</v>
+        <v>25.7796</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.98</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0396</v>
+        <v>-0.0455</v>
       </c>
       <c r="J168" t="n">
-        <v>-1.1088</v>
+        <v>-1.274</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.97</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0539</v>
+        <v>-0.0611</v>
       </c>
       <c r="J169" t="n">
-        <v>-1.5092</v>
+        <v>-1.7108</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.87</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1714</v>
+        <v>-0.1837</v>
       </c>
       <c r="J170" t="n">
-        <v>-4.7992</v>
+        <v>-5.1436</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.67</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3688</v>
+        <v>-0.3784</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.3264</v>
+        <v>-10.5952</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.95</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0568</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="J172" t="n">
-        <v>-1.0792</v>
+        <v>-1.3566</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.93</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0818</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="J173" t="n">
-        <v>-1.5542</v>
+        <v>-1.8544</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.91</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1055</v>
+        <v>-0.122</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.0045</v>
+        <v>-2.318</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.7</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3153</v>
+        <v>-0.3313</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.9907</v>
+        <v>-6.2947</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3343</v>
+        <v>-0.3497</v>
       </c>
       <c r="J176" t="n">
-        <v>-6.3517</v>
+        <v>-6.6443</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>2.11</v>
       </c>
       <c r="I177" t="n">
-        <v>1.8338</v>
+        <v>1.856</v>
       </c>
       <c r="J177" t="n">
-        <v>34.8422</v>
+        <v>35.264</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.13</v>
       </c>
       <c r="I178" t="n">
-        <v>0.367</v>
+        <v>0.3735</v>
       </c>
       <c r="J178" t="n">
-        <v>6.973</v>
+        <v>7.0965</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.09</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2555</v>
+        <v>0.271</v>
       </c>
       <c r="J179" t="n">
-        <v>4.8545</v>
+        <v>5.149</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.07</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1962</v>
+        <v>0.2156</v>
       </c>
       <c r="J180" t="n">
-        <v>3.7278</v>
+        <v>4.0964</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.99</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1226</v>
+        <v>-0.1067</v>
       </c>
       <c r="J181" t="n">
-        <v>-2.3294</v>
+        <v>-2.0273</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.35</v>
       </c>
       <c r="I182" t="n">
-        <v>0.7839</v>
+        <v>0.735</v>
       </c>
       <c r="J182" t="n">
-        <v>15.678</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.85</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1713</v>
+        <v>-0.1887</v>
       </c>
       <c r="J183" t="n">
-        <v>-3.426</v>
+        <v>-3.774</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2104</v>
+        <v>-0.2281</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.208</v>
+        <v>-4.562</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.67</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3455</v>
+        <v>-0.3601</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.91</v>
+        <v>-7.202</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.55</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4574</v>
+        <v>-0.4669</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.148</v>
+        <v>-9.337999999999999</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.6</v>
       </c>
       <c r="I187" t="n">
-        <v>1.2465</v>
+        <v>1.2204</v>
       </c>
       <c r="J187" t="n">
-        <v>24.93</v>
+        <v>24.408</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.59</v>
       </c>
       <c r="I188" t="n">
-        <v>1.2342</v>
+        <v>1.2073</v>
       </c>
       <c r="J188" t="n">
-        <v>24.684</v>
+        <v>24.146</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.37</v>
       </c>
       <c r="I189" t="n">
-        <v>0.9271</v>
+        <v>0.875</v>
       </c>
       <c r="J189" t="n">
-        <v>18.542</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.17</v>
       </c>
       <c r="I190" t="n">
-        <v>0.4697</v>
+        <v>0.4672</v>
       </c>
       <c r="J190" t="n">
-        <v>9.394</v>
+        <v>9.343999999999999</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.7</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.9424</v>
+        <v>-0.8575</v>
       </c>
       <c r="J191" t="n">
-        <v>-18.848</v>
+        <v>-17.15</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>2.13</v>
       </c>
       <c r="I192" t="n">
-        <v>1.8338</v>
+        <v>1.8466</v>
       </c>
       <c r="J192" t="n">
-        <v>31.1746</v>
+        <v>31.3922</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.4</v>
       </c>
       <c r="I193" t="n">
-        <v>0.9676</v>
+        <v>0.9176</v>
       </c>
       <c r="J193" t="n">
-        <v>16.4492</v>
+        <v>15.5992</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.24</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6204</v>
+        <v>0.6065</v>
       </c>
       <c r="J194" t="n">
-        <v>10.5468</v>
+        <v>10.3105</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.15</v>
       </c>
       <c r="I195" t="n">
-        <v>0.3963</v>
+        <v>0.4053</v>
       </c>
       <c r="J195" t="n">
-        <v>6.7371</v>
+        <v>6.8901</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.0915</v>
+        <v>-0.0636</v>
       </c>
       <c r="J196" t="n">
-        <v>-1.5555</v>
+        <v>-1.0812</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.1843</v>
+        <v>-0.2079</v>
       </c>
       <c r="J197" t="n">
-        <v>-3.1331</v>
+        <v>-3.5343</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.7</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.295</v>
+        <v>-0.3157</v>
       </c>
       <c r="J198" t="n">
-        <v>-5.015</v>
+        <v>-5.3669</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.67</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3215</v>
+        <v>-0.3415</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.4655</v>
+        <v>-5.8055</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.64</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3486</v>
+        <v>-0.3677</v>
       </c>
       <c r="J200" t="n">
-        <v>-5.9262</v>
+        <v>-6.2509</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.57</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4135</v>
+        <v>-0.4295</v>
       </c>
       <c r="J201" t="n">
-        <v>-7.0295</v>
+        <v>-7.3015</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>2.41</v>
       </c>
       <c r="I202" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J202" t="n">
-        <v>25.6732</v>
+        <v>27.1208</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.79</v>
       </c>
       <c r="I203" t="n">
-        <v>1.4022</v>
+        <v>1.3984</v>
       </c>
       <c r="J203" t="n">
-        <v>19.6308</v>
+        <v>19.5776</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.55</v>
       </c>
       <c r="I204" t="n">
-        <v>1.1367</v>
+        <v>1.1128</v>
       </c>
       <c r="J204" t="n">
-        <v>15.9138</v>
+        <v>15.5792</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.46</v>
       </c>
       <c r="I205" t="n">
-        <v>1.0263</v>
+        <v>0.9882</v>
       </c>
       <c r="J205" t="n">
-        <v>14.3682</v>
+        <v>13.8348</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.19</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4405</v>
+        <v>0.4569</v>
       </c>
       <c r="J206" t="n">
-        <v>6.167</v>
+        <v>6.3966</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.99</v>
       </c>
       <c r="I207" t="n">
-        <v>0.1218</v>
+        <v>0.0738</v>
       </c>
       <c r="J207" t="n">
-        <v>1.7052</v>
+        <v>1.0332</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.8</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1815</v>
+        <v>-0.2079</v>
       </c>
       <c r="J208" t="n">
-        <v>-2.541</v>
+        <v>-2.9106</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.58</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.396</v>
+        <v>-0.4143</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.544</v>
+        <v>-5.8002</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.41</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.5558</v>
+        <v>-0.5637</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.7812</v>
+        <v>-7.8918</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.37</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5938</v>
+        <v>-0.5988</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.3132</v>
+        <v>-8.3832</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.17</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3885</v>
+        <v>0.3859</v>
       </c>
       <c r="J212" t="n">
-        <v>7.77</v>
+        <v>7.718</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.11</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2714</v>
+        <v>0.2754</v>
       </c>
       <c r="J213" t="n">
-        <v>5.428</v>
+        <v>5.508</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.95</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0742</v>
+        <v>-0.0847</v>
       </c>
       <c r="J214" t="n">
-        <v>-1.484</v>
+        <v>-1.694</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.88</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1541</v>
+        <v>-0.1677</v>
       </c>
       <c r="J215" t="n">
-        <v>-3.082</v>
+        <v>-3.354</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.8</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2369</v>
+        <v>-0.2508</v>
       </c>
       <c r="J216" t="n">
-        <v>-4.738</v>
+        <v>-5.016</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.42</v>
       </c>
       <c r="I217" t="n">
-        <v>1.029</v>
+        <v>0.9772</v>
       </c>
       <c r="J217" t="n">
-        <v>20.58</v>
+        <v>19.544</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.4</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9971</v>
+        <v>0.9417</v>
       </c>
       <c r="J218" t="n">
-        <v>19.942</v>
+        <v>18.834</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.36</v>
       </c>
       <c r="I219" t="n">
-        <v>0.9196</v>
+        <v>0.8657</v>
       </c>
       <c r="J219" t="n">
-        <v>18.392</v>
+        <v>17.314</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.16</v>
       </c>
       <c r="I220" t="n">
-        <v>0.456</v>
+        <v>0.4522</v>
       </c>
       <c r="J220" t="n">
-        <v>9.119999999999999</v>
+        <v>9.044</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.82</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6306</v>
+        <v>-0.5843</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.612</v>
+        <v>-11.686</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.13</v>
       </c>
       <c r="I222" t="n">
-        <v>0.337</v>
+        <v>0.3321</v>
       </c>
       <c r="J222" t="n">
-        <v>7.751</v>
+        <v>7.6383</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.9</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.1247</v>
+        <v>-0.1396</v>
       </c>
       <c r="J223" t="n">
-        <v>-2.8681</v>
+        <v>-3.2108</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.88</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1458</v>
+        <v>-0.1613</v>
       </c>
       <c r="J224" t="n">
-        <v>-3.3534</v>
+        <v>-3.7099</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.88</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1458</v>
+        <v>-0.1613</v>
       </c>
       <c r="J225" t="n">
-        <v>-3.3534</v>
+        <v>-3.7099</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.74</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2865</v>
+        <v>-0.3015</v>
       </c>
       <c r="J226" t="n">
-        <v>-6.5895</v>
+        <v>-6.9345</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.51</v>
       </c>
       <c r="I227" t="n">
-        <v>1.1664</v>
+        <v>1.1287</v>
       </c>
       <c r="J227" t="n">
-        <v>26.8272</v>
+        <v>25.9601</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.18</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5193</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="J228" t="n">
-        <v>11.9439</v>
+        <v>11.6518</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.06</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1954</v>
+        <v>0.2075</v>
       </c>
       <c r="J229" t="n">
-        <v>4.4942</v>
+        <v>4.7725</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.02</v>
       </c>
       <c r="I230" t="n">
-        <v>0.059</v>
+        <v>0.0757</v>
       </c>
       <c r="J230" t="n">
-        <v>1.357</v>
+        <v>1.7411</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.0369</v>
+        <v>-0.0254</v>
       </c>
       <c r="J231" t="n">
-        <v>-0.8487</v>
+        <v>-0.5842000000000001</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.15</v>
       </c>
       <c r="I232" t="n">
-        <v>0.3491</v>
+        <v>0.3492</v>
       </c>
       <c r="J232" t="n">
-        <v>8.378399999999999</v>
+        <v>8.380800000000001</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.12</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2904</v>
+        <v>0.2937</v>
       </c>
       <c r="J233" t="n">
-        <v>6.9696</v>
+        <v>7.0488</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0867</v>
+        <v>-0.0979</v>
       </c>
       <c r="J234" t="n">
-        <v>-2.0808</v>
+        <v>-2.3496</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1215</v>
+        <v>-0.1342</v>
       </c>
       <c r="J235" t="n">
-        <v>-2.916</v>
+        <v>-3.2208</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2273</v>
+        <v>-0.2412</v>
       </c>
       <c r="J236" t="n">
-        <v>-5.4552</v>
+        <v>-5.7888</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.41</v>
       </c>
       <c r="I237" t="n">
-        <v>1.0692</v>
+        <v>1.0134</v>
       </c>
       <c r="J237" t="n">
-        <v>25.6608</v>
+        <v>24.3216</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.1</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3373</v>
+        <v>0.3339</v>
       </c>
       <c r="J238" t="n">
-        <v>8.0952</v>
+        <v>8.0136</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.08</v>
       </c>
       <c r="I239" t="n">
-        <v>0.2795</v>
+        <v>0.2804</v>
       </c>
       <c r="J239" t="n">
-        <v>6.708</v>
+        <v>6.7296</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.85</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4991</v>
+        <v>-0.4763</v>
       </c>
       <c r="J240" t="n">
-        <v>-11.9784</v>
+        <v>-11.4312</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.74</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7848000000000001</v>
+        <v>-0.7298</v>
       </c>
       <c r="J241" t="n">
-        <v>-18.8352</v>
+        <v>-17.5152</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.75</v>
       </c>
       <c r="I242" t="n">
-        <v>0.8904</v>
+        <v>0.8712</v>
       </c>
       <c r="J242" t="n">
-        <v>18.6984</v>
+        <v>18.2952</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.21</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2934</v>
+        <v>0.3107</v>
       </c>
       <c r="J243" t="n">
-        <v>6.1614</v>
+        <v>6.5247</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.14</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2067</v>
+        <v>0.2249</v>
       </c>
       <c r="J244" t="n">
-        <v>4.3407</v>
+        <v>4.7229</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.08</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1231</v>
+        <v>0.1408</v>
       </c>
       <c r="J245" t="n">
-        <v>2.5851</v>
+        <v>2.9568</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.82</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2398</v>
+        <v>-0.2488</v>
       </c>
       <c r="J246" t="n">
-        <v>-5.0358</v>
+        <v>-5.2248</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.6</v>
       </c>
       <c r="I247" t="n">
-        <v>0.8683</v>
+        <v>0.8269</v>
       </c>
       <c r="J247" t="n">
-        <v>18.2343</v>
+        <v>17.3649</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.2</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3445</v>
+        <v>0.3464</v>
       </c>
       <c r="J248" t="n">
-        <v>7.2345</v>
+        <v>7.2744</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.73</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.3036</v>
+        <v>-0.3167</v>
       </c>
       <c r="J249" t="n">
-        <v>-6.3756</v>
+        <v>-6.6507</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3418</v>
+        <v>-0.3538</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.1778</v>
+        <v>-7.4298</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.61</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4164</v>
+        <v>-0.4256</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.744400000000001</v>
+        <v>-8.9376</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.15</v>
       </c>
       <c r="I252" t="n">
-        <v>0.3804</v>
+        <v>0.3721</v>
       </c>
       <c r="J252" t="n">
-        <v>8.3688</v>
+        <v>8.186199999999999</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.86</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1658</v>
+        <v>-0.1819</v>
       </c>
       <c r="J253" t="n">
-        <v>-3.6476</v>
+        <v>-4.0018</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.84</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1863</v>
+        <v>-0.2026</v>
       </c>
       <c r="J254" t="n">
-        <v>-4.0986</v>
+        <v>-4.4572</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.83</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1965</v>
+        <v>-0.2128</v>
       </c>
       <c r="J255" t="n">
-        <v>-4.323</v>
+        <v>-4.6816</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.2166</v>
+        <v>-0.2329</v>
       </c>
       <c r="J256" t="n">
-        <v>-4.7652</v>
+        <v>-5.1238</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.31</v>
       </c>
       <c r="I257" t="n">
-        <v>0.8256</v>
+        <v>0.7794</v>
       </c>
       <c r="J257" t="n">
-        <v>18.1632</v>
+        <v>17.1468</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.31</v>
       </c>
       <c r="I258" t="n">
-        <v>0.8256</v>
+        <v>0.7794</v>
       </c>
       <c r="J258" t="n">
-        <v>18.1632</v>
+        <v>17.1468</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.24</v>
       </c>
       <c r="I259" t="n">
-        <v>0.6611</v>
+        <v>0.6344</v>
       </c>
       <c r="J259" t="n">
-        <v>14.5442</v>
+        <v>13.9568</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.01</v>
       </c>
       <c r="I260" t="n">
-        <v>0.0139</v>
+        <v>0.0315</v>
       </c>
       <c r="J260" t="n">
-        <v>0.3058</v>
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.98</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.1371</v>
+        <v>-0.1295</v>
       </c>
       <c r="J261" t="n">
-        <v>-3.0162</v>
+        <v>-2.849</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.8</v>
       </c>
       <c r="I262" t="n">
-        <v>1.4867</v>
+        <v>1.4749</v>
       </c>
       <c r="J262" t="n">
-        <v>31.2207</v>
+        <v>30.9729</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.47</v>
       </c>
       <c r="I263" t="n">
-        <v>1.0843</v>
+        <v>1.0452</v>
       </c>
       <c r="J263" t="n">
-        <v>22.7703</v>
+        <v>21.9492</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.33</v>
       </c>
       <c r="I264" t="n">
-        <v>0.8398</v>
+        <v>0.7977</v>
       </c>
       <c r="J264" t="n">
-        <v>17.6358</v>
+        <v>16.7517</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.0489</v>
       </c>
       <c r="J265" t="n">
-        <v>-1.4805</v>
+        <v>-1.0269</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.85</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.5219</v>
       </c>
       <c r="J266" t="n">
-        <v>-11.844</v>
+        <v>-10.9599</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.08</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2504</v>
+        <v>0.2456</v>
       </c>
       <c r="J267" t="n">
-        <v>5.2584</v>
+        <v>5.1576</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.92</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.0975</v>
+        <v>-0.1128</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.0475</v>
+        <v>-2.3688</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.88</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1419</v>
+        <v>-0.1584</v>
       </c>
       <c r="J269" t="n">
-        <v>-2.9799</v>
+        <v>-3.3264</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.75</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2706</v>
+        <v>-0.2871</v>
       </c>
       <c r="J270" t="n">
-        <v>-5.6826</v>
+        <v>-6.0291</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.66</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3565</v>
+        <v>-0.3704</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.4865</v>
+        <v>-7.7784</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.31</v>
       </c>
       <c r="I272" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J272" t="n">
-        <v>29.3408</v>
+        <v>30.9952</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.82</v>
       </c>
       <c r="I273" t="n">
-        <v>1.4669</v>
+        <v>1.4612</v>
       </c>
       <c r="J273" t="n">
-        <v>23.4704</v>
+        <v>23.3792</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.58</v>
       </c>
       <c r="I274" t="n">
-        <v>1.1899</v>
+        <v>1.1661</v>
       </c>
       <c r="J274" t="n">
-        <v>19.0384</v>
+        <v>18.6576</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.84</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.6266</v>
+        <v>-0.5714</v>
       </c>
       <c r="J275" t="n">
-        <v>-10.0256</v>
+        <v>-9.1424</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.7045</v>
+        <v>-0.6414</v>
       </c>
       <c r="J276" t="n">
-        <v>-11.272</v>
+        <v>-10.2624</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>0.85</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.1504</v>
+        <v>-0.1725</v>
       </c>
       <c r="J277" t="n">
-        <v>-2.4064</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.3084</v>
+        <v>-0.3277</v>
       </c>
       <c r="J278" t="n">
-        <v>-4.9344</v>
+        <v>-5.2432</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3084</v>
+        <v>-0.3277</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.9344</v>
+        <v>-5.2432</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3084</v>
+        <v>-0.3277</v>
       </c>
       <c r="J280" t="n">
-        <v>-4.9344</v>
+        <v>-5.2432</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.67</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3268</v>
+        <v>-0.3456</v>
       </c>
       <c r="J281" t="n">
-        <v>-5.2288</v>
+        <v>-5.5296</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>2.02</v>
       </c>
       <c r="I282" t="n">
-        <v>1.0728</v>
+        <v>1.066</v>
       </c>
       <c r="J282" t="n">
-        <v>19.3104</v>
+        <v>19.188</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.35</v>
       </c>
       <c r="I283" t="n">
-        <v>0.4396</v>
+        <v>0.4552</v>
       </c>
       <c r="J283" t="n">
-        <v>7.9128</v>
+        <v>8.1936</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.22</v>
       </c>
       <c r="I284" t="n">
-        <v>0.2921</v>
+        <v>0.3125</v>
       </c>
       <c r="J284" t="n">
-        <v>5.2578</v>
+        <v>5.625</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.16</v>
       </c>
       <c r="I285" t="n">
-        <v>0.2168</v>
+        <v>0.2387</v>
       </c>
       <c r="J285" t="n">
-        <v>3.9024</v>
+        <v>4.2966</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.97</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="J286" t="n">
-        <v>-1.4958</v>
+        <v>-1.512</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.31</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5756</v>
+        <v>0.5486</v>
       </c>
       <c r="J287" t="n">
-        <v>10.3608</v>
+        <v>9.8748</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.91</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.0969</v>
+        <v>-0.1153</v>
       </c>
       <c r="J288" t="n">
-        <v>-1.7442</v>
+        <v>-2.0754</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.7</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.3085</v>
+        <v>-0.326</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.553</v>
+        <v>-5.868</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.53</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4678</v>
+        <v>-0.478</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.420400000000001</v>
+        <v>-8.603999999999999</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.48</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.514</v>
+        <v>-0.5214</v>
       </c>
       <c r="J291" t="n">
-        <v>-9.252000000000001</v>
+        <v>-9.385199999999999</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.25</v>
       </c>
       <c r="I292" t="n">
-        <v>0.5364</v>
+        <v>0.5224</v>
       </c>
       <c r="J292" t="n">
-        <v>12.8736</v>
+        <v>12.5376</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.04</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1201</v>
+        <v>0.1275</v>
       </c>
       <c r="J293" t="n">
-        <v>2.8824</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.92</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1095</v>
+        <v>-0.122</v>
       </c>
       <c r="J294" t="n">
-        <v>-2.628</v>
+        <v>-2.928</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.9</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.132</v>
+        <v>-0.1452</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.168</v>
+        <v>-3.4848</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.79</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2466</v>
+        <v>-0.2605</v>
       </c>
       <c r="J296" t="n">
-        <v>-5.9184</v>
+        <v>-6.252</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.5</v>
       </c>
       <c r="I297" t="n">
-        <v>1.1774</v>
+        <v>1.1361</v>
       </c>
       <c r="J297" t="n">
-        <v>28.2576</v>
+        <v>27.2664</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.38</v>
       </c>
       <c r="I298" t="n">
-        <v>1.0098</v>
+        <v>0.946</v>
       </c>
       <c r="J298" t="n">
-        <v>24.2352</v>
+        <v>22.704</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.12</v>
       </c>
       <c r="I299" t="n">
-        <v>0.3819</v>
+        <v>0.3775</v>
       </c>
       <c r="J299" t="n">
-        <v>9.1656</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.82</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.5908</v>
+        <v>-0.5563</v>
       </c>
       <c r="J300" t="n">
-        <v>-14.1792</v>
+        <v>-13.3512</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.2282</v>
+        <v>-1.1111</v>
       </c>
       <c r="J301" t="n">
-        <v>-29.4768</v>
+        <v>-26.6664</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>0.95</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.0549</v>
+        <v>-0.0699</v>
       </c>
       <c r="J302" t="n">
-        <v>-1.1529</v>
+        <v>-1.4679</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.9</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.1153</v>
+        <v>-0.1325</v>
       </c>
       <c r="J303" t="n">
-        <v>-2.4213</v>
+        <v>-2.7825</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.89</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1266</v>
+        <v>-0.1439</v>
       </c>
       <c r="J304" t="n">
-        <v>-2.6586</v>
+        <v>-3.0219</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.7</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3139</v>
+        <v>-0.3302</v>
       </c>
       <c r="J305" t="n">
-        <v>-6.5919</v>
+        <v>-6.9342</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.68</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3329</v>
+        <v>-0.3486</v>
       </c>
       <c r="J306" t="n">
-        <v>-6.9909</v>
+        <v>-7.3206</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.56</v>
       </c>
       <c r="I307" t="n">
-        <v>1.2044</v>
+        <v>1.1741</v>
       </c>
       <c r="J307" t="n">
-        <v>25.2924</v>
+        <v>24.6561</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.36</v>
       </c>
       <c r="I308" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="J308" t="n">
-        <v>19.1898</v>
+        <v>18.0894</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.25</v>
       </c>
       <c r="I309" t="n">
-        <v>0.6684</v>
+        <v>0.6443</v>
       </c>
       <c r="J309" t="n">
-        <v>14.0364</v>
+        <v>13.5303</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.22</v>
       </c>
       <c r="I310" t="n">
-        <v>0.5991</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="J310" t="n">
-        <v>12.5811</v>
+        <v>12.2262</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.88</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4735</v>
+        <v>-0.4415</v>
       </c>
       <c r="J311" t="n">
-        <v>-9.9435</v>
+        <v>-9.2715</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>0.86</v>
       </c>
       <c r="I312" t="n">
-        <v>-0.1434</v>
+        <v>-0.1647</v>
       </c>
       <c r="J312" t="n">
-        <v>-2.7246</v>
+        <v>-3.1293</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.84</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.1653</v>
+        <v>-0.1865</v>
       </c>
       <c r="J313" t="n">
-        <v>-3.1407</v>
+        <v>-3.5435</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.75</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.2561</v>
+        <v>-0.276</v>
       </c>
       <c r="J314" t="n">
-        <v>-4.8659</v>
+        <v>-5.244</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.63</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3669</v>
+        <v>-0.3836</v>
       </c>
       <c r="J315" t="n">
-        <v>-6.9711</v>
+        <v>-7.2884</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.6</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.395</v>
+        <v>-0.4103</v>
       </c>
       <c r="J316" t="n">
-        <v>-7.505</v>
+        <v>-7.7957</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.98</v>
       </c>
       <c r="I317" t="n">
-        <v>1.6917</v>
+        <v>1.6902</v>
       </c>
       <c r="J317" t="n">
-        <v>32.1423</v>
+        <v>32.1138</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.74</v>
       </c>
       <c r="I318" t="n">
-        <v>1.4099</v>
+        <v>1.3949</v>
       </c>
       <c r="J318" t="n">
-        <v>26.7881</v>
+        <v>26.5031</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.08</v>
       </c>
       <c r="I319" t="n">
-        <v>0.2188</v>
+        <v>0.2385</v>
       </c>
       <c r="J319" t="n">
-        <v>4.1572</v>
+        <v>4.5315</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.9</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.4293</v>
+        <v>-0.3983</v>
       </c>
       <c r="J320" t="n">
-        <v>-8.156700000000001</v>
+        <v>-7.5677</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.85</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5684</v>
+        <v>-0.525</v>
       </c>
       <c r="J321" t="n">
-        <v>-10.7996</v>
+        <v>-9.975</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.21</v>
       </c>
       <c r="I322" t="n">
-        <v>0.5004</v>
+        <v>0.4826</v>
       </c>
       <c r="J322" t="n">
-        <v>10.008</v>
+        <v>9.651999999999999</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.01</v>
       </c>
       <c r="I323" t="n">
-        <v>0.0631</v>
+        <v>0.0616</v>
       </c>
       <c r="J323" t="n">
-        <v>1.262</v>
+        <v>1.232</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.8</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.2256</v>
+        <v>-0.242</v>
       </c>
       <c r="J324" t="n">
-        <v>-4.512</v>
+        <v>-4.84</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.76</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.265</v>
+        <v>-0.2808</v>
       </c>
       <c r="J325" t="n">
-        <v>-5.3</v>
+        <v>-5.616</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.67</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.3513</v>
+        <v>-0.3647</v>
       </c>
       <c r="J326" t="n">
-        <v>-7.026</v>
+        <v>-7.294</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.45</v>
       </c>
       <c r="I327" t="n">
-        <v>1.0892</v>
+        <v>1.0443</v>
       </c>
       <c r="J327" t="n">
-        <v>21.784</v>
+        <v>20.886</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.2</v>
       </c>
       <c r="I328" t="n">
-        <v>0.5694</v>
+        <v>0.5514</v>
       </c>
       <c r="J328" t="n">
-        <v>11.388</v>
+        <v>11.028</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.15</v>
       </c>
       <c r="I329" t="n">
-        <v>0.4458</v>
+        <v>0.4395</v>
       </c>
       <c r="J329" t="n">
-        <v>8.916</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.05</v>
       </c>
       <c r="I330" t="n">
-        <v>0.1646</v>
+        <v>0.178</v>
       </c>
       <c r="J330" t="n">
-        <v>3.292</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.9</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.3907</v>
+        <v>-0.3711</v>
       </c>
       <c r="J331" t="n">
-        <v>-7.814</v>
+        <v>-7.422</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.83</v>
       </c>
       <c r="I332" t="n">
-        <v>1.5171</v>
+        <v>1.5076</v>
       </c>
       <c r="J332" t="n">
-        <v>30.342</v>
+        <v>30.152</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.43</v>
       </c>
       <c r="I333" t="n">
-        <v>1.0284</v>
+        <v>0.98</v>
       </c>
       <c r="J333" t="n">
-        <v>20.568</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.33</v>
       </c>
       <c r="I334" t="n">
-        <v>0.8365</v>
+        <v>0.7955</v>
       </c>
       <c r="J334" t="n">
-        <v>16.73</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.2</v>
       </c>
       <c r="I335" t="n">
-        <v>0.5399</v>
+        <v>0.5313</v>
       </c>
       <c r="J335" t="n">
-        <v>10.798</v>
+        <v>10.626</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.75</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.8249</v>
+        <v>-0.7537</v>
       </c>
       <c r="J336" t="n">
-        <v>-16.498</v>
+        <v>-15.074</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.15</v>
       </c>
       <c r="I337" t="n">
-        <v>0.41</v>
+        <v>0.394</v>
       </c>
       <c r="J337" t="n">
-        <v>8.199999999999999</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.85</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.1703</v>
+        <v>-0.1879</v>
       </c>
       <c r="J338" t="n">
-        <v>-3.406</v>
+        <v>-3.758</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.8</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.2188</v>
+        <v>-0.2368</v>
       </c>
       <c r="J339" t="n">
-        <v>-4.376</v>
+        <v>-4.736</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.73</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2866</v>
+        <v>-0.3034</v>
       </c>
       <c r="J340" t="n">
-        <v>-5.732</v>
+        <v>-6.068</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.64</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3721</v>
+        <v>-0.3859</v>
       </c>
       <c r="J341" t="n">
-        <v>-7.442</v>
+        <v>-7.718</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>2.17</v>
       </c>
       <c r="I342" t="n">
-        <v>1.8338</v>
+        <v>1.9272</v>
       </c>
       <c r="J342" t="n">
-        <v>44.0112</v>
+        <v>46.2528</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.79</v>
       </c>
       <c r="I343" t="n">
-        <v>1.4783</v>
+        <v>1.4654</v>
       </c>
       <c r="J343" t="n">
-        <v>35.4792</v>
+        <v>35.1696</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.21</v>
       </c>
       <c r="I344" t="n">
-        <v>0.5705</v>
+        <v>0.5575</v>
       </c>
       <c r="J344" t="n">
-        <v>13.692</v>
+        <v>13.38</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.82</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.641</v>
+        <v>-0.5916</v>
       </c>
       <c r="J345" t="n">
-        <v>-15.384</v>
+        <v>-14.1984</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.4</v>
       </c>
       <c r="I346" t="n">
-        <v>-1.6223</v>
+        <v>-1.441</v>
       </c>
       <c r="J346" t="n">
-        <v>-38.9352</v>
+        <v>-34.584</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.22</v>
       </c>
       <c r="I347" t="n">
-        <v>0.4793</v>
+        <v>0.4705</v>
       </c>
       <c r="J347" t="n">
-        <v>11.5032</v>
+        <v>11.292</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.2</v>
       </c>
       <c r="I348" t="n">
-        <v>0.4426</v>
+        <v>0.4366</v>
       </c>
       <c r="J348" t="n">
-        <v>10.6224</v>
+        <v>10.4784</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.13</v>
       </c>
       <c r="I349" t="n">
-        <v>0.3096</v>
+        <v>0.312</v>
       </c>
       <c r="J349" t="n">
-        <v>7.4304</v>
+        <v>7.488</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.84</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.1969</v>
+        <v>-0.2108</v>
       </c>
       <c r="J350" t="n">
-        <v>-4.7256</v>
+        <v>-5.0592</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.55</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4734</v>
+        <v>-0.4795</v>
       </c>
       <c r="J351" t="n">
-        <v>-11.3616</v>
+        <v>-11.508</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7993/event_7993_evp_summary.xlsx
+++ b/database/event/7993/event_7993_evp_summary.xlsx
@@ -496,40 +496,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.6171</v>
+        <v>8.8621</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9086</v>
+        <v>2.2206</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8433</v>
+        <v>3.3447</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6171</v>
+        <v>8.8621</v>
       </c>
       <c r="F2" t="n">
-        <v>5.3786</v>
+        <v>2.1844</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2385</v>
+        <v>6.1908</v>
       </c>
       <c r="H2" t="n">
-        <v>9.0472</v>
+        <v>2.1844</v>
       </c>
       <c r="I2" t="n">
-        <v>9.0472</v>
+        <v>2.2984</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2385</v>
+        <v>8.0586</v>
       </c>
       <c r="K2" t="n">
-        <v>151</v>
+        <v>76</v>
       </c>
       <c r="L2" t="n">
-        <v>63</v>
+        <v>138</v>
       </c>
       <c r="M2" t="n">
-        <v>11.2857</v>
+        <v>10.357</v>
       </c>
       <c r="N2" t="n">
         <v>214</v>
@@ -542,40 +542,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.1428</v>
+        <v>6.9547</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5392</v>
+        <v>1.7427</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1721</v>
+        <v>2.4927</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1428</v>
+        <v>6.9547</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4498</v>
+        <v>0.4383</v>
       </c>
       <c r="G3" t="n">
-        <v>2.693</v>
+        <v>6.1908</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8255</v>
+        <v>0.4383</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8255</v>
+        <v>0.4612</v>
       </c>
       <c r="J3" t="n">
-        <v>2.693</v>
+        <v>6.5946</v>
       </c>
       <c r="K3" t="n">
-        <v>151</v>
+        <v>76</v>
       </c>
       <c r="L3" t="n">
-        <v>63</v>
+        <v>138</v>
       </c>
       <c r="M3" t="n">
-        <v>7.5185</v>
+        <v>7.0558</v>
       </c>
       <c r="N3" t="n">
         <v>214</v>
@@ -584,185 +584,185 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.0729</v>
+        <v>6.2834</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2711</v>
+        <v>1.5744</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6851</v>
+        <v>2.1928</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0729</v>
+        <v>6.2834</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9673</v>
+        <v>1.9772</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1056</v>
+        <v>4.209</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9673</v>
+        <v>1.9772</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9673</v>
+        <v>2.0282</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1056</v>
+        <v>4.209</v>
       </c>
       <c r="K4" t="n">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="L4" t="n">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="M4" t="n">
-        <v>5.0729</v>
+        <v>6.2372</v>
       </c>
       <c r="N4" t="n">
-        <v>214</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.375</v>
+        <v>4.7427</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0963</v>
+        <v>1.1884</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3674</v>
+        <v>1.5046</v>
       </c>
       <c r="E5" t="n">
-        <v>4.375</v>
+        <v>4.7427</v>
       </c>
       <c r="F5" t="n">
-        <v>4.375</v>
+        <v>-0.1334</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>4.8841</v>
       </c>
       <c r="H5" t="n">
-        <v>6.8505</v>
+        <v>-0.1334</v>
       </c>
       <c r="I5" t="n">
-        <v>6.8505</v>
+        <v>-0.1404</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>4.8841</v>
       </c>
       <c r="K5" t="n">
-        <v>239</v>
+        <v>76</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="M5" t="n">
-        <v>6.8505</v>
+        <v>4.7437</v>
       </c>
       <c r="N5" t="n">
-        <v>239</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.1383</v>
+        <v>3.6757</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7864</v>
+        <v>0.921</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8044</v>
+        <v>1.028</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1383</v>
+        <v>3.6757</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1383</v>
+        <v>2.6336</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.8639</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1439</v>
+        <v>3.0392</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1439</v>
+        <v>3.5404</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.8639</v>
       </c>
       <c r="K6" t="n">
-        <v>239</v>
+        <v>144</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1439</v>
+        <v>4.4043</v>
       </c>
       <c r="N6" t="n">
-        <v>239</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.9795</v>
+        <v>3.5776</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7466</v>
+        <v>0.8964</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7321</v>
+        <v>0.9842</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9795</v>
+        <v>3.5776</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5201</v>
+        <v>-0.2134</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5406</v>
+        <v>3.8434</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9796</v>
+        <v>-0.2134</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2395</v>
+        <v>-0.2189</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5406</v>
+        <v>3.8434</v>
       </c>
       <c r="K7" t="n">
-        <v>240</v>
+        <v>135</v>
       </c>
       <c r="L7" t="n">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6989</v>
+        <v>3.6245</v>
       </c>
       <c r="N7" t="n">
-        <v>303</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8">
@@ -772,40 +772,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5455</v>
+        <v>2.4472</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6378</v>
+        <v>0.6132</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5346</v>
+        <v>0.4793</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5455</v>
+        <v>2.4472</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5455</v>
+        <v>-0.5613</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2.9486</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8464</v>
+        <v>-0.5613</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8464</v>
+        <v>-0.5613</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2.9486</v>
       </c>
       <c r="K8" t="n">
-        <v>242</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8464</v>
+        <v>2.3873</v>
       </c>
       <c r="N8" t="n">
         <v>242</v>
@@ -818,40 +818,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3921</v>
+        <v>2.4079</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5994</v>
+        <v>0.6034</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4647</v>
+        <v>0.4617</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3921</v>
+        <v>2.4079</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5382</v>
+        <v>1.4506</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1461</v>
+        <v>0.9949</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8304</v>
+        <v>1.4506</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9781</v>
+        <v>1.6898</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1461</v>
+        <v>0.9949</v>
       </c>
       <c r="K9" t="n">
-        <v>240</v>
+        <v>144</v>
       </c>
       <c r="L9" t="n">
-        <v>63</v>
+        <v>159</v>
       </c>
       <c r="M9" t="n">
-        <v>2.832</v>
+        <v>2.6847</v>
       </c>
       <c r="N9" t="n">
         <v>303</v>
@@ -864,40 +864,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1718</v>
+        <v>2.0935</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5442</v>
+        <v>0.5246</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3644</v>
+        <v>0.3213</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1718</v>
+        <v>2.0935</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1718</v>
+        <v>0.9507</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1718</v>
+        <v>0.9507</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1718</v>
+        <v>0.9752</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1718</v>
+        <v>1.9122</v>
       </c>
       <c r="N10" t="n">
         <v>239</v>
@@ -906,277 +906,277 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5137</v>
+        <v>1.6683</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3793</v>
+        <v>0.418</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0649</v>
+        <v>0.1314</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5137</v>
+        <v>1.6683</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6042</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0905</v>
+        <v>1.1827</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6042</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6879</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0905</v>
+        <v>1.1827</v>
       </c>
       <c r="K11" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>63</v>
+        <v>129</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5974</v>
+        <v>1.1827</v>
       </c>
       <c r="N11" t="n">
-        <v>303</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.4136</v>
+        <v>1.2794</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3542</v>
+        <v>0.3206</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0193</v>
+        <v>-0.0423</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4136</v>
+        <v>1.2794</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4136</v>
+        <v>0.671</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4136</v>
+        <v>0.671</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4136</v>
+        <v>0.706</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4136</v>
+        <v>1.2619</v>
       </c>
       <c r="N12" t="n">
-        <v>129</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.33</v>
+        <v>1.1688</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3333</v>
+        <v>0.2929</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0188</v>
+        <v>-0.0917</v>
       </c>
       <c r="E13" t="n">
-        <v>1.33</v>
+        <v>1.1688</v>
       </c>
       <c r="F13" t="n">
-        <v>1.33</v>
+        <v>0.4712</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.7896</v>
       </c>
       <c r="H13" t="n">
-        <v>1.33</v>
+        <v>0.4712</v>
       </c>
       <c r="I13" t="n">
-        <v>1.33</v>
+        <v>0.4833</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.7896</v>
       </c>
       <c r="K13" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="M13" t="n">
-        <v>1.33</v>
+        <v>1.2729</v>
       </c>
       <c r="N13" t="n">
-        <v>129</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.3149</v>
+        <v>1.1664</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3295</v>
+        <v>0.2923</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0256</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3149</v>
+        <v>1.1664</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3149</v>
+        <v>0.4046</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.828</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3149</v>
+        <v>0.4046</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3149</v>
+        <v>0.415</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.828</v>
       </c>
       <c r="K14" t="n">
-        <v>176</v>
+        <v>67</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3149</v>
+        <v>1.243</v>
       </c>
       <c r="N14" t="n">
-        <v>176</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.2648</v>
+        <v>1.1391</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3169</v>
+        <v>0.2854</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0484</v>
+        <v>-0.105</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2648</v>
+        <v>1.1391</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2648</v>
+        <v>1.7773</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.6203</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2648</v>
+        <v>1.7773</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2648</v>
+        <v>2.0704</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.6203</v>
       </c>
       <c r="K15" t="n">
-        <v>239</v>
+        <v>144</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2648</v>
+        <v>1.4501</v>
       </c>
       <c r="N15" t="n">
-        <v>239</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2456</v>
+        <v>1.1253</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3121</v>
+        <v>0.282</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0572</v>
+        <v>-0.1112</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2456</v>
+        <v>1.1253</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2456</v>
+        <v>0.2246</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.5954</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2456</v>
+        <v>0.2246</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2456</v>
+        <v>0.2246</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.5954</v>
       </c>
       <c r="K16" t="n">
-        <v>111</v>
+        <v>43</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2456</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17">
@@ -1186,40 +1186,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1123</v>
+        <v>1.0983</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2787</v>
+        <v>0.2752</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1179</v>
+        <v>-0.1232</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1123</v>
+        <v>1.0983</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1123</v>
+        <v>0.3929</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1123</v>
+        <v>0.3929</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1123</v>
+        <v>0.403</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1123</v>
+        <v>0.9650000000000001</v>
       </c>
       <c r="N17" t="n">
         <v>239</v>
@@ -1228,277 +1228,277 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0778</v>
+        <v>1.0659</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2701</v>
+        <v>0.2671</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1336</v>
+        <v>-0.1377</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0778</v>
+        <v>1.0659</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0778</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
+        <v>1.2165</v>
+      </c>
+      <c r="H18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="n">
-        <v>1.0778</v>
-      </c>
       <c r="I18" t="n">
-        <v>1.0778</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
+        <v>1.2165</v>
+      </c>
+      <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="K18" t="n">
-        <v>176</v>
-      </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0778</v>
+        <v>1.2165</v>
       </c>
       <c r="N18" t="n">
-        <v>176</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9406</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2357</v>
+        <v>0.2343</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.196</v>
+        <v>-0.1962</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9406</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>1.571</v>
+        <v>2.0331</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6304</v>
+        <v>-1.0614</v>
       </c>
       <c r="H19" t="n">
-        <v>1.571</v>
+        <v>2.0331</v>
       </c>
       <c r="I19" t="n">
-        <v>1.571</v>
+        <v>2.1392</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6304</v>
+        <v>-1.0614</v>
       </c>
       <c r="K19" t="n">
-        <v>151</v>
+        <v>67</v>
       </c>
       <c r="L19" t="n">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9406</v>
+        <v>1.0778</v>
       </c>
       <c r="N19" t="n">
-        <v>214</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8418</v>
+        <v>0.8348</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2109</v>
+        <v>0.2092</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.241</v>
+        <v>-0.2409</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8418</v>
+        <v>0.8348</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8418</v>
+        <v>0.511</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.2251</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8418</v>
+        <v>0.511</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8418</v>
+        <v>0.5242</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.2251</v>
       </c>
       <c r="K20" t="n">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8418</v>
+        <v>0.7493</v>
       </c>
       <c r="N20" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7579</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1899</v>
+        <v>0.1954</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2792</v>
+        <v>-0.2655</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7579</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7579</v>
+        <v>-0.3904</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.9766</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7579</v>
+        <v>-0.3904</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7579</v>
+        <v>-0.3904</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.9766</v>
       </c>
       <c r="K21" t="n">
-        <v>111</v>
+        <v>43</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7579</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.5919</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1898</v>
+        <v>0.1483</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2793</v>
+        <v>-0.3494</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.5919</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7576000000000001</v>
+        <v>-0.0347</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.7986</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7576000000000001</v>
+        <v>-0.0347</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7576000000000001</v>
+        <v>-0.0365</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.7986</v>
       </c>
       <c r="K22" t="n">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.7621</v>
       </c>
       <c r="N22" t="n">
-        <v>129</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7332</v>
+        <v>0.5112</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1837</v>
+        <v>0.1281</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2904</v>
+        <v>-0.3855</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7332</v>
+        <v>0.5112</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7332</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
+        <v>0.6103</v>
+      </c>
+      <c r="H23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="n">
-        <v>0.7332</v>
-      </c>
       <c r="I23" t="n">
-        <v>0.7332</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
+        <v>0.6103</v>
+      </c>
+      <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="K23" t="n">
-        <v>106</v>
-      </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7332</v>
+        <v>0.6103</v>
       </c>
       <c r="N23" t="n">
-        <v>106</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24">
@@ -1508,40 +1508,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6687</v>
+        <v>0.5006</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1676</v>
+        <v>0.1254</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3198</v>
+        <v>-0.3902</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6687</v>
+        <v>0.5006</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6687</v>
+        <v>0.3699</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6687</v>
+        <v>0.3699</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6687</v>
+        <v>0.3699</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>242</v>
+        <v>42</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6687</v>
+        <v>0.4603</v>
       </c>
       <c r="N24" t="n">
         <v>242</v>
@@ -1554,40 +1554,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5913</v>
+        <v>0.495</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1482</v>
+        <v>0.124</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.355</v>
+        <v>-0.3927</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5913</v>
+        <v>0.495</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5913</v>
+        <v>0.5158</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.0429</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5913</v>
+        <v>0.5158</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5913</v>
+        <v>0.5427</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.0429</v>
       </c>
       <c r="K25" t="n">
-        <v>176</v>
+        <v>67</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5913</v>
+        <v>0.5856</v>
       </c>
       <c r="N25" t="n">
         <v>176</v>
@@ -1600,37 +1600,37 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4401</v>
+        <v>0.3272</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1103</v>
+        <v>0.082</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4239</v>
+        <v>-0.4677</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4401</v>
+        <v>0.3272</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4401</v>
+        <v>0.3081</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.1241</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4401</v>
+        <v>0.3081</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4401</v>
+        <v>0.316</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.1241</v>
       </c>
       <c r="K26" t="n">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M26" t="n">
         <v>0.4401</v>
@@ -1642,139 +1642,139 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.347</v>
+        <v>0.3201</v>
       </c>
       <c r="C27" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4662</v>
+        <v>-0.4708</v>
       </c>
       <c r="E27" t="n">
-        <v>0.347</v>
+        <v>0.3201</v>
       </c>
       <c r="F27" t="n">
-        <v>0.347</v>
+        <v>0.2474</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.0805</v>
       </c>
       <c r="H27" t="n">
-        <v>0.347</v>
+        <v>0.2474</v>
       </c>
       <c r="I27" t="n">
-        <v>0.347</v>
+        <v>0.2474</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.0805</v>
       </c>
       <c r="K27" t="n">
-        <v>242</v>
+        <v>43</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M27" t="n">
-        <v>0.347</v>
+        <v>0.1669</v>
       </c>
       <c r="N27" t="n">
-        <v>242</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2661</v>
+        <v>0.2066</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0667</v>
+        <v>0.0518</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5031</v>
+        <v>-0.5215</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2661</v>
+        <v>0.2066</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7624</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4963</v>
+        <v>0.7033</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7624</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7624</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4963</v>
+        <v>0.7033</v>
       </c>
       <c r="K28" t="n">
-        <v>151</v>
+        <v>42</v>
       </c>
       <c r="L28" t="n">
-        <v>63</v>
+        <v>200</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2660999999999999</v>
+        <v>0.1615000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>214</v>
+        <v>242</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1669</v>
+        <v>-0.0759</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0418</v>
+        <v>-0.019</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5482</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1669</v>
+        <v>-0.0759</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1669</v>
+        <v>2.0406</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-2.1251</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1669</v>
+        <v>2.0406</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1669</v>
+        <v>2.3771</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-2.1251</v>
       </c>
       <c r="K29" t="n">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1669</v>
+        <v>0.2519999999999998</v>
       </c>
       <c r="N29" t="n">
-        <v>106</v>
+        <v>303</v>
       </c>
     </row>
     <row r="30">
@@ -1784,40 +1784,40 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1171</v>
+        <v>-0.1298</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0293</v>
+        <v>-0.0325</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5709</v>
+        <v>-0.6718</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1171</v>
+        <v>-0.1298</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1171</v>
+        <v>0.1141</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.0024</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1171</v>
+        <v>0.1141</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1171</v>
+        <v>0.1141</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.0024</v>
       </c>
       <c r="K30" t="n">
-        <v>106</v>
+        <v>43</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1171</v>
+        <v>0.1117</v>
       </c>
       <c r="N30" t="n">
         <v>106</v>
@@ -1830,40 +1830,40 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0804</v>
+        <v>-0.1399</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0201</v>
+        <v>-0.0351</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5876</v>
+        <v>-0.6763</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0804</v>
+        <v>-0.1399</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0804</v>
+        <v>-0.1908</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.1182</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0804</v>
+        <v>-0.1908</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0804</v>
+        <v>-0.1908</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.1182</v>
       </c>
       <c r="K31" t="n">
-        <v>242</v>
+        <v>42</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0804</v>
+        <v>-0.0726</v>
       </c>
       <c r="N31" t="n">
         <v>242</v>
@@ -1872,47 +1872,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0411</v>
+        <v>-0.1584</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0103</v>
+        <v>-0.0397</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6055</v>
+        <v>-0.6846</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0411</v>
+        <v>-0.1584</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6233</v>
+        <v>0.9643</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.8472</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6233</v>
+        <v>0.9643</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6558</v>
+        <v>1.0146</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.8472</v>
       </c>
       <c r="K32" t="n">
-        <v>240</v>
+        <v>76</v>
       </c>
       <c r="L32" t="n">
-        <v>63</v>
+        <v>138</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0736</v>
+        <v>0.1674</v>
       </c>
       <c r="N32" t="n">
-        <v>303</v>
+        <v>214</v>
       </c>
     </row>
     <row r="33">
@@ -1922,40 +1922,40 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0211</v>
+        <v>-0.3186</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0053</v>
+        <v>-0.0798</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6146</v>
+        <v>-0.7561</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0211</v>
+        <v>-0.3186</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1568</v>
+        <v>0.9179</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.1357</v>
+        <v>-1.0721</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1568</v>
+        <v>0.9179</v>
       </c>
       <c r="I33" t="n">
-        <v>0.165</v>
+        <v>1.0693</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.1357</v>
+        <v>-1.0721</v>
       </c>
       <c r="K33" t="n">
-        <v>240</v>
+        <v>144</v>
       </c>
       <c r="L33" t="n">
-        <v>63</v>
+        <v>159</v>
       </c>
       <c r="M33" t="n">
-        <v>0.02930000000000002</v>
+        <v>-0.002800000000000136</v>
       </c>
       <c r="N33" t="n">
         <v>303</v>
@@ -1968,40 +1968,40 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.2172</v>
+        <v>-0.6129</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0544</v>
+        <v>-0.1536</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7231</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.2172</v>
+        <v>-0.6129</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2172</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
+        <v>-0.3645</v>
+      </c>
+      <c r="H34" t="n">
         <v>0</v>
       </c>
-      <c r="H34" t="n">
-        <v>-0.2172</v>
-      </c>
       <c r="I34" t="n">
-        <v>-0.2172</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
+        <v>-0.3645</v>
+      </c>
+      <c r="K34" t="n">
         <v>0</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>129</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" t="n">
-        <v>-0.2172</v>
+        <v>-0.3645</v>
       </c>
       <c r="N34" t="n">
         <v>129</v>
@@ -2010,90 +2010,90 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5303</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1329</v>
+        <v>-0.1775</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8656</v>
+        <v>-0.9302</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5303</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5303</v>
+        <v>-0.1593</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.5967</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5303</v>
+        <v>-0.1593</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5303</v>
+        <v>-0.1634</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.5967</v>
       </c>
       <c r="K35" t="n">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5303</v>
+        <v>-0.7601</v>
       </c>
       <c r="N35" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7601</v>
+        <v>-0.9326</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1905</v>
+        <v>-0.2337</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9702</v>
+        <v>-1.0304</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7601</v>
+        <v>-0.9326</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7601</v>
+        <v>-0.0795</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.7829</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7601</v>
+        <v>-0.0795</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7601</v>
+        <v>-0.0815</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.7829</v>
       </c>
       <c r="K36" t="n">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7601</v>
+        <v>-0.8644000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>111</v>
@@ -2102,182 +2102,182 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kauez</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7672</v>
+        <v>-0.9708</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1922</v>
+        <v>-0.2433</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9734</v>
+        <v>-1.0475</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7672</v>
+        <v>-0.9708</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7672</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
+        <v>-0.6147</v>
+      </c>
+      <c r="H37" t="n">
         <v>0</v>
       </c>
-      <c r="H37" t="n">
-        <v>-0.7672</v>
-      </c>
       <c r="I37" t="n">
-        <v>-0.7672</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
+        <v>-0.6147</v>
+      </c>
+      <c r="K37" t="n">
         <v>0</v>
       </c>
-      <c r="K37" t="n">
-        <v>242</v>
-      </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7672</v>
+        <v>-0.6147</v>
       </c>
       <c r="N37" t="n">
-        <v>242</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-1.1737</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2166</v>
+        <v>-0.2941</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0177</v>
+        <v>-1.1381</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-1.1737</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.0308</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-1.0191</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.0308</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.0324</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-1.0191</v>
       </c>
       <c r="K38" t="n">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-1.0515</v>
       </c>
       <c r="N38" t="n">
-        <v>111</v>
+        <v>176</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>kauez</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.047</v>
+        <v>-1.1786</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2623</v>
+        <v>-0.2953</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1008</v>
+        <v>-1.1403</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.047</v>
+        <v>-1.1786</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.047</v>
+        <v>-0.6087</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.4159</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.047</v>
+        <v>-0.6087</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.047</v>
+        <v>-0.6087</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.4159</v>
       </c>
       <c r="K39" t="n">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.047</v>
+        <v>-1.0246</v>
       </c>
       <c r="N39" t="n">
-        <v>106</v>
+        <v>242</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.0515</v>
+        <v>-1.251</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2635</v>
+        <v>-0.3135</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1029</v>
+        <v>-1.1726</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.0515</v>
+        <v>-1.251</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.0515</v>
+        <v>-0.7237</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-0.5357</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.0515</v>
+        <v>-0.7237</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.0515</v>
+        <v>-0.7615</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-0.5357</v>
       </c>
       <c r="K40" t="n">
-        <v>176</v>
+        <v>67</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.0515</v>
+        <v>-1.2972</v>
       </c>
       <c r="N40" t="n">
         <v>176</v>
@@ -2286,47 +2286,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.2972</v>
+        <v>-1.3804</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.325</v>
+        <v>-0.3459</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2147</v>
+        <v>-1.2304</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.2972</v>
+        <v>-1.3804</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.2972</v>
+        <v>-0.4692</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-0.5778</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.2972</v>
+        <v>-0.4692</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.2972</v>
+        <v>-0.4692</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-0.5778</v>
       </c>
       <c r="K41" t="n">
-        <v>176</v>
+        <v>43</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.2972</v>
+        <v>-1.047</v>
       </c>
       <c r="N41" t="n">
-        <v>176</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -6429,10 +6429,10 @@
         <v>1.45</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5978</v>
+        <v>0.5563</v>
       </c>
       <c r="J102" t="n">
-        <v>13.7494</v>
+        <v>12.7949</v>
       </c>
     </row>
     <row r="103">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -6629,10 +6629,10 @@
         <v>1.62</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8499</v>
+        <v>0.7427</v>
       </c>
       <c r="J107" t="n">
-        <v>19.5477</v>
+        <v>17.0821</v>
       </c>
     </row>
     <row r="108">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -6829,10 +6829,10 @@
         <v>1.2</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4566</v>
+        <v>0.4509</v>
       </c>
       <c r="J112" t="n">
-        <v>10.5018</v>
+        <v>10.3707</v>
       </c>
     </row>
     <row r="113">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -7029,10 +7029,10 @@
         <v>1.66</v>
       </c>
       <c r="I117" t="n">
-        <v>1.332</v>
+        <v>1.1847</v>
       </c>
       <c r="J117" t="n">
-        <v>30.636</v>
+        <v>27.2481</v>
       </c>
     </row>
     <row r="118">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -7069,10 +7069,10 @@
         <v>1.39</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9418</v>
+        <v>0.8115</v>
       </c>
       <c r="J118" t="n">
-        <v>21.6614</v>
+        <v>18.6645</v>
       </c>
     </row>
     <row r="119">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -7429,10 +7429,10 @@
         <v>1.23</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6273</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="J127" t="n">
-        <v>15.0552</v>
+        <v>13.8744</v>
       </c>
     </row>
     <row r="128">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -7469,10 +7469,10 @@
         <v>1.16</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4695</v>
+        <v>0.4611</v>
       </c>
       <c r="J128" t="n">
-        <v>11.268</v>
+        <v>11.0664</v>
       </c>
     </row>
     <row r="129">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -7629,10 +7629,10 @@
         <v>1.91</v>
       </c>
       <c r="I132" t="n">
-        <v>1.6232</v>
+        <v>1.4759</v>
       </c>
       <c r="J132" t="n">
-        <v>30.8408</v>
+        <v>28.0421</v>
       </c>
     </row>
     <row r="133">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -7669,10 +7669,10 @@
         <v>1.69</v>
       </c>
       <c r="I133" t="n">
-        <v>1.3457</v>
+        <v>1.1984</v>
       </c>
       <c r="J133" t="n">
-        <v>25.5683</v>
+        <v>22.7696</v>
       </c>
     </row>
     <row r="134">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -7709,10 +7709,10 @@
         <v>1.21</v>
       </c>
       <c r="I134" t="n">
-        <v>0.5616</v>
+        <v>0.5295</v>
       </c>
       <c r="J134" t="n">
-        <v>10.6704</v>
+        <v>10.0605</v>
       </c>
     </row>
     <row r="135">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -8229,10 +8229,10 @@
         <v>2.83</v>
       </c>
       <c r="I147" t="n">
-        <v>1.5386</v>
+        <v>1.3913</v>
       </c>
       <c r="J147" t="n">
-        <v>27.6948</v>
+        <v>25.0434</v>
       </c>
     </row>
     <row r="148">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -8269,10 +8269,10 @@
         <v>1.41</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5083</v>
+        <v>0.4901</v>
       </c>
       <c r="J148" t="n">
-        <v>9.1494</v>
+        <v>8.8218</v>
       </c>
     </row>
     <row r="149">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -8309,10 +8309,10 @@
         <v>1.33</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4252</v>
+        <v>0.4239</v>
       </c>
       <c r="J149" t="n">
-        <v>7.6536</v>
+        <v>7.6302</v>
       </c>
     </row>
     <row r="150">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -8429,10 +8429,10 @@
         <v>1.62</v>
       </c>
       <c r="I152" t="n">
-        <v>1.2741</v>
+        <v>1.1268</v>
       </c>
       <c r="J152" t="n">
-        <v>28.0302</v>
+        <v>24.7896</v>
       </c>
     </row>
     <row r="153">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -8469,10 +8469,10 @@
         <v>1.6</v>
       </c>
       <c r="I153" t="n">
-        <v>1.2473</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
-        <v>27.4406</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="154">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -8629,10 +8629,10 @@
         <v>1.39</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7513</v>
+        <v>0.6698</v>
       </c>
       <c r="J157" t="n">
-        <v>16.5286</v>
+        <v>14.7356</v>
       </c>
     </row>
     <row r="158">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -8829,10 +8829,10 @@
         <v>1.3</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4284</v>
+        <v>0.4268</v>
       </c>
       <c r="J162" t="n">
-        <v>11.9952</v>
+        <v>11.9504</v>
       </c>
     </row>
     <row r="163">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -9029,10 +9029,10 @@
         <v>1.71</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9207</v>
+        <v>0.7954</v>
       </c>
       <c r="J167" t="n">
-        <v>25.7796</v>
+        <v>22.2712</v>
       </c>
     </row>
     <row r="168">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -9429,10 +9429,10 @@
         <v>2.11</v>
       </c>
       <c r="I177" t="n">
-        <v>1.856</v>
+        <v>1.7087</v>
       </c>
       <c r="J177" t="n">
-        <v>35.264</v>
+        <v>32.4653</v>
       </c>
     </row>
     <row r="178">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -9629,10 +9629,10 @@
         <v>1.35</v>
       </c>
       <c r="I182" t="n">
-        <v>0.735</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="J182" t="n">
-        <v>14.7</v>
+        <v>13.156</v>
       </c>
     </row>
     <row r="183">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -9829,10 +9829,10 @@
         <v>1.6</v>
       </c>
       <c r="I187" t="n">
-        <v>1.2204</v>
+        <v>1.0731</v>
       </c>
       <c r="J187" t="n">
-        <v>24.408</v>
+        <v>21.462</v>
       </c>
     </row>
     <row r="188">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -9869,10 +9869,10 @@
         <v>1.59</v>
       </c>
       <c r="I188" t="n">
-        <v>1.2073</v>
+        <v>1.06</v>
       </c>
       <c r="J188" t="n">
-        <v>24.146</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="189">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -9909,10 +9909,10 @@
         <v>1.37</v>
       </c>
       <c r="I189" t="n">
-        <v>0.875</v>
+        <v>0.7614</v>
       </c>
       <c r="J189" t="n">
-        <v>17.5</v>
+        <v>15.228</v>
       </c>
     </row>
     <row r="190">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -9949,10 +9949,10 @@
         <v>1.17</v>
       </c>
       <c r="I190" t="n">
-        <v>0.4672</v>
+        <v>0.4593</v>
       </c>
       <c r="J190" t="n">
-        <v>9.343999999999999</v>
+        <v>9.186</v>
       </c>
     </row>
     <row r="191">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F191" t="n">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -10029,10 +10029,10 @@
         <v>2.13</v>
       </c>
       <c r="I192" t="n">
-        <v>1.8466</v>
+        <v>1.6993</v>
       </c>
       <c r="J192" t="n">
-        <v>31.3922</v>
+        <v>28.8881</v>
       </c>
     </row>
     <row r="193">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -10069,10 +10069,10 @@
         <v>1.4</v>
       </c>
       <c r="I193" t="n">
-        <v>0.9176</v>
+        <v>0.7931</v>
       </c>
       <c r="J193" t="n">
-        <v>15.5992</v>
+        <v>13.4827</v>
       </c>
     </row>
     <row r="194">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -10109,10 +10109,10 @@
         <v>1.24</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6065</v>
+        <v>0.5627</v>
       </c>
       <c r="J194" t="n">
-        <v>10.3105</v>
+        <v>9.565899999999999</v>
       </c>
     </row>
     <row r="195">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F195" t="n">
@@ -10149,10 +10149,10 @@
         <v>1.15</v>
       </c>
       <c r="I195" t="n">
-        <v>0.4053</v>
+        <v>0.4051</v>
       </c>
       <c r="J195" t="n">
-        <v>6.8901</v>
+        <v>6.8867</v>
       </c>
     </row>
     <row r="196">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -10429,10 +10429,10 @@
         <v>2.41</v>
       </c>
       <c r="I202" t="n">
-        <v>1.9372</v>
+        <v>1.9402</v>
       </c>
       <c r="J202" t="n">
-        <v>27.1208</v>
+        <v>27.1628</v>
       </c>
     </row>
     <row r="203">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -10469,10 +10469,10 @@
         <v>1.79</v>
       </c>
       <c r="I203" t="n">
-        <v>1.3984</v>
+        <v>1.2511</v>
       </c>
       <c r="J203" t="n">
-        <v>19.5776</v>
+        <v>17.5154</v>
       </c>
     </row>
     <row r="204">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -10509,10 +10509,10 @@
         <v>1.55</v>
       </c>
       <c r="I204" t="n">
-        <v>1.1128</v>
+        <v>0.9655</v>
       </c>
       <c r="J204" t="n">
-        <v>15.5792</v>
+        <v>13.517</v>
       </c>
     </row>
     <row r="205">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -10549,10 +10549,10 @@
         <v>1.46</v>
       </c>
       <c r="I205" t="n">
-        <v>0.9882</v>
+        <v>0.8487</v>
       </c>
       <c r="J205" t="n">
-        <v>13.8348</v>
+        <v>11.8818</v>
       </c>
     </row>
     <row r="206">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F206" t="n">
@@ -10589,10 +10589,10 @@
         <v>1.19</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4569</v>
+        <v>0.4512</v>
       </c>
       <c r="J206" t="n">
-        <v>6.3966</v>
+        <v>6.3168</v>
       </c>
     </row>
     <row r="207">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F207" t="n">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F208" t="n">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F209" t="n">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F210" t="n">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Semi-final</t>
         </is>
       </c>
       <c r="F211" t="n">
@@ -12816,7 +12816,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -12829,10 +12829,10 @@
         <v>1.8</v>
       </c>
       <c r="I262" t="n">
-        <v>1.4749</v>
+        <v>1.3276</v>
       </c>
       <c r="J262" t="n">
-        <v>30.9729</v>
+        <v>27.8796</v>
       </c>
     </row>
     <row r="263">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F263" t="n">
@@ -12869,10 +12869,10 @@
         <v>1.47</v>
       </c>
       <c r="I263" t="n">
-        <v>1.0452</v>
+        <v>0.8992</v>
       </c>
       <c r="J263" t="n">
-        <v>21.9492</v>
+        <v>18.8832</v>
       </c>
     </row>
     <row r="264">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F264" t="n">
@@ -12909,10 +12909,10 @@
         <v>1.33</v>
       </c>
       <c r="I264" t="n">
-        <v>0.7977</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="J264" t="n">
-        <v>16.7517</v>
+        <v>14.7861</v>
       </c>
     </row>
     <row r="265">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F265" t="n">
@@ -12976,7 +12976,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F266" t="n">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F267" t="n">
@@ -13056,7 +13056,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F268" t="n">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F269" t="n">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F270" t="n">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F271" t="n">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F272" t="n">
@@ -13229,10 +13229,10 @@
         <v>2.31</v>
       </c>
       <c r="I272" t="n">
-        <v>1.9372</v>
+        <v>1.8801</v>
       </c>
       <c r="J272" t="n">
-        <v>30.9952</v>
+        <v>30.0816</v>
       </c>
     </row>
     <row r="273">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -13269,10 +13269,10 @@
         <v>1.82</v>
       </c>
       <c r="I273" t="n">
-        <v>1.4612</v>
+        <v>1.3139</v>
       </c>
       <c r="J273" t="n">
-        <v>23.3792</v>
+        <v>21.0224</v>
       </c>
     </row>
     <row r="274">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -13309,10 +13309,10 @@
         <v>1.58</v>
       </c>
       <c r="I274" t="n">
-        <v>1.1661</v>
+        <v>1.0188</v>
       </c>
       <c r="J274" t="n">
-        <v>18.6576</v>
+        <v>16.3008</v>
       </c>
     </row>
     <row r="275">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F275" t="n">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -13456,7 +13456,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -13629,10 +13629,10 @@
         <v>2.02</v>
       </c>
       <c r="I282" t="n">
-        <v>1.066</v>
+        <v>0.919</v>
       </c>
       <c r="J282" t="n">
-        <v>19.188</v>
+        <v>16.542</v>
       </c>
     </row>
     <row r="283">
@@ -13656,7 +13656,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -13669,10 +13669,10 @@
         <v>1.35</v>
       </c>
       <c r="I283" t="n">
-        <v>0.4552</v>
+        <v>0.4498</v>
       </c>
       <c r="J283" t="n">
-        <v>8.1936</v>
+        <v>8.096399999999999</v>
       </c>
     </row>
     <row r="284">
@@ -13696,7 +13696,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F285" t="n">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F286" t="n">
@@ -13816,7 +13816,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F287" t="n">
@@ -13829,10 +13829,10 @@
         <v>1.31</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5486</v>
+        <v>0.5199</v>
       </c>
       <c r="J287" t="n">
-        <v>9.8748</v>
+        <v>9.3582</v>
       </c>
     </row>
     <row r="288">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F288" t="n">
@@ -13896,7 +13896,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F289" t="n">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F290" t="n">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F291" t="n">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F292" t="n">
@@ -14029,10 +14029,10 @@
         <v>1.25</v>
       </c>
       <c r="I292" t="n">
-        <v>0.5224</v>
+        <v>0.5006</v>
       </c>
       <c r="J292" t="n">
-        <v>12.5376</v>
+        <v>12.0144</v>
       </c>
     </row>
     <row r="293">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F293" t="n">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F294" t="n">
@@ -14136,7 +14136,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -14176,7 +14176,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -14229,10 +14229,10 @@
         <v>1.5</v>
       </c>
       <c r="I297" t="n">
-        <v>1.1361</v>
+        <v>0.9887</v>
       </c>
       <c r="J297" t="n">
-        <v>27.2664</v>
+        <v>23.7288</v>
       </c>
     </row>
     <row r="298">
@@ -14256,7 +14256,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F298" t="n">
@@ -14269,10 +14269,10 @@
         <v>1.38</v>
       </c>
       <c r="I298" t="n">
-        <v>0.946</v>
+        <v>0.8148</v>
       </c>
       <c r="J298" t="n">
-        <v>22.704</v>
+        <v>19.5552</v>
       </c>
     </row>
     <row r="299">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F299" t="n">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F300" t="n">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F301" t="n">
@@ -14416,7 +14416,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F302" t="n">
@@ -14456,7 +14456,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F303" t="n">
@@ -14496,7 +14496,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F304" t="n">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F305" t="n">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F306" t="n">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F307" t="n">
@@ -14629,10 +14629,10 @@
         <v>1.56</v>
       </c>
       <c r="I307" t="n">
-        <v>1.1741</v>
+        <v>1.0268</v>
       </c>
       <c r="J307" t="n">
-        <v>24.6561</v>
+        <v>21.5628</v>
       </c>
     </row>
     <row r="308">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F308" t="n">
@@ -14669,10 +14669,10 @@
         <v>1.36</v>
       </c>
       <c r="I308" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.7513</v>
       </c>
       <c r="J308" t="n">
-        <v>18.0894</v>
+        <v>15.7773</v>
       </c>
     </row>
     <row r="309">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -14709,10 +14709,10 @@
         <v>1.25</v>
       </c>
       <c r="I309" t="n">
-        <v>0.6443</v>
+        <v>0.5907</v>
       </c>
       <c r="J309" t="n">
-        <v>13.5303</v>
+        <v>12.4047</v>
       </c>
     </row>
     <row r="310">
@@ -14736,7 +14736,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F310" t="n">
@@ -14749,10 +14749,10 @@
         <v>1.22</v>
       </c>
       <c r="I310" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.5448</v>
       </c>
       <c r="J310" t="n">
-        <v>12.2262</v>
+        <v>11.4408</v>
       </c>
     </row>
     <row r="311">
@@ -14776,7 +14776,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F312" t="n">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F313" t="n">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -14936,7 +14936,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F315" t="n">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F316" t="n">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -15029,10 +15029,10 @@
         <v>1.98</v>
       </c>
       <c r="I317" t="n">
-        <v>1.6902</v>
+        <v>1.5429</v>
       </c>
       <c r="J317" t="n">
-        <v>32.1138</v>
+        <v>29.3151</v>
       </c>
     </row>
     <row r="318">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F318" t="n">
@@ -15069,10 +15069,10 @@
         <v>1.74</v>
       </c>
       <c r="I318" t="n">
-        <v>1.3949</v>
+        <v>1.2476</v>
       </c>
       <c r="J318" t="n">
-        <v>26.5031</v>
+        <v>23.7044</v>
       </c>
     </row>
     <row r="319">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F320" t="n">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F321" t="n">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F322" t="n">
@@ -15229,10 +15229,10 @@
         <v>1.21</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4826</v>
+        <v>0.4711</v>
       </c>
       <c r="J322" t="n">
-        <v>9.651999999999999</v>
+        <v>9.422000000000001</v>
       </c>
     </row>
     <row r="323">
@@ -15256,7 +15256,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F323" t="n">
@@ -15296,7 +15296,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F324" t="n">
@@ -15336,7 +15336,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F325" t="n">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F326" t="n">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -15429,10 +15429,10 @@
         <v>1.45</v>
       </c>
       <c r="I327" t="n">
-        <v>1.0443</v>
+        <v>0.8983</v>
       </c>
       <c r="J327" t="n">
-        <v>20.886</v>
+        <v>17.966</v>
       </c>
     </row>
     <row r="328">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F328" t="n">
@@ -15469,10 +15469,10 @@
         <v>1.2</v>
       </c>
       <c r="I328" t="n">
-        <v>0.5514</v>
+        <v>0.522</v>
       </c>
       <c r="J328" t="n">
-        <v>11.028</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="329">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -15509,10 +15509,10 @@
         <v>1.15</v>
       </c>
       <c r="I329" t="n">
-        <v>0.4395</v>
+        <v>0.4366</v>
       </c>
       <c r="J329" t="n">
-        <v>8.789999999999999</v>
+        <v>8.731999999999999</v>
       </c>
     </row>
     <row r="330">
@@ -15536,7 +15536,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F330" t="n">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -15629,10 +15629,10 @@
         <v>1.83</v>
       </c>
       <c r="I332" t="n">
-        <v>1.5076</v>
+        <v>1.3603</v>
       </c>
       <c r="J332" t="n">
-        <v>30.152</v>
+        <v>27.206</v>
       </c>
     </row>
     <row r="333">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F333" t="n">
@@ -15669,10 +15669,10 @@
         <v>1.43</v>
       </c>
       <c r="I333" t="n">
-        <v>0.98</v>
+        <v>0.8419</v>
       </c>
       <c r="J333" t="n">
-        <v>19.6</v>
+        <v>16.838</v>
       </c>
     </row>
     <row r="334">
@@ -15696,7 +15696,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F334" t="n">
@@ -15709,10 +15709,10 @@
         <v>1.33</v>
       </c>
       <c r="I334" t="n">
-        <v>0.7955</v>
+        <v>0.7025</v>
       </c>
       <c r="J334" t="n">
-        <v>15.91</v>
+        <v>14.05</v>
       </c>
     </row>
     <row r="335">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -15749,10 +15749,10 @@
         <v>1.2</v>
       </c>
       <c r="I335" t="n">
-        <v>0.5313</v>
+        <v>0.5071</v>
       </c>
       <c r="J335" t="n">
-        <v>10.626</v>
+        <v>10.142</v>
       </c>
     </row>
     <row r="336">
@@ -15776,7 +15776,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F336" t="n">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F337" t="n">
@@ -15829,10 +15829,10 @@
         <v>1.15</v>
       </c>
       <c r="I337" t="n">
-        <v>0.394</v>
+        <v>0.3939</v>
       </c>
       <c r="J337" t="n">
-        <v>7.88</v>
+        <v>7.878</v>
       </c>
     </row>
     <row r="338">
@@ -15856,7 +15856,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F338" t="n">
@@ -15896,7 +15896,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F339" t="n">
@@ -15936,7 +15936,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F340" t="n">
@@ -15976,7 +15976,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F342" t="n">
@@ -16029,10 +16029,10 @@
         <v>2.17</v>
       </c>
       <c r="I342" t="n">
-        <v>1.9272</v>
+        <v>1.7799</v>
       </c>
       <c r="J342" t="n">
-        <v>46.2528</v>
+        <v>42.7176</v>
       </c>
     </row>
     <row r="343">
@@ -16056,7 +16056,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F343" t="n">
@@ -16069,10 +16069,10 @@
         <v>1.79</v>
       </c>
       <c r="I343" t="n">
-        <v>1.4654</v>
+        <v>1.3181</v>
       </c>
       <c r="J343" t="n">
-        <v>35.1696</v>
+        <v>31.6344</v>
       </c>
     </row>
     <row r="344">
@@ -16096,7 +16096,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F344" t="n">
@@ -16109,10 +16109,10 @@
         <v>1.21</v>
       </c>
       <c r="I344" t="n">
-        <v>0.5575</v>
+        <v>0.5265</v>
       </c>
       <c r="J344" t="n">
-        <v>13.38</v>
+        <v>12.636</v>
       </c>
     </row>
     <row r="345">
@@ -16136,7 +16136,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F346" t="n">
@@ -16216,7 +16216,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F347" t="n">
@@ -16229,10 +16229,10 @@
         <v>1.22</v>
       </c>
       <c r="I347" t="n">
-        <v>0.4705</v>
+        <v>0.4619</v>
       </c>
       <c r="J347" t="n">
-        <v>11.292</v>
+        <v>11.0856</v>
       </c>
     </row>
     <row r="348">
@@ -16256,7 +16256,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F348" t="n">
@@ -16269,10 +16269,10 @@
         <v>1.2</v>
       </c>
       <c r="I348" t="n">
-        <v>0.4366</v>
+        <v>0.4341</v>
       </c>
       <c r="J348" t="n">
-        <v>10.4784</v>
+        <v>10.4184</v>
       </c>
     </row>
     <row r="349">
@@ -16296,7 +16296,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F349" t="n">
@@ -16336,7 +16336,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F350" t="n">
@@ -16376,7 +16376,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Quarter-final</t>
         </is>
       </c>
       <c r="F351" t="n">

--- a/database/event/7993/event_7993_evp_summary.xlsx
+++ b/database/event/7993/event_7993_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.8621</v>
+        <v>8.912800000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2206</v>
+        <v>2.2333</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3447</v>
+        <v>3.4544</v>
       </c>
       <c r="E2" t="n">
-        <v>8.8621</v>
+        <v>8.912800000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1844</v>
+        <v>2.2191</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1908</v>
+        <v>6.2067</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1844</v>
+        <v>2.2191</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2984</v>
+        <v>2.3393</v>
       </c>
       <c r="J2" t="n">
-        <v>8.0586</v>
+        <v>8.0512</v>
       </c>
       <c r="K2" t="n">
         <v>76</v>
@@ -529,7 +529,7 @@
         <v>138</v>
       </c>
       <c r="M2" t="n">
-        <v>10.357</v>
+        <v>10.3905</v>
       </c>
       <c r="N2" t="n">
         <v>214</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.9547</v>
+        <v>6.9675</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7427</v>
+        <v>1.7459</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4927</v>
+        <v>2.5682</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9547</v>
+        <v>6.9675</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4383</v>
+        <v>0.4351</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1908</v>
+        <v>6.2067</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4383</v>
+        <v>0.4351</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4612</v>
+        <v>0.4587</v>
       </c>
       <c r="J3" t="n">
-        <v>6.5946</v>
+        <v>6.5984</v>
       </c>
       <c r="K3" t="n">
         <v>76</v>
@@ -575,7 +575,7 @@
         <v>138</v>
       </c>
       <c r="M3" t="n">
-        <v>7.0558</v>
+        <v>7.0571</v>
       </c>
       <c r="N3" t="n">
         <v>214</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.2834</v>
+        <v>6.1044</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5744</v>
+        <v>1.5296</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1928</v>
+        <v>2.1751</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2834</v>
+        <v>6.1044</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9772</v>
+        <v>1.806</v>
       </c>
       <c r="G4" t="n">
-        <v>4.209</v>
+        <v>4.2013</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9772</v>
+        <v>1.806</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0282</v>
+        <v>1.8543</v>
       </c>
       <c r="J4" t="n">
-        <v>4.209</v>
+        <v>4.2013</v>
       </c>
       <c r="K4" t="n">
         <v>135</v>
@@ -621,7 +621,7 @@
         <v>104</v>
       </c>
       <c r="M4" t="n">
-        <v>6.2372</v>
+        <v>6.0556</v>
       </c>
       <c r="N4" t="n">
         <v>239</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.7427</v>
+        <v>4.854</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1884</v>
+        <v>1.2163</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5046</v>
+        <v>1.6054</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7427</v>
+        <v>4.854</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1334</v>
+        <v>-0.1235</v>
       </c>
       <c r="G5" t="n">
-        <v>4.8841</v>
+        <v>4.9855</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1334</v>
+        <v>-0.1235</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1404</v>
+        <v>-0.1302</v>
       </c>
       <c r="J5" t="n">
-        <v>4.8841</v>
+        <v>4.9855</v>
       </c>
       <c r="K5" t="n">
         <v>76</v>
@@ -667,7 +667,7 @@
         <v>138</v>
       </c>
       <c r="M5" t="n">
-        <v>4.7437</v>
+        <v>4.8553</v>
       </c>
       <c r="N5" t="n">
         <v>214</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6757</v>
+        <v>3.6542</v>
       </c>
       <c r="C6" t="n">
-        <v>0.921</v>
+        <v>0.9156</v>
       </c>
       <c r="D6" t="n">
-        <v>1.028</v>
+        <v>1.0589</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6757</v>
+        <v>3.6542</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6336</v>
+        <v>2.5944</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8639</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>3.0392</v>
+        <v>2.9954</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5404</v>
+        <v>3.5089</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8639</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>144</v>
@@ -713,7 +713,7 @@
         <v>159</v>
       </c>
       <c r="M6" t="n">
-        <v>4.4043</v>
+        <v>4.3905</v>
       </c>
       <c r="N6" t="n">
         <v>303</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5776</v>
+        <v>3.4912</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8964</v>
+        <v>0.8748</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9842</v>
+        <v>0.9846</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5776</v>
+        <v>3.4912</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2134</v>
+        <v>-0.3023</v>
       </c>
       <c r="G7" t="n">
-        <v>3.8434</v>
+        <v>3.8459</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2134</v>
+        <v>-0.3023</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2189</v>
+        <v>-0.3104</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8434</v>
+        <v>3.8459</v>
       </c>
       <c r="K7" t="n">
         <v>135</v>
@@ -759,7 +759,7 @@
         <v>104</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6245</v>
+        <v>3.5355</v>
       </c>
       <c r="N7" t="n">
         <v>239</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4472</v>
+        <v>2.496</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6132</v>
+        <v>0.6254</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4793</v>
+        <v>0.5313</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4472</v>
+        <v>2.496</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5613</v>
+        <v>1.5131</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9486</v>
+        <v>1.0205</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5613</v>
+        <v>1.5131</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5613</v>
+        <v>1.7725</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9486</v>
+        <v>1.0205</v>
       </c>
       <c r="K8" t="n">
-        <v>42</v>
+        <v>144</v>
       </c>
       <c r="L8" t="n">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3873</v>
+        <v>2.793</v>
       </c>
       <c r="N8" t="n">
-        <v>242</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.4079</v>
+        <v>2.4873</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6034</v>
+        <v>0.6232</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4617</v>
+        <v>0.5273</v>
       </c>
       <c r="E9" t="n">
-        <v>2.4079</v>
+        <v>2.4873</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4506</v>
+        <v>-0.5291</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9949</v>
+        <v>2.9565</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4506</v>
+        <v>-0.5291</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6898</v>
+        <v>-0.5291</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9949</v>
+        <v>2.9565</v>
       </c>
       <c r="K9" t="n">
-        <v>144</v>
+        <v>42</v>
       </c>
       <c r="L9" t="n">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="M9" t="n">
-        <v>2.6847</v>
+        <v>2.4274</v>
       </c>
       <c r="N9" t="n">
-        <v>303</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.0935</v>
+        <v>1.9608</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5246</v>
+        <v>0.4913</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3213</v>
+        <v>0.2874</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0935</v>
+        <v>1.9608</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9507</v>
+        <v>0.785</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9507</v>
+        <v>0.785</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9752</v>
+        <v>0.806</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="K10" t="n">
         <v>135</v>
@@ -897,7 +897,7 @@
         <v>104</v>
       </c>
       <c r="M10" t="n">
-        <v>1.9122</v>
+        <v>1.776</v>
       </c>
       <c r="N10" t="n">
         <v>239</v>
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.6683</v>
+        <v>1.5385</v>
       </c>
       <c r="C11" t="n">
-        <v>0.418</v>
+        <v>0.3855</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1314</v>
+        <v>0.0951</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6683</v>
+        <v>1.5385</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1827</v>
+        <v>1.0529</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1827</v>
+        <v>1.0529</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>129</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1827</v>
+        <v>1.0529</v>
       </c>
       <c r="N11" t="n">
         <v>129</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.2794</v>
+        <v>1.1783</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3206</v>
+        <v>0.2952</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0423</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2794</v>
+        <v>1.1783</v>
       </c>
       <c r="F12" t="n">
-        <v>0.671</v>
+        <v>0.6219</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.5039</v>
       </c>
       <c r="H12" t="n">
-        <v>0.671</v>
+        <v>0.6219</v>
       </c>
       <c r="I12" t="n">
-        <v>0.706</v>
+        <v>0.6556</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.5039</v>
       </c>
       <c r="K12" t="n">
         <v>67</v>
@@ -989,7 +989,7 @@
         <v>109</v>
       </c>
       <c r="M12" t="n">
-        <v>1.2619</v>
+        <v>1.1595</v>
       </c>
       <c r="N12" t="n">
         <v>176</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.1688</v>
+        <v>1.1392</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2929</v>
+        <v>0.2855</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0917</v>
+        <v>-0.0868</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1688</v>
+        <v>1.1392</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4712</v>
+        <v>0.406</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7896</v>
+        <v>0.8252</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4712</v>
+        <v>0.406</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4833</v>
+        <v>0.4169</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7896</v>
+        <v>0.8252</v>
       </c>
       <c r="K13" t="n">
         <v>135</v>
@@ -1035,7 +1035,7 @@
         <v>104</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2729</v>
+        <v>1.2421</v>
       </c>
       <c r="N13" t="n">
         <v>239</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1664</v>
+        <v>1.0859</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2923</v>
+        <v>0.2721</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.1111</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1664</v>
+        <v>1.0859</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4046</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.828</v>
+        <v>1.2365</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4046</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.415</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.828</v>
+        <v>1.2365</v>
       </c>
       <c r="K14" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>44</v>
+        <v>129</v>
       </c>
       <c r="M14" t="n">
-        <v>1.243</v>
+        <v>1.2365</v>
       </c>
       <c r="N14" t="n">
-        <v>111</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1391</v>
+        <v>1.0592</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2854</v>
+        <v>0.2654</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.105</v>
+        <v>-0.1233</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1391</v>
+        <v>1.0592</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7773</v>
+        <v>1.7742</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6203</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7773</v>
+        <v>1.7742</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0704</v>
+        <v>2.0783</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6203</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>144</v>
@@ -1127,7 +1127,7 @@
         <v>159</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4501</v>
+        <v>1.3812</v>
       </c>
       <c r="N15" t="n">
         <v>303</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1253</v>
+        <v>1.0184</v>
       </c>
       <c r="C16" t="n">
-        <v>0.282</v>
+        <v>0.2552</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1112</v>
+        <v>-0.1419</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1253</v>
+        <v>1.0184</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2246</v>
+        <v>0.1863</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5954</v>
+        <v>0.5268</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2246</v>
+        <v>0.1863</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2246</v>
+        <v>0.1863</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5954</v>
+        <v>0.5268</v>
       </c>
       <c r="K16" t="n">
         <v>43</v>
@@ -1173,7 +1173,7 @@
         <v>63</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8200000000000001</v>
+        <v>0.7131000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>106</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.0983</v>
+        <v>0.9859</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2752</v>
+        <v>0.247</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1232</v>
+        <v>-0.1567</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0983</v>
+        <v>0.9859</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3929</v>
+        <v>0.3348</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.7173</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3929</v>
+        <v>0.3348</v>
       </c>
       <c r="I17" t="n">
-        <v>0.403</v>
+        <v>0.3437</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.7173</v>
       </c>
       <c r="K17" t="n">
-        <v>135</v>
+        <v>67</v>
       </c>
       <c r="L17" t="n">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9650000000000001</v>
+        <v>1.061</v>
       </c>
       <c r="N17" t="n">
-        <v>239</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0659</v>
+        <v>0.9391</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2671</v>
+        <v>0.2353</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1377</v>
+        <v>-0.178</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0659</v>
+        <v>0.9391</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.2292</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2165</v>
+        <v>0.5665</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.2292</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.2353</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2165</v>
+        <v>0.5665</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="L18" t="n">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2165</v>
+        <v>0.8018000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>129</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9214</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2343</v>
+        <v>0.2309</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1962</v>
+        <v>-0.186</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9214</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0331</v>
+        <v>1.9979</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0614</v>
+        <v>-1.0398</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0331</v>
+        <v>1.9979</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1392</v>
+        <v>2.1061</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0614</v>
+        <v>-1.0398</v>
       </c>
       <c r="K19" t="n">
         <v>67</v>
@@ -1311,7 +1311,7 @@
         <v>109</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0778</v>
+        <v>1.0663</v>
       </c>
       <c r="N19" t="n">
         <v>176</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8348</v>
+        <v>0.77</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2092</v>
+        <v>0.1929</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2409</v>
+        <v>-0.255</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8348</v>
+        <v>0.77</v>
       </c>
       <c r="F20" t="n">
-        <v>0.511</v>
+        <v>0.4789</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2251</v>
+        <v>0.1925</v>
       </c>
       <c r="H20" t="n">
-        <v>0.511</v>
+        <v>0.4789</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5242</v>
+        <v>0.4917</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2251</v>
+        <v>0.1925</v>
       </c>
       <c r="K20" t="n">
         <v>67</v>
@@ -1357,7 +1357,7 @@
         <v>44</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7493</v>
+        <v>0.6842</v>
       </c>
       <c r="N20" t="n">
         <v>111</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7358</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1954</v>
+        <v>0.1844</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2655</v>
+        <v>-0.2706</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7358</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3904</v>
+        <v>-0.3527</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9766</v>
+        <v>0.895</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3904</v>
+        <v>-0.3527</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3904</v>
+        <v>-0.3527</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9766</v>
+        <v>0.895</v>
       </c>
       <c r="K21" t="n">
         <v>43</v>
@@ -1403,7 +1403,7 @@
         <v>63</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5423</v>
       </c>
       <c r="N21" t="n">
         <v>106</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5919</v>
+        <v>0.6203</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1483</v>
+        <v>0.1554</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3494</v>
+        <v>-0.3232</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5919</v>
+        <v>0.6203</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0347</v>
+        <v>-0.0117</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7986</v>
+        <v>0.804</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0347</v>
+        <v>-0.0117</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0365</v>
+        <v>-0.0123</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7986</v>
+        <v>0.804</v>
       </c>
       <c r="K22" t="n">
         <v>76</v>
@@ -1449,7 +1449,7 @@
         <v>138</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7621</v>
+        <v>0.7917000000000001</v>
       </c>
       <c r="N22" t="n">
         <v>214</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5112</v>
+        <v>0.4375</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1281</v>
+        <v>0.1096</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3855</v>
+        <v>-0.4065</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5112</v>
+        <v>0.4375</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.3305</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6103</v>
+        <v>0.0667</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.3305</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.3305</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6103</v>
+        <v>0.0667</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="L23" t="n">
-        <v>129</v>
+        <v>200</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6103</v>
+        <v>0.3972</v>
       </c>
       <c r="N23" t="n">
-        <v>129</v>
+        <v>242</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5006</v>
+        <v>0.3952</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1254</v>
+        <v>0.099</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3902</v>
+        <v>-0.4258</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5006</v>
+        <v>0.3952</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3699</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.4943</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3699</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3699</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.4943</v>
       </c>
       <c r="K24" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>200</v>
+        <v>129</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4603</v>
+        <v>0.4943</v>
       </c>
       <c r="N24" t="n">
-        <v>242</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.495</v>
+        <v>0.3792</v>
       </c>
       <c r="C25" t="n">
-        <v>0.124</v>
+        <v>0.095</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3927</v>
+        <v>-0.433</v>
       </c>
       <c r="E25" t="n">
-        <v>0.495</v>
+        <v>0.3792</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5158</v>
+        <v>0.452</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0429</v>
+        <v>-0.0091</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5158</v>
+        <v>0.452</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5427</v>
+        <v>0.4765</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0429</v>
+        <v>-0.0091</v>
       </c>
       <c r="K25" t="n">
         <v>67</v>
@@ -1587,7 +1587,7 @@
         <v>109</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5856</v>
+        <v>0.4674</v>
       </c>
       <c r="N25" t="n">
         <v>176</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3272</v>
+        <v>0.2661</v>
       </c>
       <c r="C26" t="n">
-        <v>0.082</v>
+        <v>0.0667</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4677</v>
+        <v>-0.4846</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3272</v>
+        <v>0.2661</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3081</v>
+        <v>0.2092</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1241</v>
+        <v>-0.0963</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3081</v>
+        <v>0.2092</v>
       </c>
       <c r="I26" t="n">
-        <v>0.316</v>
+        <v>0.2092</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1241</v>
+        <v>-0.0963</v>
       </c>
       <c r="K26" t="n">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="L26" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4401</v>
+        <v>0.1129</v>
       </c>
       <c r="N26" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3201</v>
+        <v>0.2185</v>
       </c>
       <c r="C27" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0548</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4708</v>
+        <v>-0.5063</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3201</v>
+        <v>0.2185</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2474</v>
+        <v>0.2339</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0805</v>
+        <v>0.0896</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2474</v>
+        <v>0.2339</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2474</v>
+        <v>0.2401</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.0805</v>
+        <v>0.0896</v>
       </c>
       <c r="K27" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="L27" t="n">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1669</v>
+        <v>0.3297</v>
       </c>
       <c r="N27" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28">
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2066</v>
+        <v>0.1813</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0518</v>
+        <v>0.0454</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5215</v>
+        <v>-0.5232</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2066</v>
+        <v>0.1813</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.5138</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7033</v>
+        <v>0.65</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.5138</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.5138</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7033</v>
+        <v>0.65</v>
       </c>
       <c r="K28" t="n">
         <v>42</v>
@@ -1725,7 +1725,7 @@
         <v>200</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1615000000000001</v>
+        <v>0.1362</v>
       </c>
       <c r="N28" t="n">
         <v>242</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0759</v>
+        <v>0.0228</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.019</v>
+        <v>0.0057</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.5954</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0759</v>
+        <v>0.0228</v>
       </c>
       <c r="F29" t="n">
-        <v>2.0406</v>
+        <v>2.0686</v>
       </c>
       <c r="G29" t="n">
-        <v>-2.1251</v>
+        <v>-2.0544</v>
       </c>
       <c r="H29" t="n">
-        <v>2.0406</v>
+        <v>2.0686</v>
       </c>
       <c r="I29" t="n">
-        <v>2.3771</v>
+        <v>2.4232</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.1251</v>
+        <v>-2.0544</v>
       </c>
       <c r="K29" t="n">
         <v>144</v>
@@ -1771,7 +1771,7 @@
         <v>159</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2519999999999998</v>
+        <v>0.3688000000000002</v>
       </c>
       <c r="N29" t="n">
         <v>303</v>
@@ -1780,185 +1780,185 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1298</v>
+        <v>-0.0192</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0325</v>
+        <v>-0.0048</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6718</v>
+        <v>-0.6145</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1298</v>
+        <v>-0.0192</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1141</v>
+        <v>-0.1624</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0024</v>
+        <v>0.2105</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1141</v>
+        <v>-0.1624</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1141</v>
+        <v>-0.1624</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.0024</v>
+        <v>0.2105</v>
       </c>
       <c r="K30" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L30" t="n">
-        <v>63</v>
+        <v>200</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1117</v>
+        <v>0.0481</v>
       </c>
       <c r="N30" t="n">
-        <v>106</v>
+        <v>242</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1399</v>
+        <v>-0.183</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0351</v>
+        <v>-0.0459</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6763</v>
+        <v>-0.6892</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1399</v>
+        <v>-0.183</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1908</v>
+        <v>0.0834</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1182</v>
+        <v>-0.0249</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1908</v>
+        <v>0.0834</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1908</v>
+        <v>0.0834</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1182</v>
+        <v>-0.0249</v>
       </c>
       <c r="K31" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L31" t="n">
-        <v>200</v>
+        <v>63</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0726</v>
+        <v>0.0585</v>
       </c>
       <c r="N31" t="n">
-        <v>242</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1584</v>
+        <v>-0.2632</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0397</v>
+        <v>-0.066</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6846</v>
+        <v>-0.7257</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1584</v>
+        <v>-0.2632</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9643</v>
+        <v>0.977</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.8472</v>
+        <v>-1.0758</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9643</v>
+        <v>0.977</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0146</v>
+        <v>1.1445</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8472</v>
+        <v>-1.0758</v>
       </c>
       <c r="K32" t="n">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="L32" t="n">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1674</v>
+        <v>0.06869999999999998</v>
       </c>
       <c r="N32" t="n">
-        <v>214</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3186</v>
+        <v>-0.2832</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0798</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7561</v>
+        <v>-0.7348</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3186</v>
+        <v>-0.2832</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9179</v>
+        <v>0.9083</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.0721</v>
+        <v>-0.916</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9179</v>
+        <v>0.9083</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0693</v>
+        <v>0.9575</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.0721</v>
+        <v>-0.916</v>
       </c>
       <c r="K33" t="n">
-        <v>144</v>
+        <v>76</v>
       </c>
       <c r="L33" t="n">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.002800000000000136</v>
+        <v>0.04149999999999998</v>
       </c>
       <c r="N33" t="n">
-        <v>303</v>
+        <v>214</v>
       </c>
     </row>
     <row r="34">
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6129</v>
+        <v>-0.5907</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1536</v>
+        <v>-0.148</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-0.8749</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6129</v>
+        <v>-0.5907</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.3645</v>
+        <v>-0.3423</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.3645</v>
+        <v>-0.3423</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>129</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3645</v>
+        <v>-0.3423</v>
       </c>
       <c r="N34" t="n">
         <v>129</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.6882</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1775</v>
+        <v>-0.1724</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9302</v>
+        <v>-0.9193</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.6882</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.1593</v>
+        <v>-0.1725</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.5967</v>
+        <v>-0.5635</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.1593</v>
+        <v>-0.1725</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1634</v>
+        <v>-0.1771</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.5967</v>
+        <v>-0.5635</v>
       </c>
       <c r="K35" t="n">
         <v>67</v>
@@ -2047,7 +2047,7 @@
         <v>44</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7601</v>
+        <v>-0.7406</v>
       </c>
       <c r="N35" t="n">
         <v>111</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9326</v>
+        <v>-0.9296</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2337</v>
+        <v>-0.2329</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0304</v>
+        <v>-1.0293</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9326</v>
+        <v>-0.9296</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.0795</v>
+        <v>-0.0951</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.7829</v>
+        <v>-0.7643</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.0795</v>
+        <v>-0.0951</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0815</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.7829</v>
+        <v>-0.7643</v>
       </c>
       <c r="K36" t="n">
         <v>67</v>
@@ -2093,7 +2093,7 @@
         <v>44</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8644000000000001</v>
+        <v>-0.8619</v>
       </c>
       <c r="N36" t="n">
         <v>111</v>
@@ -2102,185 +2102,185 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9708</v>
+        <v>-0.9607</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2433</v>
+        <v>-0.2407</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0475</v>
+        <v>-1.0434</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9708</v>
+        <v>-0.9607</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>0.0983</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.6147</v>
+        <v>-0.9352</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>0.0983</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>0.1036</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.6147</v>
+        <v>-0.9352</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="L37" t="n">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6147</v>
+        <v>-0.8316</v>
       </c>
       <c r="N37" t="n">
-        <v>129</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1737</v>
+        <v>-0.9622000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2941</v>
+        <v>-0.2411</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1381</v>
+        <v>-1.0441</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1737</v>
+        <v>-0.9622000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.0308</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.0191</v>
+        <v>-0.6061</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.0308</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0324</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.0191</v>
+        <v>-0.6061</v>
       </c>
       <c r="K38" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0515</v>
+        <v>-0.6061</v>
       </c>
       <c r="N38" t="n">
-        <v>176</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kauez</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1786</v>
+        <v>-1.16</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2953</v>
+        <v>-0.2907</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1403</v>
+        <v>-1.1342</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1786</v>
+        <v>-1.16</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.6087</v>
+        <v>-0.6751</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.4159</v>
+        <v>-0.4933</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.6087</v>
+        <v>-0.6751</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6087</v>
+        <v>-0.7117</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.4159</v>
+        <v>-0.4933</v>
       </c>
       <c r="K39" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="L39" t="n">
-        <v>200</v>
+        <v>109</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0246</v>
+        <v>-1.205</v>
       </c>
       <c r="N39" t="n">
-        <v>242</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>kauez</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.251</v>
+        <v>-1.1767</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3135</v>
+        <v>-0.2948</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1726</v>
+        <v>-1.1418</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.251</v>
+        <v>-1.1767</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.7237</v>
+        <v>-0.577</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.5357</v>
+        <v>-0.4457</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.7237</v>
+        <v>-0.577</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7615</v>
+        <v>-0.577</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.5357</v>
+        <v>-0.4457</v>
       </c>
       <c r="K40" t="n">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="L40" t="n">
-        <v>109</v>
+        <v>200</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2972</v>
+        <v>-1.0227</v>
       </c>
       <c r="N40" t="n">
-        <v>176</v>
+        <v>242</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.3804</v>
+        <v>-1.2943</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3459</v>
+        <v>-0.3243</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2304</v>
+        <v>-1.1954</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.3804</v>
+        <v>-1.2943</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.4692</v>
+        <v>-0.431</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.5778</v>
+        <v>-0.5299</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.4692</v>
+        <v>-0.431</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4692</v>
+        <v>-0.431</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.5778</v>
+        <v>-0.5299</v>
       </c>
       <c r="K41" t="n">
         <v>43</v>
@@ -2323,7 +2323,7 @@
         <v>63</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.047</v>
+        <v>-0.9609000000000001</v>
       </c>
       <c r="N41" t="n">
         <v>106</v>
@@ -2429,10 +2429,10 @@
         <v>1.54</v>
       </c>
       <c r="I2" t="n">
-        <v>1.192</v>
+        <v>1.2063</v>
       </c>
       <c r="J2" t="n">
-        <v>23.84</v>
+        <v>24.126</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.49</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1012</v>
+        <v>1.105</v>
       </c>
       <c r="J3" t="n">
-        <v>22.024</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.45</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0274</v>
+        <v>1.0238</v>
       </c>
       <c r="J4" t="n">
-        <v>20.548</v>
+        <v>20.476</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0466</v>
+        <v>-0.0416</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.832</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.9</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3929</v>
+        <v>-0.3539</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.858</v>
+        <v>-7.078</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.23</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5309</v>
+        <v>0.4784</v>
       </c>
       <c r="J7" t="n">
-        <v>10.618</v>
+        <v>9.568</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.06</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2027</v>
+        <v>0.1626</v>
       </c>
       <c r="J8" t="n">
-        <v>4.054</v>
+        <v>3.252</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0742</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.748</v>
+        <v>-1.484</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.58</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4414</v>
+        <v>-0.4341</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.827999999999999</v>
+        <v>-8.682</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.46</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5451</v>
+        <v>-0.5513</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.902</v>
+        <v>-11.026</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.92</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7724</v>
+        <v>1.8155</v>
       </c>
       <c r="J12" t="n">
-        <v>37.2204</v>
+        <v>38.1255</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.3</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.7185</v>
       </c>
       <c r="J13" t="n">
-        <v>15.6114</v>
+        <v>15.0885</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.23</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6028</v>
+        <v>0.5728</v>
       </c>
       <c r="J14" t="n">
-        <v>12.6588</v>
+        <v>12.0288</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1596</v>
+        <v>0.1337</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3516</v>
+        <v>2.8077</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.79</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6575</v>
+        <v>-0.6273</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.8075</v>
+        <v>-13.1733</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1507</v>
+        <v>0.1165</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1647</v>
+        <v>2.4465</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.01</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0663</v>
+        <v>0.0473</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3923</v>
+        <v>0.9933</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.87</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1696</v>
+        <v>-0.1516</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.5616</v>
+        <v>-3.1836</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.78</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2596</v>
+        <v>-0.2405</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.4516</v>
+        <v>-5.0505</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.65</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3807</v>
+        <v>-0.3678</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.9947</v>
+        <v>-7.7238</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.62</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3798</v>
+        <v>1.4179</v>
       </c>
       <c r="J22" t="n">
-        <v>30.3556</v>
+        <v>31.1938</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.45</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0628</v>
+        <v>1.0614</v>
       </c>
       <c r="J23" t="n">
-        <v>23.3816</v>
+        <v>23.3508</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.36</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8869</v>
+        <v>0.8677</v>
       </c>
       <c r="J24" t="n">
-        <v>19.5118</v>
+        <v>19.0894</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.65</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.9328</v>
       </c>
       <c r="J25" t="n">
-        <v>-20.68</v>
+        <v>-20.5216</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.63</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9809</v>
+        <v>-0.9788</v>
       </c>
       <c r="J26" t="n">
-        <v>-21.5798</v>
+        <v>-21.5336</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.13</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3431</v>
+        <v>0.2919</v>
       </c>
       <c r="J27" t="n">
-        <v>7.5482</v>
+        <v>6.4218</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0892</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.9624</v>
+        <v>-1.6676</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.92</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1141</v>
+        <v>-0.0989</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.5102</v>
+        <v>-2.1758</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.79</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2499</v>
+        <v>-0.2306</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.4978</v>
+        <v>-5.0732</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.57</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4518</v>
+        <v>-0.4458</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.9396</v>
+        <v>-9.807600000000001</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.22</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4597</v>
+        <v>0.4013</v>
       </c>
       <c r="J32" t="n">
-        <v>10.5731</v>
+        <v>9.229900000000001</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.17</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3748</v>
+        <v>0.3199</v>
       </c>
       <c r="J33" t="n">
-        <v>8.6204</v>
+        <v>7.3577</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.16</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3573</v>
+        <v>0.3033</v>
       </c>
       <c r="J34" t="n">
-        <v>8.2179</v>
+        <v>6.9759</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.05</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1437</v>
+        <v>0.1113</v>
       </c>
       <c r="J35" t="n">
-        <v>3.3051</v>
+        <v>2.5599</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.57</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4659</v>
+        <v>-0.4635</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.7157</v>
+        <v>-10.6605</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.41</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9786</v>
+        <v>0.9715</v>
       </c>
       <c r="J37" t="n">
-        <v>22.5078</v>
+        <v>22.3445</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.31</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7836</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>18.0228</v>
+        <v>17.4018</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.26</v>
       </c>
       <c r="I39" t="n">
-        <v>0.68</v>
+        <v>0.6474</v>
       </c>
       <c r="J39" t="n">
-        <v>15.64</v>
+        <v>14.8902</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.92</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3169</v>
+        <v>-0.2759</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.2887</v>
+        <v>-6.3457</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.86</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4741</v>
+        <v>-0.4329</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.9043</v>
+        <v>-9.9567</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.28</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5463</v>
+        <v>0.4866</v>
       </c>
       <c r="J42" t="n">
-        <v>19.6668</v>
+        <v>17.5176</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.23</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4667</v>
+        <v>0.4086</v>
       </c>
       <c r="J43" t="n">
-        <v>16.8012</v>
+        <v>14.7096</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.09</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2219</v>
+        <v>0.1808</v>
       </c>
       <c r="J44" t="n">
-        <v>7.9884</v>
+        <v>6.5088</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.09</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2219</v>
+        <v>0.1808</v>
       </c>
       <c r="J45" t="n">
-        <v>7.9884</v>
+        <v>6.5088</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.71</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3452</v>
+        <v>-0.3309</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.4272</v>
+        <v>-11.9124</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.51</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1533</v>
+        <v>1.1695</v>
       </c>
       <c r="J47" t="n">
-        <v>41.5188</v>
+        <v>42.102</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.34</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8694</v>
+        <v>0.8487</v>
       </c>
       <c r="J48" t="n">
-        <v>31.2984</v>
+        <v>30.5532</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.88</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4073</v>
+        <v>-0.3642</v>
       </c>
       <c r="J49" t="n">
-        <v>-14.6628</v>
+        <v>-13.1112</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.8</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6009</v>
+        <v>-0.5629</v>
       </c>
       <c r="J50" t="n">
-        <v>-21.6324</v>
+        <v>-20.2644</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.8</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6009</v>
+        <v>-0.5629</v>
       </c>
       <c r="J51" t="n">
-        <v>-21.6324</v>
+        <v>-20.2644</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.58</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2448</v>
+        <v>1.2656</v>
       </c>
       <c r="J52" t="n">
-        <v>28.6304</v>
+        <v>29.1088</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.15</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4486</v>
+        <v>0.4081</v>
       </c>
       <c r="J53" t="n">
-        <v>10.3178</v>
+        <v>9.3863</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.99</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.053</v>
       </c>
       <c r="J54" t="n">
-        <v>-1.6767</v>
+        <v>-1.219</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.96</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1845</v>
+        <v>-0.1502</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.2435</v>
+        <v>-3.4546</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.75</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7175</v>
+        <v>-0.6871</v>
       </c>
       <c r="J56" t="n">
-        <v>-16.5025</v>
+        <v>-15.8033</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.35</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7013</v>
+        <v>0.6491</v>
       </c>
       <c r="J57" t="n">
-        <v>16.1299</v>
+        <v>14.9293</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.95</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0813</v>
+        <v>-0.0677</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.8699</v>
+        <v>-1.5571</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.91</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1295</v>
+        <v>-0.1119</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.9785</v>
+        <v>-2.5737</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.71</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3313</v>
+        <v>-0.315</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.6199</v>
+        <v>-7.245</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.7</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3406</v>
+        <v>-0.3248</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.8338</v>
+        <v>-7.4704</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.86</v>
       </c>
       <c r="I62" t="n">
-        <v>1.5306</v>
+        <v>1.5648</v>
       </c>
       <c r="J62" t="n">
-        <v>29.0814</v>
+        <v>29.7312</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.54</v>
       </c>
       <c r="I63" t="n">
-        <v>1.1282</v>
+        <v>1.1424</v>
       </c>
       <c r="J63" t="n">
-        <v>21.4358</v>
+        <v>21.7056</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.46</v>
       </c>
       <c r="I64" t="n">
-        <v>1.019</v>
+        <v>1.0237</v>
       </c>
       <c r="J64" t="n">
-        <v>19.361</v>
+        <v>19.4503</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0609</v>
+        <v>-0.0577</v>
       </c>
       <c r="J65" t="n">
-        <v>-1.1571</v>
+        <v>-1.0963</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.97</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1988</v>
+        <v>-0.1706</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.7772</v>
+        <v>-3.2414</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.91</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.1095</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J67" t="n">
-        <v>-2.0805</v>
+        <v>-1.7993</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.8</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.23</v>
+        <v>-0.2141</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.37</v>
+        <v>-4.0679</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.76</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2681</v>
+        <v>-0.2522</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.0939</v>
+        <v>-4.7918</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3314</v>
+        <v>-0.3163</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.2966</v>
+        <v>-6.0097</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.6</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4123</v>
+        <v>-0.4019</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.8337</v>
+        <v>-7.6361</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.35</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8578</v>
+        <v>0.8369</v>
       </c>
       <c r="J72" t="n">
-        <v>18.8716</v>
+        <v>18.4118</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.33</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.7941</v>
       </c>
       <c r="J73" t="n">
-        <v>17.996</v>
+        <v>17.4702</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.15</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4366</v>
+        <v>0.4009</v>
       </c>
       <c r="J74" t="n">
-        <v>9.6052</v>
+        <v>8.819800000000001</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.13</v>
       </c>
       <c r="I75" t="n">
-        <v>0.389</v>
+        <v>0.3539</v>
       </c>
       <c r="J75" t="n">
-        <v>8.558</v>
+        <v>7.7858</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.93</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2932</v>
+        <v>-0.2534</v>
       </c>
       <c r="J76" t="n">
-        <v>-6.4504</v>
+        <v>-5.5748</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.34</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6605</v>
+        <v>0.603</v>
       </c>
       <c r="J77" t="n">
-        <v>14.531</v>
+        <v>13.266</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.1</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2528</v>
+        <v>0.2063</v>
       </c>
       <c r="J78" t="n">
-        <v>5.5616</v>
+        <v>4.5386</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.08</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2127</v>
+        <v>0.1703</v>
       </c>
       <c r="J79" t="n">
-        <v>4.6794</v>
+        <v>3.7466</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0989</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="J80" t="n">
-        <v>-2.1758</v>
+        <v>-1.8062</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.53</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4974</v>
+        <v>-0.4987</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.9428</v>
+        <v>-10.9714</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.21</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3512</v>
+        <v>0.3432</v>
       </c>
       <c r="J82" t="n">
-        <v>10.536</v>
+        <v>10.296</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.03</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0774</v>
+        <v>0.0643</v>
       </c>
       <c r="J83" t="n">
-        <v>2.322</v>
+        <v>1.929</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.97</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0589</v>
+        <v>-0.0461</v>
       </c>
       <c r="J84" t="n">
-        <v>-1.767</v>
+        <v>-1.383</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.93</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1123</v>
+        <v>-0.0944</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.369</v>
+        <v>-2.832</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.91</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1363</v>
+        <v>-0.117</v>
       </c>
       <c r="J86" t="n">
-        <v>-4.089</v>
+        <v>-3.51</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.69</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8352000000000001</v>
+        <v>0.7689</v>
       </c>
       <c r="J87" t="n">
-        <v>25.056</v>
+        <v>23.067</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.31</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4364</v>
+        <v>0.3709</v>
       </c>
       <c r="J88" t="n">
-        <v>13.092</v>
+        <v>11.127</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.86</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2</v>
+        <v>-0.1796</v>
       </c>
       <c r="J89" t="n">
-        <v>-6</v>
+        <v>-5.388</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.85</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2106</v>
+        <v>-0.1903</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.318</v>
+        <v>-5.709</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.82</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2415</v>
+        <v>-0.2218</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.245</v>
+        <v>-6.654</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.83</v>
       </c>
       <c r="I92" t="n">
-        <v>1.5529</v>
+        <v>1.5968</v>
       </c>
       <c r="J92" t="n">
-        <v>37.2696</v>
+        <v>38.3232</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.24</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6369</v>
+        <v>0.6027</v>
       </c>
       <c r="J93" t="n">
-        <v>15.2856</v>
+        <v>14.4648</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.02</v>
       </c>
       <c r="I94" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0589</v>
       </c>
       <c r="J94" t="n">
-        <v>1.8096</v>
+        <v>1.4136</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.93</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2892</v>
+        <v>-0.2492</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.9408</v>
+        <v>-5.9808</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.76</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.708</v>
+        <v>-0.6786</v>
       </c>
       <c r="J96" t="n">
-        <v>-16.992</v>
+        <v>-16.2864</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.59</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0125</v>
+        <v>0.9853</v>
       </c>
       <c r="J97" t="n">
-        <v>24.3</v>
+        <v>23.6472</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.03</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0984</v>
+        <v>0.073</v>
       </c>
       <c r="J98" t="n">
-        <v>2.3616</v>
+        <v>1.752</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.03</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0984</v>
+        <v>0.073</v>
       </c>
       <c r="J99" t="n">
-        <v>2.3616</v>
+        <v>1.752</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.84</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2132</v>
+        <v>-0.1925</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.1168</v>
+        <v>-4.62</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.58</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4557</v>
+        <v>-0.4518</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.9368</v>
+        <v>-10.8432</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.45</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5563</v>
+        <v>0.5216</v>
       </c>
       <c r="J102" t="n">
-        <v>12.7949</v>
+        <v>11.9968</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.11</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1943</v>
+        <v>0.1517</v>
       </c>
       <c r="J103" t="n">
-        <v>4.4689</v>
+        <v>3.4891</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.01</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0273</v>
+        <v>0.0181</v>
       </c>
       <c r="J104" t="n">
-        <v>0.6279</v>
+        <v>0.4163</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.93</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.117</v>
+        <v>-0.0985</v>
       </c>
       <c r="J105" t="n">
-        <v>-2.691</v>
+        <v>-2.2655</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.83</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.228</v>
+        <v>-0.2077</v>
       </c>
       <c r="J106" t="n">
-        <v>-5.244</v>
+        <v>-4.7771</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.62</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7427</v>
+        <v>0.799</v>
       </c>
       <c r="J107" t="n">
-        <v>17.0821</v>
+        <v>18.377</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.01</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0374</v>
+        <v>0.0281</v>
       </c>
       <c r="J108" t="n">
-        <v>0.8602</v>
+        <v>0.6463</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.93</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1087</v>
+        <v>-0.0917</v>
       </c>
       <c r="J109" t="n">
-        <v>-2.5001</v>
+        <v>-2.1091</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2391</v>
+        <v>-0.2189</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.4993</v>
+        <v>-5.0347</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.45</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5622</v>
+        <v>-0.5727</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.9306</v>
+        <v>-13.1721</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.2</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4509</v>
+        <v>0.4002</v>
       </c>
       <c r="J112" t="n">
-        <v>10.3707</v>
+        <v>9.204599999999999</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.99</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.019</v>
+        <v>-0.014</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.437</v>
+        <v>-0.322</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.86</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1834</v>
+        <v>-0.1638</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.2182</v>
+        <v>-3.7674</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.83</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2144</v>
+        <v>-0.1944</v>
       </c>
       <c r="J115" t="n">
-        <v>-4.9312</v>
+        <v>-4.4712</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.7</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3398</v>
+        <v>-0.324</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.8154</v>
+        <v>-7.452</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.66</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1847</v>
+        <v>1.1831</v>
       </c>
       <c r="J117" t="n">
-        <v>27.2481</v>
+        <v>27.2113</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.39</v>
       </c>
       <c r="I118" t="n">
-        <v>0.8115</v>
+        <v>0.7955</v>
       </c>
       <c r="J118" t="n">
-        <v>18.6645</v>
+        <v>18.2965</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.97</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1633</v>
+        <v>-0.1317</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.7559</v>
+        <v>-3.0291</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.96</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1971</v>
+        <v>-0.1624</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.5333</v>
+        <v>-3.7352</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6403</v>
+        <v>-0.6062</v>
       </c>
       <c r="J121" t="n">
-        <v>-14.7269</v>
+        <v>-13.9426</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.02</v>
       </c>
       <c r="I122" t="n">
-        <v>0.0827</v>
+        <v>0.0589</v>
       </c>
       <c r="J122" t="n">
-        <v>1.9848</v>
+        <v>1.4136</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.99</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0212</v>
+        <v>-0.0157</v>
       </c>
       <c r="J123" t="n">
-        <v>-0.5088</v>
+        <v>-0.3768</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.96</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0689</v>
+        <v>-0.0563</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.6536</v>
+        <v>-1.3512</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.095</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.28</v>
+        <v>-1.9128</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.78</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2663</v>
+        <v>-0.2468</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.3912</v>
+        <v>-5.9232</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.23</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.5666</v>
       </c>
       <c r="J127" t="n">
-        <v>13.8744</v>
+        <v>13.5984</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.16</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4611</v>
+        <v>0.4297</v>
       </c>
       <c r="J128" t="n">
-        <v>11.0664</v>
+        <v>10.3128</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.1</v>
       </c>
       <c r="I129" t="n">
-        <v>0.3243</v>
+        <v>0.2872</v>
       </c>
       <c r="J129" t="n">
-        <v>7.7832</v>
+        <v>6.8928</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.1</v>
       </c>
       <c r="I130" t="n">
-        <v>0.3243</v>
+        <v>0.2872</v>
       </c>
       <c r="J130" t="n">
-        <v>7.7832</v>
+        <v>6.8928</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.91</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3348</v>
+        <v>-0.2927</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.0352</v>
+        <v>-7.0248</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.91</v>
       </c>
       <c r="I132" t="n">
-        <v>1.4759</v>
+        <v>1.4967</v>
       </c>
       <c r="J132" t="n">
-        <v>28.0421</v>
+        <v>28.4373</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.69</v>
       </c>
       <c r="I133" t="n">
-        <v>1.1984</v>
+        <v>1.1953</v>
       </c>
       <c r="J133" t="n">
-        <v>22.7696</v>
+        <v>22.7107</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.21</v>
       </c>
       <c r="I134" t="n">
-        <v>0.5295</v>
+        <v>0.5234</v>
       </c>
       <c r="J134" t="n">
-        <v>10.0605</v>
+        <v>9.944599999999999</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.6102</v>
+        <v>-0.5768</v>
       </c>
       <c r="J135" t="n">
-        <v>-11.5938</v>
+        <v>-10.9592</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.62</v>
       </c>
       <c r="I136" t="n">
-        <v>-1.0165</v>
+        <v>-1.0222</v>
       </c>
       <c r="J136" t="n">
-        <v>-19.3135</v>
+        <v>-19.4218</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.13</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3615</v>
+        <v>0.313</v>
       </c>
       <c r="J137" t="n">
-        <v>6.8685</v>
+        <v>5.947</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.86</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.176</v>
+        <v>-0.1592</v>
       </c>
       <c r="J138" t="n">
-        <v>-3.344</v>
+        <v>-3.0248</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.79</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.245</v>
+        <v>-0.2269</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.655</v>
+        <v>-4.3111</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.74</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2924</v>
+        <v>-0.2748</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.5556</v>
+        <v>-5.2212</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.57</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4464</v>
+        <v>-0.4394</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.4816</v>
+        <v>-8.348599999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.09</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2507</v>
+        <v>0.2491</v>
       </c>
       <c r="J142" t="n">
-        <v>4.5126</v>
+        <v>4.4838</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.99</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0183</v>
+        <v>0.0299</v>
       </c>
       <c r="J143" t="n">
-        <v>0.3294</v>
+        <v>0.5382</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.57</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.4357</v>
+        <v>-0.4273</v>
       </c>
       <c r="J144" t="n">
-        <v>-7.8426</v>
+        <v>-7.6914</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.55</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4534</v>
+        <v>-0.4466</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.161199999999999</v>
+        <v>-8.0388</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.43</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5645</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.044</v>
+        <v>-10.161</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>2.83</v>
       </c>
       <c r="I147" t="n">
-        <v>1.3913</v>
+        <v>1.3395</v>
       </c>
       <c r="J147" t="n">
-        <v>25.0434</v>
+        <v>24.111</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.41</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4901</v>
+        <v>0.4459</v>
       </c>
       <c r="J148" t="n">
-        <v>8.8218</v>
+        <v>8.026199999999999</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.33</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4239</v>
+        <v>0.3675</v>
       </c>
       <c r="J149" t="n">
-        <v>7.6302</v>
+        <v>6.615</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.27</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3592</v>
+        <v>0.3057</v>
       </c>
       <c r="J150" t="n">
-        <v>6.4656</v>
+        <v>5.5026</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.58</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.482</v>
+        <v>-0.4874</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.676</v>
+        <v>-8.773199999999999</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.62</v>
       </c>
       <c r="I152" t="n">
-        <v>1.1268</v>
+        <v>1.1208</v>
       </c>
       <c r="J152" t="n">
-        <v>24.7896</v>
+        <v>24.6576</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.6</v>
       </c>
       <c r="I153" t="n">
-        <v>1.1</v>
+        <v>1.0925</v>
       </c>
       <c r="J153" t="n">
-        <v>24.2</v>
+        <v>24.035</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.08</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2616</v>
+        <v>0.2299</v>
       </c>
       <c r="J154" t="n">
-        <v>5.7552</v>
+        <v>5.0578</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.84</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5262</v>
+        <v>-0.4869</v>
       </c>
       <c r="J155" t="n">
-        <v>-11.5764</v>
+        <v>-10.7118</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.71</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.8189</v>
+        <v>-0.7996</v>
       </c>
       <c r="J156" t="n">
-        <v>-18.0158</v>
+        <v>-17.5912</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.39</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6698</v>
+        <v>0.6404</v>
       </c>
       <c r="J157" t="n">
-        <v>14.7356</v>
+        <v>14.0888</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.11</v>
       </c>
       <c r="I158" t="n">
-        <v>0.2809</v>
+        <v>0.2316</v>
       </c>
       <c r="J158" t="n">
-        <v>6.1798</v>
+        <v>5.0952</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.04</v>
       </c>
       <c r="I159" t="n">
-        <v>0.1316</v>
+        <v>0.0993</v>
       </c>
       <c r="J159" t="n">
-        <v>2.8952</v>
+        <v>2.1846</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.68</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.362</v>
+        <v>-0.348</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.964</v>
+        <v>-7.656</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4683</v>
+        <v>-0.4653</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.3026</v>
+        <v>-10.2366</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.3</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4268</v>
+        <v>0.3633</v>
       </c>
       <c r="J162" t="n">
-        <v>11.9504</v>
+        <v>10.1724</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3582</v>
+        <v>0.2978</v>
       </c>
       <c r="J163" t="n">
-        <v>10.0296</v>
+        <v>8.3384</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1788</v>
+        <v>0.1389</v>
       </c>
       <c r="J164" t="n">
-        <v>5.0064</v>
+        <v>3.8892</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.08</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1504</v>
+        <v>0.1151</v>
       </c>
       <c r="J165" t="n">
-        <v>4.2112</v>
+        <v>3.2228</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.7</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3547</v>
+        <v>-0.3412</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.9316</v>
+        <v>-9.553599999999999</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.71</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7954</v>
+        <v>0.855</v>
       </c>
       <c r="J167" t="n">
-        <v>22.2712</v>
+        <v>23.94</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.98</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0455</v>
+        <v>-0.0343</v>
       </c>
       <c r="J168" t="n">
-        <v>-1.274</v>
+        <v>-0.9604</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.97</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0611</v>
+        <v>-0.0478</v>
       </c>
       <c r="J169" t="n">
-        <v>-1.7108</v>
+        <v>-1.3384</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.87</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1837</v>
+        <v>-0.1631</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.1436</v>
+        <v>-4.5668</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.67</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3784</v>
+        <v>-0.3665</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.5952</v>
+        <v>-10.262</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.95</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.0595</v>
       </c>
       <c r="J172" t="n">
-        <v>-1.3566</v>
+        <v>-1.1305</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.93</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.0838</v>
       </c>
       <c r="J173" t="n">
-        <v>-1.8544</v>
+        <v>-1.5922</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.91</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.122</v>
+        <v>-0.1069</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.318</v>
+        <v>-2.0311</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.7</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3313</v>
+        <v>-0.315</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.2947</v>
+        <v>-5.985</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3497</v>
+        <v>-0.3344</v>
       </c>
       <c r="J176" t="n">
-        <v>-6.6443</v>
+        <v>-6.3536</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>2.11</v>
       </c>
       <c r="I177" t="n">
-        <v>1.7087</v>
+        <v>1.7562</v>
       </c>
       <c r="J177" t="n">
-        <v>32.4653</v>
+        <v>33.3678</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.13</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3735</v>
+        <v>0.3411</v>
       </c>
       <c r="J178" t="n">
-        <v>7.0965</v>
+        <v>6.4809</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.09</v>
       </c>
       <c r="I179" t="n">
-        <v>0.271</v>
+        <v>0.24</v>
       </c>
       <c r="J179" t="n">
-        <v>5.149</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.07</v>
       </c>
       <c r="I180" t="n">
-        <v>0.2156</v>
+        <v>0.1865</v>
       </c>
       <c r="J180" t="n">
-        <v>4.0964</v>
+        <v>3.5435</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.99</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1067</v>
+        <v>-0.0866</v>
       </c>
       <c r="J181" t="n">
-        <v>-2.0273</v>
+        <v>-1.6454</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.35</v>
       </c>
       <c r="I182" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.6354</v>
       </c>
       <c r="J182" t="n">
-        <v>13.156</v>
+        <v>12.708</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.85</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1887</v>
+        <v>-0.1707</v>
       </c>
       <c r="J183" t="n">
-        <v>-3.774</v>
+        <v>-3.414</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2281</v>
+        <v>-0.2093</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.562</v>
+        <v>-4.186</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.67</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3601</v>
+        <v>-0.3455</v>
       </c>
       <c r="J185" t="n">
-        <v>-7.202</v>
+        <v>-6.91</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.55</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4669</v>
+        <v>-0.4624</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.337999999999999</v>
+        <v>-9.247999999999999</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.6</v>
       </c>
       <c r="I187" t="n">
-        <v>1.0731</v>
+        <v>1.0632</v>
       </c>
       <c r="J187" t="n">
-        <v>21.462</v>
+        <v>21.264</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.59</v>
       </c>
       <c r="I188" t="n">
-        <v>1.06</v>
+        <v>1.0496</v>
       </c>
       <c r="J188" t="n">
-        <v>21.2</v>
+        <v>20.992</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.37</v>
       </c>
       <c r="I189" t="n">
-        <v>0.7614</v>
+        <v>0.7484</v>
       </c>
       <c r="J189" t="n">
-        <v>15.228</v>
+        <v>14.968</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.17</v>
       </c>
       <c r="I190" t="n">
-        <v>0.4593</v>
+        <v>0.4355</v>
       </c>
       <c r="J190" t="n">
-        <v>9.186</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.7</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.8575</v>
+        <v>-0.8455</v>
       </c>
       <c r="J191" t="n">
-        <v>-17.15</v>
+        <v>-16.91</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>2.13</v>
       </c>
       <c r="I192" t="n">
-        <v>1.6993</v>
+        <v>1.74</v>
       </c>
       <c r="J192" t="n">
-        <v>28.8881</v>
+        <v>29.58</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.4</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7931</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="J193" t="n">
-        <v>13.4827</v>
+        <v>13.3076</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.24</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5627</v>
+        <v>0.5601</v>
       </c>
       <c r="J194" t="n">
-        <v>9.565899999999999</v>
+        <v>9.521699999999999</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.15</v>
       </c>
       <c r="I195" t="n">
-        <v>0.4051</v>
+        <v>0.3738</v>
       </c>
       <c r="J195" t="n">
-        <v>6.8867</v>
+        <v>6.3546</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.0636</v>
+        <v>-0.0608</v>
       </c>
       <c r="J196" t="n">
-        <v>-1.0812</v>
+        <v>-1.0336</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.2079</v>
+        <v>-0.1928</v>
       </c>
       <c r="J197" t="n">
-        <v>-3.5343</v>
+        <v>-3.2776</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.7</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.3157</v>
+        <v>-0.3028</v>
       </c>
       <c r="J198" t="n">
-        <v>-5.3669</v>
+        <v>-5.1476</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.67</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3415</v>
+        <v>-0.3291</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.8055</v>
+        <v>-5.5947</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.64</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3677</v>
+        <v>-0.3558</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.2509</v>
+        <v>-6.0486</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.57</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4295</v>
+        <v>-0.4209</v>
       </c>
       <c r="J201" t="n">
-        <v>-7.3015</v>
+        <v>-7.1553</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>2.41</v>
       </c>
       <c r="I202" t="n">
-        <v>1.9402</v>
+        <v>2.0034</v>
       </c>
       <c r="J202" t="n">
-        <v>27.1628</v>
+        <v>28.0476</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.79</v>
       </c>
       <c r="I203" t="n">
-        <v>1.2511</v>
+        <v>1.2556</v>
       </c>
       <c r="J203" t="n">
-        <v>17.5154</v>
+        <v>17.5784</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.55</v>
       </c>
       <c r="I204" t="n">
-        <v>0.9655</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="J204" t="n">
-        <v>13.517</v>
+        <v>13.4848</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.46</v>
       </c>
       <c r="I205" t="n">
-        <v>0.8487</v>
+        <v>0.8452</v>
       </c>
       <c r="J205" t="n">
-        <v>11.8818</v>
+        <v>11.8328</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.19</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4512</v>
+        <v>0.4241</v>
       </c>
       <c r="J206" t="n">
-        <v>6.3168</v>
+        <v>5.9374</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.99</v>
       </c>
       <c r="I207" t="n">
-        <v>0.0738</v>
+        <v>0.0964</v>
       </c>
       <c r="J207" t="n">
-        <v>1.0332</v>
+        <v>1.3496</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.8</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2079</v>
+        <v>-0.1921</v>
       </c>
       <c r="J208" t="n">
-        <v>-2.9106</v>
+        <v>-2.6894</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.58</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.4143</v>
+        <v>-0.4057</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.8002</v>
+        <v>-5.6798</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.41</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.5637</v>
+        <v>-0.5698</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.8918</v>
+        <v>-7.9772</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.37</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5988</v>
+        <v>-0.6103</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.3832</v>
+        <v>-8.5442</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.17</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3859</v>
+        <v>0.3302</v>
       </c>
       <c r="J212" t="n">
-        <v>7.718</v>
+        <v>6.604</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.11</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2754</v>
+        <v>0.2266</v>
       </c>
       <c r="J213" t="n">
-        <v>5.508</v>
+        <v>4.532</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.95</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0847</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="J214" t="n">
-        <v>-1.694</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.88</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1677</v>
+        <v>-0.1476</v>
       </c>
       <c r="J215" t="n">
-        <v>-3.354</v>
+        <v>-2.952</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.8</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2508</v>
+        <v>-0.2308</v>
       </c>
       <c r="J216" t="n">
-        <v>-5.016</v>
+        <v>-4.616</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.42</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9772</v>
+        <v>0.9709</v>
       </c>
       <c r="J217" t="n">
-        <v>19.544</v>
+        <v>19.418</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.4</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9417</v>
+        <v>0.9302</v>
       </c>
       <c r="J218" t="n">
-        <v>18.834</v>
+        <v>18.604</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.36</v>
       </c>
       <c r="I219" t="n">
-        <v>0.8657</v>
+        <v>0.8469</v>
       </c>
       <c r="J219" t="n">
-        <v>17.314</v>
+        <v>16.938</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.16</v>
       </c>
       <c r="I220" t="n">
-        <v>0.4522</v>
+        <v>0.4189</v>
       </c>
       <c r="J220" t="n">
-        <v>9.044</v>
+        <v>8.378</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.82</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5843</v>
+        <v>-0.5491</v>
       </c>
       <c r="J221" t="n">
-        <v>-11.686</v>
+        <v>-10.982</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.13</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3321</v>
+        <v>0.2802</v>
       </c>
       <c r="J222" t="n">
-        <v>7.6383</v>
+        <v>6.4446</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.9</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.1396</v>
+        <v>-0.1219</v>
       </c>
       <c r="J223" t="n">
-        <v>-3.2108</v>
+        <v>-2.8037</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.88</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1613</v>
+        <v>-0.1426</v>
       </c>
       <c r="J224" t="n">
-        <v>-3.7099</v>
+        <v>-3.2798</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.88</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1613</v>
+        <v>-0.1426</v>
       </c>
       <c r="J225" t="n">
-        <v>-3.7099</v>
+        <v>-3.2798</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.74</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3015</v>
+        <v>-0.2834</v>
       </c>
       <c r="J226" t="n">
-        <v>-6.9345</v>
+        <v>-6.5182</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.51</v>
       </c>
       <c r="I227" t="n">
-        <v>1.1287</v>
+        <v>1.1415</v>
       </c>
       <c r="J227" t="n">
-        <v>25.9601</v>
+        <v>26.2545</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.18</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.4696</v>
       </c>
       <c r="J228" t="n">
-        <v>11.6518</v>
+        <v>10.8008</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.06</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2075</v>
+        <v>0.1784</v>
       </c>
       <c r="J229" t="n">
-        <v>4.7725</v>
+        <v>4.1032</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.02</v>
       </c>
       <c r="I230" t="n">
-        <v>0.0757</v>
+        <v>0.0592</v>
       </c>
       <c r="J230" t="n">
-        <v>1.7411</v>
+        <v>1.3616</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.0254</v>
+        <v>-0.02</v>
       </c>
       <c r="J231" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.15</v>
       </c>
       <c r="I232" t="n">
-        <v>0.3492</v>
+        <v>0.2953</v>
       </c>
       <c r="J232" t="n">
-        <v>8.380800000000001</v>
+        <v>7.0872</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.12</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2937</v>
+        <v>0.2435</v>
       </c>
       <c r="J233" t="n">
-        <v>7.0488</v>
+        <v>5.844</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0979</v>
+        <v>-0.0814</v>
       </c>
       <c r="J234" t="n">
-        <v>-2.3496</v>
+        <v>-1.9536</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1342</v>
+        <v>-0.1153</v>
       </c>
       <c r="J235" t="n">
-        <v>-3.2208</v>
+        <v>-2.7672</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2412</v>
+        <v>-0.221</v>
       </c>
       <c r="J236" t="n">
-        <v>-5.7888</v>
+        <v>-5.304</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.41</v>
       </c>
       <c r="I237" t="n">
-        <v>1.0134</v>
+        <v>1.0151</v>
       </c>
       <c r="J237" t="n">
-        <v>24.3216</v>
+        <v>24.3624</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.1</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3339</v>
+        <v>0.2934</v>
       </c>
       <c r="J238" t="n">
-        <v>8.0136</v>
+        <v>7.0416</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.08</v>
       </c>
       <c r="I239" t="n">
-        <v>0.2804</v>
+        <v>0.2421</v>
       </c>
       <c r="J239" t="n">
-        <v>6.7296</v>
+        <v>5.8104</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.85</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.4763</v>
+        <v>-0.4337</v>
       </c>
       <c r="J240" t="n">
-        <v>-11.4312</v>
+        <v>-10.4088</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.74</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7298</v>
+        <v>-0.6993</v>
       </c>
       <c r="J241" t="n">
-        <v>-17.5152</v>
+        <v>-16.7832</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.75</v>
       </c>
       <c r="I242" t="n">
-        <v>0.8712</v>
+        <v>0.8034</v>
       </c>
       <c r="J242" t="n">
-        <v>18.2952</v>
+        <v>16.8714</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.21</v>
       </c>
       <c r="I243" t="n">
-        <v>0.3107</v>
+        <v>0.257</v>
       </c>
       <c r="J243" t="n">
-        <v>6.5247</v>
+        <v>5.397</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.14</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2249</v>
+        <v>0.1812</v>
       </c>
       <c r="J244" t="n">
-        <v>4.7229</v>
+        <v>3.8052</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.08</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1408</v>
+        <v>0.1089</v>
       </c>
       <c r="J245" t="n">
-        <v>2.9568</v>
+        <v>2.2869</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.82</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2488</v>
+        <v>-0.2302</v>
       </c>
       <c r="J246" t="n">
-        <v>-5.2248</v>
+        <v>-4.8342</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.6</v>
       </c>
       <c r="I247" t="n">
-        <v>0.8269</v>
+        <v>0.9051</v>
       </c>
       <c r="J247" t="n">
-        <v>17.3649</v>
+        <v>19.0071</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.2</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3464</v>
+        <v>0.3383</v>
       </c>
       <c r="J248" t="n">
-        <v>7.2744</v>
+        <v>7.1043</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.73</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.3167</v>
+        <v>-0.2996</v>
       </c>
       <c r="J249" t="n">
-        <v>-6.6507</v>
+        <v>-6.2916</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3538</v>
+        <v>-0.3392</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.4298</v>
+        <v>-7.1232</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.61</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4256</v>
+        <v>-0.4176</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.9376</v>
+        <v>-8.769600000000001</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.15</v>
       </c>
       <c r="I252" t="n">
-        <v>0.3721</v>
+        <v>0.3186</v>
       </c>
       <c r="J252" t="n">
-        <v>8.186199999999999</v>
+        <v>7.0092</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.86</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1819</v>
+        <v>-0.1627</v>
       </c>
       <c r="J253" t="n">
-        <v>-4.0018</v>
+        <v>-3.5794</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.84</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2026</v>
+        <v>-0.1829</v>
       </c>
       <c r="J254" t="n">
-        <v>-4.4572</v>
+        <v>-4.0238</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.83</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2128</v>
+        <v>-0.193</v>
       </c>
       <c r="J255" t="n">
-        <v>-4.6816</v>
+        <v>-4.246</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.2329</v>
+        <v>-0.2131</v>
       </c>
       <c r="J256" t="n">
-        <v>-5.1238</v>
+        <v>-4.6882</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.31</v>
       </c>
       <c r="I257" t="n">
-        <v>0.7794</v>
+        <v>0.7527</v>
       </c>
       <c r="J257" t="n">
-        <v>17.1468</v>
+        <v>16.5594</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.31</v>
       </c>
       <c r="I258" t="n">
-        <v>0.7794</v>
+        <v>0.7527</v>
       </c>
       <c r="J258" t="n">
-        <v>17.1468</v>
+        <v>16.5594</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.24</v>
       </c>
       <c r="I259" t="n">
-        <v>0.6344</v>
+        <v>0.6007</v>
       </c>
       <c r="J259" t="n">
-        <v>13.9568</v>
+        <v>13.2154</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.01</v>
       </c>
       <c r="I260" t="n">
-        <v>0.0315</v>
+        <v>0.0216</v>
       </c>
       <c r="J260" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.4752</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.98</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.1295</v>
+        <v>-0.1022</v>
       </c>
       <c r="J261" t="n">
-        <v>-2.849</v>
+        <v>-2.2484</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.8</v>
       </c>
       <c r="I262" t="n">
-        <v>1.3276</v>
+        <v>1.333</v>
       </c>
       <c r="J262" t="n">
-        <v>27.8796</v>
+        <v>27.993</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.47</v>
       </c>
       <c r="I263" t="n">
-        <v>0.8992</v>
+        <v>0.8853</v>
       </c>
       <c r="J263" t="n">
-        <v>18.8832</v>
+        <v>18.5913</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.33</v>
       </c>
       <c r="I264" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.6929</v>
       </c>
       <c r="J264" t="n">
-        <v>14.7861</v>
+        <v>14.5509</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0489</v>
+        <v>-0.0441</v>
       </c>
       <c r="J265" t="n">
-        <v>-1.0269</v>
+        <v>-0.9261</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.85</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5219</v>
+        <v>-0.4857</v>
       </c>
       <c r="J266" t="n">
-        <v>-10.9599</v>
+        <v>-10.1997</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.08</v>
       </c>
       <c r="I267" t="n">
-        <v>0.2456</v>
+        <v>0.2013</v>
       </c>
       <c r="J267" t="n">
-        <v>5.1576</v>
+        <v>4.2273</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.92</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1128</v>
+        <v>-0.0979</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.3688</v>
+        <v>-2.0559</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.88</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1584</v>
+        <v>-0.1411</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.3264</v>
+        <v>-2.9631</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.75</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2871</v>
+        <v>-0.2688</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.0291</v>
+        <v>-5.6448</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.66</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3704</v>
+        <v>-0.3566</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.7784</v>
+        <v>-7.4886</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.31</v>
       </c>
       <c r="I272" t="n">
-        <v>1.8801</v>
+        <v>1.9408</v>
       </c>
       <c r="J272" t="n">
-        <v>30.0816</v>
+        <v>31.0528</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.82</v>
       </c>
       <c r="I273" t="n">
-        <v>1.3139</v>
+        <v>1.3174</v>
       </c>
       <c r="J273" t="n">
-        <v>21.0224</v>
+        <v>21.0784</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.58</v>
       </c>
       <c r="I274" t="n">
-        <v>1.0188</v>
+        <v>1.0108</v>
       </c>
       <c r="J274" t="n">
-        <v>16.3008</v>
+        <v>16.1728</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.84</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.5714</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="J275" t="n">
-        <v>-9.1424</v>
+        <v>-8.684799999999999</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.6414</v>
+        <v>-0.6167</v>
       </c>
       <c r="J276" t="n">
-        <v>-10.2624</v>
+        <v>-9.8672</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>0.85</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.1725</v>
+        <v>-0.1569</v>
       </c>
       <c r="J277" t="n">
-        <v>-2.76</v>
+        <v>-2.5104</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.3277</v>
+        <v>-0.3135</v>
       </c>
       <c r="J278" t="n">
-        <v>-5.2432</v>
+        <v>-5.016</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3277</v>
+        <v>-0.3135</v>
       </c>
       <c r="J279" t="n">
-        <v>-5.2432</v>
+        <v>-5.016</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3277</v>
+        <v>-0.3135</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.2432</v>
+        <v>-5.016</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.67</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3456</v>
+        <v>-0.3318</v>
       </c>
       <c r="J281" t="n">
-        <v>-5.5296</v>
+        <v>-5.3088</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>2.02</v>
       </c>
       <c r="I282" t="n">
-        <v>0.919</v>
+        <v>0.8631</v>
       </c>
       <c r="J282" t="n">
-        <v>16.542</v>
+        <v>15.5358</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.35</v>
       </c>
       <c r="I283" t="n">
-        <v>0.4498</v>
+        <v>0.3929</v>
       </c>
       <c r="J283" t="n">
-        <v>8.096399999999999</v>
+        <v>7.0722</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.22</v>
       </c>
       <c r="I284" t="n">
-        <v>0.3125</v>
+        <v>0.2615</v>
       </c>
       <c r="J284" t="n">
-        <v>5.625</v>
+        <v>4.707</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.16</v>
       </c>
       <c r="I285" t="n">
-        <v>0.2387</v>
+        <v>0.1949</v>
       </c>
       <c r="J285" t="n">
-        <v>4.2966</v>
+        <v>3.5082</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.97</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.0707</v>
       </c>
       <c r="J286" t="n">
-        <v>-1.512</v>
+        <v>-1.2726</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.31</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5199</v>
+        <v>0.5617</v>
       </c>
       <c r="J287" t="n">
-        <v>9.3582</v>
+        <v>10.1106</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.91</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1153</v>
+        <v>-0.1007</v>
       </c>
       <c r="J288" t="n">
-        <v>-2.0754</v>
+        <v>-1.8126</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.7</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.326</v>
+        <v>-0.3101</v>
       </c>
       <c r="J289" t="n">
-        <v>-5.868</v>
+        <v>-5.5818</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.53</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.478</v>
+        <v>-0.4742</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.603999999999999</v>
+        <v>-8.535600000000001</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.48</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5214</v>
+        <v>-0.5232</v>
       </c>
       <c r="J291" t="n">
-        <v>-9.385199999999999</v>
+        <v>-9.4176</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.25</v>
       </c>
       <c r="I292" t="n">
-        <v>0.5006</v>
+        <v>0.4636</v>
       </c>
       <c r="J292" t="n">
-        <v>12.0144</v>
+        <v>11.1264</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.04</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1275</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="J293" t="n">
-        <v>3.06</v>
+        <v>2.3088</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.92</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.122</v>
+        <v>-0.1038</v>
       </c>
       <c r="J294" t="n">
-        <v>-2.928</v>
+        <v>-2.4912</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.9</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1452</v>
+        <v>-0.1259</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.4848</v>
+        <v>-3.0216</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.79</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2605</v>
+        <v>-0.2408</v>
       </c>
       <c r="J296" t="n">
-        <v>-6.252</v>
+        <v>-5.7792</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.5</v>
       </c>
       <c r="I297" t="n">
-        <v>0.9887</v>
+        <v>0.9782</v>
       </c>
       <c r="J297" t="n">
-        <v>23.7288</v>
+        <v>23.4768</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.38</v>
       </c>
       <c r="I298" t="n">
-        <v>0.8148</v>
+        <v>0.7991</v>
       </c>
       <c r="J298" t="n">
-        <v>19.5552</v>
+        <v>19.1784</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.12</v>
       </c>
       <c r="I299" t="n">
-        <v>0.3775</v>
+        <v>0.3375</v>
       </c>
       <c r="J299" t="n">
-        <v>9.06</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.82</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.5563</v>
+        <v>-0.5164</v>
       </c>
       <c r="J300" t="n">
-        <v>-13.3512</v>
+        <v>-12.3936</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.1111</v>
+        <v>-1.1245</v>
       </c>
       <c r="J301" t="n">
-        <v>-26.6664</v>
+        <v>-26.988</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>0.95</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.0699</v>
+        <v>-0.0581</v>
       </c>
       <c r="J302" t="n">
-        <v>-1.4679</v>
+        <v>-1.2201</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.9</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.1325</v>
+        <v>-0.117</v>
       </c>
       <c r="J303" t="n">
-        <v>-2.7825</v>
+        <v>-2.457</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.89</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1439</v>
+        <v>-0.128</v>
       </c>
       <c r="J304" t="n">
-        <v>-3.0219</v>
+        <v>-2.688</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.7</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3302</v>
+        <v>-0.314</v>
       </c>
       <c r="J305" t="n">
-        <v>-6.9342</v>
+        <v>-6.594</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.68</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3486</v>
+        <v>-0.3333</v>
       </c>
       <c r="J306" t="n">
-        <v>-7.3206</v>
+        <v>-6.9993</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.56</v>
       </c>
       <c r="I307" t="n">
-        <v>1.0268</v>
+        <v>1.0151</v>
       </c>
       <c r="J307" t="n">
-        <v>21.5628</v>
+        <v>21.3171</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.36</v>
       </c>
       <c r="I308" t="n">
-        <v>0.7513</v>
+        <v>0.7375</v>
       </c>
       <c r="J308" t="n">
-        <v>15.7773</v>
+        <v>15.4875</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.25</v>
       </c>
       <c r="I309" t="n">
-        <v>0.5907</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="J309" t="n">
-        <v>12.4047</v>
+        <v>12.2472</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.22</v>
       </c>
       <c r="I310" t="n">
-        <v>0.5448</v>
+        <v>0.5396</v>
       </c>
       <c r="J310" t="n">
-        <v>11.4408</v>
+        <v>11.3316</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.88</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4415</v>
+        <v>-0.4021</v>
       </c>
       <c r="J311" t="n">
-        <v>-9.2715</v>
+        <v>-8.444100000000001</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>0.86</v>
       </c>
       <c r="I312" t="n">
-        <v>-0.1647</v>
+        <v>-0.1491</v>
       </c>
       <c r="J312" t="n">
-        <v>-3.1293</v>
+        <v>-2.8329</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.84</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.1865</v>
+        <v>-0.1709</v>
       </c>
       <c r="J313" t="n">
-        <v>-3.5435</v>
+        <v>-3.2471</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.75</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.276</v>
+        <v>-0.2606</v>
       </c>
       <c r="J314" t="n">
-        <v>-5.244</v>
+        <v>-4.9514</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.63</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3836</v>
+        <v>-0.3712</v>
       </c>
       <c r="J315" t="n">
-        <v>-7.2884</v>
+        <v>-7.0528</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.6</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4103</v>
+        <v>-0.3998</v>
       </c>
       <c r="J316" t="n">
-        <v>-7.7957</v>
+        <v>-7.5962</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.98</v>
       </c>
       <c r="I317" t="n">
-        <v>1.5429</v>
+        <v>1.5682</v>
       </c>
       <c r="J317" t="n">
-        <v>29.3151</v>
+        <v>29.7958</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.74</v>
       </c>
       <c r="I318" t="n">
-        <v>1.2476</v>
+        <v>1.2468</v>
       </c>
       <c r="J318" t="n">
-        <v>23.7044</v>
+        <v>23.6892</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.08</v>
       </c>
       <c r="I319" t="n">
-        <v>0.2385</v>
+        <v>0.2083</v>
       </c>
       <c r="J319" t="n">
-        <v>4.5315</v>
+        <v>3.9577</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.9</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3983</v>
+        <v>-0.3603</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.5677</v>
+        <v>-6.8457</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.85</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.525</v>
+        <v>-0.4894</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.975</v>
+        <v>-9.2986</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.21</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4711</v>
+        <v>0.4273</v>
       </c>
       <c r="J322" t="n">
-        <v>9.422000000000001</v>
+        <v>8.545999999999999</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.01</v>
       </c>
       <c r="I323" t="n">
-        <v>0.0616</v>
+        <v>0.043</v>
       </c>
       <c r="J323" t="n">
-        <v>1.232</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.8</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.242</v>
+        <v>-0.2224</v>
       </c>
       <c r="J324" t="n">
-        <v>-4.84</v>
+        <v>-4.448</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.76</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2808</v>
+        <v>-0.2621</v>
       </c>
       <c r="J325" t="n">
-        <v>-5.616</v>
+        <v>-5.242</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.67</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.3647</v>
+        <v>-0.3505</v>
       </c>
       <c r="J326" t="n">
-        <v>-7.294</v>
+        <v>-7.01</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.45</v>
       </c>
       <c r="I327" t="n">
-        <v>0.8983</v>
+        <v>0.8833</v>
       </c>
       <c r="J327" t="n">
-        <v>17.966</v>
+        <v>17.666</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.2</v>
       </c>
       <c r="I328" t="n">
-        <v>0.522</v>
+        <v>0.5108</v>
       </c>
       <c r="J328" t="n">
-        <v>10.44</v>
+        <v>10.216</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.15</v>
       </c>
       <c r="I329" t="n">
-        <v>0.4366</v>
+        <v>0.4024</v>
       </c>
       <c r="J329" t="n">
-        <v>8.731999999999999</v>
+        <v>8.048</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.05</v>
       </c>
       <c r="I330" t="n">
-        <v>0.178</v>
+        <v>0.151</v>
       </c>
       <c r="J330" t="n">
-        <v>3.56</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.9</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.3711</v>
+        <v>-0.3292</v>
       </c>
       <c r="J331" t="n">
-        <v>-7.422</v>
+        <v>-6.584</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.83</v>
       </c>
       <c r="I332" t="n">
-        <v>1.3603</v>
+        <v>1.368</v>
       </c>
       <c r="J332" t="n">
-        <v>27.206</v>
+        <v>27.36</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.43</v>
       </c>
       <c r="I333" t="n">
-        <v>0.8419</v>
+        <v>0.8284</v>
       </c>
       <c r="J333" t="n">
-        <v>16.838</v>
+        <v>16.568</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.33</v>
       </c>
       <c r="I334" t="n">
-        <v>0.7025</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J334" t="n">
-        <v>14.05</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.2</v>
       </c>
       <c r="I335" t="n">
-        <v>0.5071</v>
+        <v>0.4994</v>
       </c>
       <c r="J335" t="n">
-        <v>10.142</v>
+        <v>9.988</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.75</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.7537</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="J336" t="n">
-        <v>-15.074</v>
+        <v>-14.648</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.15</v>
       </c>
       <c r="I337" t="n">
-        <v>0.3939</v>
+        <v>0.3433</v>
       </c>
       <c r="J337" t="n">
-        <v>7.878</v>
+        <v>6.866</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.85</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.1879</v>
+        <v>-0.1703</v>
       </c>
       <c r="J338" t="n">
-        <v>-3.758</v>
+        <v>-3.406</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.8</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.2368</v>
+        <v>-0.2183</v>
       </c>
       <c r="J339" t="n">
-        <v>-4.736</v>
+        <v>-4.366</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.73</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3034</v>
+        <v>-0.286</v>
       </c>
       <c r="J340" t="n">
-        <v>-6.068</v>
+        <v>-5.72</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.64</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3859</v>
+        <v>-0.3733</v>
       </c>
       <c r="J341" t="n">
-        <v>-7.718</v>
+        <v>-7.466</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>2.17</v>
       </c>
       <c r="I342" t="n">
-        <v>1.7799</v>
+        <v>1.8374</v>
       </c>
       <c r="J342" t="n">
-        <v>42.7176</v>
+        <v>44.0976</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.79</v>
       </c>
       <c r="I343" t="n">
-        <v>1.3181</v>
+        <v>1.323</v>
       </c>
       <c r="J343" t="n">
-        <v>31.6344</v>
+        <v>31.752</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.21</v>
       </c>
       <c r="I344" t="n">
-        <v>0.5265</v>
+        <v>0.5212</v>
       </c>
       <c r="J344" t="n">
-        <v>12.636</v>
+        <v>12.5088</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.82</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.5916</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="J345" t="n">
-        <v>-14.1984</v>
+        <v>-13.392</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.4</v>
       </c>
       <c r="I346" t="n">
-        <v>-1.441</v>
+        <v>-1.5162</v>
       </c>
       <c r="J346" t="n">
-        <v>-34.584</v>
+        <v>-36.3888</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.22</v>
       </c>
       <c r="I347" t="n">
-        <v>0.4619</v>
+        <v>0.4121</v>
       </c>
       <c r="J347" t="n">
-        <v>11.0856</v>
+        <v>9.8904</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.2</v>
       </c>
       <c r="I348" t="n">
-        <v>0.4341</v>
+        <v>0.379</v>
       </c>
       <c r="J348" t="n">
-        <v>10.4184</v>
+        <v>9.096</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.13</v>
       </c>
       <c r="I349" t="n">
-        <v>0.312</v>
+        <v>0.2605</v>
       </c>
       <c r="J349" t="n">
-        <v>7.488</v>
+        <v>6.252</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.84</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2108</v>
+        <v>-0.1902</v>
       </c>
       <c r="J350" t="n">
-        <v>-5.0592</v>
+        <v>-4.5648</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.55</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4795</v>
+        <v>-0.4783</v>
       </c>
       <c r="J351" t="n">
-        <v>-11.508</v>
+        <v>-11.4792</v>
       </c>
     </row>
   </sheetData>
